--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8664" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -2443,142 +2443,40 @@
     <t>陰曆29.30.</t>
   </si>
   <si>
-    <t>靈性・本我・共鳴</t>
-  </si>
-  <si>
-    <t>魂魄・承載・延續</t>
-  </si>
-  <si>
-    <t>多元・色彩・展現</t>
-  </si>
-  <si>
     <t>界線・分際・劃定</t>
   </si>
   <si>
     <t>連結・契約・維繫</t>
   </si>
   <si>
-    <t>開啟・啟動・突破</t>
-  </si>
-  <si>
-    <t>領悟・覺察・理解</t>
-  </si>
-  <si>
-    <t>生命・新生・成長</t>
-  </si>
-  <si>
-    <t>智慧・成熟・積累</t>
-  </si>
-  <si>
-    <t>真心・感受・內在</t>
-  </si>
-  <si>
-    <t>關懷・互愛・親密</t>
-  </si>
-  <si>
-    <t>語言・表達・紀錄</t>
-  </si>
-  <si>
     <t>韻律・頻率・共鳴</t>
   </si>
   <si>
-    <t>成熟・穩固・成長</t>
-  </si>
-  <si>
-    <t>綻放・美好・漂亮</t>
-  </si>
-  <si>
     <t>調節・適應・舒展</t>
   </si>
   <si>
     <t>繁盛・堅韌・遍佈</t>
   </si>
   <si>
-    <t>根基・來源・扎根</t>
-  </si>
-  <si>
     <t>種子・起始・萌芽</t>
   </si>
   <si>
     <t>果實・事實・結實</t>
   </si>
   <si>
-    <t>分支・延展・支線</t>
-  </si>
-  <si>
-    <t>價值・金錢・資源</t>
-  </si>
-  <si>
     <t>溫潤・珍貴・護持</t>
   </si>
   <si>
     <t>結晶・精華・純化</t>
   </si>
   <si>
-    <t>家鄉・地方・溫暖</t>
-  </si>
-  <si>
-    <t>堅固・承重・歷久</t>
-  </si>
-  <si>
-    <t>壓力・稀有・承壓</t>
-  </si>
-  <si>
-    <t>資源・潛力・蘊藏</t>
-  </si>
-  <si>
-    <t>明亮・磊落・照見</t>
-  </si>
-  <si>
-    <t>滋潤・豐沛・滋養</t>
-  </si>
-  <si>
-    <t>熱忱・動能・熱力</t>
-  </si>
-  <si>
-    <t>自由・灑脫・變通</t>
-  </si>
-  <si>
-    <t>穩重・踏實・穩定</t>
-  </si>
-  <si>
     <t>衝擊・驚醒・警告</t>
   </si>
   <si>
-    <t>交換・流動・呼吸</t>
-  </si>
-  <si>
-    <t>可能・希望・潛在</t>
-  </si>
-  <si>
     <t>時期・階段・期間</t>
   </si>
   <si>
-    <t>清晰・明確・看清</t>
-  </si>
-  <si>
-    <t>時間・準時・時序</t>
-  </si>
-  <si>
-    <t>空間・容納・寬敞</t>
-  </si>
-  <si>
     <t>原因・成因・起因</t>
-  </si>
-  <si>
-    <t>福祉・轉機・好運</t>
-  </si>
-  <si>
-    <t>可能・未定・開放</t>
-  </si>
-  <si>
-    <t>夢想・願景・潛意</t>
-  </si>
-  <si>
-    <t>時機・機緣・相遇</t>
-  </si>
-  <si>
-    <t>結果・後果・完成</t>
   </si>
   <si>
     <t>晶體／結晶；精華與純化，重點是純度提高。</t>
@@ -5038,204 +4936,6 @@
     <t>秩序誤讀・命軌僵固</t>
   </si>
   <si>
-    <t>偏離・失根</t>
-  </si>
-  <si>
-    <t>離散・破碎</t>
-  </si>
-  <si>
-    <t>失色・混濁</t>
-  </si>
-  <si>
-    <t>執念・混淆</t>
-  </si>
-  <si>
-    <t>失界・隔絕</t>
-  </si>
-  <si>
-    <t>封閉・狹隘</t>
-  </si>
-  <si>
-    <t>迷幻・錯覺</t>
-  </si>
-  <si>
-    <t>崩解・解散</t>
-  </si>
-  <si>
-    <t>徬徨・偏航</t>
-  </si>
-  <si>
-    <t>慘忍・無情</t>
-  </si>
-  <si>
-    <t>壓抑・禁錮</t>
-  </si>
-  <si>
-    <t>牽制・束縛</t>
-  </si>
-  <si>
-    <t>延遲・抗拒</t>
-  </si>
-  <si>
-    <t>混淆・糾結</t>
-  </si>
-  <si>
-    <t>蒙昧・迷執</t>
-  </si>
-  <si>
-    <t>自欺・偏執</t>
-  </si>
-  <si>
-    <t>枯竭・停滯</t>
-  </si>
-  <si>
-    <t>僵化・衰退</t>
-  </si>
-  <si>
-    <t>忽視・惡化</t>
-  </si>
-  <si>
-    <t>拒絕・僵持</t>
-  </si>
-  <si>
-    <t>麻木・壓抑</t>
-  </si>
-  <si>
-    <t>佔有・疏離</t>
-  </si>
-  <si>
-    <t>失聲・誤傳</t>
-  </si>
-  <si>
-    <t>紊亂・衝突</t>
-  </si>
-  <si>
-    <t>傾倒・失根</t>
-  </si>
-  <si>
-    <t>凋謝・浮誇</t>
-  </si>
-  <si>
-    <t>阻塞・枯黃</t>
-  </si>
-  <si>
-    <t>屈服・卑微</t>
-  </si>
-  <si>
-    <t>斷裂・浮動</t>
-  </si>
-  <si>
-    <t>催熟・埋沒</t>
-  </si>
-  <si>
-    <t>未熟・空果</t>
-  </si>
-  <si>
-    <t>貪婪・無界</t>
-  </si>
-  <si>
-    <t>貪求・失衡</t>
-  </si>
-  <si>
-    <t>碎裂・失護</t>
-  </si>
-  <si>
-    <t>混濁・碎裂</t>
-  </si>
-  <si>
-    <t>失根・冷硬</t>
-  </si>
-  <si>
-    <t>封鎖・頑固</t>
-  </si>
-  <si>
-    <t>崩裂・耗損</t>
-  </si>
-  <si>
-    <t>埋沒・枯竭</t>
-  </si>
-  <si>
-    <t>堆積・散失</t>
-  </si>
-  <si>
-    <t>刺眼・過曝</t>
-  </si>
-  <si>
-    <t>封閉・壓抑</t>
-  </si>
-  <si>
-    <t>氾濫・乾涸</t>
-  </si>
-  <si>
-    <t>暴躁・焚毀</t>
-  </si>
-  <si>
-    <t>飄散・迷向</t>
-  </si>
-  <si>
-    <t>僵固・停滯</t>
-  </si>
-  <si>
-    <t>忽視・遲鈍</t>
-  </si>
-  <si>
-    <t>閉塞・散亂</t>
-  </si>
-  <si>
-    <t>遮蔽・停滯</t>
-  </si>
-  <si>
-    <t>沉陷・失察</t>
-  </si>
-  <si>
-    <t>絕望・迷航</t>
-  </si>
-  <si>
-    <t>錯序・僵化</t>
-  </si>
-  <si>
-    <t>混濁・失焦</t>
-  </si>
-  <si>
-    <t>錯失・停滯</t>
-  </si>
-  <si>
-    <t>壅塞・封閉</t>
-  </si>
-  <si>
-    <t>錯因・失察</t>
-  </si>
-  <si>
-    <t>錯失・依賴</t>
-  </si>
-  <si>
-    <t>忽視・失控</t>
-  </si>
-  <si>
-    <t>僵住・封死</t>
-  </si>
-  <si>
-    <t>沉迷・逃避</t>
-  </si>
-  <si>
-    <t>誤判・失真</t>
-  </si>
-  <si>
-    <t>錯時・勉強</t>
-  </si>
-  <si>
-    <t>填塞・誤認</t>
-  </si>
-  <si>
-    <t>逃避・執著</t>
-  </si>
-  <si>
-    <t>失序・誤判</t>
-  </si>
-  <si>
-    <t>僵化・抗拒</t>
-  </si>
-  <si>
     <t>辨認單一精神起點</t>
   </si>
   <si>
@@ -6035,36 +5735,18 @@
     <t>從整體規律理解命運，不把 Fate 簡化成固定劇本。</t>
   </si>
   <si>
-    <t>記憶・回溯・回憶</t>
-  </si>
-  <si>
     <t>範圍・領域・疆域</t>
   </si>
   <si>
-    <t>映照・映射・洞察</t>
-  </si>
-  <si>
-    <t>核心・本質・中央</t>
-  </si>
-  <si>
-    <t>方向・前進・趨勢</t>
-  </si>
-  <si>
     <t>切斷・中止・斷絕</t>
   </si>
   <si>
     <t>封存・封閉・暫斷</t>
   </si>
   <si>
-    <t>分離・分割・拆分</t>
-  </si>
-  <si>
     <t>錯誤・誤判・偏離</t>
   </si>
   <si>
-    <t>疾病・失衡・病痛</t>
-  </si>
-  <si>
     <t>死亡・終止・終結</t>
   </si>
   <si>
@@ -6074,25 +5756,7 @@
     <t>陰影・低調・內斂</t>
   </si>
   <si>
-    <t>日蝕・遮蔽・消隱</t>
-  </si>
-  <si>
     <t>災禍・危機・警告</t>
-  </si>
-  <si>
-    <t>幻覺・失真・錯認</t>
-  </si>
-  <si>
-    <t>月蝕・暗面・陰狠</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>虛空・空洞・虛無</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>混沌・變化・破序</t>
-    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>順勢・承接・規則</t>
@@ -6145,6 +5809,339 @@
   <si>
     <t>太初之道無名無形，月語者以自身承接它的流動而成。第一道顯現因而成為「德」。</t>
     <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>失源・渙散・閉塞</t>
+  </si>
+  <si>
+    <t>離散・破碎・散裂</t>
+  </si>
+  <si>
+    <t>褪色・單調・妖豔</t>
+  </si>
+  <si>
+    <t>遺忘・失憶・淡忘</t>
+  </si>
+  <si>
+    <t>越界・滲漏・僭越</t>
+  </si>
+  <si>
+    <t>侵佔・侵擾・失守</t>
+  </si>
+  <si>
+    <t>偏映・鏡裂・遮映</t>
+  </si>
+  <si>
+    <t>偏軸・失焦・外散</t>
+  </si>
+  <si>
+    <t>迷失・偏航・徬徨</t>
+  </si>
+  <si>
+    <t>藕斷・拖沓・難捨</t>
+  </si>
+  <si>
+    <t>禁錮・過閉・密封</t>
+  </si>
+  <si>
+    <t>牽制・糾纏・拖累</t>
+  </si>
+  <si>
+    <t>遲啟・難啟・抗拒</t>
+  </si>
+  <si>
+    <t>混合・未分・難拆</t>
+  </si>
+  <si>
+    <t>未悟・守舊・鈍化</t>
+  </si>
+  <si>
+    <t>自欺・拒認・強辯</t>
+  </si>
+  <si>
+    <t>萎靡・低迷・衰微</t>
+  </si>
+  <si>
+    <t>老朽・僵化・遲暮</t>
+  </si>
+  <si>
+    <t>惡化・隱疾・失察</t>
+  </si>
+  <si>
+    <t>僵持・苟延・拒終</t>
+  </si>
+  <si>
+    <t>麻木・壓抑・冷漠</t>
+  </si>
+  <si>
+    <t>佔有・依附・疏離</t>
+  </si>
+  <si>
+    <t>失語・歧義・詞窮</t>
+  </si>
+  <si>
+    <t>失諧・紊亂・亂拍</t>
+  </si>
+  <si>
+    <t>枯槁・傾倒・失範</t>
+  </si>
+  <si>
+    <t>凋謝・枯萎・浮華</t>
+  </si>
+  <si>
+    <t>枯黃・僵滯・失調</t>
+  </si>
+  <si>
+    <t>稀疏・萎頓・疲軟</t>
+  </si>
+  <si>
+    <t>鬆脫・淺植・浮萍</t>
+  </si>
+  <si>
+    <t>催熟・難萌・夭折</t>
+  </si>
+  <si>
+    <t>未熟・不實・造假</t>
+  </si>
+  <si>
+    <t>徒長・枯枝・過密</t>
+  </si>
+  <si>
+    <t>拜金・貪財・勢利</t>
+  </si>
+  <si>
+    <t>碎裂・失護・易損</t>
+  </si>
+  <si>
+    <t>混濁・雜質・失純</t>
+  </si>
+  <si>
+    <t>失所・漂泊・冷落</t>
+  </si>
+  <si>
+    <t>頑固・僵硬・累贅</t>
+  </si>
+  <si>
+    <t>過載・崩裂・耗損</t>
+  </si>
+  <si>
+    <t>埋沒・難採・荒廢</t>
+  </si>
+  <si>
+    <t>堆積・蒙蔽・積垢</t>
+  </si>
+  <si>
+    <t>刺眼・過曝・炫目</t>
+  </si>
+  <si>
+    <t>陰狠・晦澀・沉鬱</t>
+  </si>
+  <si>
+    <t>氾濫・乾涸・污濁</t>
+  </si>
+  <si>
+    <t>暴躁・灼傷・失控</t>
+  </si>
+  <si>
+    <t>放蕩・散漫・恣意</t>
+  </si>
+  <si>
+    <t>鬆散・鬆軟・下陷</t>
+  </si>
+  <si>
+    <t>遲鈍・麻痺・無感</t>
+  </si>
+  <si>
+    <t>滯塞・散逸・閉阻</t>
+  </si>
+  <si>
+    <t>久蝕・拖長・難退</t>
+  </si>
+  <si>
+    <t>沉陷・深陷・難離</t>
+  </si>
+  <si>
+    <t>絕望・渺茫・悲觀</t>
+  </si>
+  <si>
+    <t>錯序・脫節・亂期</t>
+  </si>
+  <si>
+    <t>模糊・朦朧・含混</t>
+  </si>
+  <si>
+    <t>延宕・耗時・拖久</t>
+  </si>
+  <si>
+    <t>壅塞・侷促・擁擠</t>
+  </si>
+  <si>
+    <t>藉口・牽強・歸咎</t>
+  </si>
+  <si>
+    <t>僥倖・依賴・揮霍</t>
+  </si>
+  <si>
+    <t>爆發・殃及・擴大</t>
+  </si>
+  <si>
+    <t>僵住・窄化・定局</t>
+  </si>
+  <si>
+    <t>沉夢・夢魘・逃避</t>
+  </si>
+  <si>
+    <t>迷幻・幻惑・惑亂</t>
+  </si>
+  <si>
+    <t>過早・過晚・強求</t>
+  </si>
+  <si>
+    <t>強填・假有・硬補</t>
+  </si>
+  <si>
+    <t>卸責・推責・執果</t>
+  </si>
+  <si>
+    <t>紛亂・難測・驟變</t>
+  </si>
+  <si>
+    <t>認命・盲從・僵守</t>
+  </si>
+  <si>
+    <t>精神・單一・本源</t>
+  </si>
+  <si>
+    <t>載體・多元・聚合</t>
+  </si>
+  <si>
+    <t>多元・色彩・層次</t>
+  </si>
+  <si>
+    <t>記憶・回想・保存</t>
+  </si>
+  <si>
+    <t>映照・映射・反射</t>
+  </si>
+  <si>
+    <t>核心・中心・內核</t>
+  </si>
+  <si>
+    <t>方向・朝向・指向</t>
+  </si>
+  <si>
+    <t>開啟・啟動・喚醒</t>
+  </si>
+  <si>
+    <t>分離・分割・分支</t>
+  </si>
+  <si>
+    <t>領悟・體悟・頓悟</t>
+  </si>
+  <si>
+    <t>生命・新生・活力</t>
+  </si>
+  <si>
+    <t>歲月・年長・成熟</t>
+  </si>
+  <si>
+    <t>疾病・失衡・病識</t>
+  </si>
+  <si>
+    <t>情感・心理・承載</t>
+  </si>
+  <si>
+    <t>愛意・親密・關懷</t>
+  </si>
+  <si>
+    <t>語言・字詞・表達</t>
+  </si>
+  <si>
+    <t>成熟・表率・茂盛</t>
+  </si>
+  <si>
+    <t>美麗・美好・綻放</t>
+  </si>
+  <si>
+    <t>根系・扎根・延伸</t>
+  </si>
+  <si>
+    <t>分支・枝杈・開展</t>
+  </si>
+  <si>
+    <t>價值・金錢・財富</t>
+  </si>
+  <si>
+    <t>地方・家鄉・溫暖</t>
+  </si>
+  <si>
+    <t>堅固・承重・固執</t>
+  </si>
+  <si>
+    <t>壓力・稀有・淬鍊</t>
+  </si>
+  <si>
+    <t>礦藏・潛力・蘊藏</t>
+  </si>
+  <si>
+    <t>明亮・磊落・外顯</t>
+  </si>
+  <si>
+    <t>滋潤・豐沛・水澤</t>
+  </si>
+  <si>
+    <t>熱忱・衝動・暴躁</t>
+  </si>
+  <si>
+    <t>自由・灑脫・不拘</t>
+  </si>
+  <si>
+    <t>厚重・踏實・沉穩</t>
+  </si>
+  <si>
+    <t>流動・氣流・呼吸</t>
+  </si>
+  <si>
+    <t>日蝕・遮蔽・暫變</t>
+  </si>
+  <si>
+    <t>月蝕・暗面・深層</t>
+  </si>
+  <si>
+    <t>潛在・希望・可能</t>
+  </si>
+  <si>
+    <t>清晰・明確・清楚</t>
+  </si>
+  <si>
+    <t>時間・時刻・計時</t>
+  </si>
+  <si>
+    <t>空間・餘裕・容納</t>
+  </si>
+  <si>
+    <t>轉機・祝福・好運</t>
+  </si>
+  <si>
+    <t>未定・開放・可能</t>
+  </si>
+  <si>
+    <t>夢想・願景・夢境</t>
+  </si>
+  <si>
+    <t>幻覺・失真・假象</t>
+  </si>
+  <si>
+    <t>時機・契機・合宜</t>
+  </si>
+  <si>
+    <t>虛缺・絕跡・缺少</t>
+  </si>
+  <si>
+    <t>結果・後果・成果</t>
+  </si>
+  <si>
+    <t>混沌・變數・亂局</t>
   </si>
 </sst>
 </file>
@@ -7923,7 +7920,24 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -8128,181 +8142,6 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border outline="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -8811,7 +8650,32 @@
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -8836,12 +8700,147 @@
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
         <right style="thin">
           <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
         </right>
         <top style="thin">
           <color auto="1"/>
@@ -9435,45 +9434,45 @@
   <tableColumns count="5">
     <tableColumn id="1" name="名稱" dataDxfId="42"/>
     <tableColumn id="2" name="圖騰" dataDxfId="41"/>
-    <tableColumn id="4" name="反向關鍵字" dataDxfId="40"/>
-    <tableColumn id="5" name="陰影面" dataDxfId="39"/>
-    <tableColumn id="6" name="反向含義" dataDxfId="38"/>
+    <tableColumn id="4" name="反向關鍵字" dataDxfId="0"/>
+    <tableColumn id="5" name="陰影面" dataDxfId="40"/>
+    <tableColumn id="6" name="反向含義" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:G68" totalsRowShown="0" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:G68" totalsRowShown="0" dataDxfId="38">
   <autoFilter ref="A1:G68"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="編號" dataDxfId="14"/>
-    <tableColumn id="2" name="名稱" dataDxfId="13"/>
-    <tableColumn id="3" name="圖騰" dataDxfId="12"/>
-    <tableColumn id="4" name="所屬分組" dataDxfId="11"/>
-    <tableColumn id="5" name="月相" dataDxfId="10"/>
-    <tableColumn id="6" name="符文變化歷史" dataDxfId="9"/>
-    <tableColumn id="7" name="神話故事" dataDxfId="8"/>
+    <tableColumn id="1" name="編號" dataDxfId="37"/>
+    <tableColumn id="2" name="名稱" dataDxfId="36"/>
+    <tableColumn id="3" name="圖騰" dataDxfId="35"/>
+    <tableColumn id="4" name="所屬分組" dataDxfId="34"/>
+    <tableColumn id="5" name="月相" dataDxfId="33"/>
+    <tableColumn id="6" name="符文變化歷史" dataDxfId="32"/>
+    <tableColumn id="7" name="神話故事" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="表格5" displayName="表格5" ref="A1:I67" totalsRowShown="0" headerRowBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="表格5" displayName="表格5" ref="A1:I67" totalsRowShown="0" headerRowBorderDxfId="30">
   <autoFilter ref="A1:I67"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="名稱" dataDxfId="36"/>
-    <tableColumn id="2" name="圖騰" dataDxfId="35"/>
-    <tableColumn id="3" name="所屬分組" dataDxfId="34"/>
-    <tableColumn id="4" name="月相" dataDxfId="33"/>
-    <tableColumn id="5" name="具象插圖背景" dataDxfId="32"/>
-    <tableColumn id="6" name="圖編號" dataDxfId="31"/>
-    <tableColumn id="7" name="圖檔名稱" dataDxfId="30">
+    <tableColumn id="1" name="名稱" dataDxfId="29"/>
+    <tableColumn id="2" name="圖騰" dataDxfId="28"/>
+    <tableColumn id="3" name="所屬分組" dataDxfId="27"/>
+    <tableColumn id="4" name="月相" dataDxfId="26"/>
+    <tableColumn id="5" name="具象插圖背景" dataDxfId="25"/>
+    <tableColumn id="6" name="圖編號" dataDxfId="24"/>
+    <tableColumn id="7" name="圖檔名稱" dataDxfId="23">
       <calculatedColumnFormula>CONCATENATE(F2,A2,".png")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="符文底圖代碼" dataDxfId="29"/>
-    <tableColumn id="9" name="符文卡圖代碼" dataDxfId="28"/>
+    <tableColumn id="8" name="符文底圖代碼" dataDxfId="22"/>
+    <tableColumn id="9" name="符文卡圖代碼" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9483,13 +9482,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="表格6" displayName="表格6" ref="A1:G67" totalsRowShown="0">
   <autoFilter ref="A1:G67"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="編號" dataDxfId="27"/>
-    <tableColumn id="2" name="名稱" dataDxfId="26"/>
-    <tableColumn id="6" name="靈魂課題" dataDxfId="25"/>
-    <tableColumn id="7" name="實踐挑戰" dataDxfId="24"/>
-    <tableColumn id="8" name="配套儀式建議" dataDxfId="23"/>
-    <tableColumn id="9" name="能量調和建議" dataDxfId="22"/>
-    <tableColumn id="10" name="欄1" dataDxfId="21"/>
+    <tableColumn id="1" name="編號" dataDxfId="20"/>
+    <tableColumn id="2" name="名稱" dataDxfId="19"/>
+    <tableColumn id="6" name="靈魂課題" dataDxfId="18"/>
+    <tableColumn id="7" name="實踐挑戰" dataDxfId="17"/>
+    <tableColumn id="8" name="配套儀式建議" dataDxfId="16"/>
+    <tableColumn id="9" name="能量調和建議" dataDxfId="15"/>
+    <tableColumn id="10" name="欄1" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9499,19 +9498,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="表格7" displayName="表格7" ref="A1:F67" totalsRowShown="0" headerRowCellStyle="40% - 輔色1">
   <autoFilter ref="A1:F67"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="20"/>
-    <tableColumn id="2" name="名稱" dataDxfId="19"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="18" dataCellStyle="20% - 輔色1"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="17" dataCellStyle="40% - 輔色1"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="16" dataCellStyle="20% - 輔色2"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="15" dataCellStyle="40% - 輔色2"/>
+    <tableColumn id="1" name="編號" dataDxfId="13"/>
+    <tableColumn id="2" name="名稱" dataDxfId="12"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="11" dataCellStyle="20% - 輔色1"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="10" dataCellStyle="40% - 輔色1"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="9" dataCellStyle="20% - 輔色2"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="8" dataCellStyle="40% - 輔色2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F67" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F67" totalsRowShown="0" dataDxfId="7">
   <autoFilter ref="A1:F67"/>
   <tableColumns count="6">
     <tableColumn id="1" name="編號" dataDxfId="6"/>
@@ -9758,7 +9757,7 @@
     <col min="13" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="65" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="120" t="s">
         <v>0</v>
       </c>
@@ -9816,10 +9815,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="97" t="s">
-        <v>1365</v>
+        <v>1331</v>
       </c>
       <c r="I2" s="97" t="s">
-        <v>787</v>
+        <v>1881</v>
       </c>
       <c r="J2" s="109" t="s">
         <v>16</v>
@@ -9851,10 +9850,10 @@
         <v>21</v>
       </c>
       <c r="H3" s="98" t="s">
-        <v>1366</v>
+        <v>1332</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>788</v>
+        <v>1882</v>
       </c>
       <c r="J3" s="111" t="s">
         <v>22</v>
@@ -9886,10 +9885,10 @@
         <v>15</v>
       </c>
       <c r="H4" s="98" t="s">
-        <v>1367</v>
+        <v>1333</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>789</v>
+        <v>1883</v>
       </c>
       <c r="J4" s="111" t="s">
         <v>26</v>
@@ -9921,10 +9920,10 @@
         <v>21</v>
       </c>
       <c r="H5" s="98" t="s">
-        <v>1368</v>
+        <v>1334</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>1894</v>
+        <v>1884</v>
       </c>
       <c r="J5" s="111" t="s">
         <v>30</v>
@@ -9956,10 +9955,10 @@
         <v>21</v>
       </c>
       <c r="H6" s="98" t="s">
-        <v>1369</v>
+        <v>1335</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="J6" s="111" t="s">
         <v>35</v>
@@ -9991,10 +9990,10 @@
         <v>21</v>
       </c>
       <c r="H7" s="98" t="s">
-        <v>1370</v>
+        <v>1336</v>
       </c>
       <c r="I7" s="98" t="s">
-        <v>1895</v>
+        <v>1794</v>
       </c>
       <c r="J7" s="111" t="s">
         <v>40</v>
@@ -10026,10 +10025,10 @@
         <v>15</v>
       </c>
       <c r="H8" s="98" t="s">
-        <v>1371</v>
+        <v>1337</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>1896</v>
+        <v>1885</v>
       </c>
       <c r="J8" s="111" t="s">
         <v>44</v>
@@ -10061,10 +10060,10 @@
         <v>15</v>
       </c>
       <c r="H9" s="99" t="s">
-        <v>1372</v>
+        <v>1338</v>
       </c>
       <c r="I9" s="99" t="s">
-        <v>1897</v>
+        <v>1886</v>
       </c>
       <c r="J9" s="113" t="s">
         <v>48</v>
@@ -10096,10 +10095,10 @@
         <v>21</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>1373</v>
+        <v>1339</v>
       </c>
       <c r="I10" s="97" t="s">
-        <v>1898</v>
+        <v>1887</v>
       </c>
       <c r="J10" s="109" t="s">
         <v>53</v>
@@ -10131,10 +10130,10 @@
         <v>57</v>
       </c>
       <c r="H11" s="98" t="s">
-        <v>1374</v>
+        <v>1340</v>
       </c>
       <c r="I11" s="98" t="s">
-        <v>1899</v>
+        <v>1795</v>
       </c>
       <c r="J11" s="111" t="s">
         <v>58</v>
@@ -10166,10 +10165,10 @@
         <v>57</v>
       </c>
       <c r="H12" s="98" t="s">
-        <v>1375</v>
+        <v>1341</v>
       </c>
       <c r="I12" s="98" t="s">
-        <v>1900</v>
+        <v>1796</v>
       </c>
       <c r="J12" s="111" t="s">
         <v>62</v>
@@ -10201,10 +10200,10 @@
         <v>21</v>
       </c>
       <c r="H13" s="98" t="s">
-        <v>1364</v>
+        <v>1330</v>
       </c>
       <c r="I13" s="98" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="J13" s="111" t="s">
         <v>66</v>
@@ -10236,10 +10235,10 @@
         <v>15</v>
       </c>
       <c r="H14" s="98" t="s">
-        <v>1376</v>
+        <v>1342</v>
       </c>
       <c r="I14" s="98" t="s">
-        <v>792</v>
+        <v>1888</v>
       </c>
       <c r="J14" s="111" t="s">
         <v>70</v>
@@ -10271,10 +10270,10 @@
         <v>57</v>
       </c>
       <c r="H15" s="98" t="s">
-        <v>1377</v>
+        <v>1343</v>
       </c>
       <c r="I15" s="98" t="s">
-        <v>1901</v>
+        <v>1889</v>
       </c>
       <c r="J15" s="111" t="s">
         <v>74</v>
@@ -10309,7 +10308,7 @@
         <v>78</v>
       </c>
       <c r="I16" s="98" t="s">
-        <v>793</v>
+        <v>1890</v>
       </c>
       <c r="J16" s="111" t="s">
         <v>79</v>
@@ -10341,10 +10340,10 @@
         <v>57</v>
       </c>
       <c r="H17" s="100" t="s">
-        <v>1378</v>
+        <v>1344</v>
       </c>
       <c r="I17" s="99" t="s">
-        <v>1902</v>
+        <v>1797</v>
       </c>
       <c r="J17" s="113" t="s">
         <v>83</v>
@@ -10376,10 +10375,10 @@
         <v>15</v>
       </c>
       <c r="H18" s="97" t="s">
-        <v>1379</v>
+        <v>1345</v>
       </c>
       <c r="I18" s="97" t="s">
-        <v>794</v>
+        <v>1891</v>
       </c>
       <c r="J18" s="109" t="s">
         <v>88</v>
@@ -10411,10 +10410,10 @@
         <v>15</v>
       </c>
       <c r="H19" s="98" t="s">
-        <v>1380</v>
+        <v>1346</v>
       </c>
       <c r="I19" s="98" t="s">
-        <v>795</v>
+        <v>1892</v>
       </c>
       <c r="J19" s="111" t="s">
         <v>92</v>
@@ -10446,10 +10445,10 @@
         <v>57</v>
       </c>
       <c r="H20" s="98" t="s">
-        <v>1381</v>
+        <v>1347</v>
       </c>
       <c r="I20" s="98" t="s">
-        <v>1903</v>
+        <v>1893</v>
       </c>
       <c r="J20" s="111" t="s">
         <v>96</v>
@@ -10481,10 +10480,10 @@
         <v>57</v>
       </c>
       <c r="H21" s="98" t="s">
-        <v>1382</v>
+        <v>1348</v>
       </c>
       <c r="I21" s="98" t="s">
-        <v>1904</v>
+        <v>1798</v>
       </c>
       <c r="J21" s="111" t="s">
         <v>100</v>
@@ -10516,10 +10515,10 @@
         <v>15</v>
       </c>
       <c r="H22" s="98" t="s">
-        <v>1383</v>
+        <v>1349</v>
       </c>
       <c r="I22" s="98" t="s">
-        <v>796</v>
+        <v>1894</v>
       </c>
       <c r="J22" s="111" t="s">
         <v>104</v>
@@ -10551,10 +10550,10 @@
         <v>15</v>
       </c>
       <c r="H23" s="98" t="s">
-        <v>1384</v>
+        <v>1350</v>
       </c>
       <c r="I23" s="98" t="s">
-        <v>797</v>
+        <v>1895</v>
       </c>
       <c r="J23" s="111" t="s">
         <v>108</v>
@@ -10586,10 +10585,10 @@
         <v>21</v>
       </c>
       <c r="H24" s="98" t="s">
-        <v>1385</v>
+        <v>1351</v>
       </c>
       <c r="I24" s="98" t="s">
-        <v>798</v>
+        <v>1896</v>
       </c>
       <c r="J24" s="111" t="s">
         <v>112</v>
@@ -10621,10 +10620,10 @@
         <v>15</v>
       </c>
       <c r="H25" s="99" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="I25" s="99" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="J25" s="113" t="s">
         <v>116</v>
@@ -10656,10 +10655,10 @@
         <v>15</v>
       </c>
       <c r="H26" s="97" t="s">
-        <v>1387</v>
+        <v>1353</v>
       </c>
       <c r="I26" s="97" t="s">
-        <v>800</v>
+        <v>1897</v>
       </c>
       <c r="J26" s="109" t="s">
         <v>92</v>
@@ -10691,10 +10690,10 @@
         <v>15</v>
       </c>
       <c r="H27" s="98" t="s">
-        <v>1388</v>
+        <v>1354</v>
       </c>
       <c r="I27" s="98" t="s">
-        <v>801</v>
+        <v>1898</v>
       </c>
       <c r="J27" s="111" t="s">
         <v>124</v>
@@ -10726,10 +10725,10 @@
         <v>21</v>
       </c>
       <c r="H28" s="98" t="s">
-        <v>1389</v>
+        <v>1355</v>
       </c>
       <c r="I28" s="98" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="J28" s="111" t="s">
         <v>128</v>
@@ -10761,10 +10760,10 @@
         <v>21</v>
       </c>
       <c r="H29" s="98" t="s">
-        <v>1390</v>
+        <v>1356</v>
       </c>
       <c r="I29" s="98" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="J29" s="111" t="s">
         <v>132</v>
@@ -10796,10 +10795,10 @@
         <v>15</v>
       </c>
       <c r="H30" s="98" t="s">
-        <v>1391</v>
+        <v>1357</v>
       </c>
       <c r="I30" s="98" t="s">
-        <v>804</v>
+        <v>1899</v>
       </c>
       <c r="J30" s="111" t="s">
         <v>136</v>
@@ -10831,10 +10830,10 @@
         <v>21</v>
       </c>
       <c r="H31" s="98" t="s">
-        <v>1392</v>
+        <v>1358</v>
       </c>
       <c r="I31" s="98" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="J31" s="111" t="s">
         <v>140</v>
@@ -10866,10 +10865,10 @@
         <v>21</v>
       </c>
       <c r="H32" s="98" t="s">
-        <v>1393</v>
+        <v>1359</v>
       </c>
       <c r="I32" s="98" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="J32" s="111" t="s">
         <v>144</v>
@@ -10901,10 +10900,10 @@
         <v>21</v>
       </c>
       <c r="H33" s="99" t="s">
-        <v>1394</v>
+        <v>1360</v>
       </c>
       <c r="I33" s="99" t="s">
-        <v>807</v>
+        <v>1900</v>
       </c>
       <c r="J33" s="113" t="s">
         <v>148</v>
@@ -10936,10 +10935,10 @@
         <v>21</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>1395</v>
+        <v>1361</v>
       </c>
       <c r="I34" s="97" t="s">
-        <v>808</v>
+        <v>1901</v>
       </c>
       <c r="J34" s="109" t="s">
         <v>153</v>
@@ -10971,10 +10970,10 @@
         <v>15</v>
       </c>
       <c r="H35" s="98" t="s">
-        <v>1396</v>
+        <v>1362</v>
       </c>
       <c r="I35" s="98" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="J35" s="111" t="s">
         <v>157</v>
@@ -11006,10 +11005,10 @@
         <v>15</v>
       </c>
       <c r="H36" s="98" t="s">
-        <v>1397</v>
+        <v>1363</v>
       </c>
       <c r="I36" s="98" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="J36" s="111" t="s">
         <v>161</v>
@@ -11041,10 +11040,10 @@
         <v>15</v>
       </c>
       <c r="H37" s="98" t="s">
-        <v>1398</v>
+        <v>1364</v>
       </c>
       <c r="I37" s="98" t="s">
-        <v>811</v>
+        <v>1902</v>
       </c>
       <c r="J37" s="111" t="s">
         <v>165</v>
@@ -11076,10 +11075,10 @@
         <v>15</v>
       </c>
       <c r="H38" s="98" t="s">
-        <v>1399</v>
+        <v>1365</v>
       </c>
       <c r="I38" s="98" t="s">
-        <v>812</v>
+        <v>1903</v>
       </c>
       <c r="J38" s="111" t="s">
         <v>169</v>
@@ -11111,10 +11110,10 @@
         <v>21</v>
       </c>
       <c r="H39" s="98" t="s">
-        <v>1400</v>
+        <v>1366</v>
       </c>
       <c r="I39" s="98" t="s">
-        <v>813</v>
+        <v>1904</v>
       </c>
       <c r="J39" s="111" t="s">
         <v>173</v>
@@ -11146,10 +11145,10 @@
         <v>21</v>
       </c>
       <c r="H40" s="98" t="s">
-        <v>1401</v>
+        <v>1367</v>
       </c>
       <c r="I40" s="98" t="s">
-        <v>814</v>
+        <v>1905</v>
       </c>
       <c r="J40" s="111" t="s">
         <v>177</v>
@@ -11181,10 +11180,10 @@
         <v>57</v>
       </c>
       <c r="H41" s="100" t="s">
-        <v>1402</v>
+        <v>1368</v>
       </c>
       <c r="I41" s="99" t="s">
-        <v>1905</v>
+        <v>1799</v>
       </c>
       <c r="J41" s="113" t="s">
         <v>181</v>
@@ -11216,10 +11215,10 @@
         <v>15</v>
       </c>
       <c r="H42" s="97" t="s">
-        <v>1403</v>
+        <v>1369</v>
       </c>
       <c r="I42" s="97" t="s">
-        <v>815</v>
+        <v>1906</v>
       </c>
       <c r="J42" s="109" t="s">
         <v>186</v>
@@ -11251,10 +11250,10 @@
         <v>57</v>
       </c>
       <c r="H43" s="98" t="s">
-        <v>1404</v>
+        <v>1370</v>
       </c>
       <c r="I43" s="98" t="s">
-        <v>1906</v>
+        <v>1800</v>
       </c>
       <c r="J43" s="111" t="s">
         <v>190</v>
@@ -11286,10 +11285,10 @@
         <v>21</v>
       </c>
       <c r="H44" s="98" t="s">
-        <v>1405</v>
+        <v>1371</v>
       </c>
       <c r="I44" s="98" t="s">
-        <v>816</v>
+        <v>1907</v>
       </c>
       <c r="J44" s="111" t="s">
         <v>194</v>
@@ -11321,10 +11320,10 @@
         <v>21</v>
       </c>
       <c r="H45" s="98" t="s">
-        <v>1406</v>
+        <v>1372</v>
       </c>
       <c r="I45" s="98" t="s">
-        <v>817</v>
+        <v>1908</v>
       </c>
       <c r="J45" s="111" t="s">
         <v>198</v>
@@ -11356,10 +11355,10 @@
         <v>21</v>
       </c>
       <c r="H46" s="98" t="s">
-        <v>1407</v>
+        <v>1373</v>
       </c>
       <c r="I46" s="98" t="s">
-        <v>818</v>
+        <v>1909</v>
       </c>
       <c r="J46" s="111" t="s">
         <v>202</v>
@@ -11391,10 +11390,10 @@
         <v>21</v>
       </c>
       <c r="H47" s="98" t="s">
-        <v>1408</v>
+        <v>1374</v>
       </c>
       <c r="I47" s="98" t="s">
-        <v>819</v>
+        <v>1910</v>
       </c>
       <c r="J47" s="111" t="s">
         <v>206</v>
@@ -11426,10 +11425,10 @@
         <v>21</v>
       </c>
       <c r="H48" s="98" t="s">
-        <v>1409</v>
+        <v>1375</v>
       </c>
       <c r="I48" s="98" t="s">
-        <v>820</v>
+        <v>796</v>
       </c>
       <c r="J48" s="111" t="s">
         <v>210</v>
@@ -11461,10 +11460,10 @@
         <v>21</v>
       </c>
       <c r="H49" s="99" t="s">
-        <v>1410</v>
+        <v>1376</v>
       </c>
       <c r="I49" s="99" t="s">
-        <v>821</v>
+        <v>1911</v>
       </c>
       <c r="J49" s="113" t="s">
         <v>214</v>
@@ -11496,10 +11495,10 @@
         <v>57</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>1411</v>
+        <v>1377</v>
       </c>
       <c r="I50" s="97" t="s">
-        <v>1907</v>
+        <v>1912</v>
       </c>
       <c r="J50" s="109" t="s">
         <v>219</v>
@@ -11531,10 +11530,10 @@
         <v>57</v>
       </c>
       <c r="H51" s="98" t="s">
-        <v>1412</v>
+        <v>1378</v>
       </c>
       <c r="I51" s="98" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="J51" s="111" t="s">
         <v>223</v>
@@ -11566,10 +11565,10 @@
         <v>21</v>
       </c>
       <c r="H52" s="98" t="s">
-        <v>1413</v>
+        <v>1379</v>
       </c>
       <c r="I52" s="98" t="s">
-        <v>822</v>
+        <v>1914</v>
       </c>
       <c r="J52" s="111" t="s">
         <v>227</v>
@@ -11601,10 +11600,10 @@
         <v>21</v>
       </c>
       <c r="H53" s="98" t="s">
-        <v>1414</v>
+        <v>1380</v>
       </c>
       <c r="I53" s="98" t="s">
-        <v>823</v>
+        <v>797</v>
       </c>
       <c r="J53" s="111" t="s">
         <v>231</v>
@@ -11636,10 +11635,10 @@
         <v>15</v>
       </c>
       <c r="H54" s="98" t="s">
-        <v>1415</v>
+        <v>1381</v>
       </c>
       <c r="I54" s="98" t="s">
-        <v>824</v>
+        <v>1915</v>
       </c>
       <c r="J54" s="111" t="s">
         <v>235</v>
@@ -11671,10 +11670,10 @@
         <v>21</v>
       </c>
       <c r="H55" s="98" t="s">
-        <v>1416</v>
+        <v>1382</v>
       </c>
       <c r="I55" s="98" t="s">
-        <v>825</v>
+        <v>1916</v>
       </c>
       <c r="J55" s="111" t="s">
         <v>239</v>
@@ -11706,10 +11705,10 @@
         <v>21</v>
       </c>
       <c r="H56" s="98" t="s">
-        <v>1417</v>
+        <v>1383</v>
       </c>
       <c r="I56" s="98" t="s">
-        <v>826</v>
+        <v>1917</v>
       </c>
       <c r="J56" s="111" t="s">
         <v>243</v>
@@ -11741,10 +11740,10 @@
         <v>21</v>
       </c>
       <c r="H57" s="100" t="s">
-        <v>1418</v>
+        <v>1384</v>
       </c>
       <c r="I57" s="99" t="s">
-        <v>827</v>
+        <v>798</v>
       </c>
       <c r="J57" s="113" t="s">
         <v>247</v>
@@ -11776,10 +11775,10 @@
         <v>15</v>
       </c>
       <c r="H58" s="97" t="s">
-        <v>1419</v>
+        <v>1385</v>
       </c>
       <c r="I58" s="97" t="s">
-        <v>828</v>
+        <v>1918</v>
       </c>
       <c r="J58" s="109" t="s">
         <v>252</v>
@@ -11811,10 +11810,10 @@
         <v>57</v>
       </c>
       <c r="H59" s="98" t="s">
-        <v>1420</v>
+        <v>1386</v>
       </c>
       <c r="I59" s="98" t="s">
-        <v>1908</v>
+        <v>1801</v>
       </c>
       <c r="J59" s="111" t="s">
         <v>256</v>
@@ -11846,10 +11845,10 @@
         <v>260</v>
       </c>
       <c r="H60" s="98" t="s">
-        <v>1421</v>
+        <v>1387</v>
       </c>
       <c r="I60" s="98" t="s">
-        <v>829</v>
+        <v>1919</v>
       </c>
       <c r="J60" s="111" t="s">
         <v>261</v>
@@ -11881,10 +11880,10 @@
         <v>15</v>
       </c>
       <c r="H61" s="98" t="s">
-        <v>1422</v>
+        <v>1388</v>
       </c>
       <c r="I61" s="98" t="s">
-        <v>830</v>
+        <v>1920</v>
       </c>
       <c r="J61" s="111" t="s">
         <v>265</v>
@@ -11916,10 +11915,10 @@
         <v>57</v>
       </c>
       <c r="H62" s="98" t="s">
-        <v>1423</v>
+        <v>1389</v>
       </c>
       <c r="I62" s="98" t="s">
-        <v>1909</v>
+        <v>1921</v>
       </c>
       <c r="J62" s="111" t="s">
         <v>269</v>
@@ -11951,10 +11950,10 @@
         <v>21</v>
       </c>
       <c r="H63" s="98" t="s">
-        <v>1424</v>
+        <v>1390</v>
       </c>
       <c r="I63" s="98" t="s">
-        <v>831</v>
+        <v>1922</v>
       </c>
       <c r="J63" s="111" t="s">
         <v>273</v>
@@ -11986,10 +11985,10 @@
         <v>57</v>
       </c>
       <c r="H64" s="98" t="s">
-        <v>1425</v>
+        <v>1391</v>
       </c>
       <c r="I64" s="98" t="s">
-        <v>1911</v>
+        <v>1923</v>
       </c>
       <c r="J64" s="111" t="s">
         <v>277</v>
@@ -12021,10 +12020,10 @@
         <v>21</v>
       </c>
       <c r="H65" s="100" t="s">
-        <v>1426</v>
-      </c>
-      <c r="I65" s="100" t="s">
-        <v>832</v>
+        <v>1392</v>
+      </c>
+      <c r="I65" s="99" t="s">
+        <v>1924</v>
       </c>
       <c r="J65" s="126" t="s">
         <v>281</v>
@@ -12056,10 +12055,10 @@
         <v>260</v>
       </c>
       <c r="H66" s="97" t="s">
-        <v>1427</v>
+        <v>1393</v>
       </c>
       <c r="I66" s="97" t="s">
-        <v>1912</v>
+        <v>1925</v>
       </c>
       <c r="J66" s="109" t="s">
         <v>286</v>
@@ -12091,10 +12090,10 @@
         <v>260</v>
       </c>
       <c r="H67" s="98" t="s">
-        <v>1428</v>
+        <v>1394</v>
       </c>
       <c r="I67" s="98" t="s">
-        <v>1913</v>
+        <v>1802</v>
       </c>
       <c r="J67" s="111" t="s">
         <v>289</v>
@@ -12103,15 +12102,15 @@
       <c r="M67" s="116"/>
       <c r="N67" s="116"/>
     </row>
-    <row r="68" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="21">
         <v>0</v>
       </c>
       <c r="B68" s="99" t="s">
-        <v>1914</v>
+        <v>1803</v>
       </c>
       <c r="C68" s="99" t="s">
-        <v>1915</v>
+        <v>1804</v>
       </c>
       <c r="D68" s="99"/>
       <c r="E68" s="99" t="s">
@@ -12124,13 +12123,13 @@
         <v>260</v>
       </c>
       <c r="H68" s="99" t="s">
-        <v>1916</v>
+        <v>1805</v>
       </c>
       <c r="I68" s="99" t="s">
-        <v>1918</v>
+        <v>1807</v>
       </c>
       <c r="J68" s="113" t="s">
-        <v>1917</v>
+        <v>1806</v>
       </c>
     </row>
   </sheetData>
@@ -13171,7 +13170,7 @@
         <v>34</v>
       </c>
       <c r="F36" s="128" t="s">
-        <v>833</v>
+        <v>799</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13731,7 +13730,7 @@
         <v>39</v>
       </c>
       <c r="F64" s="128" t="s">
-        <v>1429</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13799,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="B68" s="234" t="s">
-        <v>1914</v>
+        <v>1803</v>
       </c>
       <c r="C68" s="234"/>
       <c r="D68" s="234" t="s">
@@ -13809,7 +13808,7 @@
         <v>257</v>
       </c>
       <c r="F68" s="235" t="s">
-        <v>1919</v>
+        <v>1808</v>
       </c>
     </row>
   </sheetData>
@@ -13858,13 +13857,13 @@
         <v>12</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>1562</v>
+        <v>1815</v>
       </c>
       <c r="D2" s="97" t="s">
-        <v>1496</v>
+        <v>1462</v>
       </c>
       <c r="E2" s="109" t="s">
-        <v>1430</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13875,13 +13874,13 @@
         <v>19</v>
       </c>
       <c r="C3" s="98" t="s">
-        <v>1563</v>
+        <v>1816</v>
       </c>
       <c r="D3" s="98" t="s">
-        <v>1497</v>
+        <v>1463</v>
       </c>
       <c r="E3" s="111" t="s">
-        <v>1431</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13892,13 +13891,13 @@
         <v>25</v>
       </c>
       <c r="C4" s="98" t="s">
-        <v>1564</v>
+        <v>1817</v>
       </c>
       <c r="D4" s="98" t="s">
-        <v>1498</v>
+        <v>1464</v>
       </c>
       <c r="E4" s="111" t="s">
-        <v>1432</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13909,13 +13908,13 @@
         <v>29</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>1565</v>
+        <v>1818</v>
       </c>
       <c r="D5" s="98" t="s">
-        <v>1499</v>
+        <v>1465</v>
       </c>
       <c r="E5" s="111" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13926,13 +13925,13 @@
         <v>33</v>
       </c>
       <c r="C6" s="98" t="s">
-        <v>1566</v>
+        <v>1819</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>1500</v>
+        <v>1466</v>
       </c>
       <c r="E6" s="111" t="s">
-        <v>1434</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13943,13 +13942,13 @@
         <v>38</v>
       </c>
       <c r="C7" s="98" t="s">
-        <v>1567</v>
+        <v>1820</v>
       </c>
       <c r="D7" s="98" t="s">
-        <v>1501</v>
+        <v>1467</v>
       </c>
       <c r="E7" s="111" t="s">
-        <v>1435</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13960,13 +13959,13 @@
         <v>43</v>
       </c>
       <c r="C8" s="98" t="s">
-        <v>1568</v>
+        <v>1821</v>
       </c>
       <c r="D8" s="98" t="s">
-        <v>1502</v>
+        <v>1468</v>
       </c>
       <c r="E8" s="111" t="s">
-        <v>1436</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13977,13 +13976,13 @@
         <v>47</v>
       </c>
       <c r="C9" s="100" t="s">
-        <v>1569</v>
+        <v>1822</v>
       </c>
       <c r="D9" s="100" t="s">
-        <v>1503</v>
+        <v>1469</v>
       </c>
       <c r="E9" s="126" t="s">
-        <v>1437</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13994,13 +13993,13 @@
         <v>51</v>
       </c>
       <c r="C10" s="97" t="s">
-        <v>1570</v>
+        <v>1823</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>1504</v>
+        <v>1470</v>
       </c>
       <c r="E10" s="109" t="s">
-        <v>1438</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14011,13 +14010,13 @@
         <v>56</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>1571</v>
+        <v>1824</v>
       </c>
       <c r="D11" s="98" t="s">
-        <v>1505</v>
+        <v>1471</v>
       </c>
       <c r="E11" s="111" t="s">
-        <v>1439</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14028,13 +14027,13 @@
         <v>61</v>
       </c>
       <c r="C12" s="98" t="s">
-        <v>1572</v>
+        <v>1825</v>
       </c>
       <c r="D12" s="98" t="s">
-        <v>1506</v>
+        <v>1472</v>
       </c>
       <c r="E12" s="111" t="s">
-        <v>1440</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14045,13 +14044,13 @@
         <v>65</v>
       </c>
       <c r="C13" s="98" t="s">
-        <v>1573</v>
+        <v>1826</v>
       </c>
       <c r="D13" s="98" t="s">
-        <v>1507</v>
+        <v>1473</v>
       </c>
       <c r="E13" s="111" t="s">
-        <v>1441</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14062,13 +14061,13 @@
         <v>69</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>1574</v>
+        <v>1827</v>
       </c>
       <c r="D14" s="98" t="s">
-        <v>1508</v>
+        <v>1474</v>
       </c>
       <c r="E14" s="111" t="s">
-        <v>1442</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14079,13 +14078,13 @@
         <v>73</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>1575</v>
+        <v>1828</v>
       </c>
       <c r="D15" s="98" t="s">
-        <v>1509</v>
+        <v>1475</v>
       </c>
       <c r="E15" s="111" t="s">
-        <v>1443</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14096,13 +14095,13 @@
         <v>77</v>
       </c>
       <c r="C16" s="98" t="s">
-        <v>1576</v>
+        <v>1829</v>
       </c>
       <c r="D16" s="98" t="s">
-        <v>1510</v>
+        <v>1476</v>
       </c>
       <c r="E16" s="111" t="s">
-        <v>1444</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14113,13 +14112,13 @@
         <v>82</v>
       </c>
       <c r="C17" s="100" t="s">
-        <v>1577</v>
+        <v>1830</v>
       </c>
       <c r="D17" s="100" t="s">
-        <v>1511</v>
+        <v>1477</v>
       </c>
       <c r="E17" s="126" t="s">
-        <v>1445</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14130,13 +14129,13 @@
         <v>86</v>
       </c>
       <c r="C18" s="97" t="s">
-        <v>1578</v>
+        <v>1831</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>1512</v>
+        <v>1478</v>
       </c>
       <c r="E18" s="109" t="s">
-        <v>1446</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14147,13 +14146,13 @@
         <v>91</v>
       </c>
       <c r="C19" s="98" t="s">
-        <v>1579</v>
+        <v>1832</v>
       </c>
       <c r="D19" s="98" t="s">
-        <v>1513</v>
+        <v>1479</v>
       </c>
       <c r="E19" s="111" t="s">
-        <v>1447</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14164,13 +14163,13 @@
         <v>95</v>
       </c>
       <c r="C20" s="98" t="s">
-        <v>1580</v>
+        <v>1833</v>
       </c>
       <c r="D20" s="98" t="s">
-        <v>1514</v>
+        <v>1480</v>
       </c>
       <c r="E20" s="111" t="s">
-        <v>1448</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14181,13 +14180,13 @@
         <v>99</v>
       </c>
       <c r="C21" s="98" t="s">
-        <v>1581</v>
+        <v>1834</v>
       </c>
       <c r="D21" s="98" t="s">
-        <v>1515</v>
+        <v>1481</v>
       </c>
       <c r="E21" s="111" t="s">
-        <v>1449</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14198,13 +14197,13 @@
         <v>103</v>
       </c>
       <c r="C22" s="98" t="s">
-        <v>1582</v>
+        <v>1835</v>
       </c>
       <c r="D22" s="98" t="s">
-        <v>1516</v>
+        <v>1482</v>
       </c>
       <c r="E22" s="111" t="s">
-        <v>1450</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14215,13 +14214,13 @@
         <v>107</v>
       </c>
       <c r="C23" s="98" t="s">
-        <v>1583</v>
+        <v>1836</v>
       </c>
       <c r="D23" s="98" t="s">
-        <v>1517</v>
+        <v>1483</v>
       </c>
       <c r="E23" s="111" t="s">
-        <v>1451</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14232,13 +14231,13 @@
         <v>111</v>
       </c>
       <c r="C24" s="98" t="s">
-        <v>1584</v>
+        <v>1837</v>
       </c>
       <c r="D24" s="111" t="s">
-        <v>1518</v>
+        <v>1484</v>
       </c>
       <c r="E24" s="111" t="s">
-        <v>1452</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14249,13 +14248,13 @@
         <v>115</v>
       </c>
       <c r="C25" s="99" t="s">
-        <v>1585</v>
+        <v>1838</v>
       </c>
       <c r="D25" s="99" t="s">
-        <v>1519</v>
+        <v>1485</v>
       </c>
       <c r="E25" s="113" t="s">
-        <v>1453</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14266,13 +14265,13 @@
         <v>119</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1586</v>
+        <v>1839</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>1520</v>
+        <v>1486</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>1454</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14283,13 +14282,13 @@
         <v>123</v>
       </c>
       <c r="C27" s="98" t="s">
-        <v>1587</v>
+        <v>1840</v>
       </c>
       <c r="D27" s="98" t="s">
-        <v>1521</v>
+        <v>1487</v>
       </c>
       <c r="E27" s="111" t="s">
-        <v>1455</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14300,13 +14299,13 @@
         <v>127</v>
       </c>
       <c r="C28" s="98" t="s">
-        <v>1588</v>
+        <v>1841</v>
       </c>
       <c r="D28" s="98" t="s">
-        <v>1522</v>
+        <v>1488</v>
       </c>
       <c r="E28" s="111" t="s">
-        <v>1456</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14317,13 +14316,13 @@
         <v>131</v>
       </c>
       <c r="C29" s="98" t="s">
-        <v>1589</v>
+        <v>1842</v>
       </c>
       <c r="D29" s="98" t="s">
-        <v>1523</v>
+        <v>1489</v>
       </c>
       <c r="E29" s="111" t="s">
-        <v>1457</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14334,13 +14333,13 @@
         <v>135</v>
       </c>
       <c r="C30" s="98" t="s">
-        <v>1590</v>
+        <v>1843</v>
       </c>
       <c r="D30" s="98" t="s">
-        <v>1524</v>
+        <v>1490</v>
       </c>
       <c r="E30" s="111" t="s">
-        <v>1458</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14351,13 +14350,13 @@
         <v>139</v>
       </c>
       <c r="C31" s="98" t="s">
-        <v>1591</v>
+        <v>1844</v>
       </c>
       <c r="D31" s="98" t="s">
-        <v>1525</v>
+        <v>1491</v>
       </c>
       <c r="E31" s="111" t="s">
-        <v>1459</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14368,13 +14367,13 @@
         <v>143</v>
       </c>
       <c r="C32" s="98" t="s">
-        <v>1592</v>
+        <v>1845</v>
       </c>
       <c r="D32" s="98" t="s">
-        <v>1526</v>
+        <v>1492</v>
       </c>
       <c r="E32" s="111" t="s">
-        <v>1460</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14385,13 +14384,13 @@
         <v>147</v>
       </c>
       <c r="C33" s="100" t="s">
-        <v>1593</v>
+        <v>1846</v>
       </c>
       <c r="D33" s="100" t="s">
-        <v>1527</v>
+        <v>1493</v>
       </c>
       <c r="E33" s="126" t="s">
-        <v>1461</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14402,13 +14401,13 @@
         <v>151</v>
       </c>
       <c r="C34" s="97" t="s">
-        <v>1594</v>
+        <v>1847</v>
       </c>
       <c r="D34" s="97" t="s">
-        <v>1528</v>
+        <v>1494</v>
       </c>
       <c r="E34" s="109" t="s">
-        <v>1462</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14419,13 +14418,13 @@
         <v>156</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>1595</v>
+        <v>1848</v>
       </c>
       <c r="D35" s="98" t="s">
-        <v>1529</v>
+        <v>1495</v>
       </c>
       <c r="E35" s="111" t="s">
-        <v>1463</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="36" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14436,13 +14435,13 @@
         <v>160</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>1596</v>
+        <v>1849</v>
       </c>
       <c r="D36" s="98" t="s">
-        <v>1530</v>
+        <v>1496</v>
       </c>
       <c r="E36" s="111" t="s">
-        <v>1464</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14453,13 +14452,13 @@
         <v>164</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>1597</v>
+        <v>1850</v>
       </c>
       <c r="D37" s="98" t="s">
-        <v>1531</v>
+        <v>1497</v>
       </c>
       <c r="E37" s="111" t="s">
-        <v>1465</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14470,13 +14469,13 @@
         <v>168</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1598</v>
+        <v>1851</v>
       </c>
       <c r="D38" s="98" t="s">
-        <v>1532</v>
+        <v>1498</v>
       </c>
       <c r="E38" s="111" t="s">
-        <v>1466</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14487,13 +14486,13 @@
         <v>172</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1599</v>
+        <v>1852</v>
       </c>
       <c r="D39" s="98" t="s">
-        <v>1533</v>
+        <v>1499</v>
       </c>
       <c r="E39" s="111" t="s">
-        <v>1467</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="40" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14504,13 +14503,13 @@
         <v>176</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1600</v>
+        <v>1853</v>
       </c>
       <c r="D40" s="98" t="s">
-        <v>1534</v>
+        <v>1500</v>
       </c>
       <c r="E40" s="111" t="s">
-        <v>1468</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14521,13 +14520,13 @@
         <v>180</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>1601</v>
+        <v>1854</v>
       </c>
       <c r="D41" s="99" t="s">
-        <v>1535</v>
+        <v>1501</v>
       </c>
       <c r="E41" s="113" t="s">
-        <v>1469</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="42" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14538,13 +14537,13 @@
         <v>184</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>1602</v>
+        <v>1855</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>1470</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="43" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14555,13 +14554,13 @@
         <v>189</v>
       </c>
       <c r="C43" s="98" t="s">
-        <v>1603</v>
+        <v>1856</v>
       </c>
       <c r="D43" s="98" t="s">
-        <v>1537</v>
+        <v>1503</v>
       </c>
       <c r="E43" s="111" t="s">
-        <v>1471</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="44" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14572,13 +14571,13 @@
         <v>193</v>
       </c>
       <c r="C44" s="98" t="s">
-        <v>1604</v>
+        <v>1857</v>
       </c>
       <c r="D44" s="98" t="s">
-        <v>1538</v>
+        <v>1504</v>
       </c>
       <c r="E44" s="111" t="s">
-        <v>1472</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="45" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14589,13 +14588,13 @@
         <v>197</v>
       </c>
       <c r="C45" s="98" t="s">
-        <v>1605</v>
+        <v>1858</v>
       </c>
       <c r="D45" s="98" t="s">
-        <v>1539</v>
+        <v>1505</v>
       </c>
       <c r="E45" s="111" t="s">
-        <v>1473</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="46" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14606,13 +14605,13 @@
         <v>201</v>
       </c>
       <c r="C46" s="98" t="s">
-        <v>1606</v>
+        <v>1859</v>
       </c>
       <c r="D46" s="98" t="s">
-        <v>1540</v>
+        <v>1506</v>
       </c>
       <c r="E46" s="111" t="s">
-        <v>1474</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="47" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14623,13 +14622,13 @@
         <v>205</v>
       </c>
       <c r="C47" s="98" t="s">
-        <v>1607</v>
+        <v>1860</v>
       </c>
       <c r="D47" s="98" t="s">
-        <v>1541</v>
+        <v>1507</v>
       </c>
       <c r="E47" s="111" t="s">
-        <v>1475</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="48" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14640,13 +14639,13 @@
         <v>209</v>
       </c>
       <c r="C48" s="98" t="s">
-        <v>1608</v>
+        <v>1861</v>
       </c>
       <c r="D48" s="111" t="s">
-        <v>1542</v>
+        <v>1508</v>
       </c>
       <c r="E48" s="111" t="s">
-        <v>1476</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="49" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14657,13 +14656,13 @@
         <v>213</v>
       </c>
       <c r="C49" s="100" t="s">
-        <v>1609</v>
+        <v>1862</v>
       </c>
       <c r="D49" s="100" t="s">
-        <v>1543</v>
+        <v>1509</v>
       </c>
       <c r="E49" s="126" t="s">
-        <v>1477</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14674,13 +14673,13 @@
         <v>217</v>
       </c>
       <c r="C50" s="97" t="s">
-        <v>1610</v>
+        <v>1863</v>
       </c>
       <c r="D50" s="97" t="s">
-        <v>1544</v>
+        <v>1510</v>
       </c>
       <c r="E50" s="109" t="s">
-        <v>1478</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="51" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14691,13 +14690,13 @@
         <v>222</v>
       </c>
       <c r="C51" s="98" t="s">
-        <v>1611</v>
+        <v>1864</v>
       </c>
       <c r="D51" s="98" t="s">
-        <v>1545</v>
+        <v>1511</v>
       </c>
       <c r="E51" s="111" t="s">
-        <v>1479</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="52" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14708,13 +14707,13 @@
         <v>226</v>
       </c>
       <c r="C52" s="98" t="s">
-        <v>1612</v>
+        <v>1865</v>
       </c>
       <c r="D52" s="98" t="s">
-        <v>1546</v>
+        <v>1512</v>
       </c>
       <c r="E52" s="111" t="s">
-        <v>1480</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="53" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14725,13 +14724,13 @@
         <v>230</v>
       </c>
       <c r="C53" s="98" t="s">
-        <v>1613</v>
+        <v>1866</v>
       </c>
       <c r="D53" s="98" t="s">
-        <v>1547</v>
+        <v>1513</v>
       </c>
       <c r="E53" s="111" t="s">
-        <v>1481</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="54" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14742,13 +14741,13 @@
         <v>234</v>
       </c>
       <c r="C54" s="98" t="s">
-        <v>1614</v>
+        <v>1867</v>
       </c>
       <c r="D54" s="98" t="s">
-        <v>1548</v>
+        <v>1514</v>
       </c>
       <c r="E54" s="111" t="s">
-        <v>1482</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="55" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14759,13 +14758,13 @@
         <v>238</v>
       </c>
       <c r="C55" s="98" t="s">
-        <v>1615</v>
+        <v>1868</v>
       </c>
       <c r="D55" s="98" t="s">
-        <v>1549</v>
+        <v>1515</v>
       </c>
       <c r="E55" s="111" t="s">
-        <v>1483</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14776,13 +14775,13 @@
         <v>242</v>
       </c>
       <c r="C56" s="98" t="s">
-        <v>1616</v>
+        <v>1869</v>
       </c>
       <c r="D56" s="98" t="s">
-        <v>1550</v>
+        <v>1516</v>
       </c>
       <c r="E56" s="111" t="s">
-        <v>1484</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="57" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14793,13 +14792,13 @@
         <v>246</v>
       </c>
       <c r="C57" s="99" t="s">
-        <v>1617</v>
+        <v>1870</v>
       </c>
       <c r="D57" s="99" t="s">
-        <v>1551</v>
+        <v>1517</v>
       </c>
       <c r="E57" s="113" t="s">
-        <v>1485</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="58" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14810,13 +14809,13 @@
         <v>250</v>
       </c>
       <c r="C58" s="97" t="s">
-        <v>1618</v>
+        <v>1871</v>
       </c>
       <c r="D58" s="97" t="s">
-        <v>1552</v>
+        <v>1518</v>
       </c>
       <c r="E58" s="109" t="s">
-        <v>1486</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="59" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14827,13 +14826,13 @@
         <v>255</v>
       </c>
       <c r="C59" s="98" t="s">
-        <v>1619</v>
+        <v>1872</v>
       </c>
       <c r="D59" s="98" t="s">
-        <v>1553</v>
+        <v>1519</v>
       </c>
       <c r="E59" s="111" t="s">
-        <v>1487</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="60" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14844,13 +14843,13 @@
         <v>259</v>
       </c>
       <c r="C60" s="98" t="s">
-        <v>1620</v>
+        <v>1873</v>
       </c>
       <c r="D60" s="98" t="s">
-        <v>1554</v>
+        <v>1520</v>
       </c>
       <c r="E60" s="111" t="s">
-        <v>1488</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="61" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14861,13 +14860,13 @@
         <v>264</v>
       </c>
       <c r="C61" s="98" t="s">
-        <v>1621</v>
+        <v>1874</v>
       </c>
       <c r="D61" s="98" t="s">
-        <v>1555</v>
+        <v>1521</v>
       </c>
       <c r="E61" s="111" t="s">
-        <v>1489</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="62" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14878,13 +14877,13 @@
         <v>268</v>
       </c>
       <c r="C62" s="98" t="s">
-        <v>1622</v>
+        <v>1875</v>
       </c>
       <c r="D62" s="98" t="s">
-        <v>1556</v>
+        <v>1522</v>
       </c>
       <c r="E62" s="111" t="s">
-        <v>1490</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="63" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14895,13 +14894,13 @@
         <v>272</v>
       </c>
       <c r="C63" s="98" t="s">
-        <v>1623</v>
+        <v>1876</v>
       </c>
       <c r="D63" s="98" t="s">
-        <v>1557</v>
+        <v>1523</v>
       </c>
       <c r="E63" s="111" t="s">
-        <v>1491</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="64" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14912,13 +14911,13 @@
         <v>276</v>
       </c>
       <c r="C64" s="98" t="s">
-        <v>1624</v>
+        <v>1877</v>
       </c>
       <c r="D64" s="98" t="s">
-        <v>1558</v>
+        <v>1524</v>
       </c>
       <c r="E64" s="111" t="s">
-        <v>1492</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="65" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14929,13 +14928,13 @@
         <v>280</v>
       </c>
       <c r="C65" s="100" t="s">
-        <v>1625</v>
+        <v>1878</v>
       </c>
       <c r="D65" s="100" t="s">
-        <v>1559</v>
+        <v>1525</v>
       </c>
       <c r="E65" s="126" t="s">
-        <v>1493</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="66" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14946,13 +14945,13 @@
         <v>284</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>1626</v>
+        <v>1879</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>1560</v>
+        <v>1526</v>
       </c>
       <c r="E66" s="109" t="s">
-        <v>1494</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="67" spans="1:5" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14963,13 +14962,13 @@
         <v>56</v>
       </c>
       <c r="C67" s="99" t="s">
-        <v>1627</v>
+        <v>1880</v>
       </c>
       <c r="D67" s="99" t="s">
-        <v>1561</v>
+        <v>1527</v>
       </c>
       <c r="E67" s="113" t="s">
-        <v>1495</v>
+        <v>1461</v>
       </c>
     </row>
   </sheetData>
@@ -16305,7 +16304,7 @@
         <v>473</v>
       </c>
       <c r="G57" s="272" t="s">
-        <v>1924</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16503,7 +16502,7 @@
         <v>284</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>1921</v>
+        <v>1810</v>
       </c>
       <c r="E66" s="97" t="s">
         <v>490</v>
@@ -16526,7 +16525,7 @@
         <v>56</v>
       </c>
       <c r="D67" s="98" t="s">
-        <v>1921</v>
+        <v>1810</v>
       </c>
       <c r="E67" s="98" t="s">
         <v>490</v>
@@ -16543,20 +16542,20 @@
         <v>0</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>1920</v>
+        <v>1809</v>
       </c>
       <c r="C68" s="99"/>
       <c r="D68" s="99" t="s">
-        <v>1921</v>
+        <v>1810</v>
       </c>
       <c r="E68" s="99" t="s">
-        <v>1922</v>
+        <v>1811</v>
       </c>
       <c r="F68" s="113" t="s">
-        <v>1923</v>
+        <v>1812</v>
       </c>
       <c r="G68" s="269" t="s">
-        <v>1925</v>
+        <v>1814</v>
       </c>
     </row>
   </sheetData>
@@ -18516,16 +18515,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>1628</v>
+        <v>1528</v>
       </c>
       <c r="D2" s="109" t="s">
-        <v>1629</v>
+        <v>1529</v>
       </c>
       <c r="E2" s="97" t="s">
-        <v>1630</v>
+        <v>1530</v>
       </c>
       <c r="F2" s="109" t="s">
-        <v>1631</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18536,16 +18535,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="98" t="s">
-        <v>1632</v>
+        <v>1532</v>
       </c>
       <c r="D3" s="111" t="s">
-        <v>1633</v>
+        <v>1533</v>
       </c>
       <c r="E3" s="98" t="s">
-        <v>1634</v>
+        <v>1534</v>
       </c>
       <c r="F3" s="111" t="s">
-        <v>1635</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18556,16 +18555,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="98" t="s">
-        <v>1636</v>
+        <v>1536</v>
       </c>
       <c r="D4" s="111" t="s">
-        <v>1637</v>
+        <v>1537</v>
       </c>
       <c r="E4" s="98" t="s">
-        <v>1638</v>
+        <v>1538</v>
       </c>
       <c r="F4" s="111" t="s">
-        <v>1639</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18576,16 +18575,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>1640</v>
+        <v>1540</v>
       </c>
       <c r="D5" s="111" t="s">
-        <v>1641</v>
+        <v>1541</v>
       </c>
       <c r="E5" s="98" t="s">
-        <v>1642</v>
+        <v>1542</v>
       </c>
       <c r="F5" s="111" t="s">
-        <v>1643</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18596,16 +18595,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="98" t="s">
-        <v>1644</v>
+        <v>1544</v>
       </c>
       <c r="D6" s="111" t="s">
-        <v>1645</v>
+        <v>1545</v>
       </c>
       <c r="E6" s="98" t="s">
-        <v>1646</v>
+        <v>1546</v>
       </c>
       <c r="F6" s="111" t="s">
-        <v>1647</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18616,16 +18615,16 @@
         <v>36</v>
       </c>
       <c r="C7" s="98" t="s">
-        <v>1648</v>
+        <v>1548</v>
       </c>
       <c r="D7" s="111" t="s">
-        <v>1649</v>
+        <v>1549</v>
       </c>
       <c r="E7" s="98" t="s">
-        <v>1650</v>
+        <v>1550</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>1651</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18636,16 +18635,16 @@
         <v>41</v>
       </c>
       <c r="C8" s="98" t="s">
-        <v>1652</v>
+        <v>1552</v>
       </c>
       <c r="D8" s="111" t="s">
-        <v>1653</v>
+        <v>1553</v>
       </c>
       <c r="E8" s="98" t="s">
-        <v>1654</v>
+        <v>1554</v>
       </c>
       <c r="F8" s="111" t="s">
-        <v>1655</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18656,16 +18655,16 @@
         <v>45</v>
       </c>
       <c r="C9" s="99" t="s">
-        <v>1656</v>
+        <v>1556</v>
       </c>
       <c r="D9" s="113" t="s">
-        <v>1657</v>
+        <v>1557</v>
       </c>
       <c r="E9" s="100" t="s">
-        <v>1658</v>
+        <v>1558</v>
       </c>
       <c r="F9" s="126" t="s">
-        <v>1659</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18676,16 +18675,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="97" t="s">
-        <v>1660</v>
+        <v>1560</v>
       </c>
       <c r="D10" s="109" t="s">
-        <v>1661</v>
+        <v>1561</v>
       </c>
       <c r="E10" s="97" t="s">
-        <v>1662</v>
+        <v>1562</v>
       </c>
       <c r="F10" s="109" t="s">
-        <v>1663</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18696,16 +18695,16 @@
         <v>54</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>1664</v>
+        <v>1564</v>
       </c>
       <c r="D11" s="111" t="s">
-        <v>1665</v>
+        <v>1565</v>
       </c>
       <c r="E11" s="98" t="s">
-        <v>1666</v>
+        <v>1566</v>
       </c>
       <c r="F11" s="111" t="s">
-        <v>1667</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18716,16 +18715,16 @@
         <v>59</v>
       </c>
       <c r="C12" s="98" t="s">
-        <v>1668</v>
+        <v>1568</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>1669</v>
+        <v>1569</v>
       </c>
       <c r="E12" s="98" t="s">
-        <v>1670</v>
+        <v>1570</v>
       </c>
       <c r="F12" s="111" t="s">
-        <v>1671</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18736,16 +18735,16 @@
         <v>63</v>
       </c>
       <c r="C13" s="98" t="s">
-        <v>1672</v>
+        <v>1572</v>
       </c>
       <c r="D13" s="111" t="s">
-        <v>1673</v>
+        <v>1573</v>
       </c>
       <c r="E13" s="98" t="s">
-        <v>1674</v>
+        <v>1574</v>
       </c>
       <c r="F13" s="111" t="s">
-        <v>1675</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18756,16 +18755,16 @@
         <v>67</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>1676</v>
+        <v>1576</v>
       </c>
       <c r="D14" s="111" t="s">
-        <v>1677</v>
+        <v>1577</v>
       </c>
       <c r="E14" s="98" t="s">
-        <v>1678</v>
+        <v>1578</v>
       </c>
       <c r="F14" s="111" t="s">
-        <v>1679</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18776,16 +18775,16 @@
         <v>71</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>1680</v>
+        <v>1580</v>
       </c>
       <c r="D15" s="111" t="s">
-        <v>1681</v>
+        <v>1581</v>
       </c>
       <c r="E15" s="98" t="s">
-        <v>1682</v>
+        <v>1582</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>1683</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18796,16 +18795,16 @@
         <v>75</v>
       </c>
       <c r="C16" s="98" t="s">
-        <v>1684</v>
+        <v>1584</v>
       </c>
       <c r="D16" s="111" t="s">
-        <v>1685</v>
+        <v>1585</v>
       </c>
       <c r="E16" s="98" t="s">
-        <v>1686</v>
+        <v>1586</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>1687</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18816,16 +18815,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>1688</v>
+        <v>1588</v>
       </c>
       <c r="D17" s="113" t="s">
-        <v>1689</v>
+        <v>1589</v>
       </c>
       <c r="E17" s="99" t="s">
-        <v>1690</v>
+        <v>1590</v>
       </c>
       <c r="F17" s="181" t="s">
-        <v>1691</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18836,16 +18835,16 @@
         <v>84</v>
       </c>
       <c r="C18" s="97" t="s">
-        <v>1692</v>
+        <v>1592</v>
       </c>
       <c r="D18" s="109" t="s">
-        <v>1693</v>
+        <v>1593</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>1694</v>
+        <v>1594</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>1695</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18856,16 +18855,16 @@
         <v>89</v>
       </c>
       <c r="C19" s="98" t="s">
-        <v>1696</v>
+        <v>1596</v>
       </c>
       <c r="D19" s="111" t="s">
-        <v>1697</v>
+        <v>1597</v>
       </c>
       <c r="E19" s="98" t="s">
-        <v>1698</v>
+        <v>1598</v>
       </c>
       <c r="F19" s="111" t="s">
-        <v>1699</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18876,16 +18875,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="98" t="s">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="D20" s="111" t="s">
-        <v>1701</v>
+        <v>1601</v>
       </c>
       <c r="E20" s="98" t="s">
-        <v>1702</v>
+        <v>1602</v>
       </c>
       <c r="F20" s="111" t="s">
-        <v>1703</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18896,16 +18895,16 @@
         <v>97</v>
       </c>
       <c r="C21" s="98" t="s">
-        <v>1704</v>
+        <v>1604</v>
       </c>
       <c r="D21" s="111" t="s">
-        <v>1705</v>
+        <v>1605</v>
       </c>
       <c r="E21" s="98" t="s">
-        <v>1706</v>
+        <v>1606</v>
       </c>
       <c r="F21" s="111" t="s">
-        <v>1707</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18916,16 +18915,16 @@
         <v>101</v>
       </c>
       <c r="C22" s="98" t="s">
-        <v>1708</v>
+        <v>1608</v>
       </c>
       <c r="D22" s="111" t="s">
-        <v>1709</v>
+        <v>1609</v>
       </c>
       <c r="E22" s="98" t="s">
-        <v>1710</v>
+        <v>1610</v>
       </c>
       <c r="F22" s="111" t="s">
-        <v>1711</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18936,16 +18935,16 @@
         <v>105</v>
       </c>
       <c r="C23" s="98" t="s">
-        <v>1712</v>
+        <v>1612</v>
       </c>
       <c r="D23" s="111" t="s">
-        <v>1713</v>
+        <v>1613</v>
       </c>
       <c r="E23" s="98" t="s">
-        <v>1714</v>
+        <v>1614</v>
       </c>
       <c r="F23" s="111" t="s">
-        <v>1715</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18956,19 +18955,19 @@
         <v>109</v>
       </c>
       <c r="C24" s="98" t="s">
-        <v>1716</v>
+        <v>1616</v>
       </c>
       <c r="D24" s="111" t="s">
-        <v>1717</v>
+        <v>1617</v>
       </c>
       <c r="E24" s="98" t="s">
-        <v>1718</v>
+        <v>1618</v>
       </c>
       <c r="F24" s="111" t="s">
-        <v>1719</v>
+        <v>1619</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1720</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18979,16 +18978,16 @@
         <v>113</v>
       </c>
       <c r="C25" s="99" t="s">
-        <v>1721</v>
+        <v>1621</v>
       </c>
       <c r="D25" s="113" t="s">
-        <v>1722</v>
+        <v>1622</v>
       </c>
       <c r="E25" s="100" t="s">
-        <v>1723</v>
+        <v>1623</v>
       </c>
       <c r="F25" s="126" t="s">
-        <v>1724</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18999,16 +18998,16 @@
         <v>117</v>
       </c>
       <c r="C26" s="97" t="s">
-        <v>1725</v>
+        <v>1625</v>
       </c>
       <c r="D26" s="109" t="s">
-        <v>1726</v>
+        <v>1626</v>
       </c>
       <c r="E26" s="97" t="s">
-        <v>1727</v>
+        <v>1627</v>
       </c>
       <c r="F26" s="109" t="s">
-        <v>1728</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19019,16 +19018,16 @@
         <v>121</v>
       </c>
       <c r="C27" s="98" t="s">
-        <v>1729</v>
+        <v>1629</v>
       </c>
       <c r="D27" s="111" t="s">
-        <v>1730</v>
+        <v>1630</v>
       </c>
       <c r="E27" s="98" t="s">
-        <v>1731</v>
+        <v>1631</v>
       </c>
       <c r="F27" s="111" t="s">
-        <v>1732</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19039,16 +19038,16 @@
         <v>125</v>
       </c>
       <c r="C28" s="98" t="s">
-        <v>1733</v>
+        <v>1633</v>
       </c>
       <c r="D28" s="111" t="s">
-        <v>1734</v>
+        <v>1634</v>
       </c>
       <c r="E28" s="98" t="s">
-        <v>1735</v>
+        <v>1635</v>
       </c>
       <c r="F28" s="111" t="s">
-        <v>1736</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19059,16 +19058,16 @@
         <v>129</v>
       </c>
       <c r="C29" s="98" t="s">
-        <v>1737</v>
+        <v>1637</v>
       </c>
       <c r="D29" s="111" t="s">
-        <v>1738</v>
+        <v>1638</v>
       </c>
       <c r="E29" s="98" t="s">
-        <v>1739</v>
+        <v>1639</v>
       </c>
       <c r="F29" s="111" t="s">
-        <v>1740</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19079,16 +19078,16 @@
         <v>133</v>
       </c>
       <c r="C30" s="98" t="s">
-        <v>1741</v>
+        <v>1641</v>
       </c>
       <c r="D30" s="111" t="s">
-        <v>1742</v>
+        <v>1642</v>
       </c>
       <c r="E30" s="98" t="s">
-        <v>1743</v>
+        <v>1643</v>
       </c>
       <c r="F30" s="111" t="s">
-        <v>1744</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19099,16 +19098,16 @@
         <v>137</v>
       </c>
       <c r="C31" s="98" t="s">
-        <v>1745</v>
+        <v>1645</v>
       </c>
       <c r="D31" s="111" t="s">
-        <v>1746</v>
+        <v>1646</v>
       </c>
       <c r="E31" s="98" t="s">
-        <v>1747</v>
+        <v>1647</v>
       </c>
       <c r="F31" s="111" t="s">
-        <v>1748</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19119,16 +19118,16 @@
         <v>141</v>
       </c>
       <c r="C32" s="98" t="s">
-        <v>1749</v>
+        <v>1649</v>
       </c>
       <c r="D32" s="111" t="s">
-        <v>1750</v>
+        <v>1650</v>
       </c>
       <c r="E32" s="98" t="s">
-        <v>1751</v>
+        <v>1651</v>
       </c>
       <c r="F32" s="111" t="s">
-        <v>1752</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19139,16 +19138,16 @@
         <v>145</v>
       </c>
       <c r="C33" s="99" t="s">
-        <v>1753</v>
+        <v>1653</v>
       </c>
       <c r="D33" s="113" t="s">
-        <v>1754</v>
+        <v>1654</v>
       </c>
       <c r="E33" s="99" t="s">
-        <v>1755</v>
+        <v>1655</v>
       </c>
       <c r="F33" s="113" t="s">
-        <v>1756</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19159,16 +19158,16 @@
         <v>149</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>1757</v>
+        <v>1657</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>1758</v>
+        <v>1658</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>1759</v>
+        <v>1659</v>
       </c>
       <c r="F34" s="109" t="s">
-        <v>1760</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19179,16 +19178,16 @@
         <v>154</v>
       </c>
       <c r="C35" s="98" t="s">
-        <v>1761</v>
+        <v>1661</v>
       </c>
       <c r="D35" s="111" t="s">
-        <v>1762</v>
+        <v>1662</v>
       </c>
       <c r="E35" s="98" t="s">
-        <v>1763</v>
+        <v>1663</v>
       </c>
       <c r="F35" s="111" t="s">
-        <v>1764</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19199,16 +19198,16 @@
         <v>158</v>
       </c>
       <c r="C36" s="180" t="s">
-        <v>1765</v>
+        <v>1665</v>
       </c>
       <c r="D36" s="111" t="s">
-        <v>1766</v>
+        <v>1666</v>
       </c>
       <c r="E36" s="98" t="s">
-        <v>1767</v>
+        <v>1667</v>
       </c>
       <c r="F36" s="111" t="s">
-        <v>1768</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19219,16 +19218,16 @@
         <v>162</v>
       </c>
       <c r="C37" s="98" t="s">
-        <v>1769</v>
+        <v>1669</v>
       </c>
       <c r="D37" s="111" t="s">
-        <v>1770</v>
+        <v>1670</v>
       </c>
       <c r="E37" s="98" t="s">
-        <v>1771</v>
+        <v>1671</v>
       </c>
       <c r="F37" s="111" t="s">
-        <v>1772</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19239,16 +19238,16 @@
         <v>166</v>
       </c>
       <c r="C38" s="98" t="s">
-        <v>1773</v>
+        <v>1673</v>
       </c>
       <c r="D38" s="111" t="s">
-        <v>1774</v>
+        <v>1674</v>
       </c>
       <c r="E38" s="98" t="s">
-        <v>1775</v>
+        <v>1675</v>
       </c>
       <c r="F38" s="111" t="s">
-        <v>1776</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19259,16 +19258,16 @@
         <v>170</v>
       </c>
       <c r="C39" s="114" t="s">
-        <v>1777</v>
+        <v>1677</v>
       </c>
       <c r="D39" s="111" t="s">
-        <v>1778</v>
+        <v>1678</v>
       </c>
       <c r="E39" s="98" t="s">
-        <v>1779</v>
+        <v>1679</v>
       </c>
       <c r="F39" s="111" t="s">
-        <v>1780</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19279,16 +19278,16 @@
         <v>174</v>
       </c>
       <c r="C40" s="98" t="s">
-        <v>1781</v>
+        <v>1681</v>
       </c>
       <c r="D40" s="111" t="s">
-        <v>1782</v>
+        <v>1682</v>
       </c>
       <c r="E40" s="98" t="s">
-        <v>1783</v>
+        <v>1683</v>
       </c>
       <c r="F40" s="111" t="s">
-        <v>1784</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19299,16 +19298,16 @@
         <v>178</v>
       </c>
       <c r="C41" s="100" t="s">
-        <v>1785</v>
+        <v>1685</v>
       </c>
       <c r="D41" s="229" t="s">
-        <v>1786</v>
+        <v>1686</v>
       </c>
       <c r="E41" s="99" t="s">
-        <v>1787</v>
+        <v>1687</v>
       </c>
       <c r="F41" s="113" t="s">
-        <v>1788</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19319,16 +19318,16 @@
         <v>182</v>
       </c>
       <c r="C42" s="97" t="s">
-        <v>1789</v>
+        <v>1689</v>
       </c>
       <c r="D42" s="109" t="s">
-        <v>1790</v>
+        <v>1690</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>1791</v>
+        <v>1691</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>1792</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19339,16 +19338,16 @@
         <v>187</v>
       </c>
       <c r="C43" s="98" t="s">
-        <v>1793</v>
+        <v>1693</v>
       </c>
       <c r="D43" s="111" t="s">
-        <v>1794</v>
+        <v>1694</v>
       </c>
       <c r="E43" s="98" t="s">
-        <v>1795</v>
+        <v>1695</v>
       </c>
       <c r="F43" s="111" t="s">
-        <v>1796</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19359,16 +19358,16 @@
         <v>191</v>
       </c>
       <c r="C44" s="98" t="s">
-        <v>1797</v>
+        <v>1697</v>
       </c>
       <c r="D44" s="111" t="s">
-        <v>1798</v>
+        <v>1698</v>
       </c>
       <c r="E44" s="98" t="s">
-        <v>1799</v>
+        <v>1699</v>
       </c>
       <c r="F44" s="111" t="s">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19379,16 +19378,16 @@
         <v>195</v>
       </c>
       <c r="C45" s="98" t="s">
-        <v>1801</v>
+        <v>1701</v>
       </c>
       <c r="D45" s="111" t="s">
-        <v>1802</v>
+        <v>1702</v>
       </c>
       <c r="E45" s="98" t="s">
-        <v>1803</v>
+        <v>1703</v>
       </c>
       <c r="F45" s="111" t="s">
-        <v>1804</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19399,19 +19398,19 @@
         <v>199</v>
       </c>
       <c r="C46" s="98" t="s">
-        <v>1805</v>
+        <v>1705</v>
       </c>
       <c r="D46" s="111" t="s">
-        <v>1806</v>
+        <v>1706</v>
       </c>
       <c r="E46" s="98" t="s">
-        <v>1807</v>
+        <v>1707</v>
       </c>
       <c r="F46" s="111" t="s">
-        <v>1808</v>
+        <v>1708</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>1809</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19422,16 +19421,16 @@
         <v>203</v>
       </c>
       <c r="C47" s="98" t="s">
-        <v>1810</v>
+        <v>1710</v>
       </c>
       <c r="D47" s="111" t="s">
-        <v>1811</v>
+        <v>1711</v>
       </c>
       <c r="E47" s="98" t="s">
-        <v>1812</v>
+        <v>1712</v>
       </c>
       <c r="F47" s="111" t="s">
-        <v>1813</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19442,19 +19441,19 @@
         <v>207</v>
       </c>
       <c r="C48" s="98" t="s">
-        <v>1814</v>
+        <v>1714</v>
       </c>
       <c r="D48" s="111" t="s">
-        <v>1815</v>
+        <v>1715</v>
       </c>
       <c r="E48" s="98" t="s">
-        <v>1816</v>
+        <v>1716</v>
       </c>
       <c r="F48" s="111" t="s">
-        <v>1817</v>
+        <v>1717</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>1818</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19465,16 +19464,16 @@
         <v>211</v>
       </c>
       <c r="C49" s="99" t="s">
-        <v>1819</v>
+        <v>1719</v>
       </c>
       <c r="D49" s="113" t="s">
-        <v>1820</v>
+        <v>1720</v>
       </c>
       <c r="E49" s="100" t="s">
-        <v>1821</v>
+        <v>1721</v>
       </c>
       <c r="F49" s="126" t="s">
-        <v>1822</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19485,16 +19484,16 @@
         <v>215</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>1823</v>
+        <v>1723</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>1824</v>
+        <v>1724</v>
       </c>
       <c r="E50" s="97" t="s">
-        <v>1825</v>
+        <v>1725</v>
       </c>
       <c r="F50" s="109" t="s">
-        <v>1826</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19505,16 +19504,16 @@
         <v>220</v>
       </c>
       <c r="C51" s="98" t="s">
-        <v>1827</v>
+        <v>1727</v>
       </c>
       <c r="D51" s="111" t="s">
-        <v>1828</v>
+        <v>1728</v>
       </c>
       <c r="E51" s="98" t="s">
-        <v>1829</v>
+        <v>1729</v>
       </c>
       <c r="F51" s="111" t="s">
-        <v>1830</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19525,16 +19524,16 @@
         <v>224</v>
       </c>
       <c r="C52" s="98" t="s">
-        <v>1831</v>
+        <v>1731</v>
       </c>
       <c r="D52" s="111" t="s">
-        <v>1832</v>
+        <v>1732</v>
       </c>
       <c r="E52" s="98" t="s">
-        <v>1833</v>
+        <v>1733</v>
       </c>
       <c r="F52" s="111" t="s">
-        <v>1834</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19545,16 +19544,16 @@
         <v>228</v>
       </c>
       <c r="C53" s="98" t="s">
-        <v>1835</v>
+        <v>1735</v>
       </c>
       <c r="D53" s="111" t="s">
-        <v>1836</v>
+        <v>1736</v>
       </c>
       <c r="E53" s="98" t="s">
-        <v>1837</v>
+        <v>1737</v>
       </c>
       <c r="F53" s="111" t="s">
-        <v>1838</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19565,16 +19564,16 @@
         <v>232</v>
       </c>
       <c r="C54" s="98" t="s">
-        <v>1839</v>
+        <v>1739</v>
       </c>
       <c r="D54" s="111" t="s">
-        <v>1840</v>
+        <v>1740</v>
       </c>
       <c r="E54" s="98" t="s">
-        <v>1841</v>
+        <v>1741</v>
       </c>
       <c r="F54" s="111" t="s">
-        <v>1842</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19585,16 +19584,16 @@
         <v>236</v>
       </c>
       <c r="C55" s="98" t="s">
-        <v>1843</v>
+        <v>1743</v>
       </c>
       <c r="D55" s="111" t="s">
-        <v>1844</v>
+        <v>1744</v>
       </c>
       <c r="E55" s="98" t="s">
-        <v>1845</v>
+        <v>1745</v>
       </c>
       <c r="F55" s="111" t="s">
-        <v>1846</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19605,16 +19604,16 @@
         <v>240</v>
       </c>
       <c r="C56" s="98" t="s">
-        <v>1847</v>
+        <v>1747</v>
       </c>
       <c r="D56" s="111" t="s">
-        <v>1848</v>
+        <v>1748</v>
       </c>
       <c r="E56" s="98" t="s">
-        <v>1849</v>
+        <v>1749</v>
       </c>
       <c r="F56" s="111" t="s">
-        <v>1850</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19625,16 +19624,16 @@
         <v>244</v>
       </c>
       <c r="C57" s="100" t="s">
-        <v>1851</v>
+        <v>1751</v>
       </c>
       <c r="D57" s="126" t="s">
-        <v>1852</v>
+        <v>1752</v>
       </c>
       <c r="E57" s="99" t="s">
-        <v>1853</v>
+        <v>1753</v>
       </c>
       <c r="F57" s="113" t="s">
-        <v>1854</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19645,16 +19644,16 @@
         <v>248</v>
       </c>
       <c r="C58" s="97" t="s">
-        <v>1855</v>
+        <v>1755</v>
       </c>
       <c r="D58" s="109" t="s">
-        <v>1856</v>
+        <v>1756</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>1857</v>
+        <v>1757</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>1858</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19665,16 +19664,16 @@
         <v>253</v>
       </c>
       <c r="C59" s="98" t="s">
-        <v>1859</v>
+        <v>1759</v>
       </c>
       <c r="D59" s="111" t="s">
-        <v>1860</v>
+        <v>1760</v>
       </c>
       <c r="E59" s="98" t="s">
-        <v>1861</v>
+        <v>1761</v>
       </c>
       <c r="F59" s="111" t="s">
-        <v>1862</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19685,16 +19684,16 @@
         <v>257</v>
       </c>
       <c r="C60" s="98" t="s">
-        <v>1863</v>
+        <v>1763</v>
       </c>
       <c r="D60" s="111" t="s">
-        <v>1864</v>
+        <v>1764</v>
       </c>
       <c r="E60" s="98" t="s">
-        <v>1865</v>
+        <v>1765</v>
       </c>
       <c r="F60" s="111" t="s">
-        <v>1866</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19705,16 +19704,16 @@
         <v>262</v>
       </c>
       <c r="C61" s="98" t="s">
-        <v>1867</v>
+        <v>1767</v>
       </c>
       <c r="D61" s="111" t="s">
-        <v>1868</v>
+        <v>1768</v>
       </c>
       <c r="E61" s="98" t="s">
-        <v>1869</v>
+        <v>1769</v>
       </c>
       <c r="F61" s="111" t="s">
-        <v>1870</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19725,16 +19724,16 @@
         <v>266</v>
       </c>
       <c r="C62" s="98" t="s">
-        <v>1871</v>
+        <v>1771</v>
       </c>
       <c r="D62" s="111" t="s">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="E62" s="98" t="s">
-        <v>1873</v>
+        <v>1773</v>
       </c>
       <c r="F62" s="111" t="s">
-        <v>1874</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19745,16 +19744,16 @@
         <v>270</v>
       </c>
       <c r="C63" s="98" t="s">
-        <v>1875</v>
+        <v>1775</v>
       </c>
       <c r="D63" s="111" t="s">
-        <v>1876</v>
+        <v>1776</v>
       </c>
       <c r="E63" s="98" t="s">
-        <v>1877</v>
+        <v>1777</v>
       </c>
       <c r="F63" s="111" t="s">
-        <v>1878</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19765,16 +19764,16 @@
         <v>274</v>
       </c>
       <c r="C64" s="98" t="s">
-        <v>1879</v>
+        <v>1779</v>
       </c>
       <c r="D64" s="111" t="s">
-        <v>1880</v>
+        <v>1780</v>
       </c>
       <c r="E64" s="98" t="s">
-        <v>1881</v>
+        <v>1781</v>
       </c>
       <c r="F64" s="111" t="s">
-        <v>1882</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19785,16 +19784,16 @@
         <v>278</v>
       </c>
       <c r="C65" s="99" t="s">
-        <v>1883</v>
+        <v>1783</v>
       </c>
       <c r="D65" s="113" t="s">
-        <v>1884</v>
+        <v>1784</v>
       </c>
       <c r="E65" s="100" t="s">
-        <v>1885</v>
+        <v>1785</v>
       </c>
       <c r="F65" s="126" t="s">
-        <v>1886</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19805,16 +19804,16 @@
         <v>282</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>1887</v>
+        <v>1787</v>
       </c>
       <c r="D66" s="109" t="s">
-        <v>1888</v>
+        <v>1788</v>
       </c>
       <c r="E66" s="97" t="s">
-        <v>1889</v>
+        <v>1789</v>
       </c>
       <c r="F66" s="109" t="s">
-        <v>1890</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19825,16 +19824,16 @@
         <v>287</v>
       </c>
       <c r="C67" s="99" t="s">
-        <v>1891</v>
+        <v>1791</v>
       </c>
       <c r="D67" s="113" t="s">
-        <v>1888</v>
+        <v>1788</v>
       </c>
       <c r="E67" s="99" t="s">
-        <v>1892</v>
+        <v>1792</v>
       </c>
       <c r="F67" s="113" t="s">
-        <v>1893</v>
+        <v>1793</v>
       </c>
     </row>
   </sheetData>
@@ -19887,16 +19886,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="202" t="s">
-        <v>836</v>
+        <v>802</v>
       </c>
       <c r="D2" s="203" t="s">
-        <v>837</v>
+        <v>803</v>
       </c>
       <c r="E2" s="204" t="s">
-        <v>838</v>
+        <v>804</v>
       </c>
       <c r="F2" s="205" t="s">
-        <v>839</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19907,16 +19906,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="206" t="s">
-        <v>840</v>
+        <v>806</v>
       </c>
       <c r="D3" s="207" t="s">
-        <v>841</v>
+        <v>807</v>
       </c>
       <c r="E3" s="208" t="s">
-        <v>842</v>
+        <v>808</v>
       </c>
       <c r="F3" s="209" t="s">
-        <v>843</v>
+        <v>809</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19927,16 +19926,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="206" t="s">
-        <v>844</v>
+        <v>810</v>
       </c>
       <c r="D4" s="207" t="s">
-        <v>845</v>
+        <v>811</v>
       </c>
       <c r="E4" s="208" t="s">
-        <v>846</v>
+        <v>812</v>
       </c>
       <c r="F4" s="209" t="s">
-        <v>847</v>
+        <v>813</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19947,16 +19946,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="206" t="s">
-        <v>848</v>
+        <v>814</v>
       </c>
       <c r="D5" s="207" t="s">
-        <v>849</v>
+        <v>815</v>
       </c>
       <c r="E5" s="208" t="s">
-        <v>850</v>
+        <v>816</v>
       </c>
       <c r="F5" s="209" t="s">
-        <v>851</v>
+        <v>817</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19967,16 +19966,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="206" t="s">
-        <v>852</v>
+        <v>818</v>
       </c>
       <c r="D6" s="207" t="s">
-        <v>853</v>
+        <v>819</v>
       </c>
       <c r="E6" s="208" t="s">
-        <v>854</v>
+        <v>820</v>
       </c>
       <c r="F6" s="209" t="s">
-        <v>855</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19987,16 +19986,16 @@
         <v>36</v>
       </c>
       <c r="C7" s="206" t="s">
-        <v>856</v>
+        <v>822</v>
       </c>
       <c r="D7" s="207" t="s">
-        <v>857</v>
+        <v>823</v>
       </c>
       <c r="E7" s="208" t="s">
-        <v>858</v>
+        <v>824</v>
       </c>
       <c r="F7" s="209" t="s">
-        <v>859</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20007,16 +20006,16 @@
         <v>41</v>
       </c>
       <c r="C8" s="206" t="s">
-        <v>860</v>
+        <v>826</v>
       </c>
       <c r="D8" s="207" t="s">
-        <v>861</v>
+        <v>827</v>
       </c>
       <c r="E8" s="208" t="s">
-        <v>862</v>
+        <v>828</v>
       </c>
       <c r="F8" s="209" t="s">
-        <v>863</v>
+        <v>829</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20027,16 +20026,16 @@
         <v>45</v>
       </c>
       <c r="C9" s="210" t="s">
-        <v>864</v>
+        <v>830</v>
       </c>
       <c r="D9" s="211" t="s">
-        <v>865</v>
+        <v>831</v>
       </c>
       <c r="E9" s="212" t="s">
-        <v>866</v>
+        <v>832</v>
       </c>
       <c r="F9" s="213" t="s">
-        <v>867</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20047,16 +20046,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="214" t="s">
-        <v>868</v>
+        <v>834</v>
       </c>
       <c r="D10" s="215" t="s">
-        <v>869</v>
+        <v>835</v>
       </c>
       <c r="E10" s="216" t="s">
-        <v>870</v>
+        <v>836</v>
       </c>
       <c r="F10" s="205" t="s">
-        <v>871</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20067,16 +20066,16 @@
         <v>54</v>
       </c>
       <c r="C11" s="217" t="s">
-        <v>872</v>
+        <v>838</v>
       </c>
       <c r="D11" s="218" t="s">
-        <v>873</v>
+        <v>839</v>
       </c>
       <c r="E11" s="219" t="s">
-        <v>874</v>
+        <v>840</v>
       </c>
       <c r="F11" s="209" t="s">
-        <v>875</v>
+        <v>841</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20087,16 +20086,16 @@
         <v>59</v>
       </c>
       <c r="C12" s="217" t="s">
-        <v>876</v>
+        <v>842</v>
       </c>
       <c r="D12" s="218" t="s">
-        <v>877</v>
+        <v>843</v>
       </c>
       <c r="E12" s="219" t="s">
-        <v>878</v>
+        <v>844</v>
       </c>
       <c r="F12" s="209" t="s">
-        <v>879</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20107,16 +20106,16 @@
         <v>63</v>
       </c>
       <c r="C13" s="217" t="s">
-        <v>880</v>
+        <v>846</v>
       </c>
       <c r="D13" s="218" t="s">
-        <v>881</v>
+        <v>847</v>
       </c>
       <c r="E13" s="219" t="s">
-        <v>882</v>
+        <v>848</v>
       </c>
       <c r="F13" s="209" t="s">
-        <v>883</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20127,16 +20126,16 @@
         <v>67</v>
       </c>
       <c r="C14" s="217" t="s">
-        <v>884</v>
+        <v>850</v>
       </c>
       <c r="D14" s="218" t="s">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="E14" s="219" t="s">
-        <v>886</v>
+        <v>852</v>
       </c>
       <c r="F14" s="209" t="s">
-        <v>887</v>
+        <v>853</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20147,16 +20146,16 @@
         <v>71</v>
       </c>
       <c r="C15" s="217" t="s">
-        <v>888</v>
+        <v>854</v>
       </c>
       <c r="D15" s="218" t="s">
-        <v>889</v>
+        <v>855</v>
       </c>
       <c r="E15" s="219" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="F15" s="209" t="s">
-        <v>891</v>
+        <v>857</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20167,16 +20166,16 @@
         <v>75</v>
       </c>
       <c r="C16" s="217" t="s">
-        <v>892</v>
+        <v>858</v>
       </c>
       <c r="D16" s="218" t="s">
-        <v>893</v>
+        <v>859</v>
       </c>
       <c r="E16" s="219" t="s">
-        <v>894</v>
+        <v>860</v>
       </c>
       <c r="F16" s="209" t="s">
-        <v>895</v>
+        <v>861</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20187,16 +20186,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="220" t="s">
-        <v>896</v>
+        <v>862</v>
       </c>
       <c r="D17" s="221" t="s">
-        <v>897</v>
+        <v>863</v>
       </c>
       <c r="E17" s="222" t="s">
-        <v>898</v>
+        <v>864</v>
       </c>
       <c r="F17" s="213" t="s">
-        <v>899</v>
+        <v>865</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20207,16 +20206,16 @@
         <v>84</v>
       </c>
       <c r="C18" s="214" t="s">
-        <v>900</v>
+        <v>866</v>
       </c>
       <c r="D18" s="215" t="s">
-        <v>901</v>
+        <v>867</v>
       </c>
       <c r="E18" s="216" t="s">
-        <v>902</v>
+        <v>868</v>
       </c>
       <c r="F18" s="205" t="s">
-        <v>903</v>
+        <v>869</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20227,16 +20226,16 @@
         <v>89</v>
       </c>
       <c r="C19" s="217" t="s">
-        <v>904</v>
+        <v>870</v>
       </c>
       <c r="D19" s="218" t="s">
-        <v>905</v>
+        <v>871</v>
       </c>
       <c r="E19" s="219" t="s">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="F19" s="209" t="s">
-        <v>907</v>
+        <v>873</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20247,16 +20246,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="217" t="s">
-        <v>908</v>
+        <v>874</v>
       </c>
       <c r="D20" s="218" t="s">
-        <v>909</v>
+        <v>875</v>
       </c>
       <c r="E20" s="219" t="s">
-        <v>910</v>
+        <v>876</v>
       </c>
       <c r="F20" s="209" t="s">
-        <v>911</v>
+        <v>877</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20267,16 +20266,16 @@
         <v>97</v>
       </c>
       <c r="C21" s="217" t="s">
-        <v>912</v>
+        <v>878</v>
       </c>
       <c r="D21" s="218" t="s">
-        <v>913</v>
+        <v>879</v>
       </c>
       <c r="E21" s="219" t="s">
-        <v>914</v>
+        <v>880</v>
       </c>
       <c r="F21" s="209" t="s">
-        <v>915</v>
+        <v>881</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20287,16 +20286,16 @@
         <v>101</v>
       </c>
       <c r="C22" s="217" t="s">
-        <v>916</v>
+        <v>882</v>
       </c>
       <c r="D22" s="218" t="s">
-        <v>917</v>
+        <v>883</v>
       </c>
       <c r="E22" s="219" t="s">
-        <v>918</v>
+        <v>884</v>
       </c>
       <c r="F22" s="209" t="s">
-        <v>919</v>
+        <v>885</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20307,16 +20306,16 @@
         <v>105</v>
       </c>
       <c r="C23" s="217" t="s">
-        <v>920</v>
+        <v>886</v>
       </c>
       <c r="D23" s="218" t="s">
-        <v>921</v>
+        <v>887</v>
       </c>
       <c r="E23" s="219" t="s">
-        <v>922</v>
+        <v>888</v>
       </c>
       <c r="F23" s="209" t="s">
-        <v>923</v>
+        <v>889</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20327,16 +20326,16 @@
         <v>109</v>
       </c>
       <c r="C24" s="217" t="s">
-        <v>924</v>
+        <v>890</v>
       </c>
       <c r="D24" s="218" t="s">
-        <v>925</v>
+        <v>891</v>
       </c>
       <c r="E24" s="219" t="s">
-        <v>926</v>
+        <v>892</v>
       </c>
       <c r="F24" s="209" t="s">
-        <v>927</v>
+        <v>893</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20347,16 +20346,16 @@
         <v>113</v>
       </c>
       <c r="C25" s="220" t="s">
-        <v>928</v>
+        <v>894</v>
       </c>
       <c r="D25" s="221" t="s">
-        <v>929</v>
+        <v>895</v>
       </c>
       <c r="E25" s="222" t="s">
-        <v>930</v>
+        <v>896</v>
       </c>
       <c r="F25" s="213" t="s">
-        <v>931</v>
+        <v>897</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20367,16 +20366,16 @@
         <v>117</v>
       </c>
       <c r="C26" s="214" t="s">
-        <v>932</v>
+        <v>898</v>
       </c>
       <c r="D26" s="215" t="s">
-        <v>933</v>
+        <v>899</v>
       </c>
       <c r="E26" s="216" t="s">
-        <v>934</v>
+        <v>900</v>
       </c>
       <c r="F26" s="205" t="s">
-        <v>935</v>
+        <v>901</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20387,16 +20386,16 @@
         <v>121</v>
       </c>
       <c r="C27" s="217" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
       <c r="D27" s="218" t="s">
-        <v>937</v>
+        <v>903</v>
       </c>
       <c r="E27" s="219" t="s">
-        <v>938</v>
+        <v>904</v>
       </c>
       <c r="F27" s="209" t="s">
-        <v>939</v>
+        <v>905</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20407,16 +20406,16 @@
         <v>125</v>
       </c>
       <c r="C28" s="217" t="s">
-        <v>940</v>
+        <v>906</v>
       </c>
       <c r="D28" s="218" t="s">
-        <v>941</v>
+        <v>907</v>
       </c>
       <c r="E28" s="219" t="s">
-        <v>942</v>
+        <v>908</v>
       </c>
       <c r="F28" s="209" t="s">
-        <v>943</v>
+        <v>909</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20427,16 +20426,16 @@
         <v>129</v>
       </c>
       <c r="C29" s="217" t="s">
-        <v>944</v>
+        <v>910</v>
       </c>
       <c r="D29" s="218" t="s">
-        <v>945</v>
+        <v>911</v>
       </c>
       <c r="E29" s="219" t="s">
-        <v>946</v>
+        <v>912</v>
       </c>
       <c r="F29" s="209" t="s">
-        <v>947</v>
+        <v>913</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20447,16 +20446,16 @@
         <v>133</v>
       </c>
       <c r="C30" s="217" t="s">
-        <v>948</v>
+        <v>914</v>
       </c>
       <c r="D30" s="218" t="s">
-        <v>949</v>
+        <v>915</v>
       </c>
       <c r="E30" s="219" t="s">
-        <v>950</v>
+        <v>916</v>
       </c>
       <c r="F30" s="209" t="s">
-        <v>951</v>
+        <v>917</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20467,16 +20466,16 @@
         <v>137</v>
       </c>
       <c r="C31" s="217" t="s">
-        <v>952</v>
+        <v>918</v>
       </c>
       <c r="D31" s="218" t="s">
-        <v>953</v>
+        <v>919</v>
       </c>
       <c r="E31" s="219" t="s">
-        <v>954</v>
+        <v>920</v>
       </c>
       <c r="F31" s="209" t="s">
-        <v>955</v>
+        <v>921</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20487,16 +20486,16 @@
         <v>141</v>
       </c>
       <c r="C32" s="217" t="s">
-        <v>956</v>
+        <v>922</v>
       </c>
       <c r="D32" s="218" t="s">
-        <v>957</v>
+        <v>923</v>
       </c>
       <c r="E32" s="219" t="s">
-        <v>958</v>
+        <v>924</v>
       </c>
       <c r="F32" s="209" t="s">
-        <v>959</v>
+        <v>925</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20507,16 +20506,16 @@
         <v>145</v>
       </c>
       <c r="C33" s="220" t="s">
-        <v>960</v>
+        <v>926</v>
       </c>
       <c r="D33" s="221" t="s">
-        <v>961</v>
+        <v>927</v>
       </c>
       <c r="E33" s="222" t="s">
-        <v>962</v>
+        <v>928</v>
       </c>
       <c r="F33" s="213" t="s">
-        <v>963</v>
+        <v>929</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20527,16 +20526,16 @@
         <v>149</v>
       </c>
       <c r="C34" s="214" t="s">
-        <v>964</v>
+        <v>930</v>
       </c>
       <c r="D34" s="215" t="s">
-        <v>965</v>
+        <v>931</v>
       </c>
       <c r="E34" s="216" t="s">
-        <v>966</v>
+        <v>932</v>
       </c>
       <c r="F34" s="205" t="s">
-        <v>967</v>
+        <v>933</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20547,16 +20546,16 @@
         <v>154</v>
       </c>
       <c r="C35" s="217" t="s">
-        <v>968</v>
+        <v>934</v>
       </c>
       <c r="D35" s="218" t="s">
-        <v>969</v>
+        <v>935</v>
       </c>
       <c r="E35" s="219" t="s">
-        <v>970</v>
+        <v>936</v>
       </c>
       <c r="F35" s="223" t="s">
-        <v>971</v>
+        <v>937</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20567,16 +20566,16 @@
         <v>158</v>
       </c>
       <c r="C36" s="217" t="s">
-        <v>972</v>
+        <v>938</v>
       </c>
       <c r="D36" s="218" t="s">
-        <v>973</v>
+        <v>939</v>
       </c>
       <c r="E36" s="219" t="s">
-        <v>974</v>
+        <v>940</v>
       </c>
       <c r="F36" s="209" t="s">
-        <v>975</v>
+        <v>941</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20587,16 +20586,16 @@
         <v>162</v>
       </c>
       <c r="C37" s="217" t="s">
-        <v>976</v>
+        <v>942</v>
       </c>
       <c r="D37" s="218" t="s">
-        <v>977</v>
+        <v>943</v>
       </c>
       <c r="E37" s="160" t="s">
-        <v>978</v>
+        <v>944</v>
       </c>
       <c r="F37" s="209" t="s">
-        <v>979</v>
+        <v>945</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20607,16 +20606,16 @@
         <v>166</v>
       </c>
       <c r="C38" s="217" t="s">
-        <v>980</v>
+        <v>946</v>
       </c>
       <c r="D38" s="218" t="s">
-        <v>981</v>
+        <v>947</v>
       </c>
       <c r="E38" s="219" t="s">
-        <v>982</v>
+        <v>948</v>
       </c>
       <c r="F38" s="209" t="s">
-        <v>983</v>
+        <v>949</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20627,16 +20626,16 @@
         <v>170</v>
       </c>
       <c r="C39" s="217" t="s">
-        <v>984</v>
+        <v>950</v>
       </c>
       <c r="D39" s="218" t="s">
-        <v>985</v>
+        <v>951</v>
       </c>
       <c r="E39" s="219" t="s">
-        <v>986</v>
+        <v>952</v>
       </c>
       <c r="F39" s="209" t="s">
-        <v>987</v>
+        <v>953</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20647,16 +20646,16 @@
         <v>174</v>
       </c>
       <c r="C40" s="217" t="s">
-        <v>988</v>
+        <v>954</v>
       </c>
       <c r="D40" s="218" t="s">
-        <v>989</v>
+        <v>955</v>
       </c>
       <c r="E40" s="219" t="s">
-        <v>990</v>
+        <v>956</v>
       </c>
       <c r="F40" s="209" t="s">
-        <v>991</v>
+        <v>957</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20667,16 +20666,16 @@
         <v>178</v>
       </c>
       <c r="C41" s="220" t="s">
-        <v>992</v>
+        <v>958</v>
       </c>
       <c r="D41" s="221" t="s">
-        <v>993</v>
+        <v>959</v>
       </c>
       <c r="E41" s="222" t="s">
-        <v>994</v>
+        <v>960</v>
       </c>
       <c r="F41" s="224" t="s">
-        <v>995</v>
+        <v>961</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20687,16 +20686,16 @@
         <v>182</v>
       </c>
       <c r="C42" s="214" t="s">
-        <v>996</v>
+        <v>962</v>
       </c>
       <c r="D42" s="215" t="s">
-        <v>997</v>
+        <v>963</v>
       </c>
       <c r="E42" s="216" t="s">
-        <v>998</v>
+        <v>964</v>
       </c>
       <c r="F42" s="205" t="s">
-        <v>999</v>
+        <v>965</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20707,16 +20706,16 @@
         <v>187</v>
       </c>
       <c r="C43" s="217" t="s">
-        <v>1000</v>
+        <v>966</v>
       </c>
       <c r="D43" s="218" t="s">
-        <v>1001</v>
+        <v>967</v>
       </c>
       <c r="E43" s="219" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F43" s="209" t="s">
-        <v>1003</v>
+        <v>969</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20727,16 +20726,16 @@
         <v>191</v>
       </c>
       <c r="C44" s="217" t="s">
-        <v>1004</v>
+        <v>970</v>
       </c>
       <c r="D44" s="218" t="s">
-        <v>1005</v>
+        <v>971</v>
       </c>
       <c r="E44" s="219" t="s">
-        <v>1006</v>
+        <v>972</v>
       </c>
       <c r="F44" s="209" t="s">
-        <v>1007</v>
+        <v>973</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20747,16 +20746,16 @@
         <v>195</v>
       </c>
       <c r="C45" s="217" t="s">
-        <v>1008</v>
+        <v>974</v>
       </c>
       <c r="D45" s="218" t="s">
-        <v>1009</v>
+        <v>975</v>
       </c>
       <c r="E45" s="219" t="s">
-        <v>1010</v>
+        <v>976</v>
       </c>
       <c r="F45" s="209" t="s">
-        <v>1011</v>
+        <v>977</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20767,16 +20766,16 @@
         <v>199</v>
       </c>
       <c r="C46" s="217" t="s">
-        <v>1012</v>
+        <v>978</v>
       </c>
       <c r="D46" s="218" t="s">
-        <v>1013</v>
+        <v>979</v>
       </c>
       <c r="E46" s="219" t="s">
-        <v>1014</v>
+        <v>980</v>
       </c>
       <c r="F46" s="209" t="s">
-        <v>1015</v>
+        <v>981</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20787,16 +20786,16 @@
         <v>203</v>
       </c>
       <c r="C47" s="217" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
       <c r="D47" s="218" t="s">
-        <v>1017</v>
+        <v>983</v>
       </c>
       <c r="E47" s="219" t="s">
-        <v>1018</v>
+        <v>984</v>
       </c>
       <c r="F47" s="209" t="s">
-        <v>1019</v>
+        <v>985</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20807,16 +20806,16 @@
         <v>207</v>
       </c>
       <c r="C48" s="217" t="s">
-        <v>1020</v>
+        <v>986</v>
       </c>
       <c r="D48" s="218" t="s">
-        <v>1021</v>
+        <v>987</v>
       </c>
       <c r="E48" s="219" t="s">
-        <v>1022</v>
+        <v>988</v>
       </c>
       <c r="F48" s="209" t="s">
-        <v>1023</v>
+        <v>989</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20827,16 +20826,16 @@
         <v>211</v>
       </c>
       <c r="C49" s="220" t="s">
-        <v>1024</v>
+        <v>990</v>
       </c>
       <c r="D49" s="221" t="s">
-        <v>1025</v>
+        <v>991</v>
       </c>
       <c r="E49" s="222" t="s">
-        <v>1026</v>
+        <v>992</v>
       </c>
       <c r="F49" s="213" t="s">
-        <v>1027</v>
+        <v>993</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20847,16 +20846,16 @@
         <v>215</v>
       </c>
       <c r="C50" s="214" t="s">
-        <v>1028</v>
+        <v>994</v>
       </c>
       <c r="D50" s="215" t="s">
-        <v>1029</v>
+        <v>995</v>
       </c>
       <c r="E50" s="216" t="s">
-        <v>1030</v>
+        <v>996</v>
       </c>
       <c r="F50" s="205" t="s">
-        <v>1031</v>
+        <v>997</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20867,16 +20866,16 @@
         <v>220</v>
       </c>
       <c r="C51" s="217" t="s">
-        <v>1032</v>
+        <v>998</v>
       </c>
       <c r="D51" s="218" t="s">
-        <v>1033</v>
+        <v>999</v>
       </c>
       <c r="E51" s="219" t="s">
-        <v>1034</v>
+        <v>1000</v>
       </c>
       <c r="F51" s="209" t="s">
-        <v>1035</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20887,16 +20886,16 @@
         <v>224</v>
       </c>
       <c r="C52" s="217" t="s">
-        <v>1036</v>
+        <v>1002</v>
       </c>
       <c r="D52" s="218" t="s">
-        <v>1037</v>
+        <v>1003</v>
       </c>
       <c r="E52" s="219" t="s">
-        <v>1038</v>
+        <v>1004</v>
       </c>
       <c r="F52" s="209" t="s">
-        <v>1039</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20907,16 +20906,16 @@
         <v>228</v>
       </c>
       <c r="C53" s="217" t="s">
-        <v>1040</v>
+        <v>1006</v>
       </c>
       <c r="D53" s="218" t="s">
-        <v>1041</v>
+        <v>1007</v>
       </c>
       <c r="E53" s="219" t="s">
-        <v>1042</v>
+        <v>1008</v>
       </c>
       <c r="F53" s="209" t="s">
-        <v>1043</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20927,16 +20926,16 @@
         <v>232</v>
       </c>
       <c r="C54" s="217" t="s">
-        <v>1044</v>
+        <v>1010</v>
       </c>
       <c r="D54" s="218" t="s">
-        <v>1045</v>
+        <v>1011</v>
       </c>
       <c r="E54" s="219" t="s">
-        <v>1046</v>
+        <v>1012</v>
       </c>
       <c r="F54" s="209" t="s">
-        <v>1047</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20947,16 +20946,16 @@
         <v>236</v>
       </c>
       <c r="C55" s="217" t="s">
-        <v>1048</v>
+        <v>1014</v>
       </c>
       <c r="D55" s="218" t="s">
-        <v>1049</v>
+        <v>1015</v>
       </c>
       <c r="E55" s="219" t="s">
-        <v>1050</v>
+        <v>1016</v>
       </c>
       <c r="F55" s="209" t="s">
-        <v>1051</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20967,16 +20966,16 @@
         <v>240</v>
       </c>
       <c r="C56" s="217" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="D56" s="218" t="s">
-        <v>1053</v>
+        <v>1019</v>
       </c>
       <c r="E56" s="219" t="s">
-        <v>1054</v>
+        <v>1020</v>
       </c>
       <c r="F56" s="209" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20987,16 +20986,16 @@
         <v>244</v>
       </c>
       <c r="C57" s="220" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
       <c r="D57" s="221" t="s">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="E57" s="222" t="s">
-        <v>1058</v>
+        <v>1024</v>
       </c>
       <c r="F57" s="213" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21007,16 +21006,16 @@
         <v>248</v>
       </c>
       <c r="C58" s="214" t="s">
-        <v>1060</v>
+        <v>1026</v>
       </c>
       <c r="D58" s="215" t="s">
-        <v>1061</v>
+        <v>1027</v>
       </c>
       <c r="E58" s="216" t="s">
-        <v>1062</v>
+        <v>1028</v>
       </c>
       <c r="F58" s="205" t="s">
-        <v>1063</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21027,16 +21026,16 @@
         <v>253</v>
       </c>
       <c r="C59" s="217" t="s">
-        <v>1064</v>
+        <v>1030</v>
       </c>
       <c r="D59" s="218" t="s">
-        <v>1065</v>
+        <v>1031</v>
       </c>
       <c r="E59" s="219" t="s">
-        <v>1066</v>
+        <v>1032</v>
       </c>
       <c r="F59" s="209" t="s">
-        <v>1067</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21047,16 +21046,16 @@
         <v>257</v>
       </c>
       <c r="C60" s="217" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
       <c r="D60" s="218" t="s">
-        <v>1069</v>
+        <v>1035</v>
       </c>
       <c r="E60" s="219" t="s">
-        <v>1070</v>
+        <v>1036</v>
       </c>
       <c r="F60" s="209" t="s">
-        <v>1071</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21067,16 +21066,16 @@
         <v>262</v>
       </c>
       <c r="C61" s="217" t="s">
-        <v>1072</v>
+        <v>1038</v>
       </c>
       <c r="D61" s="218" t="s">
-        <v>1073</v>
+        <v>1039</v>
       </c>
       <c r="E61" s="219" t="s">
-        <v>1074</v>
+        <v>1040</v>
       </c>
       <c r="F61" s="209" t="s">
-        <v>1075</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21087,16 +21086,16 @@
         <v>266</v>
       </c>
       <c r="C62" s="217" t="s">
-        <v>1076</v>
+        <v>1042</v>
       </c>
       <c r="D62" s="218" t="s">
-        <v>1077</v>
+        <v>1043</v>
       </c>
       <c r="E62" s="219" t="s">
-        <v>1078</v>
+        <v>1044</v>
       </c>
       <c r="F62" s="209" t="s">
-        <v>1079</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21107,16 +21106,16 @@
         <v>270</v>
       </c>
       <c r="C63" s="217" t="s">
-        <v>1080</v>
+        <v>1046</v>
       </c>
       <c r="D63" s="218" t="s">
-        <v>1081</v>
+        <v>1047</v>
       </c>
       <c r="E63" s="219" t="s">
-        <v>1082</v>
+        <v>1048</v>
       </c>
       <c r="F63" s="209" t="s">
-        <v>1083</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21127,16 +21126,16 @@
         <v>274</v>
       </c>
       <c r="C64" s="217" t="s">
-        <v>1084</v>
+        <v>1050</v>
       </c>
       <c r="D64" s="218" t="s">
-        <v>1085</v>
+        <v>1051</v>
       </c>
       <c r="E64" s="219" t="s">
-        <v>1086</v>
+        <v>1052</v>
       </c>
       <c r="F64" s="209" t="s">
-        <v>1087</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="65" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21147,16 +21146,16 @@
         <v>278</v>
       </c>
       <c r="C65" s="225" t="s">
-        <v>1088</v>
+        <v>1054</v>
       </c>
       <c r="D65" s="226" t="s">
-        <v>1089</v>
+        <v>1055</v>
       </c>
       <c r="E65" s="227" t="s">
-        <v>1090</v>
+        <v>1056</v>
       </c>
       <c r="F65" s="228" t="s">
-        <v>1091</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="114" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21167,16 +21166,16 @@
         <v>282</v>
       </c>
       <c r="C66" s="214" t="s">
-        <v>1092</v>
+        <v>1058</v>
       </c>
       <c r="D66" s="215" t="s">
-        <v>1093</v>
+        <v>1059</v>
       </c>
       <c r="E66" s="216" t="s">
-        <v>1094</v>
+        <v>1060</v>
       </c>
       <c r="F66" s="205" t="s">
-        <v>1095</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="114" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21187,16 +21186,16 @@
         <v>287</v>
       </c>
       <c r="C67" s="220" t="s">
-        <v>1096</v>
+        <v>1062</v>
       </c>
       <c r="D67" s="221" t="s">
-        <v>1097</v>
+        <v>1063</v>
       </c>
       <c r="E67" s="222" t="s">
-        <v>1098</v>
+        <v>1064</v>
       </c>
       <c r="F67" s="213" t="s">
-        <v>1099</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -21250,16 +21249,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="237" t="s">
-        <v>1100</v>
+        <v>1066</v>
       </c>
       <c r="D2" s="238" t="s">
-        <v>1101</v>
+        <v>1067</v>
       </c>
       <c r="E2" s="239" t="s">
-        <v>1102</v>
+        <v>1068</v>
       </c>
       <c r="F2" s="240" t="s">
-        <v>1103</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21270,16 +21269,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="241" t="s">
-        <v>1104</v>
+        <v>1070</v>
       </c>
       <c r="D3" s="242" t="s">
-        <v>1105</v>
+        <v>1071</v>
       </c>
       <c r="E3" s="243" t="s">
-        <v>1106</v>
+        <v>1072</v>
       </c>
       <c r="F3" s="244" t="s">
-        <v>1107</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21290,16 +21289,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="241" t="s">
-        <v>1108</v>
+        <v>1074</v>
       </c>
       <c r="D4" s="242" t="s">
-        <v>1109</v>
+        <v>1075</v>
       </c>
       <c r="E4" s="243" t="s">
-        <v>1110</v>
+        <v>1076</v>
       </c>
       <c r="F4" s="244" t="s">
-        <v>1111</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21310,16 +21309,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="241" t="s">
-        <v>1112</v>
+        <v>1078</v>
       </c>
       <c r="D5" s="242" t="s">
-        <v>1113</v>
+        <v>1079</v>
       </c>
       <c r="E5" s="243" t="s">
-        <v>1114</v>
+        <v>1080</v>
       </c>
       <c r="F5" s="244" t="s">
-        <v>1115</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21330,16 +21329,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="241" t="s">
-        <v>1116</v>
+        <v>1082</v>
       </c>
       <c r="D6" s="242" t="s">
-        <v>1117</v>
+        <v>1083</v>
       </c>
       <c r="E6" s="243" t="s">
-        <v>1118</v>
+        <v>1084</v>
       </c>
       <c r="F6" s="244" t="s">
-        <v>1119</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21350,16 +21349,16 @@
         <v>36</v>
       </c>
       <c r="C7" s="241" t="s">
-        <v>1120</v>
+        <v>1086</v>
       </c>
       <c r="D7" s="242" t="s">
-        <v>1121</v>
+        <v>1087</v>
       </c>
       <c r="E7" s="243" t="s">
-        <v>1122</v>
+        <v>1088</v>
       </c>
       <c r="F7" s="244" t="s">
-        <v>1123</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21370,16 +21369,16 @@
         <v>41</v>
       </c>
       <c r="C8" s="241" t="s">
-        <v>1124</v>
+        <v>1090</v>
       </c>
       <c r="D8" s="242" t="s">
-        <v>1125</v>
+        <v>1091</v>
       </c>
       <c r="E8" s="243" t="s">
-        <v>1126</v>
+        <v>1092</v>
       </c>
       <c r="F8" s="244" t="s">
-        <v>1127</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21390,16 +21389,16 @@
         <v>45</v>
       </c>
       <c r="C9" s="245" t="s">
-        <v>1128</v>
+        <v>1094</v>
       </c>
       <c r="D9" s="246" t="s">
-        <v>1129</v>
+        <v>1095</v>
       </c>
       <c r="E9" s="247" t="s">
-        <v>1130</v>
+        <v>1096</v>
       </c>
       <c r="F9" s="248" t="s">
-        <v>1131</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21410,16 +21409,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="249" t="s">
-        <v>1132</v>
+        <v>1098</v>
       </c>
       <c r="D10" s="250" t="s">
-        <v>1133</v>
+        <v>1099</v>
       </c>
       <c r="E10" s="251" t="s">
-        <v>1134</v>
+        <v>1100</v>
       </c>
       <c r="F10" s="240" t="s">
-        <v>1135</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21430,16 +21429,16 @@
         <v>54</v>
       </c>
       <c r="C11" s="252" t="s">
-        <v>1136</v>
+        <v>1102</v>
       </c>
       <c r="D11" s="253" t="s">
-        <v>1137</v>
+        <v>1103</v>
       </c>
       <c r="E11" s="254" t="s">
-        <v>1138</v>
+        <v>1104</v>
       </c>
       <c r="F11" s="244" t="s">
-        <v>1139</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21450,16 +21449,16 @@
         <v>59</v>
       </c>
       <c r="C12" s="252" t="s">
-        <v>1140</v>
+        <v>1106</v>
       </c>
       <c r="D12" s="253" t="s">
-        <v>1141</v>
+        <v>1107</v>
       </c>
       <c r="E12" s="254" t="s">
-        <v>1142</v>
+        <v>1108</v>
       </c>
       <c r="F12" s="244" t="s">
-        <v>1143</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21470,16 +21469,16 @@
         <v>63</v>
       </c>
       <c r="C13" s="252" t="s">
-        <v>1144</v>
+        <v>1110</v>
       </c>
       <c r="D13" s="253" t="s">
-        <v>1145</v>
+        <v>1111</v>
       </c>
       <c r="E13" s="254" t="s">
-        <v>1146</v>
+        <v>1112</v>
       </c>
       <c r="F13" s="244" t="s">
-        <v>1147</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21490,16 +21489,16 @@
         <v>67</v>
       </c>
       <c r="C14" s="252" t="s">
-        <v>1148</v>
+        <v>1114</v>
       </c>
       <c r="D14" s="253" t="s">
-        <v>1149</v>
+        <v>1115</v>
       </c>
       <c r="E14" s="254" t="s">
-        <v>1150</v>
+        <v>1116</v>
       </c>
       <c r="F14" s="244" t="s">
-        <v>1151</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21510,16 +21509,16 @@
         <v>71</v>
       </c>
       <c r="C15" s="252" t="s">
-        <v>1152</v>
+        <v>1118</v>
       </c>
       <c r="D15" s="253" t="s">
-        <v>1153</v>
+        <v>1119</v>
       </c>
       <c r="E15" s="254" t="s">
-        <v>1154</v>
+        <v>1120</v>
       </c>
       <c r="F15" s="244" t="s">
-        <v>1155</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21530,16 +21529,16 @@
         <v>75</v>
       </c>
       <c r="C16" s="252" t="s">
-        <v>1156</v>
+        <v>1122</v>
       </c>
       <c r="D16" s="253" t="s">
-        <v>1157</v>
+        <v>1123</v>
       </c>
       <c r="E16" s="254" t="s">
-        <v>1158</v>
+        <v>1124</v>
       </c>
       <c r="F16" s="244" t="s">
-        <v>1159</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21550,16 +21549,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="255" t="s">
-        <v>1160</v>
+        <v>1126</v>
       </c>
       <c r="D17" s="256" t="s">
-        <v>1161</v>
+        <v>1127</v>
       </c>
       <c r="E17" s="257" t="s">
-        <v>1162</v>
+        <v>1128</v>
       </c>
       <c r="F17" s="248" t="s">
-        <v>1163</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21570,16 +21569,16 @@
         <v>84</v>
       </c>
       <c r="C18" s="249" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
       <c r="D18" s="250" t="s">
-        <v>1165</v>
+        <v>1131</v>
       </c>
       <c r="E18" s="251" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="F18" s="240" t="s">
-        <v>1167</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21590,16 +21589,16 @@
         <v>89</v>
       </c>
       <c r="C19" s="252" t="s">
-        <v>1168</v>
+        <v>1134</v>
       </c>
       <c r="D19" s="253" t="s">
-        <v>1169</v>
+        <v>1135</v>
       </c>
       <c r="E19" s="254" t="s">
-        <v>1170</v>
+        <v>1136</v>
       </c>
       <c r="F19" s="244" t="s">
-        <v>1171</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21610,16 +21609,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="252" t="s">
-        <v>1172</v>
+        <v>1138</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>1173</v>
+        <v>1139</v>
       </c>
       <c r="E20" s="254" t="s">
-        <v>1174</v>
+        <v>1140</v>
       </c>
       <c r="F20" s="244" t="s">
-        <v>1175</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21630,16 +21629,16 @@
         <v>97</v>
       </c>
       <c r="C21" s="252" t="s">
-        <v>1176</v>
+        <v>1142</v>
       </c>
       <c r="D21" s="253" t="s">
-        <v>1177</v>
+        <v>1143</v>
       </c>
       <c r="E21" s="254" t="s">
-        <v>1178</v>
+        <v>1144</v>
       </c>
       <c r="F21" s="244" t="s">
-        <v>1179</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21650,16 +21649,16 @@
         <v>101</v>
       </c>
       <c r="C22" s="252" t="s">
-        <v>1180</v>
+        <v>1146</v>
       </c>
       <c r="D22" s="253" t="s">
-        <v>1181</v>
+        <v>1147</v>
       </c>
       <c r="E22" s="254" t="s">
-        <v>1182</v>
+        <v>1148</v>
       </c>
       <c r="F22" s="244" t="s">
-        <v>1183</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21670,16 +21669,16 @@
         <v>105</v>
       </c>
       <c r="C23" s="252" t="s">
-        <v>1184</v>
+        <v>1150</v>
       </c>
       <c r="D23" s="253" t="s">
-        <v>1185</v>
+        <v>1151</v>
       </c>
       <c r="E23" s="254" t="s">
-        <v>1186</v>
+        <v>1152</v>
       </c>
       <c r="F23" s="244" t="s">
-        <v>1187</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21690,16 +21689,16 @@
         <v>109</v>
       </c>
       <c r="C24" s="252" t="s">
-        <v>1188</v>
+        <v>1154</v>
       </c>
       <c r="D24" s="253" t="s">
-        <v>1189</v>
+        <v>1155</v>
       </c>
       <c r="E24" s="254" t="s">
-        <v>1190</v>
+        <v>1156</v>
       </c>
       <c r="F24" s="244" t="s">
-        <v>1191</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21710,16 +21709,16 @@
         <v>113</v>
       </c>
       <c r="C25" s="255" t="s">
-        <v>1192</v>
+        <v>1158</v>
       </c>
       <c r="D25" s="256" t="s">
-        <v>1193</v>
+        <v>1159</v>
       </c>
       <c r="E25" s="257" t="s">
-        <v>1194</v>
+        <v>1160</v>
       </c>
       <c r="F25" s="248" t="s">
-        <v>1195</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21730,16 +21729,16 @@
         <v>117</v>
       </c>
       <c r="C26" s="249" t="s">
-        <v>1196</v>
+        <v>1162</v>
       </c>
       <c r="D26" s="250" t="s">
-        <v>1197</v>
+        <v>1163</v>
       </c>
       <c r="E26" s="251" t="s">
-        <v>1198</v>
+        <v>1164</v>
       </c>
       <c r="F26" s="240" t="s">
-        <v>1199</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21750,16 +21749,16 @@
         <v>121</v>
       </c>
       <c r="C27" s="252" t="s">
-        <v>1200</v>
+        <v>1166</v>
       </c>
       <c r="D27" s="253" t="s">
-        <v>1201</v>
+        <v>1167</v>
       </c>
       <c r="E27" s="254" t="s">
-        <v>1202</v>
+        <v>1168</v>
       </c>
       <c r="F27" s="244" t="s">
-        <v>1203</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21770,16 +21769,16 @@
         <v>125</v>
       </c>
       <c r="C28" s="252" t="s">
-        <v>1204</v>
+        <v>1170</v>
       </c>
       <c r="D28" s="253" t="s">
-        <v>1205</v>
+        <v>1171</v>
       </c>
       <c r="E28" s="254" t="s">
-        <v>1206</v>
+        <v>1172</v>
       </c>
       <c r="F28" s="244" t="s">
-        <v>1207</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21790,16 +21789,16 @@
         <v>129</v>
       </c>
       <c r="C29" s="252" t="s">
-        <v>1208</v>
+        <v>1174</v>
       </c>
       <c r="D29" s="253" t="s">
-        <v>1209</v>
+        <v>1175</v>
       </c>
       <c r="E29" s="254" t="s">
-        <v>1210</v>
+        <v>1176</v>
       </c>
       <c r="F29" s="244" t="s">
-        <v>1211</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21810,16 +21809,16 @@
         <v>133</v>
       </c>
       <c r="C30" s="252" t="s">
-        <v>1212</v>
+        <v>1178</v>
       </c>
       <c r="D30" s="253" t="s">
-        <v>1213</v>
+        <v>1179</v>
       </c>
       <c r="E30" s="254" t="s">
-        <v>1214</v>
+        <v>1180</v>
       </c>
       <c r="F30" s="244" t="s">
-        <v>1215</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21830,16 +21829,16 @@
         <v>137</v>
       </c>
       <c r="C31" s="252" t="s">
-        <v>1216</v>
+        <v>1182</v>
       </c>
       <c r="D31" s="253" t="s">
-        <v>1217</v>
+        <v>1183</v>
       </c>
       <c r="E31" s="254" t="s">
-        <v>1218</v>
+        <v>1184</v>
       </c>
       <c r="F31" s="244" t="s">
-        <v>1219</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21850,16 +21849,16 @@
         <v>141</v>
       </c>
       <c r="C32" s="252" t="s">
-        <v>1220</v>
+        <v>1186</v>
       </c>
       <c r="D32" s="253" t="s">
-        <v>1221</v>
+        <v>1187</v>
       </c>
       <c r="E32" s="254" t="s">
-        <v>1222</v>
+        <v>1188</v>
       </c>
       <c r="F32" s="244" t="s">
-        <v>1223</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21870,16 +21869,16 @@
         <v>145</v>
       </c>
       <c r="C33" s="255" t="s">
-        <v>1224</v>
+        <v>1190</v>
       </c>
       <c r="D33" s="256" t="s">
-        <v>1225</v>
+        <v>1191</v>
       </c>
       <c r="E33" s="257" t="s">
-        <v>1226</v>
+        <v>1192</v>
       </c>
       <c r="F33" s="248" t="s">
-        <v>1227</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21890,16 +21889,16 @@
         <v>149</v>
       </c>
       <c r="C34" s="249" t="s">
-        <v>1228</v>
+        <v>1194</v>
       </c>
       <c r="D34" s="250" t="s">
-        <v>1229</v>
+        <v>1195</v>
       </c>
       <c r="E34" s="251" t="s">
-        <v>1230</v>
+        <v>1196</v>
       </c>
       <c r="F34" s="240" t="s">
-        <v>1231</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21910,16 +21909,16 @@
         <v>154</v>
       </c>
       <c r="C35" s="252" t="s">
-        <v>1232</v>
+        <v>1198</v>
       </c>
       <c r="D35" s="253" t="s">
-        <v>1233</v>
+        <v>1199</v>
       </c>
       <c r="E35" s="254" t="s">
-        <v>1234</v>
+        <v>1200</v>
       </c>
       <c r="F35" s="258" t="s">
-        <v>1235</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21930,16 +21929,16 @@
         <v>158</v>
       </c>
       <c r="C36" s="252" t="s">
-        <v>1236</v>
+        <v>1202</v>
       </c>
       <c r="D36" s="253" t="s">
-        <v>1237</v>
+        <v>1203</v>
       </c>
       <c r="E36" s="254" t="s">
-        <v>1238</v>
+        <v>1204</v>
       </c>
       <c r="F36" s="244" t="s">
-        <v>1239</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21950,16 +21949,16 @@
         <v>162</v>
       </c>
       <c r="C37" s="252" t="s">
-        <v>1240</v>
+        <v>1206</v>
       </c>
       <c r="D37" s="253" t="s">
-        <v>1241</v>
+        <v>1207</v>
       </c>
       <c r="E37" s="254" t="s">
-        <v>1242</v>
+        <v>1208</v>
       </c>
       <c r="F37" s="244" t="s">
-        <v>1243</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21970,16 +21969,16 @@
         <v>166</v>
       </c>
       <c r="C38" s="252" t="s">
-        <v>1244</v>
+        <v>1210</v>
       </c>
       <c r="D38" s="253" t="s">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="E38" s="254" t="s">
-        <v>1246</v>
+        <v>1212</v>
       </c>
       <c r="F38" s="244" t="s">
-        <v>1247</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -21990,16 +21989,16 @@
         <v>170</v>
       </c>
       <c r="C39" s="252" t="s">
-        <v>1248</v>
+        <v>1214</v>
       </c>
       <c r="D39" s="253" t="s">
-        <v>1249</v>
+        <v>1215</v>
       </c>
       <c r="E39" s="254" t="s">
-        <v>1250</v>
+        <v>1216</v>
       </c>
       <c r="F39" s="244" t="s">
-        <v>1251</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22010,16 +22009,16 @@
         <v>174</v>
       </c>
       <c r="C40" s="252" t="s">
-        <v>1252</v>
+        <v>1218</v>
       </c>
       <c r="D40" s="253" t="s">
-        <v>1253</v>
+        <v>1219</v>
       </c>
       <c r="E40" s="254" t="s">
-        <v>1254</v>
+        <v>1220</v>
       </c>
       <c r="F40" s="244" t="s">
-        <v>1255</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22030,16 +22029,16 @@
         <v>178</v>
       </c>
       <c r="C41" s="255" t="s">
-        <v>1256</v>
+        <v>1222</v>
       </c>
       <c r="D41" s="256" t="s">
-        <v>1257</v>
+        <v>1223</v>
       </c>
       <c r="E41" s="257" t="s">
-        <v>1258</v>
+        <v>1224</v>
       </c>
       <c r="F41" s="259" t="s">
-        <v>1259</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22050,16 +22049,16 @@
         <v>182</v>
       </c>
       <c r="C42" s="249" t="s">
-        <v>1260</v>
+        <v>1226</v>
       </c>
       <c r="D42" s="250" t="s">
-        <v>1261</v>
+        <v>1227</v>
       </c>
       <c r="E42" s="251" t="s">
-        <v>1262</v>
+        <v>1228</v>
       </c>
       <c r="F42" s="240" t="s">
-        <v>1263</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22070,16 +22069,16 @@
         <v>187</v>
       </c>
       <c r="C43" s="252" t="s">
-        <v>1264</v>
+        <v>1230</v>
       </c>
       <c r="D43" s="253" t="s">
-        <v>1265</v>
+        <v>1231</v>
       </c>
       <c r="E43" s="254" t="s">
-        <v>1266</v>
+        <v>1232</v>
       </c>
       <c r="F43" s="244" t="s">
-        <v>1267</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22090,16 +22089,16 @@
         <v>191</v>
       </c>
       <c r="C44" s="252" t="s">
-        <v>1268</v>
+        <v>1234</v>
       </c>
       <c r="D44" s="253" t="s">
-        <v>1269</v>
+        <v>1235</v>
       </c>
       <c r="E44" s="254" t="s">
-        <v>1270</v>
+        <v>1236</v>
       </c>
       <c r="F44" s="244" t="s">
-        <v>1271</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22110,16 +22109,16 @@
         <v>195</v>
       </c>
       <c r="C45" s="252" t="s">
-        <v>1272</v>
+        <v>1238</v>
       </c>
       <c r="D45" s="253" t="s">
-        <v>1273</v>
+        <v>1239</v>
       </c>
       <c r="E45" s="254" t="s">
-        <v>1274</v>
+        <v>1240</v>
       </c>
       <c r="F45" s="244" t="s">
-        <v>1275</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22130,16 +22129,16 @@
         <v>199</v>
       </c>
       <c r="C46" s="252" t="s">
-        <v>1276</v>
+        <v>1242</v>
       </c>
       <c r="D46" s="253" t="s">
-        <v>1277</v>
+        <v>1243</v>
       </c>
       <c r="E46" s="254" t="s">
-        <v>1278</v>
+        <v>1244</v>
       </c>
       <c r="F46" s="244" t="s">
-        <v>1279</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22150,16 +22149,16 @@
         <v>203</v>
       </c>
       <c r="C47" s="252" t="s">
-        <v>1280</v>
+        <v>1246</v>
       </c>
       <c r="D47" s="253" t="s">
-        <v>1281</v>
+        <v>1247</v>
       </c>
       <c r="E47" s="254" t="s">
-        <v>1282</v>
+        <v>1248</v>
       </c>
       <c r="F47" s="244" t="s">
-        <v>1283</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22170,16 +22169,16 @@
         <v>207</v>
       </c>
       <c r="C48" s="252" t="s">
-        <v>1284</v>
+        <v>1250</v>
       </c>
       <c r="D48" s="253" t="s">
-        <v>1285</v>
+        <v>1251</v>
       </c>
       <c r="E48" s="254" t="s">
-        <v>1286</v>
+        <v>1252</v>
       </c>
       <c r="F48" s="244" t="s">
-        <v>1287</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22190,16 +22189,16 @@
         <v>211</v>
       </c>
       <c r="C49" s="255" t="s">
-        <v>1288</v>
+        <v>1254</v>
       </c>
       <c r="D49" s="256" t="s">
-        <v>1289</v>
+        <v>1255</v>
       </c>
       <c r="E49" s="257" t="s">
-        <v>1290</v>
+        <v>1256</v>
       </c>
       <c r="F49" s="248" t="s">
-        <v>1291</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22210,16 +22209,16 @@
         <v>215</v>
       </c>
       <c r="C50" s="249" t="s">
-        <v>1292</v>
+        <v>1258</v>
       </c>
       <c r="D50" s="250" t="s">
-        <v>1293</v>
+        <v>1259</v>
       </c>
       <c r="E50" s="251" t="s">
-        <v>1294</v>
+        <v>1260</v>
       </c>
       <c r="F50" s="240" t="s">
-        <v>1295</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22230,16 +22229,16 @@
         <v>220</v>
       </c>
       <c r="C51" s="252" t="s">
-        <v>1296</v>
+        <v>1262</v>
       </c>
       <c r="D51" s="253" t="s">
-        <v>1297</v>
+        <v>1263</v>
       </c>
       <c r="E51" s="254" t="s">
-        <v>1298</v>
+        <v>1264</v>
       </c>
       <c r="F51" s="244" t="s">
-        <v>1299</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22250,16 +22249,16 @@
         <v>224</v>
       </c>
       <c r="C52" s="252" t="s">
-        <v>1300</v>
+        <v>1266</v>
       </c>
       <c r="D52" s="253" t="s">
-        <v>1301</v>
+        <v>1267</v>
       </c>
       <c r="E52" s="254" t="s">
-        <v>1302</v>
+        <v>1268</v>
       </c>
       <c r="F52" s="244" t="s">
-        <v>1303</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22270,16 +22269,16 @@
         <v>228</v>
       </c>
       <c r="C53" s="252" t="s">
-        <v>1304</v>
+        <v>1270</v>
       </c>
       <c r="D53" s="253" t="s">
-        <v>1305</v>
+        <v>1271</v>
       </c>
       <c r="E53" s="254" t="s">
-        <v>1306</v>
+        <v>1272</v>
       </c>
       <c r="F53" s="244" t="s">
-        <v>1307</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22290,16 +22289,16 @@
         <v>232</v>
       </c>
       <c r="C54" s="252" t="s">
-        <v>1308</v>
+        <v>1274</v>
       </c>
       <c r="D54" s="253" t="s">
-        <v>1309</v>
+        <v>1275</v>
       </c>
       <c r="E54" s="254" t="s">
-        <v>1310</v>
+        <v>1276</v>
       </c>
       <c r="F54" s="244" t="s">
-        <v>1311</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22310,16 +22309,16 @@
         <v>236</v>
       </c>
       <c r="C55" s="252" t="s">
-        <v>1312</v>
+        <v>1278</v>
       </c>
       <c r="D55" s="253" t="s">
-        <v>1313</v>
+        <v>1279</v>
       </c>
       <c r="E55" s="254" t="s">
-        <v>1314</v>
+        <v>1280</v>
       </c>
       <c r="F55" s="244" t="s">
-        <v>1315</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22330,16 +22329,16 @@
         <v>240</v>
       </c>
       <c r="C56" s="252" t="s">
-        <v>1316</v>
+        <v>1282</v>
       </c>
       <c r="D56" s="253" t="s">
-        <v>1317</v>
+        <v>1283</v>
       </c>
       <c r="E56" s="254" t="s">
-        <v>1318</v>
+        <v>1284</v>
       </c>
       <c r="F56" s="244" t="s">
-        <v>1319</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22350,16 +22349,16 @@
         <v>244</v>
       </c>
       <c r="C57" s="255" t="s">
-        <v>1320</v>
+        <v>1286</v>
       </c>
       <c r="D57" s="256" t="s">
-        <v>1321</v>
+        <v>1287</v>
       </c>
       <c r="E57" s="257" t="s">
-        <v>1322</v>
+        <v>1288</v>
       </c>
       <c r="F57" s="248" t="s">
-        <v>1323</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22370,16 +22369,16 @@
         <v>248</v>
       </c>
       <c r="C58" s="249" t="s">
-        <v>1324</v>
+        <v>1290</v>
       </c>
       <c r="D58" s="250" t="s">
-        <v>1325</v>
+        <v>1291</v>
       </c>
       <c r="E58" s="251" t="s">
-        <v>1326</v>
+        <v>1292</v>
       </c>
       <c r="F58" s="240" t="s">
-        <v>1327</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22390,16 +22389,16 @@
         <v>253</v>
       </c>
       <c r="C59" s="252" t="s">
-        <v>1328</v>
+        <v>1294</v>
       </c>
       <c r="D59" s="253" t="s">
-        <v>1329</v>
+        <v>1295</v>
       </c>
       <c r="E59" s="254" t="s">
-        <v>1330</v>
+        <v>1296</v>
       </c>
       <c r="F59" s="244" t="s">
-        <v>1331</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22410,16 +22409,16 @@
         <v>257</v>
       </c>
       <c r="C60" s="252" t="s">
-        <v>1332</v>
+        <v>1298</v>
       </c>
       <c r="D60" s="253" t="s">
-        <v>1333</v>
+        <v>1299</v>
       </c>
       <c r="E60" s="254" t="s">
-        <v>1334</v>
+        <v>1300</v>
       </c>
       <c r="F60" s="244" t="s">
-        <v>1335</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22430,16 +22429,16 @@
         <v>262</v>
       </c>
       <c r="C61" s="252" t="s">
-        <v>1336</v>
+        <v>1302</v>
       </c>
       <c r="D61" s="253" t="s">
-        <v>1337</v>
+        <v>1303</v>
       </c>
       <c r="E61" s="254" t="s">
-        <v>1338</v>
+        <v>1304</v>
       </c>
       <c r="F61" s="244" t="s">
-        <v>1339</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22450,16 +22449,16 @@
         <v>266</v>
       </c>
       <c r="C62" s="252" t="s">
-        <v>1340</v>
+        <v>1306</v>
       </c>
       <c r="D62" s="253" t="s">
-        <v>1341</v>
+        <v>1307</v>
       </c>
       <c r="E62" s="254" t="s">
-        <v>1342</v>
+        <v>1308</v>
       </c>
       <c r="F62" s="244" t="s">
-        <v>1343</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22470,16 +22469,16 @@
         <v>270</v>
       </c>
       <c r="C63" s="252" t="s">
-        <v>1344</v>
+        <v>1310</v>
       </c>
       <c r="D63" s="253" t="s">
-        <v>1345</v>
+        <v>1311</v>
       </c>
       <c r="E63" s="254" t="s">
-        <v>1346</v>
+        <v>1312</v>
       </c>
       <c r="F63" s="244" t="s">
-        <v>1347</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22490,16 +22489,16 @@
         <v>274</v>
       </c>
       <c r="C64" s="252" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="D64" s="253" t="s">
-        <v>1349</v>
+        <v>1315</v>
       </c>
       <c r="E64" s="254" t="s">
-        <v>1350</v>
+        <v>1316</v>
       </c>
       <c r="F64" s="244" t="s">
-        <v>1351</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="65" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22510,16 +22509,16 @@
         <v>278</v>
       </c>
       <c r="C65" s="260" t="s">
-        <v>1352</v>
+        <v>1318</v>
       </c>
       <c r="D65" s="261" t="s">
-        <v>1353</v>
+        <v>1319</v>
       </c>
       <c r="E65" s="262" t="s">
-        <v>1354</v>
+        <v>1320</v>
       </c>
       <c r="F65" s="263" t="s">
-        <v>1355</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="114" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -22530,16 +22529,16 @@
         <v>282</v>
       </c>
       <c r="C66" s="249" t="s">
-        <v>1356</v>
+        <v>1322</v>
       </c>
       <c r="D66" s="250" t="s">
-        <v>1357</v>
+        <v>1323</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>1358</v>
+        <v>1324</v>
       </c>
       <c r="F66" s="240" t="s">
-        <v>1359</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="114" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22550,16 +22549,16 @@
         <v>287</v>
       </c>
       <c r="C67" s="255" t="s">
-        <v>1360</v>
+        <v>1326</v>
       </c>
       <c r="D67" s="256" t="s">
-        <v>1361</v>
+        <v>1327</v>
       </c>
       <c r="E67" s="257" t="s">
-        <v>1362</v>
+        <v>1328</v>
       </c>
       <c r="F67" s="248" t="s">
-        <v>1363</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -22668,7 +22667,7 @@
         <v>723</v>
       </c>
       <c r="F4" s="197" t="s">
-        <v>834</v>
+        <v>800</v>
       </c>
       <c r="G4" s="188"/>
     </row>
@@ -22689,7 +22688,7 @@
         <v>727</v>
       </c>
       <c r="F5" s="201" t="s">
-        <v>835</v>
+        <v>801</v>
       </c>
       <c r="G5" s="194"/>
     </row>

--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -2245,30 +2245,6 @@
     <t>我忽視突然警訊，直到衝擊真正發生。</t>
   </si>
   <si>
-    <t>我接受日蝕遮蔽，等待轉折發生。</t>
-  </si>
-  <si>
-    <t>我正在收斂外放，準備下一次轉換。</t>
-  </si>
-  <si>
-    <t>我困在遮蔽裡，轉折仍未出現。</t>
-  </si>
-  <si>
-    <t>我拒絕收斂，讓日蝕成為停滯。</t>
-  </si>
-  <si>
-    <t>我在月蝕中直視事物最陰暗面。</t>
-  </si>
-  <si>
-    <t>我開始看見先前不願面對的陰影。</t>
-  </si>
-  <si>
-    <t>我被陰暗面牽住，難以保持距離。</t>
-  </si>
-  <si>
-    <t>我沉入最暗處，失去判斷與出口。</t>
-  </si>
-  <si>
     <t>我掌握一段時辰，安排其中節奏。</t>
   </si>
   <si>
@@ -2392,22 +2368,7 @@
     <t>我拒絕後果，把責任推向外部。</t>
   </si>
   <si>
-    <t>我在混沌裡辨識變數與失序。</t>
-  </si>
-  <si>
-    <t>我開始接受既有規則暫時失效。</t>
-  </si>
-  <si>
     <t>我被變數干擾，難以建立判斷。</t>
-  </si>
-  <si>
-    <t>我在混沌中亂下結論，失去準則。</t>
-  </si>
-  <si>
-    <t>我承接命運，也看見規律秩序總和。</t>
-  </si>
-  <si>
-    <t>我開始理解自己所在的命運軌跡。</t>
   </si>
   <si>
     <t>我只看見部分規律，難以理解全貌。</t>
@@ -4441,9 +4402,6 @@
     <t>深沉者</t>
   </si>
   <si>
-    <t>希望守者</t>
-  </si>
-  <si>
     <t>階段行者</t>
   </si>
   <si>
@@ -4803,22 +4761,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>我守住希望，相信仍有可能。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我仍看得見尚未實現的可能。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我失去希望，不再相信還有可能。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我的希望變弱，可能性逐漸渺茫。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>我逃離現在，讓時間從眼前流失。</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -4856,22 +4798,6 @@
   </si>
   <si>
     <t>我開始察覺眼前所見未必真實。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我看見缺少，也接受有事物並不存在。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我開始辨認哪些地方真正有所缺失。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我拒絕承認缺失，執意把不存在當成存在。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>我試圖填補不存在之物，反而更混亂。</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -5596,22 +5522,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>有德</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>快有德</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>快沒德</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>失德</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>符文說明</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6369,6 +6279,110 @@
   </si>
   <si>
     <t>犯法、非法</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀星者</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看見預料中的偏差，也安然應對。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我開始察覺預料中的變化。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我知道會變，卻仍有些失準。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我被已知意外打亂判斷。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我直視最壞，也保持清醒。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我開始看見深處的陰暗面。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我知道最壞，卻仍難以面對。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我陷入最壞而失去出口。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看清天體運行與軌跡。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我開始辨認其中的規律。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看見偏移，卻難掌握全貌。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我誤判軌跡，失去規律。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我看清空洞，也辨認混亂。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我開始察覺其中的不實。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我身在混亂，逐漸失去準則。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我拒絕承認混亂，執意把不存在當成存在。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我接受隨機，也容納突變。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我開始察覺不可預期變數。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我亂下結論，失去準則。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我理解定論，也承接必然。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我開始看見法則形成的可能。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德為道之體現，德為開始也是結束。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德即將展開新一輪籤詩。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德即將消逝，本輪籤詩即將失效。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德消失，舊有籤詩隨時機消逝。</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -7667,7 +7681,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -8195,6 +8209,7 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="20% - 輔色1" xfId="7"/>
@@ -9990,13 +10005,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="118" t="s">
-        <v>1672</v>
+        <v>1646</v>
       </c>
       <c r="I1" s="291" t="s">
-        <v>1676</v>
+        <v>1650</v>
       </c>
       <c r="J1" s="291" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10007,7 +10022,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>1491</v>
+        <v>1469</v>
       </c>
       <c r="D2" s="86" t="s">
         <v>8</v>
@@ -10022,13 +10037,13 @@
         <v>11</v>
       </c>
       <c r="H2" s="282" t="s">
-        <v>1611</v>
+        <v>1589</v>
       </c>
       <c r="I2" s="272" t="s">
-        <v>1314</v>
+        <v>1301</v>
       </c>
       <c r="J2" s="273" t="s">
-        <v>1378</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10054,13 +10069,13 @@
         <v>16</v>
       </c>
       <c r="H3" s="281" t="s">
-        <v>1612</v>
+        <v>1590</v>
       </c>
       <c r="I3" s="87" t="s">
-        <v>1315</v>
+        <v>1302</v>
       </c>
       <c r="J3" s="99" t="s">
-        <v>1379</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10071,7 +10086,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="98" t="s">
-        <v>1492</v>
+        <v>1470</v>
       </c>
       <c r="D4" s="87" t="s">
         <v>18</v>
@@ -10086,13 +10101,13 @@
         <v>11</v>
       </c>
       <c r="H4" s="281" t="s">
-        <v>1677</v>
+        <v>1651</v>
       </c>
       <c r="I4" s="274" t="s">
-        <v>1316</v>
+        <v>1303</v>
       </c>
       <c r="J4" s="275" t="s">
-        <v>1380</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10103,7 +10118,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>1493</v>
+        <v>1471</v>
       </c>
       <c r="D5" s="98" t="s">
         <v>20</v>
@@ -10118,13 +10133,13 @@
         <v>16</v>
       </c>
       <c r="H5" s="281" t="s">
-        <v>1613</v>
+        <v>1591</v>
       </c>
       <c r="I5" s="87" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
       <c r="J5" s="99" t="s">
-        <v>1381</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10135,7 +10150,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>1494</v>
+        <v>1472</v>
       </c>
       <c r="D6" s="98" t="s">
         <v>22</v>
@@ -10150,13 +10165,13 @@
         <v>16</v>
       </c>
       <c r="H6" s="281" t="s">
-        <v>1610</v>
+        <v>1588</v>
       </c>
       <c r="I6" s="274" t="s">
-        <v>1318</v>
+        <v>1305</v>
       </c>
       <c r="J6" s="275" t="s">
-        <v>1382</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10167,7 +10182,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="92" t="s">
-        <v>1495</v>
+        <v>1473</v>
       </c>
       <c r="D7" s="98" t="s">
         <v>25</v>
@@ -10182,13 +10197,13 @@
         <v>16</v>
       </c>
       <c r="H7" s="281" t="s">
-        <v>1614</v>
+        <v>1592</v>
       </c>
       <c r="I7" s="87" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
       <c r="J7" s="99" t="s">
-        <v>1383</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10199,7 +10214,7 @@
         <v>27</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>1496</v>
+        <v>1474</v>
       </c>
       <c r="D8" s="98" t="s">
         <v>28</v>
@@ -10214,13 +10229,13 @@
         <v>11</v>
       </c>
       <c r="H8" s="281" t="s">
-        <v>1615</v>
+        <v>1593</v>
       </c>
       <c r="I8" s="274" t="s">
-        <v>1320</v>
+        <v>1307</v>
       </c>
       <c r="J8" s="275" t="s">
-        <v>1384</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10231,7 +10246,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>1497</v>
+        <v>1475</v>
       </c>
       <c r="D9" s="100" t="s">
         <v>30</v>
@@ -10246,13 +10261,13 @@
         <v>11</v>
       </c>
       <c r="H9" s="283" t="s">
-        <v>1616</v>
+        <v>1594</v>
       </c>
       <c r="I9" s="88" t="s">
-        <v>1321</v>
+        <v>1308</v>
       </c>
       <c r="J9" s="101" t="s">
-        <v>1385</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10263,7 +10278,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="289" t="s">
-        <v>1498</v>
+        <v>1476</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>32</v>
@@ -10278,13 +10293,13 @@
         <v>16</v>
       </c>
       <c r="H10" s="286" t="s">
-        <v>1621</v>
+        <v>1599</v>
       </c>
       <c r="I10" s="287" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
       <c r="J10" s="288" t="s">
-        <v>1386</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10295,7 +10310,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>1499</v>
+        <v>1477</v>
       </c>
       <c r="D11" s="87" t="s">
         <v>35</v>
@@ -10310,13 +10325,13 @@
         <v>36</v>
       </c>
       <c r="H11" s="281" t="s">
-        <v>1619</v>
+        <v>1597</v>
       </c>
       <c r="I11" s="87" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="99" t="s">
-        <v>1387</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10327,7 +10342,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="98" t="s">
-        <v>1500</v>
+        <v>1478</v>
       </c>
       <c r="D12" s="87" t="s">
         <v>39</v>
@@ -10342,13 +10357,13 @@
         <v>36</v>
       </c>
       <c r="H12" s="281" t="s">
-        <v>1620</v>
+        <v>1598</v>
       </c>
       <c r="I12" s="274" t="s">
-        <v>1323</v>
+        <v>1310</v>
       </c>
       <c r="J12" s="275" t="s">
-        <v>1388</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10359,7 +10374,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="98" t="s">
-        <v>1501</v>
+        <v>1479</v>
       </c>
       <c r="D13" s="87" t="s">
         <v>41</v>
@@ -10374,13 +10389,13 @@
         <v>16</v>
       </c>
       <c r="H13" s="281" t="s">
-        <v>1618</v>
+        <v>1596</v>
       </c>
       <c r="I13" s="87" t="s">
-        <v>1324</v>
+        <v>1311</v>
       </c>
       <c r="J13" s="99" t="s">
-        <v>1389</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10391,7 +10406,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>1502</v>
+        <v>1480</v>
       </c>
       <c r="D14" s="87" t="s">
         <v>43</v>
@@ -10406,13 +10421,13 @@
         <v>11</v>
       </c>
       <c r="H14" s="281" t="s">
-        <v>1623</v>
+        <v>1601</v>
       </c>
       <c r="I14" s="274" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
       <c r="J14" s="275" t="s">
-        <v>1390</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10423,7 +10438,7 @@
         <v>44</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>1503</v>
+        <v>1481</v>
       </c>
       <c r="D15" s="87" t="s">
         <v>45</v>
@@ -10438,13 +10453,13 @@
         <v>36</v>
       </c>
       <c r="H15" s="281" t="s">
-        <v>1617</v>
+        <v>1595</v>
       </c>
       <c r="I15" s="87" t="s">
-        <v>1326</v>
+        <v>1313</v>
       </c>
       <c r="J15" s="99" t="s">
-        <v>1391</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10455,7 +10470,7 @@
         <v>46</v>
       </c>
       <c r="C16" s="98" t="s">
-        <v>1504</v>
+        <v>1482</v>
       </c>
       <c r="D16" s="87" t="s">
         <v>47</v>
@@ -10470,13 +10485,13 @@
         <v>16</v>
       </c>
       <c r="H16" s="281" t="s">
-        <v>1624</v>
+        <v>1602</v>
       </c>
       <c r="I16" s="274" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
       <c r="J16" s="275" t="s">
-        <v>1392</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10487,7 +10502,7 @@
         <v>48</v>
       </c>
       <c r="C17" s="100" t="s">
-        <v>1505</v>
+        <v>1483</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>49</v>
@@ -10502,13 +10517,13 @@
         <v>36</v>
       </c>
       <c r="H17" s="283" t="s">
-        <v>1622</v>
+        <v>1600</v>
       </c>
       <c r="I17" s="88" t="s">
-        <v>1328</v>
+        <v>1315</v>
       </c>
       <c r="J17" s="101" t="s">
-        <v>1393</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10534,13 +10549,13 @@
         <v>11</v>
       </c>
       <c r="H18" s="286" t="s">
-        <v>1625</v>
+        <v>1603</v>
       </c>
       <c r="I18" s="287" t="s">
-        <v>1329</v>
+        <v>1316</v>
       </c>
       <c r="J18" s="288" t="s">
-        <v>1394</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10551,7 +10566,7 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1506</v>
+        <v>1484</v>
       </c>
       <c r="D19" s="87" t="s">
         <v>55</v>
@@ -10566,13 +10581,13 @@
         <v>11</v>
       </c>
       <c r="H19" s="281" t="s">
-        <v>1626</v>
+        <v>1604</v>
       </c>
       <c r="I19" s="87" t="s">
-        <v>1330</v>
+        <v>1317</v>
       </c>
       <c r="J19" s="99" t="s">
-        <v>1395</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10583,7 +10598,7 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1507</v>
+        <v>1485</v>
       </c>
       <c r="D20" s="87" t="s">
         <v>57</v>
@@ -10598,13 +10613,13 @@
         <v>36</v>
       </c>
       <c r="H20" s="281" t="s">
-        <v>1632</v>
+        <v>1610</v>
       </c>
       <c r="I20" s="274" t="s">
-        <v>1331</v>
+        <v>1318</v>
       </c>
       <c r="J20" s="275" t="s">
-        <v>1396</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10615,7 +10630,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1508</v>
+        <v>1486</v>
       </c>
       <c r="D21" s="87" t="s">
         <v>59</v>
@@ -10630,13 +10645,13 @@
         <v>36</v>
       </c>
       <c r="H21" s="281" t="s">
-        <v>1627</v>
+        <v>1605</v>
       </c>
       <c r="I21" s="87" t="s">
-        <v>1332</v>
+        <v>1319</v>
       </c>
       <c r="J21" s="99" t="s">
-        <v>1397</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10647,7 +10662,7 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1509</v>
+        <v>1487</v>
       </c>
       <c r="D22" s="87" t="s">
         <v>61</v>
@@ -10662,13 +10677,13 @@
         <v>11</v>
       </c>
       <c r="H22" s="281" t="s">
-        <v>1628</v>
+        <v>1606</v>
       </c>
       <c r="I22" s="274" t="s">
-        <v>1333</v>
+        <v>1320</v>
       </c>
       <c r="J22" s="275" t="s">
-        <v>1398</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10679,7 +10694,7 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1510</v>
+        <v>1488</v>
       </c>
       <c r="D23" s="87" t="s">
         <v>63</v>
@@ -10694,13 +10709,13 @@
         <v>11</v>
       </c>
       <c r="H23" s="281" t="s">
-        <v>1629</v>
+        <v>1607</v>
       </c>
       <c r="I23" s="87" t="s">
-        <v>1334</v>
+        <v>1321</v>
       </c>
       <c r="J23" s="99" t="s">
-        <v>1399</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10711,7 +10726,7 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1511</v>
+        <v>1489</v>
       </c>
       <c r="D24" s="87" t="s">
         <v>65</v>
@@ -10726,13 +10741,13 @@
         <v>16</v>
       </c>
       <c r="H24" s="281" t="s">
-        <v>1630</v>
+        <v>1608</v>
       </c>
       <c r="I24" s="274" t="s">
-        <v>1335</v>
+        <v>1322</v>
       </c>
       <c r="J24" s="275" t="s">
-        <v>1400</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10743,7 +10758,7 @@
         <v>66</v>
       </c>
       <c r="C25" s="89" t="s">
-        <v>1512</v>
+        <v>1490</v>
       </c>
       <c r="D25" s="89" t="s">
         <v>67</v>
@@ -10758,13 +10773,13 @@
         <v>11</v>
       </c>
       <c r="H25" s="290" t="s">
-        <v>1631</v>
+        <v>1609</v>
       </c>
       <c r="I25" s="89" t="s">
-        <v>1336</v>
+        <v>1323</v>
       </c>
       <c r="J25" s="112" t="s">
-        <v>1401</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10775,7 +10790,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1513</v>
+        <v>1491</v>
       </c>
       <c r="D26" s="86" t="s">
         <v>69</v>
@@ -10790,13 +10805,13 @@
         <v>11</v>
       </c>
       <c r="H26" s="282" t="s">
-        <v>1633</v>
+        <v>1611</v>
       </c>
       <c r="I26" s="272" t="s">
-        <v>1337</v>
+        <v>1324</v>
       </c>
       <c r="J26" s="273" t="s">
-        <v>1402</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10807,7 +10822,7 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1514</v>
+        <v>1492</v>
       </c>
       <c r="D27" s="87" t="s">
         <v>72</v>
@@ -10822,13 +10837,13 @@
         <v>11</v>
       </c>
       <c r="H27" s="281" t="s">
-        <v>1635</v>
+        <v>1613</v>
       </c>
       <c r="I27" s="87" t="s">
-        <v>1338</v>
+        <v>1325</v>
       </c>
       <c r="J27" s="99" t="s">
-        <v>1403</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10839,7 +10854,7 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1515</v>
+        <v>1493</v>
       </c>
       <c r="D28" s="87" t="s">
         <v>74</v>
@@ -10854,13 +10869,13 @@
         <v>16</v>
       </c>
       <c r="H28" s="281" t="s">
-        <v>1634</v>
+        <v>1612</v>
       </c>
       <c r="I28" s="274" t="s">
-        <v>1339</v>
+        <v>1326</v>
       </c>
       <c r="J28" s="275" t="s">
-        <v>1404</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10871,7 +10886,7 @@
         <v>75</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>1516</v>
+        <v>1494</v>
       </c>
       <c r="D29" s="87" t="s">
         <v>76</v>
@@ -10886,13 +10901,13 @@
         <v>16</v>
       </c>
       <c r="H29" s="281" t="s">
-        <v>1636</v>
+        <v>1614</v>
       </c>
       <c r="I29" s="87" t="s">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="J29" s="99" t="s">
-        <v>1405</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10903,7 +10918,7 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1517</v>
+        <v>1495</v>
       </c>
       <c r="D30" s="87" t="s">
         <v>78</v>
@@ -10918,13 +10933,13 @@
         <v>11</v>
       </c>
       <c r="H30" s="281" t="s">
-        <v>1637</v>
+        <v>1615</v>
       </c>
       <c r="I30" s="274" t="s">
-        <v>1341</v>
+        <v>1328</v>
       </c>
       <c r="J30" s="275" t="s">
-        <v>1406</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10935,7 +10950,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1518</v>
+        <v>1496</v>
       </c>
       <c r="D31" s="87" t="s">
         <v>80</v>
@@ -10950,13 +10965,13 @@
         <v>16</v>
       </c>
       <c r="H31" s="281" t="s">
-        <v>1638</v>
+        <v>1616</v>
       </c>
       <c r="I31" s="87" t="s">
-        <v>1342</v>
+        <v>1329</v>
       </c>
       <c r="J31" s="99" t="s">
-        <v>1407</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10967,7 +10982,7 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1519</v>
+        <v>1497</v>
       </c>
       <c r="D32" s="87" t="s">
         <v>82</v>
@@ -10982,13 +10997,13 @@
         <v>16</v>
       </c>
       <c r="H32" s="281" t="s">
-        <v>1640</v>
+        <v>1618</v>
       </c>
       <c r="I32" s="274" t="s">
-        <v>1343</v>
+        <v>1330</v>
       </c>
       <c r="J32" s="275" t="s">
-        <v>1408</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10999,7 +11014,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="89" t="s">
-        <v>1520</v>
+        <v>1498</v>
       </c>
       <c r="D33" s="89" t="s">
         <v>84</v>
@@ -11014,13 +11029,13 @@
         <v>16</v>
       </c>
       <c r="H33" s="290" t="s">
-        <v>1639</v>
+        <v>1617</v>
       </c>
       <c r="I33" s="89" t="s">
-        <v>1344</v>
+        <v>1331</v>
       </c>
       <c r="J33" s="112" t="s">
-        <v>1409</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11031,7 +11046,7 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1521</v>
+        <v>1499</v>
       </c>
       <c r="D34" s="86" t="s">
         <v>86</v>
@@ -11046,13 +11061,13 @@
         <v>16</v>
       </c>
       <c r="H34" s="282" t="s">
-        <v>1641</v>
+        <v>1619</v>
       </c>
       <c r="I34" s="272" t="s">
-        <v>1345</v>
+        <v>1332</v>
       </c>
       <c r="J34" s="273" t="s">
-        <v>1410</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11063,7 +11078,7 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1522</v>
+        <v>1500</v>
       </c>
       <c r="D35" s="87" t="s">
         <v>89</v>
@@ -11078,13 +11093,13 @@
         <v>11</v>
       </c>
       <c r="H35" s="281" t="s">
-        <v>1642</v>
+        <v>1620</v>
       </c>
       <c r="I35" s="87" t="s">
-        <v>1346</v>
+        <v>1333</v>
       </c>
       <c r="J35" s="99" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11095,7 +11110,7 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1523</v>
+        <v>1501</v>
       </c>
       <c r="D36" s="87" t="s">
         <v>91</v>
@@ -11110,13 +11125,13 @@
         <v>11</v>
       </c>
       <c r="H36" s="281" t="s">
-        <v>1643</v>
+        <v>1621</v>
       </c>
       <c r="I36" s="274" t="s">
-        <v>1347</v>
+        <v>1334</v>
       </c>
       <c r="J36" s="275" t="s">
-        <v>1412</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11127,7 +11142,7 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1524</v>
+        <v>1502</v>
       </c>
       <c r="D37" s="87" t="s">
         <v>93</v>
@@ -11142,13 +11157,13 @@
         <v>11</v>
       </c>
       <c r="H37" s="281" t="s">
-        <v>1644</v>
+        <v>1622</v>
       </c>
       <c r="I37" s="87" t="s">
-        <v>1348</v>
+        <v>1335</v>
       </c>
       <c r="J37" s="99" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11174,13 +11189,13 @@
         <v>11</v>
       </c>
       <c r="H38" s="281" t="s">
-        <v>1645</v>
+        <v>1623</v>
       </c>
       <c r="I38" s="274" t="s">
-        <v>1349</v>
+        <v>1336</v>
       </c>
       <c r="J38" s="275" t="s">
-        <v>1414</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11191,7 +11206,7 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1525</v>
+        <v>1503</v>
       </c>
       <c r="D39" s="87" t="s">
         <v>98</v>
@@ -11206,13 +11221,13 @@
         <v>16</v>
       </c>
       <c r="H39" s="281" t="s">
-        <v>1646</v>
+        <v>1624</v>
       </c>
       <c r="I39" s="87" t="s">
-        <v>1350</v>
+        <v>1337</v>
       </c>
       <c r="J39" s="99" t="s">
-        <v>1415</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11223,7 +11238,7 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1526</v>
+        <v>1504</v>
       </c>
       <c r="D40" s="87" t="s">
         <v>100</v>
@@ -11238,13 +11253,13 @@
         <v>16</v>
       </c>
       <c r="H40" s="281" t="s">
-        <v>1647</v>
+        <v>1625</v>
       </c>
       <c r="I40" s="274" t="s">
-        <v>1351</v>
+        <v>1338</v>
       </c>
       <c r="J40" s="275" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11255,7 +11270,7 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1527</v>
+        <v>1505</v>
       </c>
       <c r="D41" s="88" t="s">
         <v>102</v>
@@ -11270,13 +11285,13 @@
         <v>36</v>
       </c>
       <c r="H41" s="283" t="s">
-        <v>1648</v>
+        <v>1626</v>
       </c>
       <c r="I41" s="88" t="s">
-        <v>1352</v>
+        <v>1339</v>
       </c>
       <c r="J41" s="101" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11287,7 +11302,7 @@
         <v>103</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>1528</v>
+        <v>1506</v>
       </c>
       <c r="D42" s="37" t="s">
         <v>104</v>
@@ -11302,13 +11317,13 @@
         <v>11</v>
       </c>
       <c r="H42" s="286" t="s">
-        <v>1652</v>
+        <v>1630</v>
       </c>
       <c r="I42" s="287" t="s">
         <v>106</v>
       </c>
       <c r="J42" s="288" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11319,7 +11334,7 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1529</v>
+        <v>1507</v>
       </c>
       <c r="D43" s="87" t="s">
         <v>108</v>
@@ -11334,13 +11349,13 @@
         <v>36</v>
       </c>
       <c r="H43" s="281" t="s">
-        <v>1651</v>
+        <v>1629</v>
       </c>
       <c r="I43" s="87" t="s">
-        <v>1353</v>
+        <v>1340</v>
       </c>
       <c r="J43" s="99" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11351,7 +11366,7 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1530</v>
+        <v>1508</v>
       </c>
       <c r="D44" s="87" t="s">
         <v>110</v>
@@ -11366,13 +11381,13 @@
         <v>16</v>
       </c>
       <c r="H44" s="281" t="s">
-        <v>1655</v>
+        <v>1633</v>
       </c>
       <c r="I44" s="274" t="s">
-        <v>1354</v>
+        <v>1341</v>
       </c>
       <c r="J44" s="275" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11383,7 +11398,7 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1531</v>
+        <v>1509</v>
       </c>
       <c r="D45" s="87" t="s">
         <v>112</v>
@@ -11398,13 +11413,13 @@
         <v>16</v>
       </c>
       <c r="H45" s="281" t="s">
-        <v>1653</v>
+        <v>1631</v>
       </c>
       <c r="I45" s="87" t="s">
-        <v>1355</v>
+        <v>1342</v>
       </c>
       <c r="J45" s="99" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11415,7 +11430,7 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1532</v>
+        <v>1510</v>
       </c>
       <c r="D46" s="87" t="s">
         <v>114</v>
@@ -11430,13 +11445,13 @@
         <v>16</v>
       </c>
       <c r="H46" s="281" t="s">
-        <v>1649</v>
+        <v>1627</v>
       </c>
       <c r="I46" s="274" t="s">
-        <v>1356</v>
+        <v>1343</v>
       </c>
       <c r="J46" s="275" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11447,7 +11462,7 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1533</v>
+        <v>1511</v>
       </c>
       <c r="D47" s="87" t="s">
         <v>116</v>
@@ -11462,13 +11477,13 @@
         <v>16</v>
       </c>
       <c r="H47" s="281" t="s">
-        <v>1656</v>
+        <v>1634</v>
       </c>
       <c r="I47" s="87" t="s">
-        <v>1357</v>
+        <v>1344</v>
       </c>
       <c r="J47" s="99" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11479,7 +11494,7 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1534</v>
+        <v>1512</v>
       </c>
       <c r="D48" s="87" t="s">
         <v>118</v>
@@ -11494,13 +11509,13 @@
         <v>16</v>
       </c>
       <c r="H48" s="281" t="s">
-        <v>1654</v>
+        <v>1632</v>
       </c>
       <c r="I48" s="274" t="s">
-        <v>1358</v>
+        <v>1345</v>
       </c>
       <c r="J48" s="275" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11526,13 +11541,13 @@
         <v>16</v>
       </c>
       <c r="H49" s="283" t="s">
-        <v>1650</v>
+        <v>1628</v>
       </c>
       <c r="I49" s="88" t="s">
-        <v>1359</v>
+        <v>1346</v>
       </c>
       <c r="J49" s="101" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11558,13 +11573,13 @@
         <v>36</v>
       </c>
       <c r="H50" s="286" t="s">
-        <v>1816</v>
+        <v>1790</v>
       </c>
       <c r="I50" s="287" t="s">
-        <v>1360</v>
+        <v>1347</v>
       </c>
       <c r="J50" s="288" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11590,13 +11605,13 @@
         <v>36</v>
       </c>
       <c r="H51" s="281" t="s">
-        <v>1815</v>
+        <v>1789</v>
       </c>
       <c r="I51" s="87" t="s">
-        <v>1361</v>
+        <v>1348</v>
       </c>
       <c r="J51" s="99" t="s">
-        <v>1427</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11622,13 +11637,13 @@
         <v>16</v>
       </c>
       <c r="H52" s="281" t="s">
-        <v>1811</v>
+        <v>1785</v>
       </c>
       <c r="I52" s="274" t="s">
-        <v>1362</v>
+        <v>1836</v>
       </c>
       <c r="J52" s="275" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11654,13 +11669,13 @@
         <v>16</v>
       </c>
       <c r="H53" s="281" t="s">
-        <v>1657</v>
+        <v>1635</v>
       </c>
       <c r="I53" s="87" t="s">
-        <v>1363</v>
+        <v>1349</v>
       </c>
       <c r="J53" s="99" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11671,7 +11686,7 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1535</v>
+        <v>1513</v>
       </c>
       <c r="D54" s="87" t="s">
         <v>136</v>
@@ -11686,13 +11701,13 @@
         <v>11</v>
       </c>
       <c r="H54" s="281" t="s">
-        <v>1835</v>
+        <v>1809</v>
       </c>
       <c r="I54" s="274" t="s">
-        <v>1364</v>
+        <v>1350</v>
       </c>
       <c r="J54" s="275" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11718,13 +11733,13 @@
         <v>16</v>
       </c>
       <c r="H55" s="281" t="s">
-        <v>1659</v>
+        <v>1637</v>
       </c>
       <c r="I55" s="87" t="s">
-        <v>1365</v>
+        <v>1351</v>
       </c>
       <c r="J55" s="99" t="s">
-        <v>1431</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11750,13 +11765,13 @@
         <v>16</v>
       </c>
       <c r="H56" s="281" t="s">
-        <v>1660</v>
+        <v>1638</v>
       </c>
       <c r="I56" s="274" t="s">
-        <v>1366</v>
+        <v>1352</v>
       </c>
       <c r="J56" s="275" t="s">
-        <v>1432</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11782,13 +11797,13 @@
         <v>16</v>
       </c>
       <c r="H57" s="283" t="s">
-        <v>1658</v>
+        <v>1636</v>
       </c>
       <c r="I57" s="88" t="s">
-        <v>1367</v>
+        <v>1353</v>
       </c>
       <c r="J57" s="101" t="s">
-        <v>1433</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11799,7 +11814,7 @@
         <v>146</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>1536</v>
+        <v>1514</v>
       </c>
       <c r="D58" s="37" t="s">
         <v>147</v>
@@ -11814,13 +11829,13 @@
         <v>11</v>
       </c>
       <c r="H58" s="286" t="s">
-        <v>1812</v>
+        <v>1786</v>
       </c>
       <c r="I58" s="287" t="s">
-        <v>1368</v>
+        <v>1354</v>
       </c>
       <c r="J58" s="288" t="s">
-        <v>1434</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11831,7 +11846,7 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1537</v>
+        <v>1515</v>
       </c>
       <c r="D59" s="87" t="s">
         <v>150</v>
@@ -11846,13 +11861,13 @@
         <v>36</v>
       </c>
       <c r="H59" s="281" t="s">
-        <v>1813</v>
+        <v>1787</v>
       </c>
       <c r="I59" s="87" t="s">
-        <v>1369</v>
+        <v>1355</v>
       </c>
       <c r="J59" s="99" t="s">
-        <v>1435</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11863,7 +11878,7 @@
         <v>151</v>
       </c>
       <c r="C60" s="98" t="s">
-        <v>1538</v>
+        <v>1516</v>
       </c>
       <c r="D60" s="93" t="s">
         <v>152</v>
@@ -11878,13 +11893,13 @@
         <v>153</v>
       </c>
       <c r="H60" s="281" t="s">
-        <v>1823</v>
+        <v>1797</v>
       </c>
       <c r="I60" s="274" t="s">
-        <v>1370</v>
+        <v>1356</v>
       </c>
       <c r="J60" s="275" t="s">
-        <v>1436</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11895,7 +11910,7 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1539</v>
+        <v>1517</v>
       </c>
       <c r="D61" s="87" t="s">
         <v>155</v>
@@ -11910,13 +11925,13 @@
         <v>11</v>
       </c>
       <c r="H61" s="281" t="s">
-        <v>1814</v>
+        <v>1788</v>
       </c>
       <c r="I61" s="87" t="s">
-        <v>1371</v>
+        <v>1357</v>
       </c>
       <c r="J61" s="99" t="s">
-        <v>1437</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11927,7 +11942,7 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1540</v>
+        <v>1518</v>
       </c>
       <c r="D62" s="87" t="s">
         <v>157</v>
@@ -11942,13 +11957,13 @@
         <v>36</v>
       </c>
       <c r="H62" s="281" t="s">
-        <v>1822</v>
+        <v>1796</v>
       </c>
       <c r="I62" s="274" t="s">
-        <v>1372</v>
+        <v>1358</v>
       </c>
       <c r="J62" s="275" t="s">
-        <v>1438</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11959,7 +11974,7 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1541</v>
+        <v>1519</v>
       </c>
       <c r="D63" s="87" t="s">
         <v>159</v>
@@ -11974,13 +11989,13 @@
         <v>16</v>
       </c>
       <c r="H63" s="281" t="s">
-        <v>1661</v>
+        <v>1639</v>
       </c>
       <c r="I63" s="87" t="s">
-        <v>1373</v>
+        <v>1359</v>
       </c>
       <c r="J63" s="99" t="s">
-        <v>1439</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12006,13 +12021,13 @@
         <v>36</v>
       </c>
       <c r="H64" s="281" t="s">
-        <v>1662</v>
+        <v>1640</v>
       </c>
       <c r="I64" s="274" t="s">
-        <v>1374</v>
+        <v>1360</v>
       </c>
       <c r="J64" s="275" t="s">
-        <v>1440</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12023,7 +12038,7 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1542</v>
+        <v>1520</v>
       </c>
       <c r="D65" s="88" t="s">
         <v>164</v>
@@ -12038,13 +12053,13 @@
         <v>16</v>
       </c>
       <c r="H65" s="283" t="s">
-        <v>1824</v>
+        <v>1798</v>
       </c>
       <c r="I65" s="88" t="s">
-        <v>1375</v>
+        <v>1361</v>
       </c>
       <c r="J65" s="101" t="s">
-        <v>1441</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12055,7 +12070,7 @@
         <v>165</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>1543</v>
+        <v>1521</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>166</v>
@@ -12070,13 +12085,13 @@
         <v>153</v>
       </c>
       <c r="H66" s="286" t="s">
-        <v>1821</v>
+        <v>1795</v>
       </c>
       <c r="I66" s="287" t="s">
-        <v>1674</v>
+        <v>1648</v>
       </c>
       <c r="J66" s="288" t="s">
-        <v>1442</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12087,7 +12102,7 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1544</v>
+        <v>1522</v>
       </c>
       <c r="D67" s="87" t="s">
         <v>35</v>
@@ -12102,13 +12117,13 @@
         <v>153</v>
       </c>
       <c r="H67" s="281" t="s">
-        <v>1820</v>
+        <v>1794</v>
       </c>
       <c r="I67" s="87" t="s">
-        <v>1675</v>
+        <v>1649</v>
       </c>
       <c r="J67" s="99" t="s">
-        <v>1443</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12116,13 +12131,13 @@
         <v>0</v>
       </c>
       <c r="B68" s="88" t="s">
-        <v>1307</v>
+        <v>1294</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1545</v>
+        <v>1523</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>1667</v>
+        <v>1645</v>
       </c>
       <c r="E68" s="88" t="s">
         <v>167</v>
@@ -12134,13 +12149,13 @@
         <v>153</v>
       </c>
       <c r="H68" s="283" t="s">
-        <v>1663</v>
+        <v>1641</v>
       </c>
       <c r="I68" s="276" t="s">
-        <v>1376</v>
+        <v>1362</v>
       </c>
       <c r="J68" s="277" t="s">
-        <v>1664</v>
+        <v>1642</v>
       </c>
     </row>
   </sheetData>
@@ -12175,16 +12190,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="109" t="s">
-        <v>1673</v>
+        <v>1647</v>
       </c>
       <c r="D1" s="278" t="s">
-        <v>1678</v>
+        <v>1652</v>
       </c>
       <c r="E1" s="278" t="s">
-        <v>1679</v>
+        <v>1653</v>
       </c>
       <c r="F1" s="278" t="s">
-        <v>1776</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12195,13 +12210,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1709</v>
+        <v>1683</v>
       </c>
       <c r="D2" s="272" t="s">
-        <v>1710</v>
+        <v>1684</v>
       </c>
       <c r="E2" s="272" t="s">
-        <v>1680</v>
+        <v>1654</v>
       </c>
       <c r="F2" s="272"/>
     </row>
@@ -12213,13 +12228,13 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1681</v>
+        <v>1655</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>1715</v>
+        <v>1689</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1805</v>
+        <v>1779</v>
       </c>
       <c r="F3" s="87"/>
     </row>
@@ -12231,10 +12246,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1711</v>
+        <v>1685</v>
       </c>
       <c r="D4" s="274" t="s">
-        <v>1712</v>
+        <v>1686</v>
       </c>
       <c r="E4" s="274"/>
       <c r="F4" s="274"/>
@@ -12247,13 +12262,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1682</v>
+        <v>1656</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>1683</v>
+        <v>1657</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1713</v>
+        <v>1687</v>
       </c>
       <c r="F5" s="87"/>
     </row>
@@ -12265,13 +12280,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1684</v>
+        <v>1658</v>
       </c>
       <c r="D6" s="274" t="s">
-        <v>1685</v>
+        <v>1659</v>
       </c>
       <c r="E6" s="274" t="s">
-        <v>1689</v>
+        <v>1663</v>
       </c>
       <c r="F6" s="274"/>
     </row>
@@ -12283,13 +12298,13 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1686</v>
+        <v>1660</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>1716</v>
+        <v>1690</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>1690</v>
+        <v>1664</v>
       </c>
       <c r="F7" s="87"/>
     </row>
@@ -12301,10 +12316,10 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1792</v>
+        <v>1766</v>
       </c>
       <c r="D8" s="274" t="s">
-        <v>1687</v>
+        <v>1661</v>
       </c>
       <c r="E8" s="274"/>
       <c r="F8" s="274"/>
@@ -12317,10 +12332,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1714</v>
+        <v>1688</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>1688</v>
+        <v>1662</v>
       </c>
       <c r="E9" s="88"/>
       <c r="F9" s="88"/>
@@ -12333,10 +12348,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1691</v>
+        <v>1665</v>
       </c>
       <c r="D10" s="272" t="s">
-        <v>1692</v>
+        <v>1666</v>
       </c>
       <c r="E10" s="272"/>
       <c r="F10" s="272"/>
@@ -12349,13 +12364,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1693</v>
+        <v>1667</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1705</v>
+        <v>1679</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1694</v>
+        <v>1668</v>
       </c>
       <c r="F11" s="87"/>
     </row>
@@ -12367,13 +12382,13 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1696</v>
+        <v>1670</v>
       </c>
       <c r="D12" s="274" t="s">
-        <v>1697</v>
+        <v>1671</v>
       </c>
       <c r="E12" s="274" t="s">
-        <v>1695</v>
+        <v>1669</v>
       </c>
       <c r="F12" s="274"/>
     </row>
@@ -12385,16 +12400,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1707</v>
+        <v>1681</v>
       </c>
       <c r="D13" s="87" t="s">
-        <v>1698</v>
+        <v>1672</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1706</v>
+        <v>1680</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12405,13 +12420,13 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1699</v>
+        <v>1673</v>
       </c>
       <c r="D14" s="274" t="s">
-        <v>1312</v>
+        <v>1299</v>
       </c>
       <c r="E14" s="274" t="s">
-        <v>1700</v>
+        <v>1674</v>
       </c>
       <c r="F14" s="274"/>
     </row>
@@ -12423,10 +12438,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1708</v>
+        <v>1682</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>1701</v>
+        <v>1675</v>
       </c>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
@@ -12439,13 +12454,13 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1702</v>
+        <v>1676</v>
       </c>
       <c r="D16" s="274" t="s">
-        <v>1703</v>
+        <v>1677</v>
       </c>
       <c r="E16" s="274" t="s">
-        <v>1700</v>
+        <v>1674</v>
       </c>
       <c r="F16" s="274"/>
     </row>
@@ -12457,10 +12472,10 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1717</v>
+        <v>1691</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>1704</v>
+        <v>1678</v>
       </c>
       <c r="E17" s="88"/>
       <c r="F17" s="88"/>
@@ -12473,13 +12488,13 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1721</v>
+        <v>1695</v>
       </c>
       <c r="D18" s="272" t="s">
-        <v>1722</v>
+        <v>1696</v>
       </c>
       <c r="E18" s="272" t="s">
-        <v>1718</v>
+        <v>1692</v>
       </c>
       <c r="F18" s="272"/>
     </row>
@@ -12491,13 +12506,13 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1730</v>
+        <v>1704</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>1731</v>
+        <v>1705</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>1735</v>
+        <v>1709</v>
       </c>
       <c r="F19" s="87"/>
     </row>
@@ -12509,13 +12524,13 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1723</v>
+        <v>1697</v>
       </c>
       <c r="D20" s="274" t="s">
-        <v>1724</v>
+        <v>1698</v>
       </c>
       <c r="E20" s="274" t="s">
-        <v>1740</v>
+        <v>1714</v>
       </c>
       <c r="F20" s="274"/>
     </row>
@@ -12527,13 +12542,13 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1732</v>
+        <v>1706</v>
       </c>
       <c r="D21" s="87" t="s">
-        <v>1725</v>
+        <v>1699</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1736</v>
+        <v>1710</v>
       </c>
       <c r="F21" s="87"/>
     </row>
@@ -12545,13 +12560,13 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1726</v>
+        <v>1700</v>
       </c>
       <c r="D22" s="274" t="s">
-        <v>1727</v>
+        <v>1701</v>
       </c>
       <c r="E22" s="274" t="s">
-        <v>1737</v>
+        <v>1711</v>
       </c>
       <c r="F22" s="274"/>
     </row>
@@ -12563,13 +12578,13 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1728</v>
+        <v>1702</v>
       </c>
       <c r="D23" s="87" t="s">
-        <v>1729</v>
+        <v>1703</v>
       </c>
       <c r="E23" s="87" t="s">
-        <v>1719</v>
+        <v>1693</v>
       </c>
       <c r="F23" s="87"/>
     </row>
@@ -12581,13 +12596,13 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1734</v>
+        <v>1708</v>
       </c>
       <c r="D24" s="274" t="s">
-        <v>1738</v>
+        <v>1712</v>
       </c>
       <c r="E24" s="274" t="s">
-        <v>1739</v>
+        <v>1713</v>
       </c>
       <c r="F24" s="274"/>
     </row>
@@ -12599,13 +12614,13 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1745</v>
+        <v>1719</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>1733</v>
+        <v>1707</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>1720</v>
+        <v>1694</v>
       </c>
       <c r="F25" s="88"/>
     </row>
@@ -12617,16 +12632,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1741</v>
+        <v>1715</v>
       </c>
       <c r="D26" s="272" t="s">
-        <v>1756</v>
+        <v>1730</v>
       </c>
       <c r="E26" s="272" t="s">
-        <v>1753</v>
+        <v>1727</v>
       </c>
       <c r="F26" s="272" t="s">
-        <v>1802</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12637,16 +12652,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1742</v>
+        <v>1716</v>
       </c>
       <c r="D27" s="87" t="s">
-        <v>1743</v>
+        <v>1717</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1750</v>
+        <v>1724</v>
       </c>
       <c r="F27" s="87" t="s">
-        <v>1817</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12657,10 +12672,10 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1744</v>
+        <v>1718</v>
       </c>
       <c r="D28" s="274" t="s">
-        <v>1757</v>
+        <v>1731</v>
       </c>
       <c r="E28" s="274"/>
       <c r="F28" s="274"/>
@@ -12676,10 +12691,10 @@
         <v>560</v>
       </c>
       <c r="D29" s="87" t="s">
-        <v>1313</v>
+        <v>1300</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1751</v>
+        <v>1725</v>
       </c>
       <c r="F29" s="87"/>
     </row>
@@ -12691,13 +12706,13 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1746</v>
+        <v>1720</v>
       </c>
       <c r="D30" s="274" t="s">
-        <v>1747</v>
+        <v>1721</v>
       </c>
       <c r="E30" s="274" t="s">
-        <v>1754</v>
+        <v>1728</v>
       </c>
       <c r="F30" s="274"/>
     </row>
@@ -12709,7 +12724,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1758</v>
+        <v>1732</v>
       </c>
       <c r="D31" s="87"/>
       <c r="E31" s="87"/>
@@ -12723,13 +12738,13 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1748</v>
+        <v>1722</v>
       </c>
       <c r="D32" s="274" t="s">
-        <v>1749</v>
+        <v>1723</v>
       </c>
       <c r="E32" s="274" t="s">
-        <v>1752</v>
+        <v>1726</v>
       </c>
       <c r="F32" s="274"/>
     </row>
@@ -12741,11 +12756,11 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1839</v>
+        <v>1813</v>
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="88" t="s">
-        <v>1755</v>
+        <v>1729</v>
       </c>
       <c r="F33" s="88"/>
     </row>
@@ -12757,13 +12772,13 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1759</v>
+        <v>1733</v>
       </c>
       <c r="D34" s="272" t="s">
-        <v>1760</v>
+        <v>1734</v>
       </c>
       <c r="E34" s="272" t="s">
-        <v>1779</v>
+        <v>1753</v>
       </c>
       <c r="F34" s="272"/>
     </row>
@@ -12775,13 +12790,13 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1761</v>
+        <v>1735</v>
       </c>
       <c r="D35" s="87" t="s">
-        <v>1762</v>
+        <v>1736</v>
       </c>
       <c r="E35" s="87" t="s">
-        <v>1772</v>
+        <v>1746</v>
       </c>
       <c r="F35" s="87"/>
     </row>
@@ -12793,13 +12808,13 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1763</v>
+        <v>1737</v>
       </c>
       <c r="D36" s="274" t="s">
-        <v>1764</v>
+        <v>1738</v>
       </c>
       <c r="E36" s="274" t="s">
-        <v>1773</v>
+        <v>1747</v>
       </c>
       <c r="F36" s="274"/>
     </row>
@@ -12811,13 +12826,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1765</v>
+        <v>1739</v>
       </c>
       <c r="D37" s="87" t="s">
-        <v>1766</v>
+        <v>1740</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1809</v>
+        <v>1783</v>
       </c>
       <c r="F37" s="87"/>
     </row>
@@ -12829,16 +12844,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1767</v>
+        <v>1741</v>
       </c>
       <c r="D38" s="274" t="s">
-        <v>1795</v>
+        <v>1769</v>
       </c>
       <c r="E38" s="292" t="s">
-        <v>1778</v>
+        <v>1752</v>
       </c>
       <c r="F38" s="292" t="s">
-        <v>1818</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12849,13 +12864,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1768</v>
+        <v>1742</v>
       </c>
       <c r="D39" s="87" t="s">
-        <v>1769</v>
+        <v>1743</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1774</v>
+        <v>1748</v>
       </c>
       <c r="F39" s="87"/>
     </row>
@@ -12867,16 +12882,16 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1770</v>
+        <v>1744</v>
       </c>
       <c r="D40" s="274" t="s">
-        <v>1780</v>
+        <v>1754</v>
       </c>
       <c r="E40" s="274" t="s">
-        <v>1775</v>
+        <v>1749</v>
       </c>
       <c r="F40" s="274" t="s">
-        <v>1802</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12887,13 +12902,13 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D41" s="88" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E41" s="88" t="s">
         <v>1771</v>
-      </c>
-      <c r="D41" s="88" t="s">
-        <v>1796</v>
-      </c>
-      <c r="E41" s="88" t="s">
-        <v>1797</v>
       </c>
       <c r="F41" s="88"/>
     </row>
@@ -12905,16 +12920,16 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1781</v>
+        <v>1755</v>
       </c>
       <c r="D42" s="272" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E42" s="272" t="s">
         <v>1782</v>
       </c>
-      <c r="E42" s="272" t="s">
-        <v>1808</v>
-      </c>
       <c r="F42" s="272" t="s">
-        <v>1819</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12925,13 +12940,13 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1791</v>
+        <v>1765</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>1783</v>
+        <v>1757</v>
       </c>
       <c r="E43" s="87" t="s">
-        <v>1801</v>
+        <v>1775</v>
       </c>
       <c r="F43" s="87"/>
     </row>
@@ -12943,13 +12958,13 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1784</v>
+        <v>1758</v>
       </c>
       <c r="D44" s="274" t="s">
-        <v>1785</v>
+        <v>1759</v>
       </c>
       <c r="E44" s="274" t="s">
-        <v>1800</v>
+        <v>1774</v>
       </c>
       <c r="F44" s="274"/>
     </row>
@@ -12961,13 +12976,13 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>1793</v>
+        <v>1767</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1810</v>
+        <v>1784</v>
       </c>
       <c r="F45" s="87"/>
     </row>
@@ -12979,14 +12994,14 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1787</v>
+        <v>1761</v>
       </c>
       <c r="D46" s="274" t="s">
-        <v>1788</v>
+        <v>1762</v>
       </c>
       <c r="E46" s="274"/>
       <c r="F46" s="274" t="s">
-        <v>1802</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12997,16 +13012,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1789</v>
+        <v>1763</v>
       </c>
       <c r="D47" s="87" t="s">
-        <v>1794</v>
+        <v>1768</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1807</v>
+        <v>1781</v>
       </c>
       <c r="F47" s="87" t="s">
-        <v>1817</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13017,12 +13032,12 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1798</v>
+        <v>1772</v>
       </c>
       <c r="D48" s="274"/>
       <c r="E48" s="274"/>
       <c r="F48" s="274" t="s">
-        <v>1803</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13033,13 +13048,13 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1790</v>
+        <v>1764</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>1804</v>
+        <v>1778</v>
       </c>
       <c r="E49" s="88" t="s">
-        <v>1799</v>
+        <v>1773</v>
       </c>
       <c r="F49" s="88"/>
     </row>
@@ -13051,14 +13066,14 @@
         <v>122</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>1825</v>
+        <v>1799</v>
       </c>
       <c r="D50" s="272"/>
       <c r="E50" s="272" t="s">
-        <v>1832</v>
+        <v>1806</v>
       </c>
       <c r="F50" s="272" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13069,14 +13084,14 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1829</v>
+        <v>1803</v>
       </c>
       <c r="D51" s="87"/>
       <c r="E51" s="87" t="s">
-        <v>1833</v>
+        <v>1807</v>
       </c>
       <c r="F51" s="87" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13087,14 +13102,14 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1834</v>
+        <v>1808</v>
       </c>
       <c r="D52" s="274"/>
       <c r="E52" s="274" t="s">
-        <v>1836</v>
+        <v>1810</v>
       </c>
       <c r="F52" s="274" t="s">
-        <v>1803</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13105,7 +13120,7 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1830</v>
+        <v>1804</v>
       </c>
       <c r="D53" s="87"/>
       <c r="E53" s="87"/>
@@ -13119,12 +13134,12 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1837</v>
+        <v>1811</v>
       </c>
       <c r="D54" s="274"/>
       <c r="E54" s="274"/>
       <c r="F54" s="274" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13135,14 +13150,14 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1826</v>
+        <v>1800</v>
       </c>
       <c r="D55" s="87" t="s">
-        <v>1827</v>
+        <v>1801</v>
       </c>
       <c r="E55" s="87"/>
       <c r="F55" s="87" t="s">
-        <v>1802</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13153,10 +13168,10 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1838</v>
+        <v>1812</v>
       </c>
       <c r="D56" s="274" t="s">
-        <v>1828</v>
+        <v>1802</v>
       </c>
       <c r="E56" s="274"/>
       <c r="F56" s="274"/>
@@ -13169,10 +13184,10 @@
         <v>143</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>1849</v>
+        <v>1823</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>1831</v>
+        <v>1805</v>
       </c>
       <c r="E57" s="88"/>
       <c r="F57" s="88"/>
@@ -13185,14 +13200,14 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1840</v>
+        <v>1814</v>
       </c>
       <c r="D58" s="272"/>
       <c r="E58" s="272" t="s">
-        <v>1852</v>
+        <v>1826</v>
       </c>
       <c r="F58" s="272" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13203,14 +13218,14 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1841</v>
+        <v>1815</v>
       </c>
       <c r="D59" s="87"/>
       <c r="E59" s="87" t="s">
-        <v>1850</v>
+        <v>1824</v>
       </c>
       <c r="F59" s="87" t="s">
-        <v>1777</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13221,7 +13236,7 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1851</v>
+        <v>1825</v>
       </c>
       <c r="D60" s="274"/>
       <c r="E60" s="274"/>
@@ -13235,13 +13250,13 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1853</v>
+        <v>1827</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>1842</v>
+        <v>1816</v>
       </c>
       <c r="E61" s="87" t="s">
-        <v>1854</v>
+        <v>1828</v>
       </c>
       <c r="F61" s="87"/>
     </row>
@@ -13253,11 +13268,11 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1843</v>
+        <v>1817</v>
       </c>
       <c r="D62" s="274"/>
       <c r="E62" s="274" t="s">
-        <v>1854</v>
+        <v>1828</v>
       </c>
       <c r="F62" s="274"/>
     </row>
@@ -13269,10 +13284,10 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1844</v>
+        <v>1818</v>
       </c>
       <c r="D63" s="87" t="s">
-        <v>1845</v>
+        <v>1819</v>
       </c>
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
@@ -13285,12 +13300,12 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1846</v>
+        <v>1820</v>
       </c>
       <c r="D64" s="274"/>
       <c r="E64" s="274"/>
       <c r="F64" s="274" t="s">
-        <v>1806</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13301,16 +13316,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1847</v>
+        <v>1821</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>1848</v>
+        <v>1822</v>
       </c>
       <c r="E65" s="88" t="s">
-        <v>1752</v>
+        <v>1726</v>
       </c>
       <c r="F65" s="88" t="s">
-        <v>1752</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13321,12 +13336,12 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1855</v>
+        <v>1829</v>
       </c>
       <c r="D66" s="87"/>
       <c r="E66" s="87"/>
       <c r="F66" s="87" t="s">
-        <v>1858</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13337,14 +13352,14 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1856</v>
+        <v>1830</v>
       </c>
       <c r="D67" s="87"/>
       <c r="E67" s="87" t="s">
-        <v>1857</v>
+        <v>1831</v>
       </c>
       <c r="F67" s="87" t="s">
-        <v>1802</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13352,17 +13367,17 @@
         <v>0</v>
       </c>
       <c r="B68" s="210" t="s">
-        <v>1307</v>
+        <v>1294</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1860</v>
+        <v>1834</v>
       </c>
       <c r="D68" s="276" t="s">
-        <v>1861</v>
+        <v>1835</v>
       </c>
       <c r="E68" s="276"/>
       <c r="F68" s="276" t="s">
-        <v>1859</v>
+        <v>1833</v>
       </c>
     </row>
   </sheetData>
@@ -13396,7 +13411,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="54" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="261" t="s">
-        <v>1552</v>
+        <v>1530</v>
       </c>
       <c r="B1" s="261" t="s">
         <v>537</v>
@@ -13414,68 +13429,68 @@
         <v>541</v>
       </c>
       <c r="G1" s="261" t="s">
-        <v>1596</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="262" t="s">
-        <v>1578</v>
+        <v>1556</v>
       </c>
       <c r="B2" s="263" t="s">
-        <v>1546</v>
+        <v>1524</v>
       </c>
       <c r="C2" s="263" t="s">
-        <v>1551</v>
+        <v>1529</v>
       </c>
       <c r="D2" s="263" t="s">
-        <v>1553</v>
+        <v>1531</v>
       </c>
       <c r="E2" s="263" t="s">
-        <v>1554</v>
+        <v>1532</v>
       </c>
       <c r="F2" s="263" t="s">
-        <v>1594</v>
+        <v>1572</v>
       </c>
       <c r="G2" s="264" t="s">
-        <v>1597</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="167" t="s">
-        <v>1579</v>
+        <v>1557</v>
       </c>
       <c r="B3" s="169" t="s">
-        <v>1574</v>
+        <v>1552</v>
       </c>
       <c r="C3" s="169" t="s">
-        <v>1555</v>
+        <v>1533</v>
       </c>
       <c r="D3" s="169" t="s">
-        <v>1556</v>
+        <v>1534</v>
       </c>
       <c r="E3" s="169" t="s">
-        <v>1557</v>
+        <v>1535</v>
       </c>
       <c r="F3" s="169" t="s">
         <v>542</v>
       </c>
       <c r="G3" s="170" t="s">
-        <v>1598</v>
+        <v>1576</v>
       </c>
       <c r="H3" s="265"/>
     </row>
     <row r="4" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="167" t="s">
-        <v>1580</v>
+        <v>1558</v>
       </c>
       <c r="B4" s="169" t="s">
-        <v>1547</v>
+        <v>1525</v>
       </c>
       <c r="C4" s="169" t="s">
-        <v>1558</v>
+        <v>1536</v>
       </c>
       <c r="D4" s="169" t="s">
-        <v>1559</v>
+        <v>1537</v>
       </c>
       <c r="E4" s="169" t="s">
         <v>543</v>
@@ -13484,145 +13499,145 @@
         <v>544</v>
       </c>
       <c r="G4" s="170" t="s">
-        <v>1599</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="167" t="s">
-        <v>1581</v>
+        <v>1559</v>
       </c>
       <c r="B5" s="169" t="s">
-        <v>1548</v>
+        <v>1526</v>
       </c>
       <c r="C5" s="169" t="s">
-        <v>1560</v>
+        <v>1538</v>
       </c>
       <c r="D5" s="169" t="s">
-        <v>1561</v>
+        <v>1539</v>
       </c>
       <c r="E5" s="169" t="s">
-        <v>1562</v>
+        <v>1540</v>
       </c>
       <c r="F5" s="169" t="s">
         <v>545</v>
       </c>
       <c r="G5" s="170" t="s">
-        <v>1600</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="167" t="s">
-        <v>1582</v>
+        <v>1560</v>
       </c>
       <c r="B6" s="169" t="s">
-        <v>1549</v>
+        <v>1527</v>
       </c>
       <c r="C6" s="169" t="s">
-        <v>1563</v>
+        <v>1541</v>
       </c>
       <c r="D6" s="169" t="s">
-        <v>1564</v>
+        <v>1542</v>
       </c>
       <c r="E6" s="169" t="s">
-        <v>1565</v>
+        <v>1543</v>
       </c>
       <c r="F6" s="169" t="s">
         <v>546</v>
       </c>
       <c r="G6" s="170" t="s">
-        <v>1601</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="167" t="s">
-        <v>1583</v>
+        <v>1561</v>
       </c>
       <c r="B7" s="169" t="s">
-        <v>1575</v>
+        <v>1553</v>
       </c>
       <c r="C7" s="169" t="s">
-        <v>1587</v>
+        <v>1565</v>
       </c>
       <c r="D7" s="169" t="s">
-        <v>1588</v>
+        <v>1566</v>
       </c>
       <c r="E7" s="169" t="s">
-        <v>1589</v>
+        <v>1567</v>
       </c>
       <c r="F7" s="169" t="s">
-        <v>1590</v>
+        <v>1568</v>
       </c>
       <c r="G7" s="170" t="s">
-        <v>1602</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="167" t="s">
-        <v>1584</v>
+        <v>1562</v>
       </c>
       <c r="B8" s="169" t="s">
-        <v>1550</v>
+        <v>1528</v>
       </c>
       <c r="C8" s="169" t="s">
-        <v>1566</v>
+        <v>1544</v>
       </c>
       <c r="D8" s="169" t="s">
-        <v>1567</v>
+        <v>1545</v>
       </c>
       <c r="E8" s="169" t="s">
-        <v>1568</v>
+        <v>1546</v>
       </c>
       <c r="F8" s="169" t="s">
-        <v>1569</v>
+        <v>1547</v>
       </c>
       <c r="G8" s="170" t="s">
-        <v>1603</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="167" t="s">
-        <v>1585</v>
+        <v>1563</v>
       </c>
       <c r="B9" s="169" t="s">
-        <v>1576</v>
+        <v>1554</v>
       </c>
       <c r="C9" s="169" t="s">
-        <v>1591</v>
+        <v>1569</v>
       </c>
       <c r="D9" s="169" t="s">
-        <v>1595</v>
+        <v>1573</v>
       </c>
       <c r="E9" s="169" t="s">
-        <v>1593</v>
+        <v>1571</v>
       </c>
       <c r="F9" s="169" t="s">
-        <v>1592</v>
+        <v>1570</v>
       </c>
       <c r="G9" s="170" t="s">
-        <v>1604</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="175" t="s">
-        <v>1586</v>
+        <v>1564</v>
       </c>
       <c r="B10" s="176" t="s">
-        <v>1577</v>
+        <v>1555</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>1570</v>
+        <v>1548</v>
       </c>
       <c r="D10" s="176" t="s">
-        <v>1571</v>
+        <v>1549</v>
       </c>
       <c r="E10" s="176" t="s">
-        <v>1572</v>
+        <v>1550</v>
       </c>
       <c r="F10" s="176" t="s">
-        <v>1573</v>
+        <v>1551</v>
       </c>
       <c r="G10" s="178" t="s">
-        <v>1605</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -13702,10 +13717,10 @@
     <row r="20" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:3" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="266" t="s">
-        <v>1665</v>
+        <v>1643</v>
       </c>
       <c r="B21" s="267" t="s">
-        <v>1666</v>
+        <v>1644</v>
       </c>
     </row>
   </sheetData>
@@ -14524,7 +14539,7 @@
         <v>282</v>
       </c>
       <c r="D57" s="247" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14672,13 +14687,13 @@
         <v>0</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="C68" s="101" t="s">
-        <v>1309</v>
+        <v>1296</v>
       </c>
       <c r="D68" s="244" t="s">
-        <v>1311</v>
+        <v>1298</v>
       </c>
     </row>
   </sheetData>
@@ -16234,16 +16249,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="D2" s="97" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>1043</v>
+        <v>1030</v>
       </c>
       <c r="F2" s="97" t="s">
-        <v>1044</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16254,16 +16269,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1045</v>
+        <v>1032</v>
       </c>
       <c r="D3" s="99" t="s">
-        <v>1046</v>
+        <v>1033</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="F3" s="99" t="s">
-        <v>1048</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16274,16 +16289,16 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1049</v>
+        <v>1036</v>
       </c>
       <c r="D4" s="99" t="s">
-        <v>1050</v>
+        <v>1037</v>
       </c>
       <c r="E4" s="87" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="F4" s="99" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16294,16 +16309,16 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>1054</v>
+        <v>1041</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1055</v>
+        <v>1042</v>
       </c>
       <c r="F5" s="99" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16314,16 +16329,16 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
       <c r="D6" s="99" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="E6" s="87" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="F6" s="99" t="s">
-        <v>1060</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16334,16 +16349,16 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1061</v>
+        <v>1048</v>
       </c>
       <c r="D7" s="99" t="s">
-        <v>1062</v>
+        <v>1049</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
       <c r="F7" s="99" t="s">
-        <v>1064</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16354,16 +16369,16 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1065</v>
+        <v>1052</v>
       </c>
       <c r="D8" s="99" t="s">
-        <v>1066</v>
+        <v>1053</v>
       </c>
       <c r="E8" s="87" t="s">
-        <v>1067</v>
+        <v>1054</v>
       </c>
       <c r="F8" s="99" t="s">
-        <v>1068</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16374,16 +16389,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1069</v>
+        <v>1056</v>
       </c>
       <c r="D9" s="101" t="s">
-        <v>1070</v>
+        <v>1057</v>
       </c>
       <c r="E9" s="89" t="s">
-        <v>1071</v>
+        <v>1058</v>
       </c>
       <c r="F9" s="112" t="s">
-        <v>1072</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16394,16 +16409,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>1075</v>
+        <v>1062</v>
       </c>
       <c r="F10" s="97" t="s">
-        <v>1076</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16414,16 +16429,16 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
       <c r="D11" s="99" t="s">
-        <v>1078</v>
+        <v>1065</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1079</v>
+        <v>1066</v>
       </c>
       <c r="F11" s="99" t="s">
-        <v>1080</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16434,16 +16449,16 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1081</v>
+        <v>1068</v>
       </c>
       <c r="D12" s="99" t="s">
-        <v>1082</v>
+        <v>1069</v>
       </c>
       <c r="E12" s="87" t="s">
-        <v>1083</v>
+        <v>1070</v>
       </c>
       <c r="F12" s="99" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16454,16 +16469,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1085</v>
+        <v>1072</v>
       </c>
       <c r="D13" s="99" t="s">
-        <v>1086</v>
+        <v>1073</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1087</v>
+        <v>1074</v>
       </c>
       <c r="F13" s="99" t="s">
-        <v>1088</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16474,16 +16489,16 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1089</v>
+        <v>1076</v>
       </c>
       <c r="D14" s="99" t="s">
-        <v>1090</v>
+        <v>1077</v>
       </c>
       <c r="E14" s="87" t="s">
-        <v>1091</v>
+        <v>1078</v>
       </c>
       <c r="F14" s="99" t="s">
-        <v>1092</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16494,16 +16509,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1093</v>
+        <v>1080</v>
       </c>
       <c r="D15" s="99" t="s">
-        <v>1094</v>
+        <v>1081</v>
       </c>
       <c r="E15" s="87" t="s">
-        <v>1095</v>
+        <v>1082</v>
       </c>
       <c r="F15" s="99" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16514,16 +16529,16 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1097</v>
+        <v>1084</v>
       </c>
       <c r="D16" s="99" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
       <c r="F16" s="99" t="s">
-        <v>1100</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16534,16 +16549,16 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1101</v>
+        <v>1088</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>1102</v>
+        <v>1089</v>
       </c>
       <c r="E17" s="88" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
       <c r="F17" s="158" t="s">
-        <v>1104</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16554,16 +16569,16 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1105</v>
+        <v>1092</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>1106</v>
+        <v>1093</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>1107</v>
+        <v>1094</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>1108</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16574,16 +16589,16 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1109</v>
+        <v>1096</v>
       </c>
       <c r="D19" s="99" t="s">
-        <v>1110</v>
+        <v>1097</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>1111</v>
+        <v>1098</v>
       </c>
       <c r="F19" s="99" t="s">
-        <v>1112</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16594,16 +16609,16 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
       <c r="D20" s="99" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
       <c r="E20" s="87" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="F20" s="99" t="s">
-        <v>1116</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16614,16 +16629,16 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1117</v>
+        <v>1104</v>
       </c>
       <c r="D21" s="99" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
       <c r="F21" s="99" t="s">
-        <v>1120</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16634,16 +16649,16 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="D22" s="99" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="E22" s="87" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="F22" s="99" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16654,16 +16669,16 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="D23" s="99" t="s">
-        <v>1126</v>
+        <v>1113</v>
       </c>
       <c r="E23" s="87" t="s">
-        <v>1127</v>
+        <v>1114</v>
       </c>
       <c r="F23" s="99" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16674,19 +16689,19 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1129</v>
+        <v>1116</v>
       </c>
       <c r="D24" s="99" t="s">
-        <v>1130</v>
+        <v>1117</v>
       </c>
       <c r="E24" s="87" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16697,16 +16712,16 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
       <c r="D25" s="101" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="E25" s="89" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="F25" s="112" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16717,16 +16732,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="D26" s="97" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="E26" s="86" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
       <c r="F26" s="97" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16737,16 +16752,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="D27" s="99" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
       <c r="F27" s="99" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16757,16 +16772,16 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="D28" s="99" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="E28" s="87" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
       <c r="F28" s="99" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16777,16 +16792,16 @@
         <v>75</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
       <c r="D29" s="99" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1152</v>
+        <v>1139</v>
       </c>
       <c r="F29" s="99" t="s">
-        <v>1153</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16797,16 +16812,16 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1154</v>
+        <v>1141</v>
       </c>
       <c r="D30" s="99" t="s">
-        <v>1155</v>
+        <v>1142</v>
       </c>
       <c r="E30" s="87" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
       <c r="F30" s="99" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16817,16 +16832,16 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
       <c r="D31" s="99" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="E31" s="87" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="F31" s="99" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16837,16 +16852,16 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="D32" s="99" t="s">
-        <v>1163</v>
+        <v>1150</v>
       </c>
       <c r="E32" s="87" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
       <c r="F32" s="99" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16857,16 +16872,16 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
       <c r="D33" s="101" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="E33" s="88" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
       <c r="F33" s="101" t="s">
-        <v>1169</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16877,16 +16892,16 @@
         <v>85</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>1170</v>
+        <v>1157</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>1171</v>
+        <v>1158</v>
       </c>
       <c r="E34" s="86" t="s">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="F34" s="97" t="s">
-        <v>1173</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16897,16 +16912,16 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1174</v>
+        <v>1161</v>
       </c>
       <c r="D35" s="99" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
       <c r="E35" s="87" t="s">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="F35" s="99" t="s">
-        <v>1177</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16917,16 +16932,16 @@
         <v>90</v>
       </c>
       <c r="C36" s="157" t="s">
-        <v>1178</v>
+        <v>1165</v>
       </c>
       <c r="D36" s="99" t="s">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="E36" s="87" t="s">
-        <v>1180</v>
+        <v>1167</v>
       </c>
       <c r="F36" s="99" t="s">
-        <v>1181</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16937,16 +16952,16 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1182</v>
+        <v>1169</v>
       </c>
       <c r="D37" s="99" t="s">
-        <v>1183</v>
+        <v>1170</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
       <c r="F37" s="99" t="s">
-        <v>1185</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16957,16 +16972,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1186</v>
+        <v>1173</v>
       </c>
       <c r="D38" s="99" t="s">
-        <v>1187</v>
+        <v>1174</v>
       </c>
       <c r="E38" s="87" t="s">
-        <v>1188</v>
+        <v>1175</v>
       </c>
       <c r="F38" s="99" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16977,16 +16992,16 @@
         <v>97</v>
       </c>
       <c r="C39" s="102" t="s">
-        <v>1190</v>
+        <v>1177</v>
       </c>
       <c r="D39" s="99" t="s">
-        <v>1191</v>
+        <v>1178</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="F39" s="99" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16997,16 +17012,16 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
       <c r="D40" s="99" t="s">
-        <v>1195</v>
+        <v>1182</v>
       </c>
       <c r="E40" s="87" t="s">
-        <v>1196</v>
+        <v>1183</v>
       </c>
       <c r="F40" s="99" t="s">
-        <v>1197</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17017,16 +17032,16 @@
         <v>101</v>
       </c>
       <c r="C41" s="89" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="D41" s="206" t="s">
-        <v>1199</v>
+        <v>1186</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>1200</v>
+        <v>1187</v>
       </c>
       <c r="F41" s="101" t="s">
-        <v>1201</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17037,16 +17052,16 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="D42" s="97" t="s">
-        <v>1203</v>
+        <v>1190</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>1204</v>
+        <v>1191</v>
       </c>
       <c r="F42" s="41" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17057,16 +17072,16 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1206</v>
+        <v>1193</v>
       </c>
       <c r="D43" s="99" t="s">
-        <v>1207</v>
+        <v>1194</v>
       </c>
       <c r="E43" s="87" t="s">
-        <v>1208</v>
+        <v>1195</v>
       </c>
       <c r="F43" s="99" t="s">
-        <v>1209</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17077,16 +17092,16 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1210</v>
+        <v>1197</v>
       </c>
       <c r="D44" s="99" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="E44" s="87" t="s">
-        <v>1212</v>
+        <v>1199</v>
       </c>
       <c r="F44" s="99" t="s">
-        <v>1213</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17097,16 +17112,16 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1214</v>
+        <v>1201</v>
       </c>
       <c r="D45" s="99" t="s">
-        <v>1215</v>
+        <v>1202</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="F45" s="99" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17117,19 +17132,19 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1218</v>
+        <v>1205</v>
       </c>
       <c r="D46" s="99" t="s">
-        <v>1219</v>
+        <v>1206</v>
       </c>
       <c r="E46" s="87" t="s">
-        <v>1220</v>
+        <v>1207</v>
       </c>
       <c r="F46" s="99" t="s">
-        <v>1221</v>
+        <v>1208</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>1222</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17140,16 +17155,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1223</v>
+        <v>1210</v>
       </c>
       <c r="D47" s="99" t="s">
-        <v>1224</v>
+        <v>1211</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1225</v>
+        <v>1212</v>
       </c>
       <c r="F47" s="99" t="s">
-        <v>1226</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17160,19 +17175,19 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1227</v>
+        <v>1214</v>
       </c>
       <c r="D48" s="99" t="s">
-        <v>1228</v>
+        <v>1215</v>
       </c>
       <c r="E48" s="87" t="s">
-        <v>1229</v>
+        <v>1216</v>
       </c>
       <c r="F48" s="99" t="s">
-        <v>1230</v>
+        <v>1217</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>1231</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17183,16 +17198,16 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1232</v>
+        <v>1219</v>
       </c>
       <c r="D49" s="101" t="s">
-        <v>1233</v>
+        <v>1220</v>
       </c>
       <c r="E49" s="89" t="s">
-        <v>1234</v>
+        <v>1221</v>
       </c>
       <c r="F49" s="112" t="s">
-        <v>1235</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17203,16 +17218,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>1236</v>
+        <v>1223</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>1237</v>
+        <v>1224</v>
       </c>
       <c r="E50" s="86" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
       <c r="F50" s="97" t="s">
-        <v>1239</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17223,16 +17238,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1240</v>
+        <v>1227</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>1241</v>
+        <v>1228</v>
       </c>
       <c r="E51" s="87" t="s">
-        <v>1242</v>
+        <v>1229</v>
       </c>
       <c r="F51" s="99" t="s">
-        <v>1243</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17243,16 +17258,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1244</v>
+        <v>1231</v>
       </c>
       <c r="D52" s="99" t="s">
-        <v>1245</v>
+        <v>1232</v>
       </c>
       <c r="E52" s="87" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F52" s="99" t="s">
-        <v>1247</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17263,16 +17278,16 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1248</v>
+        <v>1235</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="E53" s="87" t="s">
-        <v>1250</v>
+        <v>1237</v>
       </c>
       <c r="F53" s="99" t="s">
-        <v>1251</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17283,16 +17298,16 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1252</v>
+        <v>1239</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>1253</v>
+        <v>1240</v>
       </c>
       <c r="E54" s="87" t="s">
-        <v>1254</v>
+        <v>1241</v>
       </c>
       <c r="F54" s="99" t="s">
-        <v>1255</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17303,16 +17318,16 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>1257</v>
+        <v>1244</v>
       </c>
       <c r="E55" s="87" t="s">
-        <v>1258</v>
+        <v>1245</v>
       </c>
       <c r="F55" s="99" t="s">
-        <v>1259</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17323,16 +17338,16 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1260</v>
+        <v>1247</v>
       </c>
       <c r="D56" s="99" t="s">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="E56" s="87" t="s">
-        <v>1262</v>
+        <v>1249</v>
       </c>
       <c r="F56" s="99" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17343,16 +17358,16 @@
         <v>143</v>
       </c>
       <c r="C57" s="89" t="s">
-        <v>1264</v>
+        <v>1251</v>
       </c>
       <c r="D57" s="112" t="s">
-        <v>1265</v>
+        <v>1252</v>
       </c>
       <c r="E57" s="88" t="s">
-        <v>1266</v>
+        <v>1253</v>
       </c>
       <c r="F57" s="101" t="s">
-        <v>1267</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17363,16 +17378,16 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1268</v>
+        <v>1255</v>
       </c>
       <c r="D58" s="97" t="s">
-        <v>1269</v>
+        <v>1256</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>1270</v>
+        <v>1257</v>
       </c>
       <c r="F58" s="41" t="s">
-        <v>1271</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17383,16 +17398,16 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="D59" s="99" t="s">
-        <v>1273</v>
+        <v>1260</v>
       </c>
       <c r="E59" s="87" t="s">
-        <v>1274</v>
+        <v>1261</v>
       </c>
       <c r="F59" s="99" t="s">
-        <v>1275</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17403,16 +17418,16 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1276</v>
+        <v>1263</v>
       </c>
       <c r="D60" s="99" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="E60" s="87" t="s">
-        <v>1278</v>
+        <v>1265</v>
       </c>
       <c r="F60" s="99" t="s">
-        <v>1279</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17423,16 +17438,16 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1280</v>
+        <v>1267</v>
       </c>
       <c r="D61" s="99" t="s">
-        <v>1281</v>
+        <v>1268</v>
       </c>
       <c r="E61" s="87" t="s">
-        <v>1282</v>
+        <v>1269</v>
       </c>
       <c r="F61" s="99" t="s">
-        <v>1283</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17443,16 +17458,16 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1284</v>
+        <v>1271</v>
       </c>
       <c r="D62" s="99" t="s">
-        <v>1285</v>
+        <v>1272</v>
       </c>
       <c r="E62" s="87" t="s">
-        <v>1286</v>
+        <v>1273</v>
       </c>
       <c r="F62" s="99" t="s">
-        <v>1287</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17463,16 +17478,16 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1288</v>
+        <v>1275</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="E63" s="87" t="s">
-        <v>1290</v>
+        <v>1277</v>
       </c>
       <c r="F63" s="99" t="s">
-        <v>1291</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17483,16 +17498,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1292</v>
+        <v>1279</v>
       </c>
       <c r="D64" s="99" t="s">
-        <v>1293</v>
+        <v>1280</v>
       </c>
       <c r="E64" s="87" t="s">
-        <v>1294</v>
+        <v>1281</v>
       </c>
       <c r="F64" s="99" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17503,16 +17518,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="D65" s="101" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="E65" s="89" t="s">
-        <v>1298</v>
+        <v>1285</v>
       </c>
       <c r="F65" s="112" t="s">
-        <v>1299</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17523,16 +17538,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1300</v>
+        <v>1287</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="E66" s="86" t="s">
-        <v>1302</v>
+        <v>1289</v>
       </c>
       <c r="F66" s="97" t="s">
-        <v>1303</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17543,16 +17558,16 @@
         <v>168</v>
       </c>
       <c r="C67" s="88" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
       <c r="D67" s="101" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="E67" s="88" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="F67" s="101" t="s">
-        <v>1306</v>
+        <v>1293</v>
       </c>
     </row>
   </sheetData>
@@ -17583,7 +17598,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>1490</v>
+        <v>1468</v>
       </c>
       <c r="C1" s="211" t="s">
         <v>511</v>
@@ -17626,16 +17641,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="248" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="D3" s="249" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="E3" s="250" t="s">
-        <v>1446</v>
+        <v>1432</v>
       </c>
       <c r="F3" s="251" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17826,16 +17841,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="255" t="s">
-        <v>1606</v>
+        <v>1584</v>
       </c>
       <c r="D13" s="256" t="s">
-        <v>1607</v>
+        <v>1585</v>
       </c>
       <c r="E13" s="140" t="s">
-        <v>1608</v>
+        <v>1586</v>
       </c>
       <c r="F13" s="251" t="s">
-        <v>1609</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17932,7 +17947,7 @@
         <v>620</v>
       </c>
       <c r="E18" s="253" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
       <c r="F18" s="182" t="s">
         <v>621</v>
@@ -18049,7 +18064,7 @@
         <v>642</v>
       </c>
       <c r="D24" s="256" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
       <c r="E24" s="196" t="s">
         <v>643</v>
@@ -18086,16 +18101,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="252" t="s">
-        <v>1448</v>
+        <v>1434</v>
       </c>
       <c r="D26" s="192" t="s">
         <v>649</v>
       </c>
       <c r="E26" s="253" t="s">
-        <v>1480</v>
+        <v>1462</v>
       </c>
       <c r="F26" s="254" t="s">
-        <v>1449</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18186,16 +18201,16 @@
         <v>79</v>
       </c>
       <c r="C31" s="255" t="s">
-        <v>1450</v>
+        <v>1436</v>
       </c>
       <c r="D31" s="256" t="s">
-        <v>1451</v>
+        <v>1437</v>
       </c>
       <c r="E31" s="196" t="s">
         <v>666</v>
       </c>
       <c r="F31" s="251" t="s">
-        <v>1452</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18286,16 +18301,16 @@
         <v>90</v>
       </c>
       <c r="C36" s="255" t="s">
-        <v>1453</v>
+        <v>1439</v>
       </c>
       <c r="D36" s="256" t="s">
-        <v>1454</v>
+        <v>1440</v>
       </c>
       <c r="E36" s="140" t="s">
-        <v>1455</v>
+        <v>1441</v>
       </c>
       <c r="F36" s="251" t="s">
-        <v>1456</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18306,13 +18321,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="255" t="s">
-        <v>1457</v>
+        <v>1443</v>
       </c>
       <c r="D37" s="195" t="s">
         <v>683</v>
       </c>
       <c r="E37" s="140" t="s">
-        <v>1458</v>
+        <v>1444</v>
       </c>
       <c r="F37" s="186" t="s">
         <v>684</v>
@@ -18335,7 +18350,7 @@
         <v>687</v>
       </c>
       <c r="F38" s="251" t="s">
-        <v>1459</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18406,7 +18421,7 @@
         <v>103</v>
       </c>
       <c r="C42" s="252" t="s">
-        <v>1460</v>
+        <v>1446</v>
       </c>
       <c r="D42" s="192" t="s">
         <v>700</v>
@@ -18486,16 +18501,16 @@
         <v>113</v>
       </c>
       <c r="C46" s="255" t="s">
-        <v>1461</v>
+        <v>1447</v>
       </c>
       <c r="D46" s="195" t="s">
         <v>715</v>
       </c>
       <c r="E46" s="140" t="s">
-        <v>1462</v>
+        <v>1448</v>
       </c>
       <c r="F46" s="251" t="s">
-        <v>1463</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18506,16 +18521,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="255" t="s">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="D47" s="256" t="s">
-        <v>1465</v>
+        <v>1451</v>
       </c>
       <c r="E47" s="140" t="s">
-        <v>1466</v>
+        <v>1452</v>
       </c>
       <c r="F47" s="251" t="s">
-        <v>1467</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18546,16 +18561,16 @@
         <v>119</v>
       </c>
       <c r="C49" s="257" t="s">
-        <v>1468</v>
+        <v>1454</v>
       </c>
       <c r="D49" s="258" t="s">
-        <v>1469</v>
+        <v>1455</v>
       </c>
       <c r="E49" s="259" t="s">
-        <v>1470</v>
+        <v>1456</v>
       </c>
       <c r="F49" s="260" t="s">
-        <v>1471</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18565,17 +18580,17 @@
       <c r="B50" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C50" s="191" t="s">
-        <v>720</v>
-      </c>
-      <c r="D50" s="192" t="s">
-        <v>721</v>
-      </c>
-      <c r="E50" s="193" t="s">
-        <v>722</v>
-      </c>
-      <c r="F50" s="182" t="s">
-        <v>723</v>
+      <c r="C50" s="252" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D50" s="293" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E50" s="253" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F50" s="254" t="s">
+        <v>1840</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18585,17 +18600,17 @@
       <c r="B51" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="194" t="s">
-        <v>724</v>
-      </c>
-      <c r="D51" s="195" t="s">
-        <v>725</v>
-      </c>
-      <c r="E51" s="196" t="s">
-        <v>726</v>
-      </c>
-      <c r="F51" s="186" t="s">
-        <v>727</v>
+      <c r="C51" s="255" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D51" s="256" t="s">
+        <v>1842</v>
+      </c>
+      <c r="E51" s="140" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F51" s="251" t="s">
+        <v>1844</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18606,16 +18621,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="255" t="s">
-        <v>1472</v>
+        <v>1845</v>
       </c>
       <c r="D52" s="256" t="s">
-        <v>1473</v>
+        <v>1846</v>
       </c>
       <c r="E52" s="140" t="s">
-        <v>1475</v>
+        <v>1847</v>
       </c>
       <c r="F52" s="251" t="s">
-        <v>1474</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18626,16 +18641,16 @@
         <v>132</v>
       </c>
       <c r="C53" s="194" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="D53" s="195" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E53" s="196" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F53" s="186" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18646,16 +18661,16 @@
         <v>135</v>
       </c>
       <c r="C54" s="194" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D54" s="195" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="E54" s="196" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="F54" s="186" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18666,16 +18681,16 @@
         <v>137</v>
       </c>
       <c r="C55" s="194" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="E55" s="196" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="F55" s="251" t="s">
-        <v>1476</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18686,16 +18701,16 @@
         <v>140</v>
       </c>
       <c r="C56" s="255" t="s">
-        <v>1477</v>
+        <v>1459</v>
       </c>
       <c r="D56" s="256" t="s">
-        <v>1478</v>
+        <v>1460</v>
       </c>
       <c r="E56" s="140" t="s">
-        <v>1479</v>
+        <v>1461</v>
       </c>
       <c r="F56" s="186" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18706,16 +18721,16 @@
         <v>143</v>
       </c>
       <c r="C57" s="197" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D57" s="198" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E57" s="259" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
       <c r="F57" s="190" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18726,16 +18741,16 @@
         <v>146</v>
       </c>
       <c r="C58" s="191" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="D58" s="192" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="E58" s="193" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="F58" s="182" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18746,16 +18761,16 @@
         <v>149</v>
       </c>
       <c r="C59" s="194" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="D59" s="195" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="E59" s="196" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="F59" s="186" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18766,16 +18781,16 @@
         <v>151</v>
       </c>
       <c r="C60" s="194" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="D60" s="195" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="E60" s="196" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="F60" s="186" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18786,16 +18801,16 @@
         <v>154</v>
       </c>
       <c r="C61" s="194" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="D61" s="195" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="E61" s="196" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="F61" s="186" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18806,16 +18821,16 @@
         <v>156</v>
       </c>
       <c r="C62" s="255" t="s">
-        <v>1484</v>
+        <v>1466</v>
       </c>
       <c r="D62" s="256" t="s">
-        <v>1485</v>
+        <v>1467</v>
       </c>
       <c r="E62" s="196" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="F62" s="186" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18826,16 +18841,16 @@
         <v>158</v>
       </c>
       <c r="C63" s="194" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="D63" s="195" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="E63" s="196" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="F63" s="186" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18846,16 +18861,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="255" t="s">
-        <v>1486</v>
+        <v>1849</v>
       </c>
       <c r="D64" s="256" t="s">
-        <v>1487</v>
+        <v>1850</v>
       </c>
       <c r="E64" s="140" t="s">
-        <v>1489</v>
+        <v>1851</v>
       </c>
       <c r="F64" s="251" t="s">
-        <v>1488</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18866,16 +18881,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="202" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="D65" s="203" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="E65" s="204" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="F65" s="205" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18885,17 +18900,17 @@
       <c r="B66" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C66" s="191" t="s">
-        <v>769</v>
-      </c>
-      <c r="D66" s="192" t="s">
-        <v>770</v>
+      <c r="C66" s="252" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D66" s="293" t="s">
+        <v>1854</v>
       </c>
       <c r="E66" s="193" t="s">
-        <v>771</v>
-      </c>
-      <c r="F66" s="182" t="s">
-        <v>772</v>
+        <v>761</v>
+      </c>
+      <c r="F66" s="254" t="s">
+        <v>1855</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18905,17 +18920,17 @@
       <c r="B67" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="C67" s="197" t="s">
-        <v>773</v>
-      </c>
-      <c r="D67" s="198" t="s">
-        <v>774</v>
+      <c r="C67" s="257" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D67" s="258" t="s">
+        <v>1857</v>
       </c>
       <c r="E67" s="199" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="F67" s="190" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -18923,19 +18938,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>1307</v>
+        <v>1294</v>
       </c>
       <c r="C68" s="268" t="s">
-        <v>1668</v>
+        <v>1858</v>
       </c>
       <c r="D68" s="269" t="s">
-        <v>1669</v>
+        <v>1859</v>
       </c>
       <c r="E68" s="270" t="s">
-        <v>1670</v>
+        <v>1860</v>
       </c>
       <c r="F68" s="271" t="s">
-        <v>1671</v>
+        <v>1861</v>
       </c>
     </row>
   </sheetData>
@@ -18989,16 +19004,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="212" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="D2" s="213" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="E2" s="214" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="F2" s="215" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19009,16 +19024,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="216" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="D3" s="217" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="E3" s="218" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="F3" s="219" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19029,16 +19044,16 @@
         <v>17</v>
       </c>
       <c r="C4" s="216" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="D4" s="217" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="E4" s="218" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="F4" s="219" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19049,16 +19064,16 @@
         <v>19</v>
       </c>
       <c r="C5" s="216" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="D5" s="217" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="E5" s="218" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="F5" s="219" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19069,16 +19084,16 @@
         <v>21</v>
       </c>
       <c r="C6" s="216" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="D6" s="217" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="E6" s="218" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="F6" s="219" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19089,16 +19104,16 @@
         <v>24</v>
       </c>
       <c r="C7" s="216" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="D7" s="217" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="E7" s="218" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="F7" s="219" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19109,16 +19124,16 @@
         <v>27</v>
       </c>
       <c r="C8" s="216" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="D8" s="217" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="E8" s="218" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="F8" s="219" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19129,16 +19144,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="220" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="D9" s="221" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="E9" s="222" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="F9" s="223" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19149,16 +19164,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="224" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="D10" s="225" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="E10" s="226" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="F10" s="215" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19169,16 +19184,16 @@
         <v>34</v>
       </c>
       <c r="C11" s="227" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="D11" s="228" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="E11" s="229" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="F11" s="219" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19189,16 +19204,16 @@
         <v>38</v>
       </c>
       <c r="C12" s="227" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="D12" s="228" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="E12" s="229" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="F12" s="219" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19209,16 +19224,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="227" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="D13" s="228" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="E13" s="229" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="F13" s="219" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19229,16 +19244,16 @@
         <v>42</v>
       </c>
       <c r="C14" s="227" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="D14" s="228" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="E14" s="229" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="F14" s="219" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19249,16 +19264,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="227" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="D15" s="228" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="E15" s="229" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="F15" s="219" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19269,16 +19284,16 @@
         <v>46</v>
       </c>
       <c r="C16" s="227" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="D16" s="228" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="E16" s="229" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="F16" s="219" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19289,16 +19304,16 @@
         <v>48</v>
       </c>
       <c r="C17" s="230" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="D17" s="231" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="E17" s="232" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19309,16 +19324,16 @@
         <v>50</v>
       </c>
       <c r="C18" s="224" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="D18" s="225" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="E18" s="226" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="F18" s="215" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19329,16 +19344,16 @@
         <v>54</v>
       </c>
       <c r="C19" s="227" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="D19" s="228" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="E19" s="229" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="F19" s="219" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19349,16 +19364,16 @@
         <v>56</v>
       </c>
       <c r="C20" s="227" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="D20" s="228" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="E20" s="229" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="F20" s="219" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19369,16 +19384,16 @@
         <v>58</v>
       </c>
       <c r="C21" s="227" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="D21" s="228" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="E21" s="229" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="F21" s="219" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19389,16 +19404,16 @@
         <v>60</v>
       </c>
       <c r="C22" s="227" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="D22" s="228" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E22" s="229" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="F22" s="219" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19409,16 +19424,16 @@
         <v>62</v>
       </c>
       <c r="C23" s="227" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="D23" s="228" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E23" s="229" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="F23" s="219" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19429,16 +19444,16 @@
         <v>64</v>
       </c>
       <c r="C24" s="227" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="D24" s="228" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="E24" s="229" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="F24" s="219" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19449,16 +19464,16 @@
         <v>66</v>
       </c>
       <c r="C25" s="230" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="D25" s="231" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="E25" s="232" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="F25" s="223" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19469,16 +19484,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="224" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="D26" s="225" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="E26" s="226" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="F26" s="215" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19489,16 +19504,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="227" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="D27" s="228" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="E27" s="229" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="F27" s="219" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19509,16 +19524,16 @@
         <v>73</v>
       </c>
       <c r="C28" s="227" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="D28" s="228" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="E28" s="229" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="F28" s="219" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19529,16 +19544,16 @@
         <v>75</v>
       </c>
       <c r="C29" s="227" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="D29" s="228" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="E29" s="229" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="F29" s="219" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19549,16 +19564,16 @@
         <v>77</v>
       </c>
       <c r="C30" s="227" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="D30" s="228" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="E30" s="229" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="F30" s="219" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19569,16 +19584,16 @@
         <v>79</v>
       </c>
       <c r="C31" s="227" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="D31" s="228" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="E31" s="229" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="F31" s="219" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19589,16 +19604,16 @@
         <v>81</v>
       </c>
       <c r="C32" s="227" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="D32" s="228" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="E32" s="229" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19609,16 +19624,16 @@
         <v>83</v>
       </c>
       <c r="C33" s="230" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="D33" s="231" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="E33" s="232" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="F33" s="223" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19629,16 +19644,16 @@
         <v>85</v>
       </c>
       <c r="C34" s="224" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="D34" s="225" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="E34" s="226" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="F34" s="215" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19649,16 +19664,16 @@
         <v>88</v>
       </c>
       <c r="C35" s="227" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="D35" s="228" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="E35" s="229" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="F35" s="233" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19669,16 +19684,16 @@
         <v>90</v>
       </c>
       <c r="C36" s="227" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="D36" s="228" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="E36" s="229" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="F36" s="219" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19689,16 +19704,16 @@
         <v>92</v>
       </c>
       <c r="C37" s="227" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="D37" s="228" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="E37" s="229" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="F37" s="219" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19709,16 +19724,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="227" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="D38" s="228" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="E38" s="229" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="F38" s="219" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19729,16 +19744,16 @@
         <v>97</v>
       </c>
       <c r="C39" s="227" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="D39" s="228" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="E39" s="229" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="F39" s="219" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19749,16 +19764,16 @@
         <v>99</v>
       </c>
       <c r="C40" s="227" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="D40" s="228" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="E40" s="229" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="F40" s="219" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19769,16 +19784,16 @@
         <v>101</v>
       </c>
       <c r="C41" s="230" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="D41" s="231" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="E41" s="232" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="F41" s="234" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19789,16 +19804,16 @@
         <v>103</v>
       </c>
       <c r="C42" s="224" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="D42" s="225" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="E42" s="226" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="F42" s="215" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19809,16 +19824,16 @@
         <v>107</v>
       </c>
       <c r="C43" s="227" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="D43" s="228" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="E43" s="229" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="F43" s="219" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19829,16 +19844,16 @@
         <v>109</v>
       </c>
       <c r="C44" s="227" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="D44" s="228" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="E44" s="229" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="F44" s="219" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19849,16 +19864,16 @@
         <v>111</v>
       </c>
       <c r="C45" s="227" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="D45" s="228" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="E45" s="229" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="F45" s="219" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19869,16 +19884,16 @@
         <v>113</v>
       </c>
       <c r="C46" s="227" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="D46" s="228" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="E46" s="229" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="F46" s="219" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19889,16 +19904,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="227" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="D47" s="228" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="E47" s="229" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="F47" s="219" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19909,16 +19924,16 @@
         <v>117</v>
       </c>
       <c r="C48" s="227" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="D48" s="228" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="E48" s="229" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="F48" s="219" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19929,16 +19944,16 @@
         <v>119</v>
       </c>
       <c r="C49" s="230" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="D49" s="231" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="E49" s="232" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="F49" s="223" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19949,16 +19964,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="224" t="s">
-        <v>969</v>
+        <v>956</v>
       </c>
       <c r="D50" s="225" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
       <c r="E50" s="226" t="s">
-        <v>971</v>
+        <v>958</v>
       </c>
       <c r="F50" s="215" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19969,16 +19984,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="227" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="D51" s="228" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="E51" s="229" t="s">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="F51" s="219" t="s">
-        <v>976</v>
+        <v>963</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19989,16 +20004,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="227" t="s">
-        <v>977</v>
+        <v>964</v>
       </c>
       <c r="D52" s="228" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
       <c r="E52" s="229" t="s">
-        <v>979</v>
+        <v>966</v>
       </c>
       <c r="F52" s="219" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20009,16 +20024,16 @@
         <v>132</v>
       </c>
       <c r="C53" s="227" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="D53" s="228" t="s">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="E53" s="229" t="s">
-        <v>983</v>
+        <v>970</v>
       </c>
       <c r="F53" s="219" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20029,16 +20044,16 @@
         <v>135</v>
       </c>
       <c r="C54" s="227" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
       <c r="D54" s="228" t="s">
-        <v>986</v>
+        <v>973</v>
       </c>
       <c r="E54" s="229" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="F54" s="219" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20049,16 +20064,16 @@
         <v>137</v>
       </c>
       <c r="C55" s="227" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="D55" s="228" t="s">
-        <v>990</v>
+        <v>977</v>
       </c>
       <c r="E55" s="229" t="s">
-        <v>991</v>
+        <v>978</v>
       </c>
       <c r="F55" s="219" t="s">
-        <v>992</v>
+        <v>979</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20069,16 +20084,16 @@
         <v>140</v>
       </c>
       <c r="C56" s="227" t="s">
-        <v>993</v>
+        <v>980</v>
       </c>
       <c r="D56" s="228" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="E56" s="229" t="s">
-        <v>995</v>
+        <v>982</v>
       </c>
       <c r="F56" s="219" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20089,16 +20104,16 @@
         <v>143</v>
       </c>
       <c r="C57" s="230" t="s">
-        <v>997</v>
+        <v>984</v>
       </c>
       <c r="D57" s="231" t="s">
-        <v>998</v>
+        <v>985</v>
       </c>
       <c r="E57" s="232" t="s">
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="F57" s="223" t="s">
-        <v>1000</v>
+        <v>987</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20109,16 +20124,16 @@
         <v>146</v>
       </c>
       <c r="C58" s="224" t="s">
-        <v>1001</v>
+        <v>988</v>
       </c>
       <c r="D58" s="225" t="s">
-        <v>1002</v>
+        <v>989</v>
       </c>
       <c r="E58" s="226" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="F58" s="215" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20129,16 +20144,16 @@
         <v>149</v>
       </c>
       <c r="C59" s="227" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="D59" s="228" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="E59" s="229" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="F59" s="219" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20149,16 +20164,16 @@
         <v>151</v>
       </c>
       <c r="C60" s="227" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="D60" s="228" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E60" s="229" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="F60" s="219" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20169,16 +20184,16 @@
         <v>154</v>
       </c>
       <c r="C61" s="227" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="D61" s="228" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="E61" s="229" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="F61" s="219" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20189,16 +20204,16 @@
         <v>156</v>
       </c>
       <c r="C62" s="227" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="D62" s="228" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E62" s="229" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="F62" s="219" t="s">
-        <v>1020</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20209,16 +20224,16 @@
         <v>158</v>
       </c>
       <c r="C63" s="227" t="s">
-        <v>1021</v>
+        <v>1008</v>
       </c>
       <c r="D63" s="228" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="E63" s="229" t="s">
-        <v>1023</v>
+        <v>1010</v>
       </c>
       <c r="F63" s="219" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20229,16 +20244,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="227" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="D64" s="228" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="E64" s="229" t="s">
-        <v>1027</v>
+        <v>1014</v>
       </c>
       <c r="F64" s="219" t="s">
-        <v>1028</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20249,16 +20264,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="235" t="s">
-        <v>1029</v>
+        <v>1016</v>
       </c>
       <c r="D65" s="236" t="s">
-        <v>1030</v>
+        <v>1017</v>
       </c>
       <c r="E65" s="237" t="s">
-        <v>1031</v>
+        <v>1018</v>
       </c>
       <c r="F65" s="238" t="s">
-        <v>1032</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20269,16 +20284,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="224" t="s">
-        <v>1033</v>
+        <v>1020</v>
       </c>
       <c r="D66" s="225" t="s">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="E66" s="226" t="s">
-        <v>1035</v>
+        <v>1022</v>
       </c>
       <c r="F66" s="215" t="s">
-        <v>1036</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20289,16 +20304,16 @@
         <v>168</v>
       </c>
       <c r="C67" s="230" t="s">
-        <v>1037</v>
+        <v>1024</v>
       </c>
       <c r="D67" s="231" t="s">
-        <v>1038</v>
+        <v>1025</v>
       </c>
       <c r="E67" s="232" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="F67" s="223" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1864">
   <si>
     <t>編號</t>
   </si>
@@ -3145,10 +3145,6 @@
 關係：互動消失。健康：轉向靜止休息。</t>
   </si>
   <si>
-    <t>愛情：遮蔽發生。事業：轉折進入日蝕。
-關係：表現變少。健康：能量被遮。</t>
-  </si>
-  <si>
     <t>愛情：遮蔽漸深。事業：轉折靠近。
 關係：外在表現減少。健康：能量下降。</t>
   </si>
@@ -3161,38 +3157,6 @@
 關係：重新出現。健康：恢復明朗。</t>
   </si>
   <si>
-    <t>愛情：暗面完整出現。事業：暗處被看見。
-關係：暗面影響很大。健康：壓抑明顯。</t>
-  </si>
-  <si>
-    <t>愛情：暗面漸現。事業：隱情浮出。
-關係：陰影加深。健康：深層感受出現。</t>
-  </si>
-  <si>
-    <t>愛情：暗面開始減弱。事業：隱情被消化。
-關係：陰影變淡。健康：壓抑緩解。</t>
-  </si>
-  <si>
-    <t>愛情：暗面退去。事業：暗面消退。
-關係：陰影不再影響最大。健康：回到表面狀態。</t>
-  </si>
-  <si>
-    <t>愛情：希望明確。事業：遠方看得見。
-關係：共同方向存在。健康：改善可期。</t>
-  </si>
-  <si>
-    <t>愛情：希望漸亮。事業：遠方出現。
-關係：方向看得出。健康：改善跡象出現。</t>
-  </si>
-  <si>
-    <t>愛情：希望轉弱。事業：遠方迷航。
-關係：方向不清楚。健康：改善感下降。</t>
-  </si>
-  <si>
-    <t>愛情：希望減弱。事業：遠方目標消失。
-關係：方向消失。健康：回到眼前現況。</t>
-  </si>
-  <si>
     <t>愛情：進入特定時期。事業：時段清楚。
 關係：時段有序。健康：時程明確。</t>
   </si>
@@ -3369,10 +3333,6 @@
 關係：相遇不再成立。健康：等待下一時機。</t>
   </si>
   <si>
-    <t>愛情：空洞明顯。事業：內容還沒成形。
-關係：感到空缺。健康：虛弱可感。</t>
-  </si>
-  <si>
     <t>愛情：空缺出現。事業：看見還沒成形。
 關係：空洞看得出。健康：虛弱初現。</t>
   </si>
@@ -3401,10 +3361,6 @@
 關係：結局改變。健康：重新評估。</t>
   </si>
   <si>
-    <t>愛情：變數大量出現。事業：規則暫失效。
-關係：混亂最明顯。健康：狀態混亂。</t>
-  </si>
-  <si>
     <t>愛情：變數增加。事業：規則開始減弱。
 關係：混亂可見。健康：秩序變弱。</t>
   </si>
@@ -3417,20 +3373,8 @@
 關係：變數穩定。健康：狀態恢復正常。</t>
   </si>
   <si>
-    <t>愛情：方向明顯。事業：整體規律形成。
-關係：走向看得見。健康：模式穩定。</t>
-  </si>
-  <si>
     <t>愛情：方向慢慢清楚。事業：規律漸出現。
 關係：走向形成。健康：模式看得出。</t>
-  </si>
-  <si>
-    <t>愛情：方向偏移。事業：規律難讀。
-關係：走向不穩。健康：模式失準。</t>
-  </si>
-  <si>
-    <t>愛情：舊方向改變。事業：規律改變。
-關係：走向改變。健康：模式改變。</t>
   </si>
   <si>
     <t>辨認單一精神起點</t>
@@ -6383,6 +6327,84 @@
   </si>
   <si>
     <t>德消失，舊有籤詩隨時機消逝。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：小變可應。事業：偏差可控。
+關係：小問題可解。健康：小恙可調。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：可接受的最壞。事業：到低點可守。
+關係：暗面可見。健康：有隱患但可控制。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：預留最壞打算。事業：宜留退路。
+關係：快看到看陰暗面。健康：及早預防。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：最壞時機已過。事業：勿陷悲觀。
+關係：陰影面變淡。健康：隱患處理中。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：暗面退去。事業：最低線消退。
+關係：陰影不再影響。健康：回到表面狀態。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：軌跡相合。事業：走勢可循。
+關係：看共同存在。健康：尋律而安。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：逐漸看到軌跡。事業：遠景漸明。
+關係：快有脈絡。健康：快有規律。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：走向偏移。事業：快看不到遠景。
+關係：彼此失準。健康：律動失衡。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：軌跡錯判。事業：沒有遠景。
+關係：方向消失。健康：規律大亂。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：看清虛假面。事業：內容還沒成形。
+關係：看破假象。健康：虛弱可感。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：變數大量出現。事業：為可控隨機。
+關係：可控制的混亂。健康：波動可調。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：命運明顯。事業：整體定局形成。
+關係：命中注定。健康：模式穩定。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：開始受限。事業：規律難讀。
+關係：開始受限。健康：模式失準。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛情：困於宿命。事業：失策認命。
+關係：走向改變。健康：模式改變。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德不參與抽籤</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -6578,7 +6600,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6646,6 +6668,30 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59978026673177287"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79985961485641044"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59978026673177287"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79985961485641044"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59978026673177287"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -7681,7 +7727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="294">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -8210,6 +8256,39 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="20% - 輔色1" xfId="7"/>
@@ -9737,8 +9816,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F67" totalsRowShown="0" dataDxfId="6">
-  <autoFilter ref="A1:F67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F68" totalsRowShown="0" dataDxfId="6">
+  <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
     <tableColumn id="1" name="編號" dataDxfId="5"/>
     <tableColumn id="2" name="名稱" dataDxfId="4"/>
@@ -10005,13 +10084,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="118" t="s">
-        <v>1646</v>
+        <v>1632</v>
       </c>
       <c r="I1" s="291" t="s">
-        <v>1650</v>
+        <v>1636</v>
       </c>
       <c r="J1" s="291" t="s">
-        <v>1363</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10022,7 +10101,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>1469</v>
+        <v>1455</v>
       </c>
       <c r="D2" s="86" t="s">
         <v>8</v>
@@ -10037,13 +10116,13 @@
         <v>11</v>
       </c>
       <c r="H2" s="282" t="s">
-        <v>1589</v>
+        <v>1575</v>
       </c>
       <c r="I2" s="272" t="s">
-        <v>1301</v>
+        <v>1287</v>
       </c>
       <c r="J2" s="273" t="s">
-        <v>1364</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10069,13 +10148,13 @@
         <v>16</v>
       </c>
       <c r="H3" s="281" t="s">
-        <v>1590</v>
+        <v>1576</v>
       </c>
       <c r="I3" s="87" t="s">
-        <v>1302</v>
+        <v>1288</v>
       </c>
       <c r="J3" s="99" t="s">
-        <v>1365</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10086,7 +10165,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="98" t="s">
-        <v>1470</v>
+        <v>1456</v>
       </c>
       <c r="D4" s="87" t="s">
         <v>18</v>
@@ -10101,13 +10180,13 @@
         <v>11</v>
       </c>
       <c r="H4" s="281" t="s">
-        <v>1651</v>
+        <v>1637</v>
       </c>
       <c r="I4" s="274" t="s">
-        <v>1303</v>
+        <v>1289</v>
       </c>
       <c r="J4" s="275" t="s">
-        <v>1366</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10118,7 +10197,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>1471</v>
+        <v>1457</v>
       </c>
       <c r="D5" s="98" t="s">
         <v>20</v>
@@ -10133,13 +10212,13 @@
         <v>16</v>
       </c>
       <c r="H5" s="281" t="s">
-        <v>1591</v>
+        <v>1577</v>
       </c>
       <c r="I5" s="87" t="s">
-        <v>1304</v>
+        <v>1290</v>
       </c>
       <c r="J5" s="99" t="s">
-        <v>1367</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10150,7 +10229,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>1472</v>
+        <v>1458</v>
       </c>
       <c r="D6" s="98" t="s">
         <v>22</v>
@@ -10165,13 +10244,13 @@
         <v>16</v>
       </c>
       <c r="H6" s="281" t="s">
-        <v>1588</v>
+        <v>1574</v>
       </c>
       <c r="I6" s="274" t="s">
-        <v>1305</v>
+        <v>1291</v>
       </c>
       <c r="J6" s="275" t="s">
-        <v>1368</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10182,7 +10261,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="92" t="s">
-        <v>1473</v>
+        <v>1459</v>
       </c>
       <c r="D7" s="98" t="s">
         <v>25</v>
@@ -10197,13 +10276,13 @@
         <v>16</v>
       </c>
       <c r="H7" s="281" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="I7" s="87" t="s">
-        <v>1306</v>
+        <v>1292</v>
       </c>
       <c r="J7" s="99" t="s">
-        <v>1369</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10214,7 +10293,7 @@
         <v>27</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>1474</v>
+        <v>1460</v>
       </c>
       <c r="D8" s="98" t="s">
         <v>28</v>
@@ -10229,13 +10308,13 @@
         <v>11</v>
       </c>
       <c r="H8" s="281" t="s">
-        <v>1593</v>
+        <v>1579</v>
       </c>
       <c r="I8" s="274" t="s">
-        <v>1307</v>
+        <v>1293</v>
       </c>
       <c r="J8" s="275" t="s">
-        <v>1370</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10246,7 +10325,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>1475</v>
+        <v>1461</v>
       </c>
       <c r="D9" s="100" t="s">
         <v>30</v>
@@ -10261,13 +10340,13 @@
         <v>11</v>
       </c>
       <c r="H9" s="283" t="s">
-        <v>1594</v>
+        <v>1580</v>
       </c>
       <c r="I9" s="88" t="s">
-        <v>1308</v>
+        <v>1294</v>
       </c>
       <c r="J9" s="101" t="s">
-        <v>1371</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10278,7 +10357,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="289" t="s">
-        <v>1476</v>
+        <v>1462</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>32</v>
@@ -10293,13 +10372,13 @@
         <v>16</v>
       </c>
       <c r="H10" s="286" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="I10" s="287" t="s">
-        <v>1309</v>
+        <v>1295</v>
       </c>
       <c r="J10" s="288" t="s">
-        <v>1372</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10310,7 +10389,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>1477</v>
+        <v>1463</v>
       </c>
       <c r="D11" s="87" t="s">
         <v>35</v>
@@ -10325,13 +10404,13 @@
         <v>36</v>
       </c>
       <c r="H11" s="281" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
       <c r="I11" s="87" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="99" t="s">
-        <v>1373</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10342,7 +10421,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="98" t="s">
-        <v>1478</v>
+        <v>1464</v>
       </c>
       <c r="D12" s="87" t="s">
         <v>39</v>
@@ -10357,13 +10436,13 @@
         <v>36</v>
       </c>
       <c r="H12" s="281" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="I12" s="274" t="s">
-        <v>1310</v>
+        <v>1296</v>
       </c>
       <c r="J12" s="275" t="s">
-        <v>1374</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10374,7 +10453,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="98" t="s">
-        <v>1479</v>
+        <v>1465</v>
       </c>
       <c r="D13" s="87" t="s">
         <v>41</v>
@@ -10389,13 +10468,13 @@
         <v>16</v>
       </c>
       <c r="H13" s="281" t="s">
-        <v>1596</v>
+        <v>1582</v>
       </c>
       <c r="I13" s="87" t="s">
-        <v>1311</v>
+        <v>1297</v>
       </c>
       <c r="J13" s="99" t="s">
-        <v>1375</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10406,7 +10485,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>1480</v>
+        <v>1466</v>
       </c>
       <c r="D14" s="87" t="s">
         <v>43</v>
@@ -10421,13 +10500,13 @@
         <v>11</v>
       </c>
       <c r="H14" s="281" t="s">
-        <v>1601</v>
+        <v>1587</v>
       </c>
       <c r="I14" s="274" t="s">
-        <v>1312</v>
+        <v>1298</v>
       </c>
       <c r="J14" s="275" t="s">
-        <v>1376</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10438,7 +10517,7 @@
         <v>44</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>1481</v>
+        <v>1467</v>
       </c>
       <c r="D15" s="87" t="s">
         <v>45</v>
@@ -10453,13 +10532,13 @@
         <v>36</v>
       </c>
       <c r="H15" s="281" t="s">
-        <v>1595</v>
+        <v>1581</v>
       </c>
       <c r="I15" s="87" t="s">
-        <v>1313</v>
+        <v>1299</v>
       </c>
       <c r="J15" s="99" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10470,7 +10549,7 @@
         <v>46</v>
       </c>
       <c r="C16" s="98" t="s">
-        <v>1482</v>
+        <v>1468</v>
       </c>
       <c r="D16" s="87" t="s">
         <v>47</v>
@@ -10485,13 +10564,13 @@
         <v>16</v>
       </c>
       <c r="H16" s="281" t="s">
-        <v>1602</v>
+        <v>1588</v>
       </c>
       <c r="I16" s="274" t="s">
-        <v>1314</v>
+        <v>1300</v>
       </c>
       <c r="J16" s="275" t="s">
-        <v>1378</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10502,7 +10581,7 @@
         <v>48</v>
       </c>
       <c r="C17" s="100" t="s">
-        <v>1483</v>
+        <v>1469</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>49</v>
@@ -10517,13 +10596,13 @@
         <v>36</v>
       </c>
       <c r="H17" s="283" t="s">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="I17" s="88" t="s">
-        <v>1315</v>
+        <v>1301</v>
       </c>
       <c r="J17" s="101" t="s">
-        <v>1379</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10549,13 +10628,13 @@
         <v>11</v>
       </c>
       <c r="H18" s="286" t="s">
-        <v>1603</v>
+        <v>1589</v>
       </c>
       <c r="I18" s="287" t="s">
-        <v>1316</v>
+        <v>1302</v>
       </c>
       <c r="J18" s="288" t="s">
-        <v>1380</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10566,7 +10645,7 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1484</v>
+        <v>1470</v>
       </c>
       <c r="D19" s="87" t="s">
         <v>55</v>
@@ -10581,13 +10660,13 @@
         <v>11</v>
       </c>
       <c r="H19" s="281" t="s">
-        <v>1604</v>
+        <v>1590</v>
       </c>
       <c r="I19" s="87" t="s">
-        <v>1317</v>
+        <v>1303</v>
       </c>
       <c r="J19" s="99" t="s">
-        <v>1381</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10598,7 +10677,7 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1485</v>
+        <v>1471</v>
       </c>
       <c r="D20" s="87" t="s">
         <v>57</v>
@@ -10613,13 +10692,13 @@
         <v>36</v>
       </c>
       <c r="H20" s="281" t="s">
-        <v>1610</v>
+        <v>1596</v>
       </c>
       <c r="I20" s="274" t="s">
-        <v>1318</v>
+        <v>1304</v>
       </c>
       <c r="J20" s="275" t="s">
-        <v>1382</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10630,7 +10709,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1486</v>
+        <v>1472</v>
       </c>
       <c r="D21" s="87" t="s">
         <v>59</v>
@@ -10645,13 +10724,13 @@
         <v>36</v>
       </c>
       <c r="H21" s="281" t="s">
-        <v>1605</v>
+        <v>1591</v>
       </c>
       <c r="I21" s="87" t="s">
-        <v>1319</v>
+        <v>1305</v>
       </c>
       <c r="J21" s="99" t="s">
-        <v>1383</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10662,7 +10741,7 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1487</v>
+        <v>1473</v>
       </c>
       <c r="D22" s="87" t="s">
         <v>61</v>
@@ -10677,13 +10756,13 @@
         <v>11</v>
       </c>
       <c r="H22" s="281" t="s">
-        <v>1606</v>
+        <v>1592</v>
       </c>
       <c r="I22" s="274" t="s">
-        <v>1320</v>
+        <v>1306</v>
       </c>
       <c r="J22" s="275" t="s">
-        <v>1384</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10694,7 +10773,7 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1488</v>
+        <v>1474</v>
       </c>
       <c r="D23" s="87" t="s">
         <v>63</v>
@@ -10709,13 +10788,13 @@
         <v>11</v>
       </c>
       <c r="H23" s="281" t="s">
-        <v>1607</v>
+        <v>1593</v>
       </c>
       <c r="I23" s="87" t="s">
-        <v>1321</v>
+        <v>1307</v>
       </c>
       <c r="J23" s="99" t="s">
-        <v>1385</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10726,7 +10805,7 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1489</v>
+        <v>1475</v>
       </c>
       <c r="D24" s="87" t="s">
         <v>65</v>
@@ -10741,13 +10820,13 @@
         <v>16</v>
       </c>
       <c r="H24" s="281" t="s">
-        <v>1608</v>
+        <v>1594</v>
       </c>
       <c r="I24" s="274" t="s">
-        <v>1322</v>
+        <v>1308</v>
       </c>
       <c r="J24" s="275" t="s">
-        <v>1386</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10758,7 +10837,7 @@
         <v>66</v>
       </c>
       <c r="C25" s="89" t="s">
-        <v>1490</v>
+        <v>1476</v>
       </c>
       <c r="D25" s="89" t="s">
         <v>67</v>
@@ -10773,13 +10852,13 @@
         <v>11</v>
       </c>
       <c r="H25" s="290" t="s">
-        <v>1609</v>
+        <v>1595</v>
       </c>
       <c r="I25" s="89" t="s">
-        <v>1323</v>
+        <v>1309</v>
       </c>
       <c r="J25" s="112" t="s">
-        <v>1387</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10790,7 +10869,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1491</v>
+        <v>1477</v>
       </c>
       <c r="D26" s="86" t="s">
         <v>69</v>
@@ -10805,13 +10884,13 @@
         <v>11</v>
       </c>
       <c r="H26" s="282" t="s">
-        <v>1611</v>
+        <v>1597</v>
       </c>
       <c r="I26" s="272" t="s">
-        <v>1324</v>
+        <v>1310</v>
       </c>
       <c r="J26" s="273" t="s">
-        <v>1388</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10822,7 +10901,7 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1492</v>
+        <v>1478</v>
       </c>
       <c r="D27" s="87" t="s">
         <v>72</v>
@@ -10837,13 +10916,13 @@
         <v>11</v>
       </c>
       <c r="H27" s="281" t="s">
-        <v>1613</v>
+        <v>1599</v>
       </c>
       <c r="I27" s="87" t="s">
-        <v>1325</v>
+        <v>1311</v>
       </c>
       <c r="J27" s="99" t="s">
-        <v>1389</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10854,7 +10933,7 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1493</v>
+        <v>1479</v>
       </c>
       <c r="D28" s="87" t="s">
         <v>74</v>
@@ -10869,13 +10948,13 @@
         <v>16</v>
       </c>
       <c r="H28" s="281" t="s">
-        <v>1612</v>
+        <v>1598</v>
       </c>
       <c r="I28" s="274" t="s">
-        <v>1326</v>
+        <v>1312</v>
       </c>
       <c r="J28" s="275" t="s">
-        <v>1390</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10886,7 +10965,7 @@
         <v>75</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>1494</v>
+        <v>1480</v>
       </c>
       <c r="D29" s="87" t="s">
         <v>76</v>
@@ -10901,13 +10980,13 @@
         <v>16</v>
       </c>
       <c r="H29" s="281" t="s">
-        <v>1614</v>
+        <v>1600</v>
       </c>
       <c r="I29" s="87" t="s">
-        <v>1327</v>
+        <v>1313</v>
       </c>
       <c r="J29" s="99" t="s">
-        <v>1391</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10918,7 +10997,7 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1495</v>
+        <v>1481</v>
       </c>
       <c r="D30" s="87" t="s">
         <v>78</v>
@@ -10933,13 +11012,13 @@
         <v>11</v>
       </c>
       <c r="H30" s="281" t="s">
-        <v>1615</v>
+        <v>1601</v>
       </c>
       <c r="I30" s="274" t="s">
-        <v>1328</v>
+        <v>1314</v>
       </c>
       <c r="J30" s="275" t="s">
-        <v>1392</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10950,7 +11029,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1496</v>
+        <v>1482</v>
       </c>
       <c r="D31" s="87" t="s">
         <v>80</v>
@@ -10965,13 +11044,13 @@
         <v>16</v>
       </c>
       <c r="H31" s="281" t="s">
-        <v>1616</v>
+        <v>1602</v>
       </c>
       <c r="I31" s="87" t="s">
-        <v>1329</v>
+        <v>1315</v>
       </c>
       <c r="J31" s="99" t="s">
-        <v>1393</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10982,7 +11061,7 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1497</v>
+        <v>1483</v>
       </c>
       <c r="D32" s="87" t="s">
         <v>82</v>
@@ -10997,13 +11076,13 @@
         <v>16</v>
       </c>
       <c r="H32" s="281" t="s">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="I32" s="274" t="s">
-        <v>1330</v>
+        <v>1316</v>
       </c>
       <c r="J32" s="275" t="s">
-        <v>1394</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11014,7 +11093,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="89" t="s">
-        <v>1498</v>
+        <v>1484</v>
       </c>
       <c r="D33" s="89" t="s">
         <v>84</v>
@@ -11029,13 +11108,13 @@
         <v>16</v>
       </c>
       <c r="H33" s="290" t="s">
-        <v>1617</v>
+        <v>1603</v>
       </c>
       <c r="I33" s="89" t="s">
-        <v>1331</v>
+        <v>1317</v>
       </c>
       <c r="J33" s="112" t="s">
-        <v>1395</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11046,7 +11125,7 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1499</v>
+        <v>1485</v>
       </c>
       <c r="D34" s="86" t="s">
         <v>86</v>
@@ -11061,13 +11140,13 @@
         <v>16</v>
       </c>
       <c r="H34" s="282" t="s">
-        <v>1619</v>
+        <v>1605</v>
       </c>
       <c r="I34" s="272" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="J34" s="273" t="s">
-        <v>1396</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11078,7 +11157,7 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1500</v>
+        <v>1486</v>
       </c>
       <c r="D35" s="87" t="s">
         <v>89</v>
@@ -11093,13 +11172,13 @@
         <v>11</v>
       </c>
       <c r="H35" s="281" t="s">
-        <v>1620</v>
+        <v>1606</v>
       </c>
       <c r="I35" s="87" t="s">
-        <v>1333</v>
+        <v>1319</v>
       </c>
       <c r="J35" s="99" t="s">
-        <v>1397</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11110,7 +11189,7 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1501</v>
+        <v>1487</v>
       </c>
       <c r="D36" s="87" t="s">
         <v>91</v>
@@ -11125,13 +11204,13 @@
         <v>11</v>
       </c>
       <c r="H36" s="281" t="s">
-        <v>1621</v>
+        <v>1607</v>
       </c>
       <c r="I36" s="274" t="s">
-        <v>1334</v>
+        <v>1320</v>
       </c>
       <c r="J36" s="275" t="s">
-        <v>1398</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11142,7 +11221,7 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1502</v>
+        <v>1488</v>
       </c>
       <c r="D37" s="87" t="s">
         <v>93</v>
@@ -11157,13 +11236,13 @@
         <v>11</v>
       </c>
       <c r="H37" s="281" t="s">
-        <v>1622</v>
+        <v>1608</v>
       </c>
       <c r="I37" s="87" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="J37" s="99" t="s">
-        <v>1399</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11189,13 +11268,13 @@
         <v>11</v>
       </c>
       <c r="H38" s="281" t="s">
-        <v>1623</v>
+        <v>1609</v>
       </c>
       <c r="I38" s="274" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
       <c r="J38" s="275" t="s">
-        <v>1400</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11206,7 +11285,7 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1503</v>
+        <v>1489</v>
       </c>
       <c r="D39" s="87" t="s">
         <v>98</v>
@@ -11221,13 +11300,13 @@
         <v>16</v>
       </c>
       <c r="H39" s="281" t="s">
-        <v>1624</v>
+        <v>1610</v>
       </c>
       <c r="I39" s="87" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="J39" s="99" t="s">
-        <v>1401</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11238,7 +11317,7 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1504</v>
+        <v>1490</v>
       </c>
       <c r="D40" s="87" t="s">
         <v>100</v>
@@ -11253,13 +11332,13 @@
         <v>16</v>
       </c>
       <c r="H40" s="281" t="s">
-        <v>1625</v>
+        <v>1611</v>
       </c>
       <c r="I40" s="274" t="s">
-        <v>1338</v>
+        <v>1324</v>
       </c>
       <c r="J40" s="275" t="s">
-        <v>1402</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11270,7 +11349,7 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1505</v>
+        <v>1491</v>
       </c>
       <c r="D41" s="88" t="s">
         <v>102</v>
@@ -11285,13 +11364,13 @@
         <v>36</v>
       </c>
       <c r="H41" s="283" t="s">
-        <v>1626</v>
+        <v>1612</v>
       </c>
       <c r="I41" s="88" t="s">
-        <v>1339</v>
+        <v>1325</v>
       </c>
       <c r="J41" s="101" t="s">
-        <v>1403</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11302,7 +11381,7 @@
         <v>103</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>1506</v>
+        <v>1492</v>
       </c>
       <c r="D42" s="37" t="s">
         <v>104</v>
@@ -11317,13 +11396,13 @@
         <v>11</v>
       </c>
       <c r="H42" s="286" t="s">
-        <v>1630</v>
+        <v>1616</v>
       </c>
       <c r="I42" s="287" t="s">
         <v>106</v>
       </c>
       <c r="J42" s="288" t="s">
-        <v>1404</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11334,7 +11413,7 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1507</v>
+        <v>1493</v>
       </c>
       <c r="D43" s="87" t="s">
         <v>108</v>
@@ -11349,13 +11428,13 @@
         <v>36</v>
       </c>
       <c r="H43" s="281" t="s">
-        <v>1629</v>
+        <v>1615</v>
       </c>
       <c r="I43" s="87" t="s">
-        <v>1340</v>
+        <v>1326</v>
       </c>
       <c r="J43" s="99" t="s">
-        <v>1405</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11366,7 +11445,7 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1508</v>
+        <v>1494</v>
       </c>
       <c r="D44" s="87" t="s">
         <v>110</v>
@@ -11381,13 +11460,13 @@
         <v>16</v>
       </c>
       <c r="H44" s="281" t="s">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="I44" s="274" t="s">
-        <v>1341</v>
+        <v>1327</v>
       </c>
       <c r="J44" s="275" t="s">
-        <v>1406</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11398,7 +11477,7 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1509</v>
+        <v>1495</v>
       </c>
       <c r="D45" s="87" t="s">
         <v>112</v>
@@ -11413,13 +11492,13 @@
         <v>16</v>
       </c>
       <c r="H45" s="281" t="s">
-        <v>1631</v>
+        <v>1617</v>
       </c>
       <c r="I45" s="87" t="s">
-        <v>1342</v>
+        <v>1328</v>
       </c>
       <c r="J45" s="99" t="s">
-        <v>1407</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11430,7 +11509,7 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1510</v>
+        <v>1496</v>
       </c>
       <c r="D46" s="87" t="s">
         <v>114</v>
@@ -11445,13 +11524,13 @@
         <v>16</v>
       </c>
       <c r="H46" s="281" t="s">
-        <v>1627</v>
+        <v>1613</v>
       </c>
       <c r="I46" s="274" t="s">
-        <v>1343</v>
+        <v>1329</v>
       </c>
       <c r="J46" s="275" t="s">
-        <v>1408</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11462,7 +11541,7 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1511</v>
+        <v>1497</v>
       </c>
       <c r="D47" s="87" t="s">
         <v>116</v>
@@ -11477,13 +11556,13 @@
         <v>16</v>
       </c>
       <c r="H47" s="281" t="s">
-        <v>1634</v>
+        <v>1620</v>
       </c>
       <c r="I47" s="87" t="s">
-        <v>1344</v>
+        <v>1330</v>
       </c>
       <c r="J47" s="99" t="s">
-        <v>1409</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11494,7 +11573,7 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1512</v>
+        <v>1498</v>
       </c>
       <c r="D48" s="87" t="s">
         <v>118</v>
@@ -11509,13 +11588,13 @@
         <v>16</v>
       </c>
       <c r="H48" s="281" t="s">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="I48" s="274" t="s">
-        <v>1345</v>
+        <v>1331</v>
       </c>
       <c r="J48" s="275" t="s">
-        <v>1410</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11541,13 +11620,13 @@
         <v>16</v>
       </c>
       <c r="H49" s="283" t="s">
-        <v>1628</v>
+        <v>1614</v>
       </c>
       <c r="I49" s="88" t="s">
-        <v>1346</v>
+        <v>1332</v>
       </c>
       <c r="J49" s="101" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11573,13 +11652,13 @@
         <v>36</v>
       </c>
       <c r="H50" s="286" t="s">
-        <v>1790</v>
+        <v>1776</v>
       </c>
       <c r="I50" s="287" t="s">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="J50" s="288" t="s">
-        <v>1412</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11605,13 +11684,13 @@
         <v>36</v>
       </c>
       <c r="H51" s="281" t="s">
-        <v>1789</v>
+        <v>1775</v>
       </c>
       <c r="I51" s="87" t="s">
-        <v>1348</v>
+        <v>1334</v>
       </c>
       <c r="J51" s="99" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11637,13 +11716,13 @@
         <v>16</v>
       </c>
       <c r="H52" s="281" t="s">
-        <v>1785</v>
+        <v>1771</v>
       </c>
       <c r="I52" s="274" t="s">
-        <v>1836</v>
+        <v>1822</v>
       </c>
       <c r="J52" s="275" t="s">
-        <v>1414</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11669,13 +11748,13 @@
         <v>16</v>
       </c>
       <c r="H53" s="281" t="s">
-        <v>1635</v>
+        <v>1621</v>
       </c>
       <c r="I53" s="87" t="s">
-        <v>1349</v>
+        <v>1335</v>
       </c>
       <c r="J53" s="99" t="s">
-        <v>1415</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11686,7 +11765,7 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1513</v>
+        <v>1499</v>
       </c>
       <c r="D54" s="87" t="s">
         <v>136</v>
@@ -11701,13 +11780,13 @@
         <v>11</v>
       </c>
       <c r="H54" s="281" t="s">
-        <v>1809</v>
+        <v>1795</v>
       </c>
       <c r="I54" s="274" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
       <c r="J54" s="275" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11733,13 +11812,13 @@
         <v>16</v>
       </c>
       <c r="H55" s="281" t="s">
-        <v>1637</v>
+        <v>1623</v>
       </c>
       <c r="I55" s="87" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="J55" s="99" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11765,13 +11844,13 @@
         <v>16</v>
       </c>
       <c r="H56" s="281" t="s">
-        <v>1638</v>
+        <v>1624</v>
       </c>
       <c r="I56" s="274" t="s">
-        <v>1352</v>
+        <v>1338</v>
       </c>
       <c r="J56" s="275" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11797,13 +11876,13 @@
         <v>16</v>
       </c>
       <c r="H57" s="283" t="s">
-        <v>1636</v>
+        <v>1622</v>
       </c>
       <c r="I57" s="88" t="s">
-        <v>1353</v>
+        <v>1339</v>
       </c>
       <c r="J57" s="101" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11814,7 +11893,7 @@
         <v>146</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="D58" s="37" t="s">
         <v>147</v>
@@ -11829,13 +11908,13 @@
         <v>11</v>
       </c>
       <c r="H58" s="286" t="s">
-        <v>1786</v>
+        <v>1772</v>
       </c>
       <c r="I58" s="287" t="s">
-        <v>1354</v>
+        <v>1340</v>
       </c>
       <c r="J58" s="288" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11846,7 +11925,7 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1515</v>
+        <v>1501</v>
       </c>
       <c r="D59" s="87" t="s">
         <v>150</v>
@@ -11861,13 +11940,13 @@
         <v>36</v>
       </c>
       <c r="H59" s="281" t="s">
-        <v>1787</v>
+        <v>1773</v>
       </c>
       <c r="I59" s="87" t="s">
-        <v>1355</v>
+        <v>1341</v>
       </c>
       <c r="J59" s="99" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11878,7 +11957,7 @@
         <v>151</v>
       </c>
       <c r="C60" s="98" t="s">
-        <v>1516</v>
+        <v>1502</v>
       </c>
       <c r="D60" s="93" t="s">
         <v>152</v>
@@ -11893,13 +11972,13 @@
         <v>153</v>
       </c>
       <c r="H60" s="281" t="s">
-        <v>1797</v>
+        <v>1783</v>
       </c>
       <c r="I60" s="274" t="s">
-        <v>1356</v>
+        <v>1342</v>
       </c>
       <c r="J60" s="275" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11910,7 +11989,7 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1517</v>
+        <v>1503</v>
       </c>
       <c r="D61" s="87" t="s">
         <v>155</v>
@@ -11925,13 +12004,13 @@
         <v>11</v>
       </c>
       <c r="H61" s="281" t="s">
-        <v>1788</v>
+        <v>1774</v>
       </c>
       <c r="I61" s="87" t="s">
-        <v>1357</v>
+        <v>1343</v>
       </c>
       <c r="J61" s="99" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11942,7 +12021,7 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D62" s="87" t="s">
         <v>157</v>
@@ -11957,13 +12036,13 @@
         <v>36</v>
       </c>
       <c r="H62" s="281" t="s">
-        <v>1796</v>
+        <v>1782</v>
       </c>
       <c r="I62" s="274" t="s">
-        <v>1358</v>
+        <v>1344</v>
       </c>
       <c r="J62" s="275" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11974,7 +12053,7 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1519</v>
+        <v>1505</v>
       </c>
       <c r="D63" s="87" t="s">
         <v>159</v>
@@ -11989,13 +12068,13 @@
         <v>16</v>
       </c>
       <c r="H63" s="281" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="I63" s="87" t="s">
-        <v>1359</v>
+        <v>1345</v>
       </c>
       <c r="J63" s="99" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12021,13 +12100,13 @@
         <v>36</v>
       </c>
       <c r="H64" s="281" t="s">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="I64" s="274" t="s">
-        <v>1360</v>
+        <v>1346</v>
       </c>
       <c r="J64" s="275" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12038,7 +12117,7 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="D65" s="88" t="s">
         <v>164</v>
@@ -12053,13 +12132,13 @@
         <v>16</v>
       </c>
       <c r="H65" s="283" t="s">
-        <v>1798</v>
+        <v>1784</v>
       </c>
       <c r="I65" s="88" t="s">
-        <v>1361</v>
+        <v>1347</v>
       </c>
       <c r="J65" s="101" t="s">
-        <v>1427</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12070,7 +12149,7 @@
         <v>165</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>1521</v>
+        <v>1507</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>166</v>
@@ -12085,13 +12164,13 @@
         <v>153</v>
       </c>
       <c r="H66" s="286" t="s">
-        <v>1795</v>
+        <v>1781</v>
       </c>
       <c r="I66" s="287" t="s">
-        <v>1648</v>
+        <v>1634</v>
       </c>
       <c r="J66" s="288" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12102,7 +12181,7 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1522</v>
+        <v>1508</v>
       </c>
       <c r="D67" s="87" t="s">
         <v>35</v>
@@ -12117,13 +12196,13 @@
         <v>153</v>
       </c>
       <c r="H67" s="281" t="s">
-        <v>1794</v>
+        <v>1780</v>
       </c>
       <c r="I67" s="87" t="s">
-        <v>1649</v>
+        <v>1635</v>
       </c>
       <c r="J67" s="99" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12131,13 +12210,13 @@
         <v>0</v>
       </c>
       <c r="B68" s="88" t="s">
-        <v>1294</v>
+        <v>1280</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1523</v>
+        <v>1509</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>1645</v>
+        <v>1631</v>
       </c>
       <c r="E68" s="88" t="s">
         <v>167</v>
@@ -12149,13 +12228,13 @@
         <v>153</v>
       </c>
       <c r="H68" s="283" t="s">
-        <v>1641</v>
+        <v>1627</v>
       </c>
       <c r="I68" s="276" t="s">
-        <v>1362</v>
+        <v>1348</v>
       </c>
       <c r="J68" s="277" t="s">
-        <v>1642</v>
+        <v>1628</v>
       </c>
     </row>
   </sheetData>
@@ -12190,16 +12269,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="109" t="s">
-        <v>1647</v>
+        <v>1633</v>
       </c>
       <c r="D1" s="278" t="s">
-        <v>1652</v>
+        <v>1638</v>
       </c>
       <c r="E1" s="278" t="s">
-        <v>1653</v>
+        <v>1639</v>
       </c>
       <c r="F1" s="278" t="s">
-        <v>1750</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12210,13 +12289,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1683</v>
+        <v>1669</v>
       </c>
       <c r="D2" s="272" t="s">
-        <v>1684</v>
+        <v>1670</v>
       </c>
       <c r="E2" s="272" t="s">
-        <v>1654</v>
+        <v>1640</v>
       </c>
       <c r="F2" s="272"/>
     </row>
@@ -12228,13 +12307,13 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1655</v>
+        <v>1641</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>1689</v>
+        <v>1675</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1779</v>
+        <v>1765</v>
       </c>
       <c r="F3" s="87"/>
     </row>
@@ -12246,10 +12325,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1685</v>
+        <v>1671</v>
       </c>
       <c r="D4" s="274" t="s">
-        <v>1686</v>
+        <v>1672</v>
       </c>
       <c r="E4" s="274"/>
       <c r="F4" s="274"/>
@@ -12262,13 +12341,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1656</v>
+        <v>1642</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>1657</v>
+        <v>1643</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1687</v>
+        <v>1673</v>
       </c>
       <c r="F5" s="87"/>
     </row>
@@ -12280,13 +12359,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1658</v>
+        <v>1644</v>
       </c>
       <c r="D6" s="274" t="s">
-        <v>1659</v>
+        <v>1645</v>
       </c>
       <c r="E6" s="274" t="s">
-        <v>1663</v>
+        <v>1649</v>
       </c>
       <c r="F6" s="274"/>
     </row>
@@ -12298,13 +12377,13 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1660</v>
+        <v>1646</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>1690</v>
+        <v>1676</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>1664</v>
+        <v>1650</v>
       </c>
       <c r="F7" s="87"/>
     </row>
@@ -12316,10 +12395,10 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1766</v>
+        <v>1752</v>
       </c>
       <c r="D8" s="274" t="s">
-        <v>1661</v>
+        <v>1647</v>
       </c>
       <c r="E8" s="274"/>
       <c r="F8" s="274"/>
@@ -12332,10 +12411,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1688</v>
+        <v>1674</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>1662</v>
+        <v>1648</v>
       </c>
       <c r="E9" s="88"/>
       <c r="F9" s="88"/>
@@ -12348,10 +12427,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1665</v>
+        <v>1651</v>
       </c>
       <c r="D10" s="272" t="s">
-        <v>1666</v>
+        <v>1652</v>
       </c>
       <c r="E10" s="272"/>
       <c r="F10" s="272"/>
@@ -12364,13 +12443,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1667</v>
+        <v>1653</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1679</v>
+        <v>1665</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1668</v>
+        <v>1654</v>
       </c>
       <c r="F11" s="87"/>
     </row>
@@ -12382,13 +12461,13 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1670</v>
+        <v>1656</v>
       </c>
       <c r="D12" s="274" t="s">
-        <v>1671</v>
+        <v>1657</v>
       </c>
       <c r="E12" s="274" t="s">
-        <v>1669</v>
+        <v>1655</v>
       </c>
       <c r="F12" s="274"/>
     </row>
@@ -12400,16 +12479,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1681</v>
+        <v>1667</v>
       </c>
       <c r="D13" s="87" t="s">
-        <v>1672</v>
+        <v>1658</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1680</v>
+        <v>1666</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>1751</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12420,13 +12499,13 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1673</v>
+        <v>1659</v>
       </c>
       <c r="D14" s="274" t="s">
-        <v>1299</v>
+        <v>1285</v>
       </c>
       <c r="E14" s="274" t="s">
-        <v>1674</v>
+        <v>1660</v>
       </c>
       <c r="F14" s="274"/>
     </row>
@@ -12438,10 +12517,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1682</v>
+        <v>1668</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>1675</v>
+        <v>1661</v>
       </c>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
@@ -12454,13 +12533,13 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1676</v>
+        <v>1662</v>
       </c>
       <c r="D16" s="274" t="s">
-        <v>1677</v>
+        <v>1663</v>
       </c>
       <c r="E16" s="274" t="s">
-        <v>1674</v>
+        <v>1660</v>
       </c>
       <c r="F16" s="274"/>
     </row>
@@ -12472,10 +12551,10 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1691</v>
+        <v>1677</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>1678</v>
+        <v>1664</v>
       </c>
       <c r="E17" s="88"/>
       <c r="F17" s="88"/>
@@ -12488,13 +12567,13 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1695</v>
+        <v>1681</v>
       </c>
       <c r="D18" s="272" t="s">
-        <v>1696</v>
+        <v>1682</v>
       </c>
       <c r="E18" s="272" t="s">
-        <v>1692</v>
+        <v>1678</v>
       </c>
       <c r="F18" s="272"/>
     </row>
@@ -12506,13 +12585,13 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1704</v>
+        <v>1690</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>1705</v>
+        <v>1691</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>1709</v>
+        <v>1695</v>
       </c>
       <c r="F19" s="87"/>
     </row>
@@ -12524,13 +12603,13 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1697</v>
+        <v>1683</v>
       </c>
       <c r="D20" s="274" t="s">
-        <v>1698</v>
+        <v>1684</v>
       </c>
       <c r="E20" s="274" t="s">
-        <v>1714</v>
+        <v>1700</v>
       </c>
       <c r="F20" s="274"/>
     </row>
@@ -12542,13 +12621,13 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1706</v>
+        <v>1692</v>
       </c>
       <c r="D21" s="87" t="s">
-        <v>1699</v>
+        <v>1685</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1710</v>
+        <v>1696</v>
       </c>
       <c r="F21" s="87"/>
     </row>
@@ -12560,13 +12639,13 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1700</v>
+        <v>1686</v>
       </c>
       <c r="D22" s="274" t="s">
-        <v>1701</v>
+        <v>1687</v>
       </c>
       <c r="E22" s="274" t="s">
-        <v>1711</v>
+        <v>1697</v>
       </c>
       <c r="F22" s="274"/>
     </row>
@@ -12578,13 +12657,13 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1702</v>
+        <v>1688</v>
       </c>
       <c r="D23" s="87" t="s">
-        <v>1703</v>
+        <v>1689</v>
       </c>
       <c r="E23" s="87" t="s">
-        <v>1693</v>
+        <v>1679</v>
       </c>
       <c r="F23" s="87"/>
     </row>
@@ -12596,13 +12675,13 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1708</v>
+        <v>1694</v>
       </c>
       <c r="D24" s="274" t="s">
-        <v>1712</v>
+        <v>1698</v>
       </c>
       <c r="E24" s="274" t="s">
-        <v>1713</v>
+        <v>1699</v>
       </c>
       <c r="F24" s="274"/>
     </row>
@@ -12614,13 +12693,13 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1719</v>
+        <v>1705</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>1707</v>
+        <v>1693</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>1694</v>
+        <v>1680</v>
       </c>
       <c r="F25" s="88"/>
     </row>
@@ -12632,16 +12711,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1715</v>
+        <v>1701</v>
       </c>
       <c r="D26" s="272" t="s">
-        <v>1730</v>
+        <v>1716</v>
       </c>
       <c r="E26" s="272" t="s">
-        <v>1727</v>
+        <v>1713</v>
       </c>
       <c r="F26" s="272" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12652,16 +12731,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1716</v>
+        <v>1702</v>
       </c>
       <c r="D27" s="87" t="s">
-        <v>1717</v>
+        <v>1703</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1724</v>
+        <v>1710</v>
       </c>
       <c r="F27" s="87" t="s">
-        <v>1791</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12672,10 +12751,10 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1718</v>
+        <v>1704</v>
       </c>
       <c r="D28" s="274" t="s">
-        <v>1731</v>
+        <v>1717</v>
       </c>
       <c r="E28" s="274"/>
       <c r="F28" s="274"/>
@@ -12691,10 +12770,10 @@
         <v>560</v>
       </c>
       <c r="D29" s="87" t="s">
-        <v>1300</v>
+        <v>1286</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1725</v>
+        <v>1711</v>
       </c>
       <c r="F29" s="87"/>
     </row>
@@ -12706,13 +12785,13 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1720</v>
+        <v>1706</v>
       </c>
       <c r="D30" s="274" t="s">
-        <v>1721</v>
+        <v>1707</v>
       </c>
       <c r="E30" s="274" t="s">
-        <v>1728</v>
+        <v>1714</v>
       </c>
       <c r="F30" s="274"/>
     </row>
@@ -12724,7 +12803,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1732</v>
+        <v>1718</v>
       </c>
       <c r="D31" s="87"/>
       <c r="E31" s="87"/>
@@ -12738,13 +12817,13 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1722</v>
+        <v>1708</v>
       </c>
       <c r="D32" s="274" t="s">
-        <v>1723</v>
+        <v>1709</v>
       </c>
       <c r="E32" s="274" t="s">
-        <v>1726</v>
+        <v>1712</v>
       </c>
       <c r="F32" s="274"/>
     </row>
@@ -12756,11 +12835,11 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1813</v>
+        <v>1799</v>
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="88" t="s">
-        <v>1729</v>
+        <v>1715</v>
       </c>
       <c r="F33" s="88"/>
     </row>
@@ -12772,13 +12851,13 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1733</v>
+        <v>1719</v>
       </c>
       <c r="D34" s="272" t="s">
-        <v>1734</v>
+        <v>1720</v>
       </c>
       <c r="E34" s="272" t="s">
-        <v>1753</v>
+        <v>1739</v>
       </c>
       <c r="F34" s="272"/>
     </row>
@@ -12790,13 +12869,13 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1735</v>
+        <v>1721</v>
       </c>
       <c r="D35" s="87" t="s">
-        <v>1736</v>
+        <v>1722</v>
       </c>
       <c r="E35" s="87" t="s">
-        <v>1746</v>
+        <v>1732</v>
       </c>
       <c r="F35" s="87"/>
     </row>
@@ -12808,13 +12887,13 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1737</v>
+        <v>1723</v>
       </c>
       <c r="D36" s="274" t="s">
-        <v>1738</v>
+        <v>1724</v>
       </c>
       <c r="E36" s="274" t="s">
-        <v>1747</v>
+        <v>1733</v>
       </c>
       <c r="F36" s="274"/>
     </row>
@@ -12826,13 +12905,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1739</v>
+        <v>1725</v>
       </c>
       <c r="D37" s="87" t="s">
-        <v>1740</v>
+        <v>1726</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1783</v>
+        <v>1769</v>
       </c>
       <c r="F37" s="87"/>
     </row>
@@ -12844,16 +12923,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1741</v>
+        <v>1727</v>
       </c>
       <c r="D38" s="274" t="s">
-        <v>1769</v>
+        <v>1755</v>
       </c>
       <c r="E38" s="292" t="s">
-        <v>1752</v>
+        <v>1738</v>
       </c>
       <c r="F38" s="292" t="s">
-        <v>1792</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12864,13 +12943,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1742</v>
+        <v>1728</v>
       </c>
       <c r="D39" s="87" t="s">
-        <v>1743</v>
+        <v>1729</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1748</v>
+        <v>1734</v>
       </c>
       <c r="F39" s="87"/>
     </row>
@@ -12882,16 +12961,16 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1744</v>
+        <v>1730</v>
       </c>
       <c r="D40" s="274" t="s">
-        <v>1754</v>
+        <v>1740</v>
       </c>
       <c r="E40" s="274" t="s">
-        <v>1749</v>
+        <v>1735</v>
       </c>
       <c r="F40" s="274" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12902,13 +12981,13 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1745</v>
+        <v>1731</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>1770</v>
+        <v>1756</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>1771</v>
+        <v>1757</v>
       </c>
       <c r="F41" s="88"/>
     </row>
@@ -12920,16 +12999,16 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1755</v>
+        <v>1741</v>
       </c>
       <c r="D42" s="272" t="s">
-        <v>1756</v>
+        <v>1742</v>
       </c>
       <c r="E42" s="272" t="s">
-        <v>1782</v>
+        <v>1768</v>
       </c>
       <c r="F42" s="272" t="s">
-        <v>1793</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12940,13 +13019,13 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1765</v>
+        <v>1751</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>1757</v>
+        <v>1743</v>
       </c>
       <c r="E43" s="87" t="s">
-        <v>1775</v>
+        <v>1761</v>
       </c>
       <c r="F43" s="87"/>
     </row>
@@ -12958,13 +13037,13 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1758</v>
+        <v>1744</v>
       </c>
       <c r="D44" s="274" t="s">
-        <v>1759</v>
+        <v>1745</v>
       </c>
       <c r="E44" s="274" t="s">
-        <v>1774</v>
+        <v>1760</v>
       </c>
       <c r="F44" s="274"/>
     </row>
@@ -12976,13 +13055,13 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1760</v>
+        <v>1746</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>1767</v>
+        <v>1753</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1784</v>
+        <v>1770</v>
       </c>
       <c r="F45" s="87"/>
     </row>
@@ -12994,14 +13073,14 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1761</v>
+        <v>1747</v>
       </c>
       <c r="D46" s="274" t="s">
-        <v>1762</v>
+        <v>1748</v>
       </c>
       <c r="E46" s="274"/>
       <c r="F46" s="274" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13012,16 +13091,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1763</v>
+        <v>1749</v>
       </c>
       <c r="D47" s="87" t="s">
-        <v>1768</v>
+        <v>1754</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1781</v>
+        <v>1767</v>
       </c>
       <c r="F47" s="87" t="s">
-        <v>1791</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13032,12 +13111,12 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1772</v>
+        <v>1758</v>
       </c>
       <c r="D48" s="274"/>
       <c r="E48" s="274"/>
       <c r="F48" s="274" t="s">
-        <v>1777</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13048,13 +13127,13 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D49" s="88" t="s">
         <v>1764</v>
       </c>
-      <c r="D49" s="88" t="s">
-        <v>1778</v>
-      </c>
       <c r="E49" s="88" t="s">
-        <v>1773</v>
+        <v>1759</v>
       </c>
       <c r="F49" s="88"/>
     </row>
@@ -13066,14 +13145,14 @@
         <v>122</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>1799</v>
+        <v>1785</v>
       </c>
       <c r="D50" s="272"/>
       <c r="E50" s="272" t="s">
-        <v>1806</v>
+        <v>1792</v>
       </c>
       <c r="F50" s="272" t="s">
-        <v>1751</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13084,14 +13163,14 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1803</v>
+        <v>1789</v>
       </c>
       <c r="D51" s="87"/>
       <c r="E51" s="87" t="s">
-        <v>1807</v>
+        <v>1793</v>
       </c>
       <c r="F51" s="87" t="s">
-        <v>1751</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13102,14 +13181,14 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1808</v>
+        <v>1794</v>
       </c>
       <c r="D52" s="274"/>
       <c r="E52" s="274" t="s">
-        <v>1810</v>
+        <v>1796</v>
       </c>
       <c r="F52" s="274" t="s">
-        <v>1777</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13120,7 +13199,7 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1804</v>
+        <v>1790</v>
       </c>
       <c r="D53" s="87"/>
       <c r="E53" s="87"/>
@@ -13134,12 +13213,12 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1811</v>
+        <v>1797</v>
       </c>
       <c r="D54" s="274"/>
       <c r="E54" s="274"/>
       <c r="F54" s="274" t="s">
-        <v>1751</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13150,14 +13229,14 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1800</v>
+        <v>1786</v>
       </c>
       <c r="D55" s="87" t="s">
-        <v>1801</v>
+        <v>1787</v>
       </c>
       <c r="E55" s="87"/>
       <c r="F55" s="87" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13168,10 +13247,10 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1812</v>
+        <v>1798</v>
       </c>
       <c r="D56" s="274" t="s">
-        <v>1802</v>
+        <v>1788</v>
       </c>
       <c r="E56" s="274"/>
       <c r="F56" s="274"/>
@@ -13184,10 +13263,10 @@
         <v>143</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>1823</v>
+        <v>1809</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>1805</v>
+        <v>1791</v>
       </c>
       <c r="E57" s="88"/>
       <c r="F57" s="88"/>
@@ -13200,14 +13279,14 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1814</v>
+        <v>1800</v>
       </c>
       <c r="D58" s="272"/>
       <c r="E58" s="272" t="s">
-        <v>1826</v>
+        <v>1812</v>
       </c>
       <c r="F58" s="272" t="s">
-        <v>1751</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13218,14 +13297,14 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1815</v>
+        <v>1801</v>
       </c>
       <c r="D59" s="87"/>
       <c r="E59" s="87" t="s">
-        <v>1824</v>
+        <v>1810</v>
       </c>
       <c r="F59" s="87" t="s">
-        <v>1751</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13236,7 +13315,7 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1825</v>
+        <v>1811</v>
       </c>
       <c r="D60" s="274"/>
       <c r="E60" s="274"/>
@@ -13250,13 +13329,13 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1827</v>
+        <v>1813</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>1816</v>
+        <v>1802</v>
       </c>
       <c r="E61" s="87" t="s">
-        <v>1828</v>
+        <v>1814</v>
       </c>
       <c r="F61" s="87"/>
     </row>
@@ -13268,11 +13347,11 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1817</v>
+        <v>1803</v>
       </c>
       <c r="D62" s="274"/>
       <c r="E62" s="274" t="s">
-        <v>1828</v>
+        <v>1814</v>
       </c>
       <c r="F62" s="274"/>
     </row>
@@ -13284,10 +13363,10 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1818</v>
+        <v>1804</v>
       </c>
       <c r="D63" s="87" t="s">
-        <v>1819</v>
+        <v>1805</v>
       </c>
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
@@ -13300,12 +13379,12 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1820</v>
+        <v>1806</v>
       </c>
       <c r="D64" s="274"/>
       <c r="E64" s="274"/>
       <c r="F64" s="274" t="s">
-        <v>1780</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13316,16 +13395,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1821</v>
+        <v>1807</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>1822</v>
+        <v>1808</v>
       </c>
       <c r="E65" s="88" t="s">
-        <v>1726</v>
+        <v>1712</v>
       </c>
       <c r="F65" s="88" t="s">
-        <v>1726</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13336,12 +13415,12 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1829</v>
+        <v>1815</v>
       </c>
       <c r="D66" s="87"/>
       <c r="E66" s="87"/>
       <c r="F66" s="87" t="s">
-        <v>1832</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13352,14 +13431,14 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1830</v>
+        <v>1816</v>
       </c>
       <c r="D67" s="87"/>
       <c r="E67" s="87" t="s">
-        <v>1831</v>
+        <v>1817</v>
       </c>
       <c r="F67" s="87" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13367,17 +13446,17 @@
         <v>0</v>
       </c>
       <c r="B68" s="210" t="s">
-        <v>1294</v>
+        <v>1280</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1834</v>
+        <v>1820</v>
       </c>
       <c r="D68" s="276" t="s">
-        <v>1835</v>
+        <v>1821</v>
       </c>
       <c r="E68" s="276"/>
       <c r="F68" s="276" t="s">
-        <v>1833</v>
+        <v>1819</v>
       </c>
     </row>
   </sheetData>
@@ -13411,7 +13490,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="54" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="261" t="s">
-        <v>1530</v>
+        <v>1516</v>
       </c>
       <c r="B1" s="261" t="s">
         <v>537</v>
@@ -13429,68 +13508,68 @@
         <v>541</v>
       </c>
       <c r="G1" s="261" t="s">
-        <v>1574</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="262" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
       <c r="B2" s="263" t="s">
-        <v>1524</v>
+        <v>1510</v>
       </c>
       <c r="C2" s="263" t="s">
-        <v>1529</v>
+        <v>1515</v>
       </c>
       <c r="D2" s="263" t="s">
-        <v>1531</v>
+        <v>1517</v>
       </c>
       <c r="E2" s="263" t="s">
-        <v>1532</v>
+        <v>1518</v>
       </c>
       <c r="F2" s="263" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="G2" s="264" t="s">
-        <v>1575</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="167" t="s">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="B3" s="169" t="s">
-        <v>1552</v>
+        <v>1538</v>
       </c>
       <c r="C3" s="169" t="s">
-        <v>1533</v>
+        <v>1519</v>
       </c>
       <c r="D3" s="169" t="s">
-        <v>1534</v>
+        <v>1520</v>
       </c>
       <c r="E3" s="169" t="s">
-        <v>1535</v>
+        <v>1521</v>
       </c>
       <c r="F3" s="169" t="s">
         <v>542</v>
       </c>
       <c r="G3" s="170" t="s">
-        <v>1576</v>
+        <v>1562</v>
       </c>
       <c r="H3" s="265"/>
     </row>
     <row r="4" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="167" t="s">
-        <v>1558</v>
+        <v>1544</v>
       </c>
       <c r="B4" s="169" t="s">
-        <v>1525</v>
+        <v>1511</v>
       </c>
       <c r="C4" s="169" t="s">
-        <v>1536</v>
+        <v>1522</v>
       </c>
       <c r="D4" s="169" t="s">
-        <v>1537</v>
+        <v>1523</v>
       </c>
       <c r="E4" s="169" t="s">
         <v>543</v>
@@ -13499,145 +13578,145 @@
         <v>544</v>
       </c>
       <c r="G4" s="170" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="167" t="s">
-        <v>1559</v>
+        <v>1545</v>
       </c>
       <c r="B5" s="169" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C5" s="169" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D5" s="169" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E5" s="169" t="s">
         <v>1526</v>
-      </c>
-      <c r="C5" s="169" t="s">
-        <v>1538</v>
-      </c>
-      <c r="D5" s="169" t="s">
-        <v>1539</v>
-      </c>
-      <c r="E5" s="169" t="s">
-        <v>1540</v>
       </c>
       <c r="F5" s="169" t="s">
         <v>545</v>
       </c>
       <c r="G5" s="170" t="s">
-        <v>1578</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="167" t="s">
-        <v>1560</v>
+        <v>1546</v>
       </c>
       <c r="B6" s="169" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C6" s="169" t="s">
         <v>1527</v>
       </c>
-      <c r="C6" s="169" t="s">
-        <v>1541</v>
-      </c>
       <c r="D6" s="169" t="s">
-        <v>1542</v>
+        <v>1528</v>
       </c>
       <c r="E6" s="169" t="s">
-        <v>1543</v>
+        <v>1529</v>
       </c>
       <c r="F6" s="169" t="s">
         <v>546</v>
       </c>
       <c r="G6" s="170" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="167" t="s">
-        <v>1561</v>
+        <v>1547</v>
       </c>
       <c r="B7" s="169" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C7" s="169" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D7" s="169" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E7" s="169" t="s">
         <v>1553</v>
       </c>
-      <c r="C7" s="169" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D7" s="169" t="s">
+      <c r="F7" s="169" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G7" s="170" t="s">
         <v>1566</v>
-      </c>
-      <c r="E7" s="169" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F7" s="169" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G7" s="170" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="167" t="s">
-        <v>1562</v>
+        <v>1548</v>
       </c>
       <c r="B8" s="169" t="s">
-        <v>1528</v>
+        <v>1514</v>
       </c>
       <c r="C8" s="169" t="s">
-        <v>1544</v>
+        <v>1530</v>
       </c>
       <c r="D8" s="169" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="E8" s="169" t="s">
-        <v>1546</v>
+        <v>1532</v>
       </c>
       <c r="F8" s="169" t="s">
-        <v>1547</v>
+        <v>1533</v>
       </c>
       <c r="G8" s="170" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="167" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="B9" s="169" t="s">
-        <v>1554</v>
+        <v>1540</v>
       </c>
       <c r="C9" s="169" t="s">
-        <v>1569</v>
+        <v>1555</v>
       </c>
       <c r="D9" s="169" t="s">
-        <v>1573</v>
+        <v>1559</v>
       </c>
       <c r="E9" s="169" t="s">
-        <v>1571</v>
+        <v>1557</v>
       </c>
       <c r="F9" s="169" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="G9" s="170" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="175" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="B10" s="176" t="s">
-        <v>1555</v>
+        <v>1541</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>1548</v>
+        <v>1534</v>
       </c>
       <c r="D10" s="176" t="s">
-        <v>1549</v>
+        <v>1535</v>
       </c>
       <c r="E10" s="176" t="s">
-        <v>1550</v>
+        <v>1536</v>
       </c>
       <c r="F10" s="176" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="G10" s="178" t="s">
-        <v>1583</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -13717,10 +13796,10 @@
     <row r="20" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:3" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="266" t="s">
-        <v>1643</v>
+        <v>1629</v>
       </c>
       <c r="B21" s="267" t="s">
-        <v>1644</v>
+        <v>1630</v>
       </c>
     </row>
   </sheetData>
@@ -14539,7 +14618,7 @@
         <v>282</v>
       </c>
       <c r="D57" s="247" t="s">
-        <v>1297</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14687,13 +14766,13 @@
         <v>0</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>1295</v>
+        <v>1281</v>
       </c>
       <c r="C68" s="101" t="s">
-        <v>1296</v>
+        <v>1282</v>
       </c>
       <c r="D68" s="244" t="s">
-        <v>1298</v>
+        <v>1284</v>
       </c>
     </row>
   </sheetData>
@@ -16249,16 +16328,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="D2" s="97" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="F2" s="97" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16269,16 +16348,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="D3" s="99" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
       <c r="F3" s="99" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16289,16 +16368,16 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="D4" s="99" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="E4" s="87" t="s">
-        <v>1038</v>
+        <v>1024</v>
       </c>
       <c r="F4" s="99" t="s">
-        <v>1039</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16309,16 +16388,16 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1040</v>
+        <v>1026</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>1041</v>
+        <v>1027</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1042</v>
+        <v>1028</v>
       </c>
       <c r="F5" s="99" t="s">
-        <v>1043</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16329,16 +16408,16 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1044</v>
+        <v>1030</v>
       </c>
       <c r="D6" s="99" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="E6" s="87" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
       <c r="F6" s="99" t="s">
-        <v>1047</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16349,16 +16428,16 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="D7" s="99" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>1050</v>
+        <v>1036</v>
       </c>
       <c r="F7" s="99" t="s">
-        <v>1051</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16369,16 +16448,16 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1052</v>
+        <v>1038</v>
       </c>
       <c r="D8" s="99" t="s">
-        <v>1053</v>
+        <v>1039</v>
       </c>
       <c r="E8" s="87" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="F8" s="99" t="s">
-        <v>1055</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16389,16 +16468,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="D9" s="101" t="s">
-        <v>1057</v>
+        <v>1043</v>
       </c>
       <c r="E9" s="89" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="F9" s="112" t="s">
-        <v>1059</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16409,16 +16488,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1060</v>
+        <v>1046</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>1061</v>
+        <v>1047</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>1062</v>
+        <v>1048</v>
       </c>
       <c r="F10" s="97" t="s">
-        <v>1063</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16429,16 +16508,16 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="D11" s="99" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
       <c r="F11" s="99" t="s">
-        <v>1067</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16449,16 +16528,16 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1068</v>
+        <v>1054</v>
       </c>
       <c r="D12" s="99" t="s">
-        <v>1069</v>
+        <v>1055</v>
       </c>
       <c r="E12" s="87" t="s">
-        <v>1070</v>
+        <v>1056</v>
       </c>
       <c r="F12" s="99" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16469,16 +16548,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1072</v>
+        <v>1058</v>
       </c>
       <c r="D13" s="99" t="s">
-        <v>1073</v>
+        <v>1059</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1074</v>
+        <v>1060</v>
       </c>
       <c r="F13" s="99" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16489,16 +16568,16 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1076</v>
+        <v>1062</v>
       </c>
       <c r="D14" s="99" t="s">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="E14" s="87" t="s">
-        <v>1078</v>
+        <v>1064</v>
       </c>
       <c r="F14" s="99" t="s">
-        <v>1079</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16509,16 +16588,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1080</v>
+        <v>1066</v>
       </c>
       <c r="D15" s="99" t="s">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="E15" s="87" t="s">
-        <v>1082</v>
+        <v>1068</v>
       </c>
       <c r="F15" s="99" t="s">
-        <v>1083</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16529,16 +16608,16 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1084</v>
+        <v>1070</v>
       </c>
       <c r="D16" s="99" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>1086</v>
+        <v>1072</v>
       </c>
       <c r="F16" s="99" t="s">
-        <v>1087</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16549,16 +16628,16 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1088</v>
+        <v>1074</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>1089</v>
+        <v>1075</v>
       </c>
       <c r="E17" s="88" t="s">
-        <v>1090</v>
+        <v>1076</v>
       </c>
       <c r="F17" s="158" t="s">
-        <v>1091</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16569,16 +16648,16 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1092</v>
+        <v>1078</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>1095</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16589,16 +16668,16 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1096</v>
+        <v>1082</v>
       </c>
       <c r="D19" s="99" t="s">
-        <v>1097</v>
+        <v>1083</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="F19" s="99" t="s">
-        <v>1099</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16609,16 +16688,16 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1100</v>
+        <v>1086</v>
       </c>
       <c r="D20" s="99" t="s">
-        <v>1101</v>
+        <v>1087</v>
       </c>
       <c r="E20" s="87" t="s">
-        <v>1102</v>
+        <v>1088</v>
       </c>
       <c r="F20" s="99" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16629,16 +16708,16 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1104</v>
+        <v>1090</v>
       </c>
       <c r="D21" s="99" t="s">
-        <v>1105</v>
+        <v>1091</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1106</v>
+        <v>1092</v>
       </c>
       <c r="F21" s="99" t="s">
-        <v>1107</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16649,16 +16728,16 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1108</v>
+        <v>1094</v>
       </c>
       <c r="D22" s="99" t="s">
-        <v>1109</v>
+        <v>1095</v>
       </c>
       <c r="E22" s="87" t="s">
-        <v>1110</v>
+        <v>1096</v>
       </c>
       <c r="F22" s="99" t="s">
-        <v>1111</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16669,16 +16748,16 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1112</v>
+        <v>1098</v>
       </c>
       <c r="D23" s="99" t="s">
-        <v>1113</v>
+        <v>1099</v>
       </c>
       <c r="E23" s="87" t="s">
-        <v>1114</v>
+        <v>1100</v>
       </c>
       <c r="F23" s="99" t="s">
-        <v>1115</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16689,19 +16768,19 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="D24" s="99" t="s">
-        <v>1117</v>
+        <v>1103</v>
       </c>
       <c r="E24" s="87" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>1119</v>
+        <v>1105</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1120</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16712,16 +16791,16 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="D25" s="101" t="s">
-        <v>1122</v>
+        <v>1108</v>
       </c>
       <c r="E25" s="89" t="s">
-        <v>1123</v>
+        <v>1109</v>
       </c>
       <c r="F25" s="112" t="s">
-        <v>1124</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16732,16 +16811,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1125</v>
+        <v>1111</v>
       </c>
       <c r="D26" s="97" t="s">
-        <v>1126</v>
+        <v>1112</v>
       </c>
       <c r="E26" s="86" t="s">
-        <v>1127</v>
+        <v>1113</v>
       </c>
       <c r="F26" s="97" t="s">
-        <v>1128</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16752,16 +16831,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1129</v>
+        <v>1115</v>
       </c>
       <c r="D27" s="99" t="s">
-        <v>1130</v>
+        <v>1116</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1131</v>
+        <v>1117</v>
       </c>
       <c r="F27" s="99" t="s">
-        <v>1132</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16772,16 +16851,16 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1133</v>
+        <v>1119</v>
       </c>
       <c r="D28" s="99" t="s">
-        <v>1134</v>
+        <v>1120</v>
       </c>
       <c r="E28" s="87" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
       <c r="F28" s="99" t="s">
-        <v>1136</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16792,16 +16871,16 @@
         <v>75</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>1137</v>
+        <v>1123</v>
       </c>
       <c r="D29" s="99" t="s">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1139</v>
+        <v>1125</v>
       </c>
       <c r="F29" s="99" t="s">
-        <v>1140</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16812,16 +16891,16 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1141</v>
+        <v>1127</v>
       </c>
       <c r="D30" s="99" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="E30" s="87" t="s">
-        <v>1143</v>
+        <v>1129</v>
       </c>
       <c r="F30" s="99" t="s">
-        <v>1144</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16832,16 +16911,16 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1145</v>
+        <v>1131</v>
       </c>
       <c r="D31" s="99" t="s">
-        <v>1146</v>
+        <v>1132</v>
       </c>
       <c r="E31" s="87" t="s">
-        <v>1147</v>
+        <v>1133</v>
       </c>
       <c r="F31" s="99" t="s">
-        <v>1148</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16852,16 +16931,16 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1149</v>
+        <v>1135</v>
       </c>
       <c r="D32" s="99" t="s">
-        <v>1150</v>
+        <v>1136</v>
       </c>
       <c r="E32" s="87" t="s">
-        <v>1151</v>
+        <v>1137</v>
       </c>
       <c r="F32" s="99" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -16872,16 +16951,16 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1153</v>
+        <v>1139</v>
       </c>
       <c r="D33" s="101" t="s">
-        <v>1154</v>
+        <v>1140</v>
       </c>
       <c r="E33" s="88" t="s">
-        <v>1155</v>
+        <v>1141</v>
       </c>
       <c r="F33" s="101" t="s">
-        <v>1156</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16892,16 +16971,16 @@
         <v>85</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>1157</v>
+        <v>1143</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>1158</v>
+        <v>1144</v>
       </c>
       <c r="E34" s="86" t="s">
-        <v>1159</v>
+        <v>1145</v>
       </c>
       <c r="F34" s="97" t="s">
-        <v>1160</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16912,16 +16991,16 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1161</v>
+        <v>1147</v>
       </c>
       <c r="D35" s="99" t="s">
-        <v>1162</v>
+        <v>1148</v>
       </c>
       <c r="E35" s="87" t="s">
-        <v>1163</v>
+        <v>1149</v>
       </c>
       <c r="F35" s="99" t="s">
-        <v>1164</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16932,16 +17011,16 @@
         <v>90</v>
       </c>
       <c r="C36" s="157" t="s">
-        <v>1165</v>
+        <v>1151</v>
       </c>
       <c r="D36" s="99" t="s">
-        <v>1166</v>
+        <v>1152</v>
       </c>
       <c r="E36" s="87" t="s">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="F36" s="99" t="s">
-        <v>1168</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16952,16 +17031,16 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1169</v>
+        <v>1155</v>
       </c>
       <c r="D37" s="99" t="s">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1171</v>
+        <v>1157</v>
       </c>
       <c r="F37" s="99" t="s">
-        <v>1172</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16972,16 +17051,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1173</v>
+        <v>1159</v>
       </c>
       <c r="D38" s="99" t="s">
-        <v>1174</v>
+        <v>1160</v>
       </c>
       <c r="E38" s="87" t="s">
-        <v>1175</v>
+        <v>1161</v>
       </c>
       <c r="F38" s="99" t="s">
-        <v>1176</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16992,16 +17071,16 @@
         <v>97</v>
       </c>
       <c r="C39" s="102" t="s">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="D39" s="99" t="s">
-        <v>1178</v>
+        <v>1164</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1179</v>
+        <v>1165</v>
       </c>
       <c r="F39" s="99" t="s">
-        <v>1180</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17012,16 +17091,16 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1181</v>
+        <v>1167</v>
       </c>
       <c r="D40" s="99" t="s">
-        <v>1182</v>
+        <v>1168</v>
       </c>
       <c r="E40" s="87" t="s">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="F40" s="99" t="s">
-        <v>1184</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17032,16 +17111,16 @@
         <v>101</v>
       </c>
       <c r="C41" s="89" t="s">
-        <v>1185</v>
+        <v>1171</v>
       </c>
       <c r="D41" s="206" t="s">
-        <v>1186</v>
+        <v>1172</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>1187</v>
+        <v>1173</v>
       </c>
       <c r="F41" s="101" t="s">
-        <v>1188</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17052,16 +17131,16 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1189</v>
+        <v>1175</v>
       </c>
       <c r="D42" s="97" t="s">
-        <v>1190</v>
+        <v>1176</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>1191</v>
+        <v>1177</v>
       </c>
       <c r="F42" s="41" t="s">
-        <v>1192</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17072,16 +17151,16 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1193</v>
+        <v>1179</v>
       </c>
       <c r="D43" s="99" t="s">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="E43" s="87" t="s">
-        <v>1195</v>
+        <v>1181</v>
       </c>
       <c r="F43" s="99" t="s">
-        <v>1196</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17092,16 +17171,16 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="D44" s="99" t="s">
-        <v>1198</v>
+        <v>1184</v>
       </c>
       <c r="E44" s="87" t="s">
-        <v>1199</v>
+        <v>1185</v>
       </c>
       <c r="F44" s="99" t="s">
-        <v>1200</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17112,16 +17191,16 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1201</v>
+        <v>1187</v>
       </c>
       <c r="D45" s="99" t="s">
-        <v>1202</v>
+        <v>1188</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1203</v>
+        <v>1189</v>
       </c>
       <c r="F45" s="99" t="s">
-        <v>1204</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17132,19 +17211,19 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1205</v>
+        <v>1191</v>
       </c>
       <c r="D46" s="99" t="s">
-        <v>1206</v>
+        <v>1192</v>
       </c>
       <c r="E46" s="87" t="s">
-        <v>1207</v>
+        <v>1193</v>
       </c>
       <c r="F46" s="99" t="s">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>1209</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17155,16 +17234,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1210</v>
+        <v>1196</v>
       </c>
       <c r="D47" s="99" t="s">
-        <v>1211</v>
+        <v>1197</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1212</v>
+        <v>1198</v>
       </c>
       <c r="F47" s="99" t="s">
-        <v>1213</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17175,19 +17254,19 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1214</v>
+        <v>1200</v>
       </c>
       <c r="D48" s="99" t="s">
-        <v>1215</v>
+        <v>1201</v>
       </c>
       <c r="E48" s="87" t="s">
-        <v>1216</v>
+        <v>1202</v>
       </c>
       <c r="F48" s="99" t="s">
-        <v>1217</v>
+        <v>1203</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>1218</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17198,16 +17277,16 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1219</v>
+        <v>1205</v>
       </c>
       <c r="D49" s="101" t="s">
-        <v>1220</v>
+        <v>1206</v>
       </c>
       <c r="E49" s="89" t="s">
-        <v>1221</v>
+        <v>1207</v>
       </c>
       <c r="F49" s="112" t="s">
-        <v>1222</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17218,16 +17297,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>1223</v>
+        <v>1209</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>1224</v>
+        <v>1210</v>
       </c>
       <c r="E50" s="86" t="s">
-        <v>1225</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="97" t="s">
-        <v>1226</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17238,16 +17317,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1227</v>
+        <v>1213</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>1228</v>
+        <v>1214</v>
       </c>
       <c r="E51" s="87" t="s">
-        <v>1229</v>
+        <v>1215</v>
       </c>
       <c r="F51" s="99" t="s">
-        <v>1230</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17258,16 +17337,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1231</v>
+        <v>1217</v>
       </c>
       <c r="D52" s="99" t="s">
-        <v>1232</v>
+        <v>1218</v>
       </c>
       <c r="E52" s="87" t="s">
-        <v>1233</v>
+        <v>1219</v>
       </c>
       <c r="F52" s="99" t="s">
-        <v>1234</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17278,16 +17357,16 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1235</v>
+        <v>1221</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>1236</v>
+        <v>1222</v>
       </c>
       <c r="E53" s="87" t="s">
-        <v>1237</v>
+        <v>1223</v>
       </c>
       <c r="F53" s="99" t="s">
-        <v>1238</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17298,16 +17377,16 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1239</v>
+        <v>1225</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>1240</v>
+        <v>1226</v>
       </c>
       <c r="E54" s="87" t="s">
-        <v>1241</v>
+        <v>1227</v>
       </c>
       <c r="F54" s="99" t="s">
-        <v>1242</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17318,16 +17397,16 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1243</v>
+        <v>1229</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>1244</v>
+        <v>1230</v>
       </c>
       <c r="E55" s="87" t="s">
-        <v>1245</v>
+        <v>1231</v>
       </c>
       <c r="F55" s="99" t="s">
-        <v>1246</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17338,16 +17417,16 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="D56" s="99" t="s">
-        <v>1248</v>
+        <v>1234</v>
       </c>
       <c r="E56" s="87" t="s">
-        <v>1249</v>
+        <v>1235</v>
       </c>
       <c r="F56" s="99" t="s">
-        <v>1250</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17358,16 +17437,16 @@
         <v>143</v>
       </c>
       <c r="C57" s="89" t="s">
-        <v>1251</v>
+        <v>1237</v>
       </c>
       <c r="D57" s="112" t="s">
-        <v>1252</v>
+        <v>1238</v>
       </c>
       <c r="E57" s="88" t="s">
-        <v>1253</v>
+        <v>1239</v>
       </c>
       <c r="F57" s="101" t="s">
-        <v>1254</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17378,16 +17457,16 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1255</v>
+        <v>1241</v>
       </c>
       <c r="D58" s="97" t="s">
-        <v>1256</v>
+        <v>1242</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>1257</v>
+        <v>1243</v>
       </c>
       <c r="F58" s="41" t="s">
-        <v>1258</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17398,16 +17477,16 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1259</v>
+        <v>1245</v>
       </c>
       <c r="D59" s="99" t="s">
-        <v>1260</v>
+        <v>1246</v>
       </c>
       <c r="E59" s="87" t="s">
-        <v>1261</v>
+        <v>1247</v>
       </c>
       <c r="F59" s="99" t="s">
-        <v>1262</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17418,16 +17497,16 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1263</v>
+        <v>1249</v>
       </c>
       <c r="D60" s="99" t="s">
-        <v>1264</v>
+        <v>1250</v>
       </c>
       <c r="E60" s="87" t="s">
-        <v>1265</v>
+        <v>1251</v>
       </c>
       <c r="F60" s="99" t="s">
-        <v>1266</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17438,16 +17517,16 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1267</v>
+        <v>1253</v>
       </c>
       <c r="D61" s="99" t="s">
-        <v>1268</v>
+        <v>1254</v>
       </c>
       <c r="E61" s="87" t="s">
-        <v>1269</v>
+        <v>1255</v>
       </c>
       <c r="F61" s="99" t="s">
-        <v>1270</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17458,16 +17537,16 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1271</v>
+        <v>1257</v>
       </c>
       <c r="D62" s="99" t="s">
-        <v>1272</v>
+        <v>1258</v>
       </c>
       <c r="E62" s="87" t="s">
-        <v>1273</v>
+        <v>1259</v>
       </c>
       <c r="F62" s="99" t="s">
-        <v>1274</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17478,16 +17557,16 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1275</v>
+        <v>1261</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>1276</v>
+        <v>1262</v>
       </c>
       <c r="E63" s="87" t="s">
-        <v>1277</v>
+        <v>1263</v>
       </c>
       <c r="F63" s="99" t="s">
-        <v>1278</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17498,16 +17577,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1279</v>
+        <v>1265</v>
       </c>
       <c r="D64" s="99" t="s">
-        <v>1280</v>
+        <v>1266</v>
       </c>
       <c r="E64" s="87" t="s">
-        <v>1281</v>
+        <v>1267</v>
       </c>
       <c r="F64" s="99" t="s">
-        <v>1282</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17518,16 +17597,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1283</v>
+        <v>1269</v>
       </c>
       <c r="D65" s="101" t="s">
-        <v>1284</v>
+        <v>1270</v>
       </c>
       <c r="E65" s="89" t="s">
-        <v>1285</v>
+        <v>1271</v>
       </c>
       <c r="F65" s="112" t="s">
-        <v>1286</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17538,16 +17617,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1287</v>
+        <v>1273</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>1288</v>
+        <v>1274</v>
       </c>
       <c r="E66" s="86" t="s">
-        <v>1289</v>
+        <v>1275</v>
       </c>
       <c r="F66" s="97" t="s">
-        <v>1290</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17558,16 +17637,16 @@
         <v>168</v>
       </c>
       <c r="C67" s="88" t="s">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="D67" s="101" t="s">
-        <v>1288</v>
+        <v>1274</v>
       </c>
       <c r="E67" s="88" t="s">
-        <v>1292</v>
+        <v>1278</v>
       </c>
       <c r="F67" s="101" t="s">
-        <v>1293</v>
+        <v>1279</v>
       </c>
     </row>
   </sheetData>
@@ -17598,7 +17677,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>1468</v>
+        <v>1454</v>
       </c>
       <c r="C1" s="211" t="s">
         <v>511</v>
@@ -17641,16 +17720,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="248" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="D3" s="249" t="s">
-        <v>1431</v>
+        <v>1417</v>
       </c>
       <c r="E3" s="250" t="s">
-        <v>1432</v>
+        <v>1418</v>
       </c>
       <c r="F3" s="251" t="s">
-        <v>1433</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17841,16 +17920,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="255" t="s">
-        <v>1584</v>
+        <v>1570</v>
       </c>
       <c r="D13" s="256" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
       <c r="E13" s="140" t="s">
-        <v>1586</v>
+        <v>1572</v>
       </c>
       <c r="F13" s="251" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17947,7 +18026,7 @@
         <v>620</v>
       </c>
       <c r="E18" s="253" t="s">
-        <v>1463</v>
+        <v>1449</v>
       </c>
       <c r="F18" s="182" t="s">
         <v>621</v>
@@ -18064,7 +18143,7 @@
         <v>642</v>
       </c>
       <c r="D24" s="256" t="s">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="E24" s="196" t="s">
         <v>643</v>
@@ -18101,16 +18180,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="252" t="s">
-        <v>1434</v>
+        <v>1420</v>
       </c>
       <c r="D26" s="192" t="s">
         <v>649</v>
       </c>
       <c r="E26" s="253" t="s">
-        <v>1462</v>
+        <v>1448</v>
       </c>
       <c r="F26" s="254" t="s">
-        <v>1435</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18201,16 +18280,16 @@
         <v>79</v>
       </c>
       <c r="C31" s="255" t="s">
-        <v>1436</v>
+        <v>1422</v>
       </c>
       <c r="D31" s="256" t="s">
-        <v>1437</v>
+        <v>1423</v>
       </c>
       <c r="E31" s="196" t="s">
         <v>666</v>
       </c>
       <c r="F31" s="251" t="s">
-        <v>1438</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18301,16 +18380,16 @@
         <v>90</v>
       </c>
       <c r="C36" s="255" t="s">
-        <v>1439</v>
+        <v>1425</v>
       </c>
       <c r="D36" s="256" t="s">
-        <v>1440</v>
+        <v>1426</v>
       </c>
       <c r="E36" s="140" t="s">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="F36" s="251" t="s">
-        <v>1442</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18321,13 +18400,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="255" t="s">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="D37" s="195" t="s">
         <v>683</v>
       </c>
       <c r="E37" s="140" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="F37" s="186" t="s">
         <v>684</v>
@@ -18350,7 +18429,7 @@
         <v>687</v>
       </c>
       <c r="F38" s="251" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18421,7 +18500,7 @@
         <v>103</v>
       </c>
       <c r="C42" s="252" t="s">
-        <v>1446</v>
+        <v>1432</v>
       </c>
       <c r="D42" s="192" t="s">
         <v>700</v>
@@ -18501,16 +18580,16 @@
         <v>113</v>
       </c>
       <c r="C46" s="255" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
       <c r="D46" s="195" t="s">
         <v>715</v>
       </c>
       <c r="E46" s="140" t="s">
-        <v>1448</v>
+        <v>1434</v>
       </c>
       <c r="F46" s="251" t="s">
-        <v>1449</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18521,16 +18600,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="255" t="s">
-        <v>1450</v>
+        <v>1436</v>
       </c>
       <c r="D47" s="256" t="s">
-        <v>1451</v>
+        <v>1437</v>
       </c>
       <c r="E47" s="140" t="s">
-        <v>1452</v>
+        <v>1438</v>
       </c>
       <c r="F47" s="251" t="s">
-        <v>1453</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18561,16 +18640,16 @@
         <v>119</v>
       </c>
       <c r="C49" s="257" t="s">
-        <v>1454</v>
+        <v>1440</v>
       </c>
       <c r="D49" s="258" t="s">
-        <v>1455</v>
+        <v>1441</v>
       </c>
       <c r="E49" s="259" t="s">
-        <v>1456</v>
+        <v>1442</v>
       </c>
       <c r="F49" s="260" t="s">
-        <v>1457</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18581,16 +18660,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="252" t="s">
-        <v>1837</v>
+        <v>1823</v>
       </c>
       <c r="D50" s="293" t="s">
-        <v>1838</v>
+        <v>1824</v>
       </c>
       <c r="E50" s="253" t="s">
-        <v>1839</v>
+        <v>1825</v>
       </c>
       <c r="F50" s="254" t="s">
-        <v>1840</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18601,16 +18680,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="255" t="s">
-        <v>1841</v>
+        <v>1827</v>
       </c>
       <c r="D51" s="256" t="s">
-        <v>1842</v>
+        <v>1828</v>
       </c>
       <c r="E51" s="140" t="s">
-        <v>1843</v>
+        <v>1829</v>
       </c>
       <c r="F51" s="251" t="s">
-        <v>1844</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18621,16 +18700,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="255" t="s">
-        <v>1845</v>
+        <v>1831</v>
       </c>
       <c r="D52" s="256" t="s">
-        <v>1846</v>
+        <v>1832</v>
       </c>
       <c r="E52" s="140" t="s">
-        <v>1847</v>
+        <v>1833</v>
       </c>
       <c r="F52" s="251" t="s">
-        <v>1848</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18690,7 +18769,7 @@
         <v>730</v>
       </c>
       <c r="F55" s="251" t="s">
-        <v>1458</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18701,13 +18780,13 @@
         <v>140</v>
       </c>
       <c r="C56" s="255" t="s">
-        <v>1459</v>
+        <v>1445</v>
       </c>
       <c r="D56" s="256" t="s">
-        <v>1460</v>
+        <v>1446</v>
       </c>
       <c r="E56" s="140" t="s">
-        <v>1461</v>
+        <v>1447</v>
       </c>
       <c r="F56" s="186" t="s">
         <v>731</v>
@@ -18727,7 +18806,7 @@
         <v>733</v>
       </c>
       <c r="E57" s="259" t="s">
-        <v>1465</v>
+        <v>1451</v>
       </c>
       <c r="F57" s="190" t="s">
         <v>734</v>
@@ -18821,10 +18900,10 @@
         <v>156</v>
       </c>
       <c r="C62" s="255" t="s">
-        <v>1466</v>
+        <v>1452</v>
       </c>
       <c r="D62" s="256" t="s">
-        <v>1467</v>
+        <v>1453</v>
       </c>
       <c r="E62" s="196" t="s">
         <v>751</v>
@@ -18861,16 +18940,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="255" t="s">
-        <v>1849</v>
+        <v>1835</v>
       </c>
       <c r="D64" s="256" t="s">
-        <v>1850</v>
+        <v>1836</v>
       </c>
       <c r="E64" s="140" t="s">
-        <v>1851</v>
+        <v>1837</v>
       </c>
       <c r="F64" s="251" t="s">
-        <v>1852</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18901,16 +18980,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="252" t="s">
-        <v>1853</v>
+        <v>1839</v>
       </c>
       <c r="D66" s="293" t="s">
-        <v>1854</v>
+        <v>1840</v>
       </c>
       <c r="E66" s="193" t="s">
         <v>761</v>
       </c>
       <c r="F66" s="254" t="s">
-        <v>1855</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18921,10 +19000,10 @@
         <v>168</v>
       </c>
       <c r="C67" s="257" t="s">
-        <v>1856</v>
+        <v>1842</v>
       </c>
       <c r="D67" s="258" t="s">
-        <v>1857</v>
+        <v>1843</v>
       </c>
       <c r="E67" s="199" t="s">
         <v>762</v>
@@ -18938,19 +19017,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>1294</v>
+        <v>1280</v>
       </c>
       <c r="C68" s="268" t="s">
-        <v>1858</v>
+        <v>1844</v>
       </c>
       <c r="D68" s="269" t="s">
-        <v>1859</v>
+        <v>1845</v>
       </c>
       <c r="E68" s="270" t="s">
-        <v>1860</v>
+        <v>1846</v>
       </c>
       <c r="F68" s="271" t="s">
-        <v>1861</v>
+        <v>1847</v>
       </c>
     </row>
   </sheetData>
@@ -19964,16 +20043,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="224" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D50" s="225" t="s">
         <v>956</v>
       </c>
-      <c r="D50" s="225" t="s">
+      <c r="E50" s="226" t="s">
         <v>957</v>
       </c>
-      <c r="E50" s="226" t="s">
+      <c r="F50" s="215" t="s">
         <v>958</v>
-      </c>
-      <c r="F50" s="215" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19984,16 +20063,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="227" t="s">
-        <v>960</v>
+        <v>1849</v>
       </c>
       <c r="D51" s="228" t="s">
-        <v>961</v>
+        <v>1850</v>
       </c>
       <c r="E51" s="229" t="s">
-        <v>962</v>
+        <v>1851</v>
       </c>
       <c r="F51" s="219" t="s">
-        <v>963</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20004,16 +20083,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="227" t="s">
-        <v>964</v>
+        <v>1853</v>
       </c>
       <c r="D52" s="228" t="s">
-        <v>965</v>
+        <v>1854</v>
       </c>
       <c r="E52" s="229" t="s">
-        <v>966</v>
+        <v>1855</v>
       </c>
       <c r="F52" s="219" t="s">
-        <v>967</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20024,16 +20103,16 @@
         <v>132</v>
       </c>
       <c r="C53" s="227" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="D53" s="228" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="E53" s="229" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="F53" s="219" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20044,16 +20123,16 @@
         <v>135</v>
       </c>
       <c r="C54" s="227" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="D54" s="228" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="E54" s="229" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="F54" s="219" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20064,16 +20143,16 @@
         <v>137</v>
       </c>
       <c r="C55" s="227" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="D55" s="228" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
       <c r="E55" s="229" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="F55" s="219" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20084,16 +20163,16 @@
         <v>140</v>
       </c>
       <c r="C56" s="227" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="D56" s="228" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="E56" s="229" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="F56" s="219" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20104,16 +20183,16 @@
         <v>143</v>
       </c>
       <c r="C57" s="230" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="D57" s="231" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="E57" s="232" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="F57" s="223" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20124,16 +20203,16 @@
         <v>146</v>
       </c>
       <c r="C58" s="224" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="D58" s="225" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="E58" s="226" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="F58" s="215" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20144,16 +20223,16 @@
         <v>149</v>
       </c>
       <c r="C59" s="227" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="D59" s="228" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
       <c r="E59" s="229" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="F59" s="219" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20164,16 +20243,16 @@
         <v>151</v>
       </c>
       <c r="C60" s="227" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="D60" s="228" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
       <c r="E60" s="229" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="F60" s="219" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20184,16 +20263,16 @@
         <v>154</v>
       </c>
       <c r="C61" s="227" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="D61" s="228" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="E61" s="229" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="F61" s="219" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20204,16 +20283,16 @@
         <v>156</v>
       </c>
       <c r="C62" s="227" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="D62" s="228" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="E62" s="229" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="F62" s="219" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20224,16 +20303,16 @@
         <v>158</v>
       </c>
       <c r="C63" s="227" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="D63" s="228" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="E63" s="229" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="F63" s="219" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20244,84 +20323,104 @@
         <v>160</v>
       </c>
       <c r="C64" s="227" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D64" s="228" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E64" s="229" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F64" s="219" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="146">
+        <v>64</v>
+      </c>
+      <c r="B65" s="75" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" s="235" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D65" s="236" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E65" s="237" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F65" s="238" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="294">
+        <v>65</v>
+      </c>
+      <c r="B66" s="76" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" s="212" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D66" s="213" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E66" s="302" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F66" s="299" t="s">
         <v>1012</v>
       </c>
-      <c r="D64" s="228" t="s">
+    </row>
+    <row r="67" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="295">
+        <v>66</v>
+      </c>
+      <c r="B67" s="70" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" s="216" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D67" s="217" t="s">
         <v>1013</v>
       </c>
-      <c r="E64" s="229" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F64" s="219" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="147">
-        <v>64</v>
-      </c>
-      <c r="B65" s="77" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="235" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D65" s="236" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E65" s="237" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F65" s="238" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="148">
-        <v>65</v>
-      </c>
-      <c r="B66" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C66" s="224" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D66" s="225" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E66" s="226" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F66" s="215" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="146">
-        <v>66</v>
-      </c>
-      <c r="B67" s="75" t="s">
-        <v>168</v>
-      </c>
-      <c r="C67" s="230" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D67" s="231" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E67" s="232" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F67" s="223" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="E67" s="303" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F67" s="300" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="296">
+        <v>0</v>
+      </c>
+      <c r="B68" s="77" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C68" s="297" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D68" s="298" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E68" s="304" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F68" s="301" t="s">
+        <v>1863</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="1864">
   <si>
     <t>編號</t>
   </si>
@@ -3651,12 +3651,6 @@
     <t>清晨朗誦內心語句三遍，讓聲音帶動能量流動。</t>
   </si>
   <si>
-    <t>練習準確傳遞訊息與意思</t>
-  </si>
-  <si>
-    <t>把今天最重要的一句話說清楚</t>
-  </si>
-  <si>
     <t>調整生命節奏以回歸內在調和</t>
   </si>
   <si>
@@ -3918,12 +3912,6 @@
     <t>登高遠眺並以言語放風，釋放壓力。</t>
   </si>
   <si>
-    <t>在變化中保有真正的自由</t>
-  </si>
-  <si>
-    <t>今天放下一項不必要的束縛</t>
-  </si>
-  <si>
     <t>在混亂中練習穩固與耐心</t>
   </si>
   <si>
@@ -3945,12 +3933,6 @@
     <t>於風雨之夜燃香召喚驚醒能量。</t>
   </si>
   <si>
-    <t>辨認突然出現的警告訊號</t>
-  </si>
-  <si>
-    <t>記錄今天一項突發警訊</t>
-  </si>
-  <si>
     <t>保持交換與流動暢通</t>
   </si>
   <si>
@@ -4156,9 +4138,6 @@
   </si>
   <si>
     <t>在混沌中辨識變數</t>
-  </si>
-  <si>
-    <t>系統</t>
   </si>
   <si>
     <t>把現行規則與例外分開寫，標出暫時失效之處。</t>
@@ -6405,6 +6384,34 @@
   </si>
   <si>
     <t>德不參與抽籤</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>練習準確傳遞訊息與意思，把最重要的一句話說清楚。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>在變化中保有真正自由，放下一項不必要的束縛。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>辨認突然出現的警告訊號，記錄今天一項突發警訊</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始抽張指引籤詩吧</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始抽張指引籤詩吧</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始抽張指引籤詩吧</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -6695,7 +6702,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="77">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -7647,21 +7654,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -7699,6 +7691,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -7727,7 +7749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="303">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -8176,8 +8198,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
@@ -8210,10 +8230,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="44" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="44" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="44" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -8224,7 +8240,7 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
@@ -8238,7 +8254,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8249,7 +8265,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8289,6 +8305,10 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="76" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="77" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="20% - 輔色1" xfId="7"/>
@@ -8303,7 +8323,143 @@
     <cellStyle name="好" xfId="4"/>
     <cellStyle name="備註" xfId="6"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -8644,159 +8800,6 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border>
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -9709,92 +9712,91 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:H68" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:H68" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A1:H68"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="編號" dataDxfId="53"/>
-    <tableColumn id="2" name="符文名稱" dataDxfId="52"/>
-    <tableColumn id="3" name="英文" dataDxfId="51"/>
-    <tableColumn id="4" name="圖騰" dataDxfId="50"/>
-    <tableColumn id="5" name="所屬分組" dataDxfId="49"/>
-    <tableColumn id="6" name="月相" dataDxfId="48"/>
-    <tableColumn id="7" name="卡片屬性" dataDxfId="47"/>
-    <tableColumn id="13" name="符文說明" dataDxfId="46"/>
+    <tableColumn id="1" name="編號" dataDxfId="52"/>
+    <tableColumn id="2" name="符文名稱" dataDxfId="51"/>
+    <tableColumn id="3" name="英文" dataDxfId="50"/>
+    <tableColumn id="4" name="圖騰" dataDxfId="49"/>
+    <tableColumn id="5" name="所屬分組" dataDxfId="48"/>
+    <tableColumn id="6" name="月相" dataDxfId="47"/>
+    <tableColumn id="7" name="卡片屬性" dataDxfId="46"/>
+    <tableColumn id="13" name="符文說明" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表格2" displayName="表格2" ref="A1:C68" totalsRowShown="0" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表格2" displayName="表格2" ref="A1:C68" totalsRowShown="0" dataDxfId="44">
   <autoFilter ref="A1:C68"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="編號" dataDxfId="44"/>
-    <tableColumn id="2" name="符文名稱" dataDxfId="43"/>
-    <tableColumn id="7" name="正向關鍵詞" dataDxfId="42"/>
+    <tableColumn id="1" name="編號" dataDxfId="43"/>
+    <tableColumn id="2" name="符文名稱" dataDxfId="42"/>
+    <tableColumn id="7" name="正向關鍵詞" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="表格9" displayName="表格9" ref="A1:G10" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="表格9" displayName="表格9" ref="A1:G10" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A1:G10"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="分組" dataDxfId="39"/>
-    <tableColumn id="2" name="分組說明" dataDxfId="38"/>
-    <tableColumn id="3" name="特質" dataDxfId="37"/>
-    <tableColumn id="4" name="風格模組" dataDxfId="36"/>
-    <tableColumn id="5" name="可能語氣" dataDxfId="35"/>
-    <tableColumn id="6" name="style" dataDxfId="34"/>
-    <tableColumn id="7" name="所屬符文" dataDxfId="33"/>
+    <tableColumn id="1" name="分組" dataDxfId="38"/>
+    <tableColumn id="2" name="分組說明" dataDxfId="37"/>
+    <tableColumn id="3" name="特質" dataDxfId="36"/>
+    <tableColumn id="4" name="風格模組" dataDxfId="35"/>
+    <tableColumn id="5" name="可能語氣" dataDxfId="34"/>
+    <tableColumn id="6" name="style" dataDxfId="33"/>
+    <tableColumn id="7" name="所屬符文" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:D68" totalsRowShown="0" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:D68" totalsRowShown="0" dataDxfId="31">
   <autoFilter ref="A1:D68"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="編號" dataDxfId="31"/>
-    <tableColumn id="2" name="名稱" dataDxfId="30"/>
-    <tableColumn id="6" name="符文變化歷史" dataDxfId="29"/>
-    <tableColumn id="7" name="神話故事" dataDxfId="28"/>
+    <tableColumn id="1" name="編號" dataDxfId="30"/>
+    <tableColumn id="2" name="名稱" dataDxfId="29"/>
+    <tableColumn id="6" name="符文變化歷史" dataDxfId="28"/>
+    <tableColumn id="7" name="神話故事" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="表格5" displayName="表格5" ref="A1:G67" totalsRowShown="0" headerRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="表格5" displayName="表格5" ref="A1:G67" totalsRowShown="0" headerRowBorderDxfId="26">
   <autoFilter ref="A1:G67"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="名稱" dataDxfId="26"/>
-    <tableColumn id="2" name="圖騰" dataDxfId="25"/>
-    <tableColumn id="5" name="具象插圖背景" dataDxfId="24"/>
-    <tableColumn id="6" name="圖編號" dataDxfId="23"/>
-    <tableColumn id="7" name="圖檔名稱" dataDxfId="22">
+    <tableColumn id="1" name="名稱" dataDxfId="25"/>
+    <tableColumn id="2" name="圖騰" dataDxfId="24"/>
+    <tableColumn id="5" name="具象插圖背景" dataDxfId="23"/>
+    <tableColumn id="6" name="圖編號" dataDxfId="22"/>
+    <tableColumn id="7" name="圖檔名稱" dataDxfId="21">
       <calculatedColumnFormula>CONCATENATE(D2,A2,".png")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="符文底圖代碼" dataDxfId="21"/>
-    <tableColumn id="9" name="符文卡圖代碼" dataDxfId="20"/>
+    <tableColumn id="8" name="符文底圖代碼" dataDxfId="20"/>
+    <tableColumn id="9" name="符文卡圖代碼" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="表格6" displayName="表格6" ref="A1:G67" totalsRowShown="0">
-  <autoFilter ref="A1:G67"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="編號" dataDxfId="19"/>
-    <tableColumn id="2" name="名稱" dataDxfId="18"/>
-    <tableColumn id="6" name="靈魂課題" dataDxfId="17"/>
-    <tableColumn id="7" name="實踐挑戰" dataDxfId="16"/>
-    <tableColumn id="8" name="配套儀式建議" dataDxfId="15"/>
-    <tableColumn id="9" name="能量調和建議" dataDxfId="14"/>
-    <tableColumn id="10" name="欄1" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="表格6" displayName="表格6" ref="A1:F68" totalsRowShown="0">
+  <autoFilter ref="A1:F68"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="編號" dataDxfId="5"/>
+    <tableColumn id="2" name="名稱" dataDxfId="4"/>
+    <tableColumn id="6" name="靈魂課題" dataDxfId="3"/>
+    <tableColumn id="7" name="實踐挑戰" dataDxfId="2"/>
+    <tableColumn id="8" name="配套儀式建議" dataDxfId="1"/>
+    <tableColumn id="9" name="能量調和建議" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9804,27 +9806,27 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="表格7" displayName="表格7" ref="A1:F68" totalsRowShown="0" headerRowCellStyle="40% - 輔色1">
   <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="12"/>
-    <tableColumn id="2" name="符文名稱" dataDxfId="11"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="10" dataCellStyle="20% - 輔色1"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="9" dataCellStyle="40% - 輔色1"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="8" dataCellStyle="20% - 輔色2"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="7" dataCellStyle="40% - 輔色2"/>
+    <tableColumn id="1" name="編號" dataDxfId="18"/>
+    <tableColumn id="2" name="符文名稱" dataDxfId="17"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="16" dataCellStyle="20% - 輔色1"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="15" dataCellStyle="40% - 輔色1"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="14" dataCellStyle="20% - 輔色2"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="13" dataCellStyle="40% - 輔色2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F68" totalsRowShown="0" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F68" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="5"/>
-    <tableColumn id="2" name="名稱" dataDxfId="4"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="3"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="2"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="1"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="0"/>
+    <tableColumn id="1" name="編號" dataDxfId="11"/>
+    <tableColumn id="2" name="名稱" dataDxfId="10"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="9"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="8"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="7"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10084,13 +10086,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="118" t="s">
-        <v>1632</v>
-      </c>
-      <c r="I1" s="291" t="s">
-        <v>1636</v>
-      </c>
-      <c r="J1" s="291" t="s">
-        <v>1349</v>
+        <v>1625</v>
+      </c>
+      <c r="I1" s="287" t="s">
+        <v>1629</v>
+      </c>
+      <c r="J1" s="287" t="s">
+        <v>1342</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10101,7 +10103,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="96" t="s">
-        <v>1455</v>
+        <v>1448</v>
       </c>
       <c r="D2" s="86" t="s">
         <v>8</v>
@@ -10115,14 +10117,14 @@
       <c r="G2" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="282" t="s">
-        <v>1575</v>
-      </c>
-      <c r="I2" s="272" t="s">
-        <v>1287</v>
-      </c>
-      <c r="J2" s="273" t="s">
-        <v>1350</v>
+      <c r="H2" s="278" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I2" s="268" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J2" s="269" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10147,14 +10149,14 @@
       <c r="G3" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="281" t="s">
-        <v>1576</v>
+      <c r="H3" s="277" t="s">
+        <v>1569</v>
       </c>
       <c r="I3" s="87" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="J3" s="99" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10165,7 +10167,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="98" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="D4" s="87" t="s">
         <v>18</v>
@@ -10179,14 +10181,14 @@
       <c r="G4" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="281" t="s">
-        <v>1637</v>
-      </c>
-      <c r="I4" s="274" t="s">
-        <v>1289</v>
-      </c>
-      <c r="J4" s="275" t="s">
-        <v>1352</v>
+      <c r="H4" s="277" t="s">
+        <v>1630</v>
+      </c>
+      <c r="I4" s="270" t="s">
+        <v>1282</v>
+      </c>
+      <c r="J4" s="271" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10197,7 +10199,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="92" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
       <c r="D5" s="98" t="s">
         <v>20</v>
@@ -10211,14 +10213,14 @@
       <c r="G5" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="281" t="s">
-        <v>1577</v>
+      <c r="H5" s="277" t="s">
+        <v>1570</v>
       </c>
       <c r="I5" s="87" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="J5" s="99" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10229,7 +10231,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
       <c r="D6" s="98" t="s">
         <v>22</v>
@@ -10243,14 +10245,14 @@
       <c r="G6" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="281" t="s">
-        <v>1574</v>
-      </c>
-      <c r="I6" s="274" t="s">
-        <v>1291</v>
-      </c>
-      <c r="J6" s="275" t="s">
-        <v>1354</v>
+      <c r="H6" s="277" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I6" s="270" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J6" s="271" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10261,7 +10263,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="92" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
       <c r="D7" s="98" t="s">
         <v>25</v>
@@ -10275,14 +10277,14 @@
       <c r="G7" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="281" t="s">
-        <v>1578</v>
+      <c r="H7" s="277" t="s">
+        <v>1571</v>
       </c>
       <c r="I7" s="87" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="J7" s="99" t="s">
-        <v>1355</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10293,7 +10295,7 @@
         <v>27</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>1460</v>
+        <v>1453</v>
       </c>
       <c r="D8" s="98" t="s">
         <v>28</v>
@@ -10307,14 +10309,14 @@
       <c r="G8" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="281" t="s">
-        <v>1579</v>
-      </c>
-      <c r="I8" s="274" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J8" s="275" t="s">
-        <v>1356</v>
+      <c r="H8" s="277" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I8" s="270" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J8" s="271" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10325,7 +10327,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
       <c r="D9" s="100" t="s">
         <v>30</v>
@@ -10339,25 +10341,25 @@
       <c r="G9" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="283" t="s">
-        <v>1580</v>
+      <c r="H9" s="279" t="s">
+        <v>1573</v>
       </c>
       <c r="I9" s="88" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="J9" s="101" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="284">
+      <c r="A10" s="280">
         <v>9</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="289" t="s">
-        <v>1462</v>
+      <c r="C10" s="285" t="s">
+        <v>1455</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>32</v>
@@ -10368,17 +10370,17 @@
       <c r="F10" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="285" t="s">
+      <c r="G10" s="281" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="286" t="s">
-        <v>1585</v>
-      </c>
-      <c r="I10" s="287" t="s">
-        <v>1295</v>
-      </c>
-      <c r="J10" s="288" t="s">
-        <v>1358</v>
+      <c r="H10" s="282" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I10" s="283" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J10" s="284" t="s">
+        <v>1351</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10389,7 +10391,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="D11" s="87" t="s">
         <v>35</v>
@@ -10403,14 +10405,14 @@
       <c r="G11" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="281" t="s">
-        <v>1583</v>
+      <c r="H11" s="277" t="s">
+        <v>1576</v>
       </c>
       <c r="I11" s="87" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="99" t="s">
-        <v>1359</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10421,7 +10423,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="98" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
       <c r="D12" s="87" t="s">
         <v>39</v>
@@ -10435,14 +10437,14 @@
       <c r="G12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="281" t="s">
-        <v>1584</v>
-      </c>
-      <c r="I12" s="274" t="s">
-        <v>1296</v>
-      </c>
-      <c r="J12" s="275" t="s">
-        <v>1360</v>
+      <c r="H12" s="277" t="s">
+        <v>1577</v>
+      </c>
+      <c r="I12" s="270" t="s">
+        <v>1289</v>
+      </c>
+      <c r="J12" s="271" t="s">
+        <v>1353</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10453,7 +10455,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="98" t="s">
-        <v>1465</v>
+        <v>1458</v>
       </c>
       <c r="D13" s="87" t="s">
         <v>41</v>
@@ -10467,14 +10469,14 @@
       <c r="G13" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="281" t="s">
-        <v>1582</v>
+      <c r="H13" s="277" t="s">
+        <v>1575</v>
       </c>
       <c r="I13" s="87" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="J13" s="99" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10485,7 +10487,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="D14" s="87" t="s">
         <v>43</v>
@@ -10499,14 +10501,14 @@
       <c r="G14" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="281" t="s">
-        <v>1587</v>
-      </c>
-      <c r="I14" s="274" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J14" s="275" t="s">
-        <v>1362</v>
+      <c r="H14" s="277" t="s">
+        <v>1580</v>
+      </c>
+      <c r="I14" s="270" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J14" s="271" t="s">
+        <v>1355</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10517,7 +10519,7 @@
         <v>44</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="D15" s="87" t="s">
         <v>45</v>
@@ -10531,14 +10533,14 @@
       <c r="G15" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="281" t="s">
-        <v>1581</v>
+      <c r="H15" s="277" t="s">
+        <v>1574</v>
       </c>
       <c r="I15" s="87" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
       <c r="J15" s="99" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10549,7 +10551,7 @@
         <v>46</v>
       </c>
       <c r="C16" s="98" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
       <c r="D16" s="87" t="s">
         <v>47</v>
@@ -10563,14 +10565,14 @@
       <c r="G16" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="281" t="s">
-        <v>1588</v>
-      </c>
-      <c r="I16" s="274" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J16" s="275" t="s">
-        <v>1364</v>
+      <c r="H16" s="277" t="s">
+        <v>1581</v>
+      </c>
+      <c r="I16" s="270" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J16" s="271" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10581,7 +10583,7 @@
         <v>48</v>
       </c>
       <c r="C17" s="100" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>49</v>
@@ -10595,18 +10597,18 @@
       <c r="G17" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="283" t="s">
-        <v>1586</v>
+      <c r="H17" s="279" t="s">
+        <v>1579</v>
       </c>
       <c r="I17" s="88" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="J17" s="101" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="284">
+      <c r="A18" s="280">
         <v>17</v>
       </c>
       <c r="B18" s="37" t="s">
@@ -10624,17 +10626,17 @@
       <c r="F18" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="285" t="s">
+      <c r="G18" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="286" t="s">
-        <v>1589</v>
-      </c>
-      <c r="I18" s="287" t="s">
-        <v>1302</v>
-      </c>
-      <c r="J18" s="288" t="s">
-        <v>1366</v>
+      <c r="H18" s="282" t="s">
+        <v>1582</v>
+      </c>
+      <c r="I18" s="283" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J18" s="284" t="s">
+        <v>1359</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10645,7 +10647,7 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1470</v>
+        <v>1463</v>
       </c>
       <c r="D19" s="87" t="s">
         <v>55</v>
@@ -10659,14 +10661,14 @@
       <c r="G19" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="281" t="s">
-        <v>1590</v>
+      <c r="H19" s="277" t="s">
+        <v>1583</v>
       </c>
       <c r="I19" s="87" t="s">
-        <v>1303</v>
+        <v>1296</v>
       </c>
       <c r="J19" s="99" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10677,7 +10679,7 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1471</v>
+        <v>1464</v>
       </c>
       <c r="D20" s="87" t="s">
         <v>57</v>
@@ -10691,14 +10693,14 @@
       <c r="G20" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="281" t="s">
-        <v>1596</v>
-      </c>
-      <c r="I20" s="274" t="s">
-        <v>1304</v>
-      </c>
-      <c r="J20" s="275" t="s">
-        <v>1368</v>
+      <c r="H20" s="277" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I20" s="270" t="s">
+        <v>1297</v>
+      </c>
+      <c r="J20" s="271" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10709,7 +10711,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1472</v>
+        <v>1465</v>
       </c>
       <c r="D21" s="87" t="s">
         <v>59</v>
@@ -10723,14 +10725,14 @@
       <c r="G21" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="281" t="s">
-        <v>1591</v>
+      <c r="H21" s="277" t="s">
+        <v>1584</v>
       </c>
       <c r="I21" s="87" t="s">
-        <v>1305</v>
+        <v>1298</v>
       </c>
       <c r="J21" s="99" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10741,7 +10743,7 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
       <c r="D22" s="87" t="s">
         <v>61</v>
@@ -10755,14 +10757,14 @@
       <c r="G22" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="281" t="s">
-        <v>1592</v>
-      </c>
-      <c r="I22" s="274" t="s">
-        <v>1306</v>
-      </c>
-      <c r="J22" s="275" t="s">
-        <v>1370</v>
+      <c r="H22" s="277" t="s">
+        <v>1585</v>
+      </c>
+      <c r="I22" s="270" t="s">
+        <v>1299</v>
+      </c>
+      <c r="J22" s="271" t="s">
+        <v>1363</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10773,7 +10775,7 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
       <c r="D23" s="87" t="s">
         <v>63</v>
@@ -10787,14 +10789,14 @@
       <c r="G23" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="281" t="s">
-        <v>1593</v>
+      <c r="H23" s="277" t="s">
+        <v>1586</v>
       </c>
       <c r="I23" s="87" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
       <c r="J23" s="99" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10805,7 +10807,7 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1475</v>
+        <v>1468</v>
       </c>
       <c r="D24" s="87" t="s">
         <v>65</v>
@@ -10819,25 +10821,25 @@
       <c r="G24" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="281" t="s">
-        <v>1594</v>
-      </c>
-      <c r="I24" s="274" t="s">
-        <v>1308</v>
-      </c>
-      <c r="J24" s="275" t="s">
-        <v>1372</v>
+      <c r="H24" s="277" t="s">
+        <v>1587</v>
+      </c>
+      <c r="I24" s="270" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J24" s="271" t="s">
+        <v>1365</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="279">
+      <c r="A25" s="275">
         <v>24</v>
       </c>
       <c r="B25" s="89" t="s">
         <v>66</v>
       </c>
       <c r="C25" s="89" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
       <c r="D25" s="89" t="s">
         <v>67</v>
@@ -10848,17 +10850,17 @@
       <c r="F25" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="280" t="s">
+      <c r="G25" s="276" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="290" t="s">
-        <v>1595</v>
+      <c r="H25" s="286" t="s">
+        <v>1588</v>
       </c>
       <c r="I25" s="89" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="J25" s="112" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10869,7 +10871,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
       <c r="D26" s="86" t="s">
         <v>69</v>
@@ -10883,14 +10885,14 @@
       <c r="G26" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="282" t="s">
-        <v>1597</v>
-      </c>
-      <c r="I26" s="272" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J26" s="273" t="s">
-        <v>1374</v>
+      <c r="H26" s="278" t="s">
+        <v>1590</v>
+      </c>
+      <c r="I26" s="268" t="s">
+        <v>1303</v>
+      </c>
+      <c r="J26" s="269" t="s">
+        <v>1367</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10901,7 +10903,7 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
       <c r="D27" s="87" t="s">
         <v>72</v>
@@ -10915,14 +10917,14 @@
       <c r="G27" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="281" t="s">
-        <v>1599</v>
+      <c r="H27" s="277" t="s">
+        <v>1592</v>
       </c>
       <c r="I27" s="87" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="J27" s="99" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10933,7 +10935,7 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="D28" s="87" t="s">
         <v>74</v>
@@ -10947,14 +10949,14 @@
       <c r="G28" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="281" t="s">
-        <v>1598</v>
-      </c>
-      <c r="I28" s="274" t="s">
-        <v>1312</v>
-      </c>
-      <c r="J28" s="275" t="s">
-        <v>1376</v>
+      <c r="H28" s="277" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I28" s="270" t="s">
+        <v>1305</v>
+      </c>
+      <c r="J28" s="271" t="s">
+        <v>1369</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10965,7 +10967,7 @@
         <v>75</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
       <c r="D29" s="87" t="s">
         <v>76</v>
@@ -10979,14 +10981,14 @@
       <c r="G29" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="281" t="s">
-        <v>1600</v>
+      <c r="H29" s="277" t="s">
+        <v>1593</v>
       </c>
       <c r="I29" s="87" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
       <c r="J29" s="99" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10997,7 +10999,7 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
       <c r="D30" s="87" t="s">
         <v>78</v>
@@ -11011,14 +11013,14 @@
       <c r="G30" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="281" t="s">
-        <v>1601</v>
-      </c>
-      <c r="I30" s="274" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J30" s="275" t="s">
-        <v>1378</v>
+      <c r="H30" s="277" t="s">
+        <v>1594</v>
+      </c>
+      <c r="I30" s="270" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J30" s="271" t="s">
+        <v>1371</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11029,7 +11031,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1482</v>
+        <v>1475</v>
       </c>
       <c r="D31" s="87" t="s">
         <v>80</v>
@@ -11043,14 +11045,14 @@
       <c r="G31" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H31" s="281" t="s">
-        <v>1602</v>
+      <c r="H31" s="277" t="s">
+        <v>1595</v>
       </c>
       <c r="I31" s="87" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
       <c r="J31" s="99" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11061,7 +11063,7 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="D32" s="87" t="s">
         <v>82</v>
@@ -11075,25 +11077,25 @@
       <c r="G32" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="281" t="s">
-        <v>1604</v>
-      </c>
-      <c r="I32" s="274" t="s">
-        <v>1316</v>
-      </c>
-      <c r="J32" s="275" t="s">
-        <v>1380</v>
+      <c r="H32" s="277" t="s">
+        <v>1597</v>
+      </c>
+      <c r="I32" s="270" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J32" s="271" t="s">
+        <v>1373</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="279">
+      <c r="A33" s="275">
         <v>32</v>
       </c>
       <c r="B33" s="89" t="s">
         <v>83</v>
       </c>
       <c r="C33" s="89" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
       <c r="D33" s="89" t="s">
         <v>84</v>
@@ -11104,17 +11106,17 @@
       <c r="F33" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="280" t="s">
+      <c r="G33" s="276" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="290" t="s">
-        <v>1603</v>
+      <c r="H33" s="286" t="s">
+        <v>1596</v>
       </c>
       <c r="I33" s="89" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
       <c r="J33" s="112" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11125,7 +11127,7 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1485</v>
+        <v>1478</v>
       </c>
       <c r="D34" s="86" t="s">
         <v>86</v>
@@ -11139,14 +11141,14 @@
       <c r="G34" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="H34" s="282" t="s">
-        <v>1605</v>
-      </c>
-      <c r="I34" s="272" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J34" s="273" t="s">
-        <v>1382</v>
+      <c r="H34" s="278" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I34" s="268" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J34" s="269" t="s">
+        <v>1375</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11157,7 +11159,7 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
       <c r="D35" s="87" t="s">
         <v>89</v>
@@ -11171,14 +11173,14 @@
       <c r="G35" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="281" t="s">
-        <v>1606</v>
+      <c r="H35" s="277" t="s">
+        <v>1599</v>
       </c>
       <c r="I35" s="87" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="J35" s="99" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11189,7 +11191,7 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="D36" s="87" t="s">
         <v>91</v>
@@ -11203,14 +11205,14 @@
       <c r="G36" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="281" t="s">
-        <v>1607</v>
-      </c>
-      <c r="I36" s="274" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J36" s="275" t="s">
-        <v>1384</v>
+      <c r="H36" s="277" t="s">
+        <v>1600</v>
+      </c>
+      <c r="I36" s="270" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J36" s="271" t="s">
+        <v>1377</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11221,7 +11223,7 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="D37" s="87" t="s">
         <v>93</v>
@@ -11235,14 +11237,14 @@
       <c r="G37" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="281" t="s">
-        <v>1608</v>
+      <c r="H37" s="277" t="s">
+        <v>1601</v>
       </c>
       <c r="I37" s="87" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="J37" s="99" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11267,14 +11269,14 @@
       <c r="G38" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="281" t="s">
-        <v>1609</v>
-      </c>
-      <c r="I38" s="274" t="s">
-        <v>1322</v>
-      </c>
-      <c r="J38" s="275" t="s">
-        <v>1386</v>
+      <c r="H38" s="277" t="s">
+        <v>1602</v>
+      </c>
+      <c r="I38" s="270" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J38" s="271" t="s">
+        <v>1379</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11285,7 +11287,7 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="D39" s="87" t="s">
         <v>98</v>
@@ -11299,14 +11301,14 @@
       <c r="G39" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="281" t="s">
-        <v>1610</v>
+      <c r="H39" s="277" t="s">
+        <v>1603</v>
       </c>
       <c r="I39" s="87" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
       <c r="J39" s="99" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11317,7 +11319,7 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="D40" s="87" t="s">
         <v>100</v>
@@ -11331,14 +11333,14 @@
       <c r="G40" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H40" s="281" t="s">
-        <v>1611</v>
-      </c>
-      <c r="I40" s="274" t="s">
-        <v>1324</v>
-      </c>
-      <c r="J40" s="275" t="s">
-        <v>1388</v>
+      <c r="H40" s="277" t="s">
+        <v>1604</v>
+      </c>
+      <c r="I40" s="270" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J40" s="271" t="s">
+        <v>1381</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11349,7 +11351,7 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1491</v>
+        <v>1484</v>
       </c>
       <c r="D41" s="88" t="s">
         <v>102</v>
@@ -11363,25 +11365,25 @@
       <c r="G41" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="283" t="s">
-        <v>1612</v>
+      <c r="H41" s="279" t="s">
+        <v>1605</v>
       </c>
       <c r="I41" s="88" t="s">
-        <v>1325</v>
+        <v>1318</v>
       </c>
       <c r="J41" s="101" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="284">
+      <c r="A42" s="280">
         <v>41</v>
       </c>
       <c r="B42" s="37" t="s">
         <v>103</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="D42" s="37" t="s">
         <v>104</v>
@@ -11392,17 +11394,17 @@
       <c r="F42" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="G42" s="285" t="s">
+      <c r="G42" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="286" t="s">
-        <v>1616</v>
-      </c>
-      <c r="I42" s="287" t="s">
+      <c r="H42" s="282" t="s">
+        <v>1609</v>
+      </c>
+      <c r="I42" s="283" t="s">
         <v>106</v>
       </c>
-      <c r="J42" s="288" t="s">
-        <v>1390</v>
+      <c r="J42" s="284" t="s">
+        <v>1383</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11413,7 +11415,7 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
       <c r="D43" s="87" t="s">
         <v>108</v>
@@ -11427,14 +11429,14 @@
       <c r="G43" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H43" s="281" t="s">
-        <v>1615</v>
+      <c r="H43" s="277" t="s">
+        <v>1608</v>
       </c>
       <c r="I43" s="87" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
       <c r="J43" s="99" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11445,7 +11447,7 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
       <c r="D44" s="87" t="s">
         <v>110</v>
@@ -11459,14 +11461,14 @@
       <c r="G44" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="281" t="s">
-        <v>1619</v>
-      </c>
-      <c r="I44" s="274" t="s">
-        <v>1327</v>
-      </c>
-      <c r="J44" s="275" t="s">
-        <v>1392</v>
+      <c r="H44" s="277" t="s">
+        <v>1612</v>
+      </c>
+      <c r="I44" s="270" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J44" s="271" t="s">
+        <v>1385</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11477,7 +11479,7 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
       <c r="D45" s="87" t="s">
         <v>112</v>
@@ -11491,14 +11493,14 @@
       <c r="G45" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="281" t="s">
-        <v>1617</v>
+      <c r="H45" s="277" t="s">
+        <v>1610</v>
       </c>
       <c r="I45" s="87" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
       <c r="J45" s="99" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11509,7 +11511,7 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
       <c r="D46" s="87" t="s">
         <v>114</v>
@@ -11523,14 +11525,14 @@
       <c r="G46" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="281" t="s">
-        <v>1613</v>
-      </c>
-      <c r="I46" s="274" t="s">
-        <v>1329</v>
-      </c>
-      <c r="J46" s="275" t="s">
-        <v>1394</v>
+      <c r="H46" s="277" t="s">
+        <v>1606</v>
+      </c>
+      <c r="I46" s="270" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J46" s="271" t="s">
+        <v>1387</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11541,7 +11543,7 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
       <c r="D47" s="87" t="s">
         <v>116</v>
@@ -11555,14 +11557,14 @@
       <c r="G47" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="281" t="s">
-        <v>1620</v>
+      <c r="H47" s="277" t="s">
+        <v>1613</v>
       </c>
       <c r="I47" s="87" t="s">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="J47" s="99" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11573,7 +11575,7 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
       <c r="D48" s="87" t="s">
         <v>118</v>
@@ -11587,14 +11589,14 @@
       <c r="G48" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="281" t="s">
-        <v>1618</v>
-      </c>
-      <c r="I48" s="274" t="s">
-        <v>1331</v>
-      </c>
-      <c r="J48" s="275" t="s">
-        <v>1396</v>
+      <c r="H48" s="277" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I48" s="270" t="s">
+        <v>1324</v>
+      </c>
+      <c r="J48" s="271" t="s">
+        <v>1389</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11619,18 +11621,18 @@
       <c r="G49" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H49" s="283" t="s">
-        <v>1614</v>
+      <c r="H49" s="279" t="s">
+        <v>1607</v>
       </c>
       <c r="I49" s="88" t="s">
-        <v>1332</v>
+        <v>1325</v>
       </c>
       <c r="J49" s="101" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="284">
+      <c r="A50" s="280">
         <v>49</v>
       </c>
       <c r="B50" s="37" t="s">
@@ -11648,17 +11650,17 @@
       <c r="F50" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="G50" s="289" t="s">
+      <c r="G50" s="285" t="s">
         <v>36</v>
       </c>
-      <c r="H50" s="286" t="s">
-        <v>1776</v>
-      </c>
-      <c r="I50" s="287" t="s">
-        <v>1333</v>
-      </c>
-      <c r="J50" s="288" t="s">
-        <v>1398</v>
+      <c r="H50" s="282" t="s">
+        <v>1769</v>
+      </c>
+      <c r="I50" s="283" t="s">
+        <v>1326</v>
+      </c>
+      <c r="J50" s="284" t="s">
+        <v>1391</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11683,14 +11685,14 @@
       <c r="G51" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="H51" s="281" t="s">
-        <v>1775</v>
+      <c r="H51" s="277" t="s">
+        <v>1768</v>
       </c>
       <c r="I51" s="87" t="s">
-        <v>1334</v>
+        <v>1327</v>
       </c>
       <c r="J51" s="99" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11715,14 +11717,14 @@
       <c r="G52" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="H52" s="281" t="s">
-        <v>1771</v>
-      </c>
-      <c r="I52" s="274" t="s">
-        <v>1822</v>
-      </c>
-      <c r="J52" s="275" t="s">
-        <v>1400</v>
+      <c r="H52" s="277" t="s">
+        <v>1764</v>
+      </c>
+      <c r="I52" s="270" t="s">
+        <v>1815</v>
+      </c>
+      <c r="J52" s="271" t="s">
+        <v>1393</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11747,14 +11749,14 @@
       <c r="G53" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="H53" s="281" t="s">
-        <v>1621</v>
+      <c r="H53" s="277" t="s">
+        <v>1614</v>
       </c>
       <c r="I53" s="87" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
       <c r="J53" s="99" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11765,7 +11767,7 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="D54" s="87" t="s">
         <v>136</v>
@@ -11779,14 +11781,14 @@
       <c r="G54" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="281" t="s">
-        <v>1795</v>
-      </c>
-      <c r="I54" s="274" t="s">
-        <v>1336</v>
-      </c>
-      <c r="J54" s="275" t="s">
-        <v>1402</v>
+      <c r="H54" s="277" t="s">
+        <v>1788</v>
+      </c>
+      <c r="I54" s="270" t="s">
+        <v>1329</v>
+      </c>
+      <c r="J54" s="271" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11811,14 +11813,14 @@
       <c r="G55" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="281" t="s">
-        <v>1623</v>
+      <c r="H55" s="277" t="s">
+        <v>1616</v>
       </c>
       <c r="I55" s="87" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
       <c r="J55" s="99" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11843,14 +11845,14 @@
       <c r="G56" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H56" s="281" t="s">
-        <v>1624</v>
-      </c>
-      <c r="I56" s="274" t="s">
-        <v>1338</v>
-      </c>
-      <c r="J56" s="275" t="s">
-        <v>1404</v>
+      <c r="H56" s="277" t="s">
+        <v>1617</v>
+      </c>
+      <c r="I56" s="270" t="s">
+        <v>1331</v>
+      </c>
+      <c r="J56" s="271" t="s">
+        <v>1397</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11875,25 +11877,25 @@
       <c r="G57" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="H57" s="283" t="s">
-        <v>1622</v>
+      <c r="H57" s="279" t="s">
+        <v>1615</v>
       </c>
       <c r="I57" s="88" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
       <c r="J57" s="101" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="284">
+      <c r="A58" s="280">
         <v>57</v>
       </c>
       <c r="B58" s="37" t="s">
         <v>146</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="D58" s="37" t="s">
         <v>147</v>
@@ -11904,17 +11906,17 @@
       <c r="F58" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="289" t="s">
+      <c r="G58" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="286" t="s">
-        <v>1772</v>
-      </c>
-      <c r="I58" s="287" t="s">
-        <v>1340</v>
-      </c>
-      <c r="J58" s="288" t="s">
-        <v>1406</v>
+      <c r="H58" s="282" t="s">
+        <v>1765</v>
+      </c>
+      <c r="I58" s="283" t="s">
+        <v>1333</v>
+      </c>
+      <c r="J58" s="284" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11925,7 +11927,7 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="D59" s="87" t="s">
         <v>150</v>
@@ -11939,14 +11941,14 @@
       <c r="G59" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="H59" s="281" t="s">
-        <v>1773</v>
+      <c r="H59" s="277" t="s">
+        <v>1766</v>
       </c>
       <c r="I59" s="87" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="J59" s="99" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11957,7 +11959,7 @@
         <v>151</v>
       </c>
       <c r="C60" s="98" t="s">
-        <v>1502</v>
+        <v>1495</v>
       </c>
       <c r="D60" s="93" t="s">
         <v>152</v>
@@ -11971,14 +11973,14 @@
       <c r="G60" s="98" t="s">
         <v>153</v>
       </c>
-      <c r="H60" s="281" t="s">
-        <v>1783</v>
-      </c>
-      <c r="I60" s="274" t="s">
-        <v>1342</v>
-      </c>
-      <c r="J60" s="275" t="s">
-        <v>1408</v>
+      <c r="H60" s="277" t="s">
+        <v>1776</v>
+      </c>
+      <c r="I60" s="270" t="s">
+        <v>1335</v>
+      </c>
+      <c r="J60" s="271" t="s">
+        <v>1401</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11989,7 +11991,7 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1503</v>
+        <v>1496</v>
       </c>
       <c r="D61" s="87" t="s">
         <v>155</v>
@@ -12003,14 +12005,14 @@
       <c r="G61" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="281" t="s">
-        <v>1774</v>
+      <c r="H61" s="277" t="s">
+        <v>1767</v>
       </c>
       <c r="I61" s="87" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
       <c r="J61" s="99" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12021,7 +12023,7 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1504</v>
+        <v>1497</v>
       </c>
       <c r="D62" s="87" t="s">
         <v>157</v>
@@ -12035,14 +12037,14 @@
       <c r="G62" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="H62" s="281" t="s">
-        <v>1782</v>
-      </c>
-      <c r="I62" s="274" t="s">
-        <v>1344</v>
-      </c>
-      <c r="J62" s="275" t="s">
-        <v>1410</v>
+      <c r="H62" s="277" t="s">
+        <v>1775</v>
+      </c>
+      <c r="I62" s="270" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J62" s="271" t="s">
+        <v>1403</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12053,7 +12055,7 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="D63" s="87" t="s">
         <v>159</v>
@@ -12067,14 +12069,14 @@
       <c r="G63" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="H63" s="281" t="s">
-        <v>1625</v>
+      <c r="H63" s="277" t="s">
+        <v>1618</v>
       </c>
       <c r="I63" s="87" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
       <c r="J63" s="99" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12099,14 +12101,14 @@
       <c r="G64" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="H64" s="281" t="s">
-        <v>1626</v>
-      </c>
-      <c r="I64" s="274" t="s">
-        <v>1346</v>
-      </c>
-      <c r="J64" s="275" t="s">
-        <v>1412</v>
+      <c r="H64" s="277" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I64" s="270" t="s">
+        <v>1339</v>
+      </c>
+      <c r="J64" s="271" t="s">
+        <v>1405</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12117,7 +12119,7 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="D65" s="88" t="s">
         <v>164</v>
@@ -12131,25 +12133,25 @@
       <c r="G65" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H65" s="283" t="s">
-        <v>1784</v>
+      <c r="H65" s="279" t="s">
+        <v>1777</v>
       </c>
       <c r="I65" s="88" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
       <c r="J65" s="101" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="284">
+      <c r="A66" s="280">
         <v>65</v>
       </c>
       <c r="B66" s="37" t="s">
         <v>165</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>1507</v>
+        <v>1500</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>166</v>
@@ -12160,17 +12162,17 @@
       <c r="F66" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="G66" s="285" t="s">
+      <c r="G66" s="281" t="s">
         <v>153</v>
       </c>
-      <c r="H66" s="286" t="s">
-        <v>1781</v>
-      </c>
-      <c r="I66" s="287" t="s">
-        <v>1634</v>
-      </c>
-      <c r="J66" s="288" t="s">
-        <v>1414</v>
+      <c r="H66" s="282" t="s">
+        <v>1774</v>
+      </c>
+      <c r="I66" s="283" t="s">
+        <v>1627</v>
+      </c>
+      <c r="J66" s="284" t="s">
+        <v>1407</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12181,7 +12183,7 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="D67" s="87" t="s">
         <v>35</v>
@@ -12195,14 +12197,14 @@
       <c r="G67" s="93" t="s">
         <v>153</v>
       </c>
-      <c r="H67" s="281" t="s">
-        <v>1780</v>
+      <c r="H67" s="277" t="s">
+        <v>1773</v>
       </c>
       <c r="I67" s="87" t="s">
-        <v>1635</v>
+        <v>1628</v>
       </c>
       <c r="J67" s="99" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12210,13 +12212,13 @@
         <v>0</v>
       </c>
       <c r="B68" s="88" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>1631</v>
+        <v>1624</v>
       </c>
       <c r="E68" s="88" t="s">
         <v>167</v>
@@ -12227,14 +12229,14 @@
       <c r="G68" s="95" t="s">
         <v>153</v>
       </c>
-      <c r="H68" s="283" t="s">
-        <v>1627</v>
-      </c>
-      <c r="I68" s="276" t="s">
-        <v>1348</v>
-      </c>
-      <c r="J68" s="277" t="s">
-        <v>1628</v>
+      <c r="H68" s="279" t="s">
+        <v>1620</v>
+      </c>
+      <c r="I68" s="272" t="s">
+        <v>1341</v>
+      </c>
+      <c r="J68" s="273" t="s">
+        <v>1621</v>
       </c>
     </row>
   </sheetData>
@@ -12269,16 +12271,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="109" t="s">
-        <v>1633</v>
-      </c>
-      <c r="D1" s="278" t="s">
-        <v>1638</v>
-      </c>
-      <c r="E1" s="278" t="s">
-        <v>1639</v>
-      </c>
-      <c r="F1" s="278" t="s">
-        <v>1736</v>
+        <v>1626</v>
+      </c>
+      <c r="D1" s="274" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1" s="274" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F1" s="274" t="s">
+        <v>1729</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12289,15 +12291,15 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1669</v>
-      </c>
-      <c r="D2" s="272" t="s">
-        <v>1670</v>
-      </c>
-      <c r="E2" s="272" t="s">
-        <v>1640</v>
-      </c>
-      <c r="F2" s="272"/>
+        <v>1662</v>
+      </c>
+      <c r="D2" s="268" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E2" s="268" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F2" s="268"/>
     </row>
     <row r="3" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="114">
@@ -12307,13 +12309,13 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>1675</v>
+        <v>1668</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
       <c r="F3" s="87"/>
     </row>
@@ -12325,13 +12327,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1671</v>
-      </c>
-      <c r="D4" s="274" t="s">
-        <v>1672</v>
-      </c>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
+        <v>1664</v>
+      </c>
+      <c r="D4" s="270" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
     </row>
     <row r="5" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="114">
@@ -12341,13 +12343,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1642</v>
+        <v>1635</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>1643</v>
+        <v>1636</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1673</v>
+        <v>1666</v>
       </c>
       <c r="F5" s="87"/>
     </row>
@@ -12359,15 +12361,15 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1644</v>
-      </c>
-      <c r="D6" s="274" t="s">
-        <v>1645</v>
-      </c>
-      <c r="E6" s="274" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F6" s="274"/>
+        <v>1637</v>
+      </c>
+      <c r="D6" s="270" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E6" s="270" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F6" s="270"/>
     </row>
     <row r="7" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="114">
@@ -12377,13 +12379,13 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1646</v>
+        <v>1639</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>1676</v>
+        <v>1669</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="F7" s="87"/>
     </row>
@@ -12395,13 +12397,13 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1752</v>
-      </c>
-      <c r="D8" s="274" t="s">
-        <v>1647</v>
-      </c>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
+        <v>1745</v>
+      </c>
+      <c r="D8" s="270" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E8" s="270"/>
+      <c r="F8" s="270"/>
     </row>
     <row r="9" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="115">
@@ -12411,10 +12413,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1674</v>
+        <v>1667</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="E9" s="88"/>
       <c r="F9" s="88"/>
@@ -12427,13 +12429,13 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1651</v>
-      </c>
-      <c r="D10" s="272" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E10" s="272"/>
-      <c r="F10" s="272"/>
+        <v>1644</v>
+      </c>
+      <c r="D10" s="268" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E10" s="268"/>
+      <c r="F10" s="268"/>
     </row>
     <row r="11" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="114">
@@ -12443,13 +12445,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1653</v>
+        <v>1646</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1665</v>
+        <v>1658</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1654</v>
+        <v>1647</v>
       </c>
       <c r="F11" s="87"/>
     </row>
@@ -12461,15 +12463,15 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1656</v>
-      </c>
-      <c r="D12" s="274" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E12" s="274" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F12" s="274"/>
+        <v>1649</v>
+      </c>
+      <c r="D12" s="270" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E12" s="270" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F12" s="270"/>
     </row>
     <row r="13" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="114">
@@ -12479,16 +12481,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1667</v>
+        <v>1660</v>
       </c>
       <c r="D13" s="87" t="s">
-        <v>1658</v>
+        <v>1651</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1666</v>
+        <v>1659</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12499,15 +12501,15 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D14" s="274" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E14" s="274" t="s">
-        <v>1660</v>
-      </c>
-      <c r="F14" s="274"/>
+        <v>1652</v>
+      </c>
+      <c r="D14" s="270" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E14" s="270" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F14" s="270"/>
     </row>
     <row r="15" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="114">
@@ -12517,10 +12519,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1668</v>
+        <v>1661</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>1661</v>
+        <v>1654</v>
       </c>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
@@ -12533,15 +12535,15 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1662</v>
-      </c>
-      <c r="D16" s="274" t="s">
-        <v>1663</v>
-      </c>
-      <c r="E16" s="274" t="s">
-        <v>1660</v>
-      </c>
-      <c r="F16" s="274"/>
+        <v>1655</v>
+      </c>
+      <c r="D16" s="270" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E16" s="270" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F16" s="270"/>
     </row>
     <row r="17" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="115">
@@ -12551,10 +12553,10 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1677</v>
+        <v>1670</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>1664</v>
+        <v>1657</v>
       </c>
       <c r="E17" s="88"/>
       <c r="F17" s="88"/>
@@ -12567,15 +12569,15 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1681</v>
-      </c>
-      <c r="D18" s="272" t="s">
-        <v>1682</v>
-      </c>
-      <c r="E18" s="272" t="s">
-        <v>1678</v>
-      </c>
-      <c r="F18" s="272"/>
+        <v>1674</v>
+      </c>
+      <c r="D18" s="268" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E18" s="268" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F18" s="268"/>
     </row>
     <row r="19" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="114">
@@ -12585,13 +12587,13 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1690</v>
+        <v>1683</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>1691</v>
+        <v>1684</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>1695</v>
+        <v>1688</v>
       </c>
       <c r="F19" s="87"/>
     </row>
@@ -12603,15 +12605,15 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1683</v>
-      </c>
-      <c r="D20" s="274" t="s">
-        <v>1684</v>
-      </c>
-      <c r="E20" s="274" t="s">
-        <v>1700</v>
-      </c>
-      <c r="F20" s="274"/>
+        <v>1676</v>
+      </c>
+      <c r="D20" s="270" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E20" s="270" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F20" s="270"/>
     </row>
     <row r="21" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="114">
@@ -12621,13 +12623,13 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1692</v>
+        <v>1685</v>
       </c>
       <c r="D21" s="87" t="s">
-        <v>1685</v>
+        <v>1678</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1696</v>
+        <v>1689</v>
       </c>
       <c r="F21" s="87"/>
     </row>
@@ -12639,15 +12641,15 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D22" s="274" t="s">
-        <v>1687</v>
-      </c>
-      <c r="E22" s="274" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F22" s="274"/>
+        <v>1679</v>
+      </c>
+      <c r="D22" s="270" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E22" s="270" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F22" s="270"/>
     </row>
     <row r="23" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="114">
@@ -12657,13 +12659,13 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1688</v>
+        <v>1681</v>
       </c>
       <c r="D23" s="87" t="s">
-        <v>1689</v>
+        <v>1682</v>
       </c>
       <c r="E23" s="87" t="s">
-        <v>1679</v>
+        <v>1672</v>
       </c>
       <c r="F23" s="87"/>
     </row>
@@ -12675,15 +12677,15 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1694</v>
-      </c>
-      <c r="D24" s="274" t="s">
-        <v>1698</v>
-      </c>
-      <c r="E24" s="274" t="s">
-        <v>1699</v>
-      </c>
-      <c r="F24" s="274"/>
+        <v>1687</v>
+      </c>
+      <c r="D24" s="270" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E24" s="270" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F24" s="270"/>
     </row>
     <row r="25" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="115">
@@ -12693,13 +12695,13 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1705</v>
+        <v>1698</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>1693</v>
+        <v>1686</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>1680</v>
+        <v>1673</v>
       </c>
       <c r="F25" s="88"/>
     </row>
@@ -12711,16 +12713,16 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1701</v>
-      </c>
-      <c r="D26" s="272" t="s">
-        <v>1716</v>
-      </c>
-      <c r="E26" s="272" t="s">
-        <v>1713</v>
-      </c>
-      <c r="F26" s="272" t="s">
-        <v>1762</v>
+        <v>1694</v>
+      </c>
+      <c r="D26" s="268" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E26" s="268" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F26" s="268" t="s">
+        <v>1755</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12731,16 +12733,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1702</v>
+        <v>1695</v>
       </c>
       <c r="D27" s="87" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E27" s="87" t="s">
         <v>1703</v>
       </c>
-      <c r="E27" s="87" t="s">
-        <v>1710</v>
-      </c>
       <c r="F27" s="87" t="s">
-        <v>1777</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12751,13 +12753,13 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1704</v>
-      </c>
-      <c r="D28" s="274" t="s">
-        <v>1717</v>
-      </c>
-      <c r="E28" s="274"/>
-      <c r="F28" s="274"/>
+        <v>1697</v>
+      </c>
+      <c r="D28" s="270" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E28" s="270"/>
+      <c r="F28" s="270"/>
     </row>
     <row r="29" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="114">
@@ -12770,10 +12772,10 @@
         <v>560</v>
       </c>
       <c r="D29" s="87" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1711</v>
+        <v>1704</v>
       </c>
       <c r="F29" s="87"/>
     </row>
@@ -12785,15 +12787,15 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1706</v>
-      </c>
-      <c r="D30" s="274" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D30" s="270" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E30" s="270" t="s">
         <v>1707</v>
       </c>
-      <c r="E30" s="274" t="s">
-        <v>1714</v>
-      </c>
-      <c r="F30" s="274"/>
+      <c r="F30" s="270"/>
     </row>
     <row r="31" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="114">
@@ -12803,7 +12805,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
       <c r="D31" s="87"/>
       <c r="E31" s="87"/>
@@ -12817,15 +12819,15 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D32" s="274" t="s">
-        <v>1709</v>
-      </c>
-      <c r="E32" s="274" t="s">
-        <v>1712</v>
-      </c>
-      <c r="F32" s="274"/>
+        <v>1701</v>
+      </c>
+      <c r="D32" s="270" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E32" s="270" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F32" s="270"/>
     </row>
     <row r="33" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="115">
@@ -12835,11 +12837,11 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="88" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
       <c r="F33" s="88"/>
     </row>
@@ -12851,15 +12853,15 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1719</v>
-      </c>
-      <c r="D34" s="272" t="s">
-        <v>1720</v>
-      </c>
-      <c r="E34" s="272" t="s">
-        <v>1739</v>
-      </c>
-      <c r="F34" s="272"/>
+        <v>1712</v>
+      </c>
+      <c r="D34" s="268" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E34" s="268" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F34" s="268"/>
     </row>
     <row r="35" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="114">
@@ -12869,13 +12871,13 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1721</v>
+        <v>1714</v>
       </c>
       <c r="D35" s="87" t="s">
-        <v>1722</v>
+        <v>1715</v>
       </c>
       <c r="E35" s="87" t="s">
-        <v>1732</v>
+        <v>1725</v>
       </c>
       <c r="F35" s="87"/>
     </row>
@@ -12887,15 +12889,15 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1723</v>
-      </c>
-      <c r="D36" s="274" t="s">
-        <v>1724</v>
-      </c>
-      <c r="E36" s="274" t="s">
-        <v>1733</v>
-      </c>
-      <c r="F36" s="274"/>
+        <v>1716</v>
+      </c>
+      <c r="D36" s="270" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E36" s="270" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F36" s="270"/>
     </row>
     <row r="37" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="114">
@@ -12905,13 +12907,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1725</v>
+        <v>1718</v>
       </c>
       <c r="D37" s="87" t="s">
-        <v>1726</v>
+        <v>1719</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1769</v>
+        <v>1762</v>
       </c>
       <c r="F37" s="87"/>
     </row>
@@ -12923,16 +12925,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1727</v>
-      </c>
-      <c r="D38" s="274" t="s">
-        <v>1755</v>
-      </c>
-      <c r="E38" s="292" t="s">
-        <v>1738</v>
-      </c>
-      <c r="F38" s="292" t="s">
-        <v>1778</v>
+        <v>1720</v>
+      </c>
+      <c r="D38" s="270" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E38" s="288" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F38" s="288" t="s">
+        <v>1771</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12943,13 +12945,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1728</v>
+        <v>1721</v>
       </c>
       <c r="D39" s="87" t="s">
-        <v>1729</v>
+        <v>1722</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1734</v>
+        <v>1727</v>
       </c>
       <c r="F39" s="87"/>
     </row>
@@ -12961,16 +12963,16 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1730</v>
-      </c>
-      <c r="D40" s="274" t="s">
-        <v>1740</v>
-      </c>
-      <c r="E40" s="274" t="s">
-        <v>1735</v>
-      </c>
-      <c r="F40" s="274" t="s">
-        <v>1762</v>
+        <v>1723</v>
+      </c>
+      <c r="D40" s="270" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E40" s="270" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F40" s="270" t="s">
+        <v>1755</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12981,13 +12983,13 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1731</v>
+        <v>1724</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>1756</v>
+        <v>1749</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>1757</v>
+        <v>1750</v>
       </c>
       <c r="F41" s="88"/>
     </row>
@@ -12999,16 +13001,16 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1741</v>
-      </c>
-      <c r="D42" s="272" t="s">
-        <v>1742</v>
-      </c>
-      <c r="E42" s="272" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F42" s="272" t="s">
-        <v>1779</v>
+        <v>1734</v>
+      </c>
+      <c r="D42" s="268" t="s">
+        <v>1735</v>
+      </c>
+      <c r="E42" s="268" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F42" s="268" t="s">
+        <v>1772</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13019,13 +13021,13 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>1743</v>
+        <v>1736</v>
       </c>
       <c r="E43" s="87" t="s">
-        <v>1761</v>
+        <v>1754</v>
       </c>
       <c r="F43" s="87"/>
     </row>
@@ -13037,15 +13039,15 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1744</v>
-      </c>
-      <c r="D44" s="274" t="s">
-        <v>1745</v>
-      </c>
-      <c r="E44" s="274" t="s">
-        <v>1760</v>
-      </c>
-      <c r="F44" s="274"/>
+        <v>1737</v>
+      </c>
+      <c r="D44" s="270" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E44" s="270" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F44" s="270"/>
     </row>
     <row r="45" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="114">
@@ -13055,13 +13057,13 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D45" s="87" t="s">
         <v>1746</v>
       </c>
-      <c r="D45" s="87" t="s">
-        <v>1753</v>
-      </c>
       <c r="E45" s="87" t="s">
-        <v>1770</v>
+        <v>1763</v>
       </c>
       <c r="F45" s="87"/>
     </row>
@@ -13073,14 +13075,14 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D46" s="274" t="s">
-        <v>1748</v>
-      </c>
-      <c r="E46" s="274"/>
-      <c r="F46" s="274" t="s">
-        <v>1762</v>
+        <v>1740</v>
+      </c>
+      <c r="D46" s="270" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E46" s="270"/>
+      <c r="F46" s="270" t="s">
+        <v>1755</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13091,16 +13093,16 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1749</v>
+        <v>1742</v>
       </c>
       <c r="D47" s="87" t="s">
-        <v>1754</v>
+        <v>1747</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1767</v>
+        <v>1760</v>
       </c>
       <c r="F47" s="87" t="s">
-        <v>1777</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13111,12 +13113,12 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1758</v>
-      </c>
-      <c r="D48" s="274"/>
-      <c r="E48" s="274"/>
-      <c r="F48" s="274" t="s">
-        <v>1763</v>
+        <v>1751</v>
+      </c>
+      <c r="D48" s="270"/>
+      <c r="E48" s="270"/>
+      <c r="F48" s="270" t="s">
+        <v>1756</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13127,13 +13129,13 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
       <c r="E49" s="88" t="s">
-        <v>1759</v>
+        <v>1752</v>
       </c>
       <c r="F49" s="88"/>
     </row>
@@ -13145,14 +13147,14 @@
         <v>122</v>
       </c>
       <c r="C50" s="86" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D50" s="268"/>
+      <c r="E50" s="268" t="s">
         <v>1785</v>
       </c>
-      <c r="D50" s="272"/>
-      <c r="E50" s="272" t="s">
-        <v>1792</v>
-      </c>
-      <c r="F50" s="272" t="s">
-        <v>1737</v>
+      <c r="F50" s="268" t="s">
+        <v>1730</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13163,14 +13165,14 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1789</v>
+        <v>1782</v>
       </c>
       <c r="D51" s="87"/>
       <c r="E51" s="87" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="F51" s="87" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13181,14 +13183,14 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1794</v>
-      </c>
-      <c r="D52" s="274"/>
-      <c r="E52" s="274" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F52" s="274" t="s">
-        <v>1763</v>
+        <v>1787</v>
+      </c>
+      <c r="D52" s="270"/>
+      <c r="E52" s="270" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F52" s="270" t="s">
+        <v>1756</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13199,7 +13201,7 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1790</v>
+        <v>1783</v>
       </c>
       <c r="D53" s="87"/>
       <c r="E53" s="87"/>
@@ -13213,12 +13215,12 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1797</v>
-      </c>
-      <c r="D54" s="274"/>
-      <c r="E54" s="274"/>
-      <c r="F54" s="274" t="s">
-        <v>1737</v>
+        <v>1790</v>
+      </c>
+      <c r="D54" s="270"/>
+      <c r="E54" s="270"/>
+      <c r="F54" s="270" t="s">
+        <v>1730</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13229,14 +13231,14 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1786</v>
+        <v>1779</v>
       </c>
       <c r="D55" s="87" t="s">
-        <v>1787</v>
+        <v>1780</v>
       </c>
       <c r="E55" s="87"/>
       <c r="F55" s="87" t="s">
-        <v>1762</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13247,13 +13249,13 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D56" s="274" t="s">
-        <v>1788</v>
-      </c>
-      <c r="E56" s="274"/>
-      <c r="F56" s="274"/>
+        <v>1791</v>
+      </c>
+      <c r="D56" s="270" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E56" s="270"/>
+      <c r="F56" s="270"/>
     </row>
     <row r="57" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="115">
@@ -13263,10 +13265,10 @@
         <v>143</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>1809</v>
+        <v>1802</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>1791</v>
+        <v>1784</v>
       </c>
       <c r="E57" s="88"/>
       <c r="F57" s="88"/>
@@ -13279,14 +13281,14 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1800</v>
-      </c>
-      <c r="D58" s="272"/>
-      <c r="E58" s="272" t="s">
-        <v>1812</v>
-      </c>
-      <c r="F58" s="272" t="s">
-        <v>1737</v>
+        <v>1793</v>
+      </c>
+      <c r="D58" s="268"/>
+      <c r="E58" s="268" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F58" s="268" t="s">
+        <v>1730</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13297,14 +13299,14 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1801</v>
+        <v>1794</v>
       </c>
       <c r="D59" s="87"/>
       <c r="E59" s="87" t="s">
-        <v>1810</v>
+        <v>1803</v>
       </c>
       <c r="F59" s="87" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13315,11 +13317,11 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D60" s="274"/>
-      <c r="E60" s="274"/>
-      <c r="F60" s="274"/>
+        <v>1804</v>
+      </c>
+      <c r="D60" s="270"/>
+      <c r="E60" s="270"/>
+      <c r="F60" s="270"/>
     </row>
     <row r="61" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="114">
@@ -13329,13 +13331,13 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1813</v>
+        <v>1806</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>1802</v>
+        <v>1795</v>
       </c>
       <c r="E61" s="87" t="s">
-        <v>1814</v>
+        <v>1807</v>
       </c>
       <c r="F61" s="87"/>
     </row>
@@ -13347,13 +13349,13 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1803</v>
-      </c>
-      <c r="D62" s="274"/>
-      <c r="E62" s="274" t="s">
-        <v>1814</v>
-      </c>
-      <c r="F62" s="274"/>
+        <v>1796</v>
+      </c>
+      <c r="D62" s="270"/>
+      <c r="E62" s="270" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F62" s="270"/>
     </row>
     <row r="63" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="114">
@@ -13363,10 +13365,10 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1804</v>
+        <v>1797</v>
       </c>
       <c r="D63" s="87" t="s">
-        <v>1805</v>
+        <v>1798</v>
       </c>
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
@@ -13379,12 +13381,12 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1806</v>
-      </c>
-      <c r="D64" s="274"/>
-      <c r="E64" s="274"/>
-      <c r="F64" s="274" t="s">
-        <v>1766</v>
+        <v>1799</v>
+      </c>
+      <c r="D64" s="270"/>
+      <c r="E64" s="270"/>
+      <c r="F64" s="270" t="s">
+        <v>1759</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13395,16 +13397,16 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1807</v>
+        <v>1800</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>1808</v>
+        <v>1801</v>
       </c>
       <c r="E65" s="88" t="s">
-        <v>1712</v>
+        <v>1705</v>
       </c>
       <c r="F65" s="88" t="s">
-        <v>1712</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13415,12 +13417,12 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1815</v>
+        <v>1808</v>
       </c>
       <c r="D66" s="87"/>
       <c r="E66" s="87"/>
       <c r="F66" s="87" t="s">
-        <v>1818</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13431,14 +13433,14 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1816</v>
+        <v>1809</v>
       </c>
       <c r="D67" s="87"/>
       <c r="E67" s="87" t="s">
-        <v>1817</v>
+        <v>1810</v>
       </c>
       <c r="F67" s="87" t="s">
-        <v>1762</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13446,17 +13448,17 @@
         <v>0</v>
       </c>
       <c r="B68" s="210" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1820</v>
-      </c>
-      <c r="D68" s="276" t="s">
-        <v>1821</v>
-      </c>
-      <c r="E68" s="276"/>
-      <c r="F68" s="276" t="s">
-        <v>1819</v>
+        <v>1813</v>
+      </c>
+      <c r="D68" s="272" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E68" s="272"/>
+      <c r="F68" s="272" t="s">
+        <v>1812</v>
       </c>
     </row>
   </sheetData>
@@ -13489,87 +13491,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="54" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="261" t="s">
-        <v>1516</v>
-      </c>
-      <c r="B1" s="261" t="s">
+      <c r="A1" s="259" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B1" s="259" t="s">
         <v>537</v>
       </c>
-      <c r="C1" s="261" t="s">
+      <c r="C1" s="259" t="s">
         <v>538</v>
       </c>
-      <c r="D1" s="261" t="s">
+      <c r="D1" s="259" t="s">
         <v>539</v>
       </c>
-      <c r="E1" s="261" t="s">
+      <c r="E1" s="259" t="s">
         <v>540</v>
       </c>
-      <c r="F1" s="261" t="s">
+      <c r="F1" s="259" t="s">
         <v>541</v>
       </c>
-      <c r="G1" s="261" t="s">
-        <v>1560</v>
+      <c r="G1" s="259" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="262" t="s">
-        <v>1542</v>
-      </c>
-      <c r="B2" s="263" t="s">
+      <c r="A2" s="260" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B2" s="261" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C2" s="261" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D2" s="261" t="s">
         <v>1510</v>
       </c>
-      <c r="C2" s="263" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D2" s="263" t="s">
-        <v>1517</v>
-      </c>
-      <c r="E2" s="263" t="s">
-        <v>1518</v>
-      </c>
-      <c r="F2" s="263" t="s">
-        <v>1558</v>
-      </c>
-      <c r="G2" s="264" t="s">
-        <v>1561</v>
+      <c r="E2" s="261" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F2" s="261" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G2" s="262" t="s">
+        <v>1554</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="167" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="B3" s="169" t="s">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="C3" s="169" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
       <c r="D3" s="169" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="E3" s="169" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="F3" s="169" t="s">
         <v>542</v>
       </c>
       <c r="G3" s="170" t="s">
-        <v>1562</v>
-      </c>
-      <c r="H3" s="265"/>
+        <v>1555</v>
+      </c>
+      <c r="H3" s="263"/>
     </row>
     <row r="4" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="167" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="B4" s="169" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="C4" s="169" t="s">
-        <v>1522</v>
+        <v>1515</v>
       </c>
       <c r="D4" s="169" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
       <c r="E4" s="169" t="s">
         <v>543</v>
@@ -13578,145 +13580,145 @@
         <v>544</v>
       </c>
       <c r="G4" s="170" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="167" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="B5" s="169" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="C5" s="169" t="s">
-        <v>1524</v>
+        <v>1517</v>
       </c>
       <c r="D5" s="169" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="E5" s="169" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
       <c r="F5" s="169" t="s">
         <v>545</v>
       </c>
       <c r="G5" s="170" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="167" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="B6" s="169" t="s">
-        <v>1513</v>
+        <v>1506</v>
       </c>
       <c r="C6" s="169" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
       <c r="D6" s="169" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
       <c r="E6" s="169" t="s">
-        <v>1529</v>
+        <v>1522</v>
       </c>
       <c r="F6" s="169" t="s">
         <v>546</v>
       </c>
       <c r="G6" s="170" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="167" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B7" s="169" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C7" s="169" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D7" s="169" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E7" s="169" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F7" s="169" t="s">
         <v>1547</v>
       </c>
-      <c r="B7" s="169" t="s">
-        <v>1539</v>
-      </c>
-      <c r="C7" s="169" t="s">
-        <v>1551</v>
-      </c>
-      <c r="D7" s="169" t="s">
-        <v>1552</v>
-      </c>
-      <c r="E7" s="169" t="s">
-        <v>1553</v>
-      </c>
-      <c r="F7" s="169" t="s">
-        <v>1554</v>
-      </c>
       <c r="G7" s="170" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="167" t="s">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="B8" s="169" t="s">
-        <v>1514</v>
+        <v>1507</v>
       </c>
       <c r="C8" s="169" t="s">
-        <v>1530</v>
+        <v>1523</v>
       </c>
       <c r="D8" s="169" t="s">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="E8" s="169" t="s">
-        <v>1532</v>
+        <v>1525</v>
       </c>
       <c r="F8" s="169" t="s">
-        <v>1533</v>
+        <v>1526</v>
       </c>
       <c r="G8" s="170" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="167" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B9" s="169" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C9" s="169" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D9" s="169" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E9" s="169" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F9" s="169" t="s">
         <v>1549</v>
       </c>
-      <c r="B9" s="169" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C9" s="169" t="s">
-        <v>1555</v>
-      </c>
-      <c r="D9" s="169" t="s">
-        <v>1559</v>
-      </c>
-      <c r="E9" s="169" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F9" s="169" t="s">
-        <v>1556</v>
-      </c>
       <c r="G9" s="170" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="175" t="s">
-        <v>1550</v>
+        <v>1543</v>
       </c>
       <c r="B10" s="176" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>1534</v>
+        <v>1527</v>
       </c>
       <c r="D10" s="176" t="s">
-        <v>1535</v>
+        <v>1528</v>
       </c>
       <c r="E10" s="176" t="s">
-        <v>1536</v>
+        <v>1529</v>
       </c>
       <c r="F10" s="176" t="s">
-        <v>1537</v>
+        <v>1530</v>
       </c>
       <c r="G10" s="178" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -13795,11 +13797,11 @@
     </row>
     <row r="20" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:3" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="266" t="s">
-        <v>1629</v>
-      </c>
-      <c r="B21" s="267" t="s">
-        <v>1630</v>
+      <c r="A21" s="301" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B21" s="302" t="s">
+        <v>1623</v>
       </c>
     </row>
   </sheetData>
@@ -13847,7 +13849,7 @@
       <c r="C2" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="245" t="s">
+      <c r="D2" s="243" t="s">
         <v>173</v>
       </c>
     </row>
@@ -13861,7 +13863,7 @@
       <c r="C3" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="D3" s="246" t="s">
+      <c r="D3" s="244" t="s">
         <v>175</v>
       </c>
     </row>
@@ -13875,7 +13877,7 @@
       <c r="C4" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="246" t="s">
+      <c r="D4" s="244" t="s">
         <v>177</v>
       </c>
     </row>
@@ -13889,7 +13891,7 @@
       <c r="C5" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="246" t="s">
+      <c r="D5" s="244" t="s">
         <v>179</v>
       </c>
     </row>
@@ -13903,7 +13905,7 @@
       <c r="C6" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="246" t="s">
+      <c r="D6" s="244" t="s">
         <v>181</v>
       </c>
     </row>
@@ -13917,7 +13919,7 @@
       <c r="C7" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="246" t="s">
+      <c r="D7" s="244" t="s">
         <v>183</v>
       </c>
     </row>
@@ -13931,7 +13933,7 @@
       <c r="C8" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="246" t="s">
+      <c r="D8" s="244" t="s">
         <v>185</v>
       </c>
     </row>
@@ -13945,7 +13947,7 @@
       <c r="C9" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="D9" s="247" t="s">
+      <c r="D9" s="245" t="s">
         <v>187</v>
       </c>
     </row>
@@ -13959,7 +13961,7 @@
       <c r="C10" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="245" t="s">
+      <c r="D10" s="243" t="s">
         <v>189</v>
       </c>
     </row>
@@ -13973,7 +13975,7 @@
       <c r="C11" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="246" t="s">
+      <c r="D11" s="244" t="s">
         <v>191</v>
       </c>
     </row>
@@ -13987,7 +13989,7 @@
       <c r="C12" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="246" t="s">
+      <c r="D12" s="244" t="s">
         <v>193</v>
       </c>
     </row>
@@ -14001,7 +14003,7 @@
       <c r="C13" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="246" t="s">
+      <c r="D13" s="244" t="s">
         <v>195</v>
       </c>
     </row>
@@ -14015,7 +14017,7 @@
       <c r="C14" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="246" t="s">
+      <c r="D14" s="244" t="s">
         <v>197</v>
       </c>
     </row>
@@ -14029,7 +14031,7 @@
       <c r="C15" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="246" t="s">
+      <c r="D15" s="244" t="s">
         <v>199</v>
       </c>
     </row>
@@ -14043,7 +14045,7 @@
       <c r="C16" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="246" t="s">
+      <c r="D16" s="244" t="s">
         <v>201</v>
       </c>
     </row>
@@ -14057,7 +14059,7 @@
       <c r="C17" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="247" t="s">
+      <c r="D17" s="245" t="s">
         <v>203</v>
       </c>
     </row>
@@ -14071,7 +14073,7 @@
       <c r="C18" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="245" t="s">
+      <c r="D18" s="243" t="s">
         <v>205</v>
       </c>
     </row>
@@ -14085,7 +14087,7 @@
       <c r="C19" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="D19" s="246" t="s">
+      <c r="D19" s="244" t="s">
         <v>207</v>
       </c>
     </row>
@@ -14099,7 +14101,7 @@
       <c r="C20" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="246" t="s">
+      <c r="D20" s="244" t="s">
         <v>209</v>
       </c>
     </row>
@@ -14113,7 +14115,7 @@
       <c r="C21" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="D21" s="246" t="s">
+      <c r="D21" s="244" t="s">
         <v>211</v>
       </c>
     </row>
@@ -14127,7 +14129,7 @@
       <c r="C22" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="D22" s="246" t="s">
+      <c r="D22" s="244" t="s">
         <v>213</v>
       </c>
     </row>
@@ -14141,7 +14143,7 @@
       <c r="C23" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="D23" s="246" t="s">
+      <c r="D23" s="244" t="s">
         <v>215</v>
       </c>
     </row>
@@ -14155,7 +14157,7 @@
       <c r="C24" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="D24" s="246" t="s">
+      <c r="D24" s="244" t="s">
         <v>217</v>
       </c>
     </row>
@@ -14169,7 +14171,7 @@
       <c r="C25" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="D25" s="247" t="s">
+      <c r="D25" s="245" t="s">
         <v>219</v>
       </c>
     </row>
@@ -14183,7 +14185,7 @@
       <c r="C26" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="D26" s="245" t="s">
+      <c r="D26" s="243" t="s">
         <v>221</v>
       </c>
     </row>
@@ -14197,7 +14199,7 @@
       <c r="C27" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="D27" s="246" t="s">
+      <c r="D27" s="244" t="s">
         <v>223</v>
       </c>
     </row>
@@ -14211,7 +14213,7 @@
       <c r="C28" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="D28" s="246" t="s">
+      <c r="D28" s="244" t="s">
         <v>225</v>
       </c>
     </row>
@@ -14225,7 +14227,7 @@
       <c r="C29" s="39" t="s">
         <v>226</v>
       </c>
-      <c r="D29" s="246" t="s">
+      <c r="D29" s="244" t="s">
         <v>227</v>
       </c>
     </row>
@@ -14239,7 +14241,7 @@
       <c r="C30" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="D30" s="246" t="s">
+      <c r="D30" s="244" t="s">
         <v>229</v>
       </c>
     </row>
@@ -14253,7 +14255,7 @@
       <c r="C31" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="D31" s="246" t="s">
+      <c r="D31" s="244" t="s">
         <v>231</v>
       </c>
     </row>
@@ -14267,7 +14269,7 @@
       <c r="C32" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="D32" s="246" t="s">
+      <c r="D32" s="244" t="s">
         <v>233</v>
       </c>
     </row>
@@ -14281,7 +14283,7 @@
       <c r="C33" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="D33" s="247" t="s">
+      <c r="D33" s="245" t="s">
         <v>235</v>
       </c>
     </row>
@@ -14295,7 +14297,7 @@
       <c r="C34" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="D34" s="245" t="s">
+      <c r="D34" s="243" t="s">
         <v>237</v>
       </c>
     </row>
@@ -14309,7 +14311,7 @@
       <c r="C35" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="D35" s="246" t="s">
+      <c r="D35" s="244" t="s">
         <v>239</v>
       </c>
     </row>
@@ -14323,7 +14325,7 @@
       <c r="C36" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="246" t="s">
+      <c r="D36" s="244" t="s">
         <v>241</v>
       </c>
     </row>
@@ -14337,7 +14339,7 @@
       <c r="C37" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="D37" s="246" t="s">
+      <c r="D37" s="244" t="s">
         <v>243</v>
       </c>
     </row>
@@ -14351,7 +14353,7 @@
       <c r="C38" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="D38" s="246" t="s">
+      <c r="D38" s="244" t="s">
         <v>245</v>
       </c>
     </row>
@@ -14365,7 +14367,7 @@
       <c r="C39" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="D39" s="246" t="s">
+      <c r="D39" s="244" t="s">
         <v>247</v>
       </c>
     </row>
@@ -14379,7 +14381,7 @@
       <c r="C40" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="D40" s="246" t="s">
+      <c r="D40" s="244" t="s">
         <v>249</v>
       </c>
     </row>
@@ -14393,7 +14395,7 @@
       <c r="C41" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="D41" s="247" t="s">
+      <c r="D41" s="245" t="s">
         <v>251</v>
       </c>
     </row>
@@ -14407,7 +14409,7 @@
       <c r="C42" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="D42" s="245" t="s">
+      <c r="D42" s="243" t="s">
         <v>253</v>
       </c>
     </row>
@@ -14421,7 +14423,7 @@
       <c r="C43" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="D43" s="246" t="s">
+      <c r="D43" s="244" t="s">
         <v>255</v>
       </c>
     </row>
@@ -14435,7 +14437,7 @@
       <c r="C44" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="D44" s="246" t="s">
+      <c r="D44" s="244" t="s">
         <v>257</v>
       </c>
     </row>
@@ -14449,7 +14451,7 @@
       <c r="C45" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="D45" s="246" t="s">
+      <c r="D45" s="244" t="s">
         <v>259</v>
       </c>
     </row>
@@ -14463,7 +14465,7 @@
       <c r="C46" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="D46" s="246" t="s">
+      <c r="D46" s="244" t="s">
         <v>261</v>
       </c>
     </row>
@@ -14477,7 +14479,7 @@
       <c r="C47" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="D47" s="246" t="s">
+      <c r="D47" s="244" t="s">
         <v>263</v>
       </c>
     </row>
@@ -14491,7 +14493,7 @@
       <c r="C48" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="D48" s="246" t="s">
+      <c r="D48" s="244" t="s">
         <v>265</v>
       </c>
     </row>
@@ -14505,7 +14507,7 @@
       <c r="C49" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="D49" s="247" t="s">
+      <c r="D49" s="245" t="s">
         <v>267</v>
       </c>
     </row>
@@ -14519,7 +14521,7 @@
       <c r="C50" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="D50" s="245" t="s">
+      <c r="D50" s="243" t="s">
         <v>269</v>
       </c>
     </row>
@@ -14533,7 +14535,7 @@
       <c r="C51" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="D51" s="246" t="s">
+      <c r="D51" s="244" t="s">
         <v>271</v>
       </c>
     </row>
@@ -14547,7 +14549,7 @@
       <c r="C52" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="D52" s="246" t="s">
+      <c r="D52" s="244" t="s">
         <v>273</v>
       </c>
     </row>
@@ -14561,7 +14563,7 @@
       <c r="C53" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="D53" s="246" t="s">
+      <c r="D53" s="244" t="s">
         <v>275</v>
       </c>
     </row>
@@ -14575,7 +14577,7 @@
       <c r="C54" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="D54" s="246" t="s">
+      <c r="D54" s="244" t="s">
         <v>277</v>
       </c>
     </row>
@@ -14589,7 +14591,7 @@
       <c r="C55" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="D55" s="246" t="s">
+      <c r="D55" s="244" t="s">
         <v>279</v>
       </c>
     </row>
@@ -14603,7 +14605,7 @@
       <c r="C56" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="D56" s="246" t="s">
+      <c r="D56" s="244" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14617,8 +14619,8 @@
       <c r="C57" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="D57" s="247" t="s">
-        <v>1283</v>
+      <c r="D57" s="245" t="s">
+        <v>1276</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14631,7 +14633,7 @@
       <c r="C58" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="D58" s="245" t="s">
+      <c r="D58" s="243" t="s">
         <v>284</v>
       </c>
     </row>
@@ -14645,7 +14647,7 @@
       <c r="C59" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="D59" s="246" t="s">
+      <c r="D59" s="244" t="s">
         <v>286</v>
       </c>
     </row>
@@ -14659,7 +14661,7 @@
       <c r="C60" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="D60" s="246" t="s">
+      <c r="D60" s="244" t="s">
         <v>288</v>
       </c>
     </row>
@@ -14673,7 +14675,7 @@
       <c r="C61" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="D61" s="246" t="s">
+      <c r="D61" s="244" t="s">
         <v>290</v>
       </c>
     </row>
@@ -14687,7 +14689,7 @@
       <c r="C62" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="D62" s="246" t="s">
+      <c r="D62" s="244" t="s">
         <v>292</v>
       </c>
     </row>
@@ -14701,7 +14703,7 @@
       <c r="C63" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="D63" s="246" t="s">
+      <c r="D63" s="244" t="s">
         <v>294</v>
       </c>
     </row>
@@ -14715,7 +14717,7 @@
       <c r="C64" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="D64" s="246" t="s">
+      <c r="D64" s="244" t="s">
         <v>296</v>
       </c>
     </row>
@@ -14729,7 +14731,7 @@
       <c r="C65" s="112" t="s">
         <v>297</v>
       </c>
-      <c r="D65" s="247" t="s">
+      <c r="D65" s="245" t="s">
         <v>298</v>
       </c>
     </row>
@@ -14743,11 +14745,11 @@
       <c r="C66" s="97" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="242" t="s">
+      <c r="D66" s="244" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="102" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="240">
         <v>66</v>
       </c>
@@ -14757,7 +14759,7 @@
       <c r="C67" s="99" t="s">
         <v>301</v>
       </c>
-      <c r="D67" s="243" t="s">
+      <c r="D67" s="245" t="s">
         <v>302</v>
       </c>
     </row>
@@ -14766,13 +14768,13 @@
         <v>0</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="C68" s="101" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D68" s="244" t="s">
-        <v>1284</v>
+        <v>1275</v>
+      </c>
+      <c r="D68" s="242" t="s">
+        <v>1277</v>
       </c>
     </row>
   </sheetData>
@@ -16285,7 +16287,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.25" style="32" customWidth="1"/>
@@ -16297,7 +16299,7 @@
     <col min="7" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="106" t="s">
         <v>0</v>
       </c>
@@ -16316,11 +16318,8 @@
       <c r="F1" s="119" t="s">
         <v>510</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="103">
         <v>1</v>
       </c>
@@ -16340,7 +16339,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="104">
         <v>2</v>
       </c>
@@ -16360,7 +16359,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="104">
         <v>3</v>
       </c>
@@ -16380,7 +16379,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="104">
         <v>4</v>
       </c>
@@ -16400,7 +16399,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="104">
         <v>5</v>
       </c>
@@ -16420,7 +16419,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="104">
         <v>6</v>
       </c>
@@ -16440,7 +16439,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="104">
         <v>7</v>
       </c>
@@ -16460,7 +16459,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="111">
         <v>8</v>
       </c>
@@ -16480,7 +16479,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="103">
         <v>9</v>
       </c>
@@ -16500,7 +16499,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="104">
         <v>10</v>
       </c>
@@ -16520,7 +16519,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="104">
         <v>11</v>
       </c>
@@ -16540,7 +16539,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="104">
         <v>12</v>
       </c>
@@ -16560,7 +16559,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="104">
         <v>13</v>
       </c>
@@ -16580,7 +16579,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="104">
         <v>14</v>
       </c>
@@ -16600,7 +16599,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="104">
         <v>15</v>
       </c>
@@ -16620,7 +16619,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="105">
         <v>16</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121">
         <v>17</v>
       </c>
@@ -16660,7 +16659,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="104">
         <v>18</v>
       </c>
@@ -16680,7 +16679,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="104">
         <v>19</v>
       </c>
@@ -16700,7 +16699,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="104">
         <v>20</v>
       </c>
@@ -16720,7 +16719,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="104">
         <v>21</v>
       </c>
@@ -16740,7 +16739,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="104">
         <v>22</v>
       </c>
@@ -16760,7 +16759,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="104">
         <v>23</v>
       </c>
@@ -16777,13 +16776,10 @@
         <v>1104</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="111">
         <v>24</v>
       </c>
@@ -16791,19 +16787,19 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D25" s="101" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E25" s="89" t="s">
         <v>1107</v>
       </c>
-      <c r="D25" s="101" t="s">
+      <c r="F25" s="112" t="s">
         <v>1108</v>
       </c>
-      <c r="E25" s="89" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F25" s="112" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="103">
         <v>25</v>
       </c>
@@ -16811,19 +16807,19 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D26" s="97" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E26" s="86" t="s">
         <v>1111</v>
       </c>
-      <c r="D26" s="97" t="s">
+      <c r="F26" s="97" t="s">
         <v>1112</v>
       </c>
-      <c r="E26" s="86" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F26" s="97" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="104">
         <v>26</v>
       </c>
@@ -16831,19 +16827,19 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D27" s="99" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E27" s="87" t="s">
         <v>1115</v>
       </c>
-      <c r="D27" s="99" t="s">
+      <c r="F27" s="99" t="s">
         <v>1116</v>
       </c>
-      <c r="E27" s="87" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F27" s="99" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="104">
         <v>27</v>
       </c>
@@ -16851,19 +16847,19 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D28" s="99" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E28" s="87" t="s">
         <v>1119</v>
       </c>
-      <c r="D28" s="99" t="s">
+      <c r="F28" s="99" t="s">
         <v>1120</v>
       </c>
-      <c r="E28" s="87" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F28" s="99" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="104">
         <v>28</v>
       </c>
@@ -16871,19 +16867,19 @@
         <v>75</v>
       </c>
       <c r="C29" s="87" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D29" s="99" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E29" s="87" t="s">
         <v>1123</v>
       </c>
-      <c r="D29" s="99" t="s">
+      <c r="F29" s="99" t="s">
         <v>1124</v>
       </c>
-      <c r="E29" s="87" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F29" s="99" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="104">
         <v>29</v>
       </c>
@@ -16891,19 +16887,19 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D30" s="99" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E30" s="87" t="s">
         <v>1127</v>
       </c>
-      <c r="D30" s="99" t="s">
+      <c r="F30" s="99" t="s">
         <v>1128</v>
       </c>
-      <c r="E30" s="87" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F30" s="99" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="104">
         <v>30</v>
       </c>
@@ -16911,19 +16907,19 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D31" s="99" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E31" s="87" t="s">
         <v>1131</v>
       </c>
-      <c r="D31" s="99" t="s">
+      <c r="F31" s="99" t="s">
         <v>1132</v>
       </c>
-      <c r="E31" s="87" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F31" s="99" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="104">
         <v>31</v>
       </c>
@@ -16931,19 +16927,19 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D32" s="99" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E32" s="87" t="s">
         <v>1135</v>
       </c>
-      <c r="D32" s="99" t="s">
+      <c r="F32" s="99" t="s">
         <v>1136</v>
       </c>
-      <c r="E32" s="87" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F32" s="99" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="105">
         <v>32</v>
       </c>
@@ -16951,19 +16947,19 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D33" s="101" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E33" s="88" t="s">
         <v>1139</v>
       </c>
-      <c r="D33" s="101" t="s">
+      <c r="F33" s="101" t="s">
         <v>1140</v>
       </c>
-      <c r="E33" s="88" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F33" s="101" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="103">
         <v>33</v>
       </c>
@@ -16971,19 +16967,19 @@
         <v>85</v>
       </c>
       <c r="C34" s="37" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E34" s="86" t="s">
         <v>1143</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="F34" s="97" t="s">
         <v>1144</v>
       </c>
-      <c r="E34" s="86" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F34" s="97" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="104">
         <v>34</v>
       </c>
@@ -16991,19 +16987,19 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D35" s="99" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E35" s="87" t="s">
         <v>1147</v>
       </c>
-      <c r="D35" s="99" t="s">
+      <c r="F35" s="99" t="s">
         <v>1148</v>
       </c>
-      <c r="E35" s="87" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F35" s="99" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="104">
         <v>35</v>
       </c>
@@ -17011,19 +17007,19 @@
         <v>90</v>
       </c>
       <c r="C36" s="157" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D36" s="99" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E36" s="87" t="s">
         <v>1151</v>
       </c>
-      <c r="D36" s="99" t="s">
+      <c r="F36" s="99" t="s">
         <v>1152</v>
       </c>
-      <c r="E36" s="87" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F36" s="99" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="104">
         <v>36</v>
       </c>
@@ -17031,19 +17027,19 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D37" s="99" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E37" s="87" t="s">
         <v>1155</v>
       </c>
-      <c r="D37" s="99" t="s">
+      <c r="F37" s="99" t="s">
         <v>1156</v>
       </c>
-      <c r="E37" s="87" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F37" s="99" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="104">
         <v>37</v>
       </c>
@@ -17051,19 +17047,19 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D38" s="99" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E38" s="87" t="s">
         <v>1159</v>
       </c>
-      <c r="D38" s="99" t="s">
+      <c r="F38" s="99" t="s">
         <v>1160</v>
       </c>
-      <c r="E38" s="87" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F38" s="99" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="104">
         <v>38</v>
       </c>
@@ -17071,19 +17067,19 @@
         <v>97</v>
       </c>
       <c r="C39" s="102" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D39" s="99" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E39" s="87" t="s">
         <v>1163</v>
       </c>
-      <c r="D39" s="99" t="s">
+      <c r="F39" s="99" t="s">
         <v>1164</v>
       </c>
-      <c r="E39" s="87" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F39" s="99" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="104">
         <v>39</v>
       </c>
@@ -17091,19 +17087,19 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D40" s="99" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E40" s="87" t="s">
         <v>1167</v>
       </c>
-      <c r="D40" s="99" t="s">
+      <c r="F40" s="99" t="s">
         <v>1168</v>
       </c>
-      <c r="E40" s="87" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F40" s="99" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="105">
         <v>40</v>
       </c>
@@ -17111,19 +17107,19 @@
         <v>101</v>
       </c>
       <c r="C41" s="89" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D41" s="206" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E41" s="88" t="s">
         <v>1171</v>
       </c>
-      <c r="D41" s="206" t="s">
+      <c r="F41" s="101" t="s">
         <v>1172</v>
       </c>
-      <c r="E41" s="88" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F41" s="101" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="121">
         <v>41</v>
       </c>
@@ -17131,19 +17127,19 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D42" s="97" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E42" s="37" t="s">
         <v>1175</v>
       </c>
-      <c r="D42" s="97" t="s">
+      <c r="F42" s="41" t="s">
         <v>1176</v>
       </c>
-      <c r="E42" s="37" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F42" s="41" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="104">
         <v>42</v>
       </c>
@@ -17151,19 +17147,19 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D43" s="99" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E43" s="87" t="s">
         <v>1179</v>
       </c>
-      <c r="D43" s="99" t="s">
+      <c r="F43" s="99" t="s">
         <v>1180</v>
       </c>
-      <c r="E43" s="87" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F43" s="99" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="104">
         <v>43</v>
       </c>
@@ -17171,19 +17167,19 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D44" s="99" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E44" s="87" t="s">
         <v>1183</v>
       </c>
-      <c r="D44" s="99" t="s">
+      <c r="F44" s="99" t="s">
         <v>1184</v>
       </c>
-      <c r="E44" s="87" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F44" s="99" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="104">
         <v>44</v>
       </c>
@@ -17191,19 +17187,19 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D45" s="99" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E45" s="87" t="s">
         <v>1187</v>
       </c>
-      <c r="D45" s="99" t="s">
+      <c r="F45" s="99" t="s">
         <v>1188</v>
       </c>
-      <c r="E45" s="87" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F45" s="99" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="104">
         <v>45</v>
       </c>
@@ -17211,22 +17207,19 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D46" s="99" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E46" s="87" t="s">
         <v>1191</v>
       </c>
-      <c r="D46" s="99" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E46" s="87" t="s">
-        <v>1193</v>
-      </c>
       <c r="F46" s="99" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="104">
         <v>46</v>
       </c>
@@ -17234,19 +17227,19 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D47" s="99" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="F47" s="99" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="104">
         <v>47</v>
       </c>
@@ -17254,19 +17247,16 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="D48" s="99" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="E48" s="87" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="F48" s="99" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>1204</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17277,16 +17267,16 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="D49" s="101" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="E49" s="89" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="F49" s="112" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17297,16 +17287,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="E50" s="86" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="F50" s="97" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17317,16 +17307,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="E51" s="87" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="F51" s="99" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17337,16 +17327,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="D52" s="99" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="E52" s="87" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="F52" s="99" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17357,16 +17347,16 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="E53" s="87" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="F53" s="99" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17377,16 +17367,16 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="E54" s="87" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="F54" s="99" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17397,16 +17387,16 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="E55" s="87" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="F55" s="99" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17417,16 +17407,16 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="D56" s="99" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="E56" s="87" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="F56" s="99" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17437,16 +17427,16 @@
         <v>143</v>
       </c>
       <c r="C57" s="89" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="D57" s="112" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="E57" s="88" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="F57" s="101" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17457,16 +17447,16 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="D58" s="97" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="F58" s="41" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17477,16 +17467,16 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="D59" s="99" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="E59" s="87" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="F59" s="99" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17497,16 +17487,16 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="D60" s="99" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="E60" s="87" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="F60" s="99" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17517,16 +17507,16 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="D61" s="99" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="E61" s="87" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="F61" s="99" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17537,16 +17527,16 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="D62" s="99" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E62" s="87" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="F62" s="99" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17557,16 +17547,16 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="E63" s="87" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="F63" s="99" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17577,76 +17567,96 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="D64" s="99" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="E64" s="87" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="F64" s="99" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="111">
         <v>64</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="89" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="88" t="s">
+      <c r="C65" s="89" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D65" s="112" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E65" s="89" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F65" s="112" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="19">
+        <v>65</v>
+      </c>
+      <c r="B66" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" s="86" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D66" s="86" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E66" s="86" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F66" s="97" t="s">
         <v>1269</v>
       </c>
-      <c r="D65" s="101" t="s">
+    </row>
+    <row r="67" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="20">
+        <v>66</v>
+      </c>
+      <c r="B67" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" s="87" t="s">
         <v>1270</v>
       </c>
-      <c r="E65" s="89" t="s">
+      <c r="D67" s="87" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E67" s="87" t="s">
         <v>1271</v>
       </c>
-      <c r="F65" s="112" t="s">
+      <c r="F67" s="99" t="s">
         <v>1272</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="103">
-        <v>65</v>
-      </c>
-      <c r="B66" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C66" s="86" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D66" s="97" t="s">
-        <v>1274</v>
-      </c>
-      <c r="E66" s="86" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F66" s="97" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="111">
-        <v>66</v>
-      </c>
-      <c r="B67" s="89" t="s">
-        <v>168</v>
-      </c>
-      <c r="C67" s="88" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D67" s="101" t="s">
-        <v>1274</v>
-      </c>
-      <c r="E67" s="88" t="s">
-        <v>1278</v>
-      </c>
-      <c r="F67" s="101" t="s">
-        <v>1279</v>
+    <row r="68" spans="1:6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="21">
+        <v>0</v>
+      </c>
+      <c r="B68" s="88" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C68" s="88" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D68" s="88" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E68" s="88" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F68" s="101" t="s">
+        <v>1862</v>
       </c>
     </row>
   </sheetData>
@@ -17677,7 +17687,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="C1" s="211" t="s">
         <v>511</v>
@@ -17719,17 +17729,17 @@
       <c r="B3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="248" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D3" s="249" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E3" s="250" t="s">
-        <v>1418</v>
-      </c>
-      <c r="F3" s="251" t="s">
-        <v>1419</v>
+      <c r="C3" s="246" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D3" s="247" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E3" s="248" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F3" s="249" t="s">
+        <v>1412</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17919,17 +17929,17 @@
       <c r="B13" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="255" t="s">
-        <v>1570</v>
-      </c>
-      <c r="D13" s="256" t="s">
-        <v>1571</v>
+      <c r="C13" s="253" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D13" s="254" t="s">
+        <v>1564</v>
       </c>
       <c r="E13" s="140" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F13" s="251" t="s">
-        <v>1573</v>
+        <v>1565</v>
+      </c>
+      <c r="F13" s="249" t="s">
+        <v>1566</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18025,8 +18035,8 @@
       <c r="D18" s="192" t="s">
         <v>620</v>
       </c>
-      <c r="E18" s="253" t="s">
-        <v>1449</v>
+      <c r="E18" s="251" t="s">
+        <v>1442</v>
       </c>
       <c r="F18" s="182" t="s">
         <v>621</v>
@@ -18142,8 +18152,8 @@
       <c r="C24" s="194" t="s">
         <v>642</v>
       </c>
-      <c r="D24" s="256" t="s">
-        <v>1450</v>
+      <c r="D24" s="254" t="s">
+        <v>1443</v>
       </c>
       <c r="E24" s="196" t="s">
         <v>643</v>
@@ -18179,17 +18189,17 @@
       <c r="B26" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="252" t="s">
-        <v>1420</v>
+      <c r="C26" s="250" t="s">
+        <v>1413</v>
       </c>
       <c r="D26" s="192" t="s">
         <v>649</v>
       </c>
-      <c r="E26" s="253" t="s">
-        <v>1448</v>
-      </c>
-      <c r="F26" s="254" t="s">
-        <v>1421</v>
+      <c r="E26" s="251" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F26" s="252" t="s">
+        <v>1414</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18279,17 +18289,17 @@
       <c r="B31" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="255" t="s">
-        <v>1422</v>
-      </c>
-      <c r="D31" s="256" t="s">
-        <v>1423</v>
+      <c r="C31" s="253" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D31" s="254" t="s">
+        <v>1416</v>
       </c>
       <c r="E31" s="196" t="s">
         <v>666</v>
       </c>
-      <c r="F31" s="251" t="s">
-        <v>1424</v>
+      <c r="F31" s="249" t="s">
+        <v>1417</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18379,17 +18389,17 @@
       <c r="B36" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C36" s="255" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D36" s="256" t="s">
-        <v>1426</v>
+      <c r="C36" s="253" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D36" s="254" t="s">
+        <v>1419</v>
       </c>
       <c r="E36" s="140" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F36" s="251" t="s">
-        <v>1428</v>
+        <v>1420</v>
+      </c>
+      <c r="F36" s="249" t="s">
+        <v>1421</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18399,14 +18409,14 @@
       <c r="B37" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="255" t="s">
-        <v>1429</v>
+      <c r="C37" s="253" t="s">
+        <v>1422</v>
       </c>
       <c r="D37" s="195" t="s">
         <v>683</v>
       </c>
       <c r="E37" s="140" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
       <c r="F37" s="186" t="s">
         <v>684</v>
@@ -18428,8 +18438,8 @@
       <c r="E38" s="196" t="s">
         <v>687</v>
       </c>
-      <c r="F38" s="251" t="s">
-        <v>1431</v>
+      <c r="F38" s="249" t="s">
+        <v>1424</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18499,8 +18509,8 @@
       <c r="B42" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="252" t="s">
-        <v>1432</v>
+      <c r="C42" s="250" t="s">
+        <v>1425</v>
       </c>
       <c r="D42" s="192" t="s">
         <v>700</v>
@@ -18579,17 +18589,17 @@
       <c r="B46" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="255" t="s">
-        <v>1433</v>
+      <c r="C46" s="253" t="s">
+        <v>1426</v>
       </c>
       <c r="D46" s="195" t="s">
         <v>715</v>
       </c>
       <c r="E46" s="140" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F46" s="251" t="s">
-        <v>1435</v>
+        <v>1427</v>
+      </c>
+      <c r="F46" s="249" t="s">
+        <v>1428</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18599,17 +18609,17 @@
       <c r="B47" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="255" t="s">
-        <v>1436</v>
-      </c>
-      <c r="D47" s="256" t="s">
-        <v>1437</v>
+      <c r="C47" s="253" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D47" s="254" t="s">
+        <v>1430</v>
       </c>
       <c r="E47" s="140" t="s">
-        <v>1438</v>
-      </c>
-      <c r="F47" s="251" t="s">
-        <v>1439</v>
+        <v>1431</v>
+      </c>
+      <c r="F47" s="249" t="s">
+        <v>1432</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18639,17 +18649,17 @@
       <c r="B49" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="257" t="s">
-        <v>1440</v>
-      </c>
-      <c r="D49" s="258" t="s">
-        <v>1441</v>
-      </c>
-      <c r="E49" s="259" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F49" s="260" t="s">
-        <v>1443</v>
+      <c r="C49" s="255" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D49" s="256" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E49" s="257" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F49" s="258" t="s">
+        <v>1436</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18659,17 +18669,17 @@
       <c r="B50" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C50" s="252" t="s">
-        <v>1823</v>
-      </c>
-      <c r="D50" s="293" t="s">
-        <v>1824</v>
-      </c>
-      <c r="E50" s="253" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F50" s="254" t="s">
-        <v>1826</v>
+      <c r="C50" s="250" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D50" s="289" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E50" s="251" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F50" s="252" t="s">
+        <v>1819</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18679,17 +18689,17 @@
       <c r="B51" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="255" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D51" s="256" t="s">
-        <v>1828</v>
+      <c r="C51" s="253" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D51" s="254" t="s">
+        <v>1821</v>
       </c>
       <c r="E51" s="140" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F51" s="251" t="s">
-        <v>1830</v>
+        <v>1822</v>
+      </c>
+      <c r="F51" s="249" t="s">
+        <v>1823</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18699,17 +18709,17 @@
       <c r="B52" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="C52" s="255" t="s">
-        <v>1831</v>
-      </c>
-      <c r="D52" s="256" t="s">
-        <v>1832</v>
+      <c r="C52" s="253" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D52" s="254" t="s">
+        <v>1825</v>
       </c>
       <c r="E52" s="140" t="s">
-        <v>1833</v>
-      </c>
-      <c r="F52" s="251" t="s">
-        <v>1834</v>
+        <v>1826</v>
+      </c>
+      <c r="F52" s="249" t="s">
+        <v>1827</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18768,8 +18778,8 @@
       <c r="E55" s="196" t="s">
         <v>730</v>
       </c>
-      <c r="F55" s="251" t="s">
-        <v>1444</v>
+      <c r="F55" s="249" t="s">
+        <v>1437</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18779,14 +18789,14 @@
       <c r="B56" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="C56" s="255" t="s">
-        <v>1445</v>
-      </c>
-      <c r="D56" s="256" t="s">
-        <v>1446</v>
+      <c r="C56" s="253" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D56" s="254" t="s">
+        <v>1439</v>
       </c>
       <c r="E56" s="140" t="s">
-        <v>1447</v>
+        <v>1440</v>
       </c>
       <c r="F56" s="186" t="s">
         <v>731</v>
@@ -18805,8 +18815,8 @@
       <c r="D57" s="198" t="s">
         <v>733</v>
       </c>
-      <c r="E57" s="259" t="s">
-        <v>1451</v>
+      <c r="E57" s="257" t="s">
+        <v>1444</v>
       </c>
       <c r="F57" s="190" t="s">
         <v>734</v>
@@ -18899,11 +18909,11 @@
       <c r="B62" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="C62" s="255" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D62" s="256" t="s">
-        <v>1453</v>
+      <c r="C62" s="253" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D62" s="254" t="s">
+        <v>1446</v>
       </c>
       <c r="E62" s="196" t="s">
         <v>751</v>
@@ -18939,17 +18949,17 @@
       <c r="B64" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="C64" s="255" t="s">
-        <v>1835</v>
-      </c>
-      <c r="D64" s="256" t="s">
-        <v>1836</v>
+      <c r="C64" s="253" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D64" s="254" t="s">
+        <v>1829</v>
       </c>
       <c r="E64" s="140" t="s">
-        <v>1837</v>
-      </c>
-      <c r="F64" s="251" t="s">
-        <v>1838</v>
+        <v>1830</v>
+      </c>
+      <c r="F64" s="249" t="s">
+        <v>1831</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18979,17 +18989,17 @@
       <c r="B66" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C66" s="252" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D66" s="293" t="s">
-        <v>1840</v>
+      <c r="C66" s="250" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D66" s="289" t="s">
+        <v>1833</v>
       </c>
       <c r="E66" s="193" t="s">
         <v>761</v>
       </c>
-      <c r="F66" s="254" t="s">
-        <v>1841</v>
+      <c r="F66" s="252" t="s">
+        <v>1834</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18999,11 +19009,11 @@
       <c r="B67" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="C67" s="257" t="s">
-        <v>1842</v>
-      </c>
-      <c r="D67" s="258" t="s">
-        <v>1843</v>
+      <c r="C67" s="255" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D67" s="256" t="s">
+        <v>1836</v>
       </c>
       <c r="E67" s="199" t="s">
         <v>762</v>
@@ -19017,19 +19027,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C68" s="268" t="s">
-        <v>1844</v>
-      </c>
-      <c r="D68" s="269" t="s">
-        <v>1845</v>
-      </c>
-      <c r="E68" s="270" t="s">
-        <v>1846</v>
-      </c>
-      <c r="F68" s="271" t="s">
-        <v>1847</v>
+        <v>1273</v>
+      </c>
+      <c r="C68" s="264" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D68" s="265" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E68" s="266" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F68" s="267" t="s">
+        <v>1840</v>
       </c>
     </row>
   </sheetData>
@@ -20043,7 +20053,7 @@
         <v>122</v>
       </c>
       <c r="C50" s="224" t="s">
-        <v>1848</v>
+        <v>1841</v>
       </c>
       <c r="D50" s="225" t="s">
         <v>956</v>
@@ -20063,16 +20073,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="227" t="s">
-        <v>1849</v>
+        <v>1842</v>
       </c>
       <c r="D51" s="228" t="s">
-        <v>1850</v>
+        <v>1843</v>
       </c>
       <c r="E51" s="229" t="s">
-        <v>1851</v>
+        <v>1844</v>
       </c>
       <c r="F51" s="219" t="s">
-        <v>1852</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20083,16 +20093,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="227" t="s">
-        <v>1853</v>
+        <v>1846</v>
       </c>
       <c r="D52" s="228" t="s">
-        <v>1854</v>
+        <v>1847</v>
       </c>
       <c r="E52" s="229" t="s">
-        <v>1855</v>
+        <v>1848</v>
       </c>
       <c r="F52" s="219" t="s">
-        <v>1856</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20323,7 +20333,7 @@
         <v>160</v>
       </c>
       <c r="C64" s="227" t="s">
-        <v>1857</v>
+        <v>1850</v>
       </c>
       <c r="D64" s="228" t="s">
         <v>1003</v>
@@ -20356,63 +20366,63 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="294">
+      <c r="A66" s="290">
         <v>65</v>
       </c>
       <c r="B66" s="76" t="s">
         <v>165</v>
       </c>
       <c r="C66" s="212" t="s">
-        <v>1858</v>
+        <v>1851</v>
       </c>
       <c r="D66" s="213" t="s">
         <v>1010</v>
       </c>
-      <c r="E66" s="302" t="s">
+      <c r="E66" s="298" t="s">
         <v>1011</v>
       </c>
-      <c r="F66" s="299" t="s">
+      <c r="F66" s="295" t="s">
         <v>1012</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="295">
+      <c r="A67" s="291">
         <v>66</v>
       </c>
       <c r="B67" s="70" t="s">
         <v>168</v>
       </c>
       <c r="C67" s="216" t="s">
-        <v>1859</v>
+        <v>1852</v>
       </c>
       <c r="D67" s="217" t="s">
         <v>1013</v>
       </c>
-      <c r="E67" s="303" t="s">
-        <v>1860</v>
-      </c>
-      <c r="F67" s="300" t="s">
-        <v>1861</v>
+      <c r="E67" s="299" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F67" s="296" t="s">
+        <v>1854</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="296">
+      <c r="A68" s="292">
         <v>0</v>
       </c>
       <c r="B68" s="77" t="s">
-        <v>1862</v>
-      </c>
-      <c r="C68" s="297" t="s">
-        <v>1863</v>
-      </c>
-      <c r="D68" s="298" t="s">
-        <v>1863</v>
-      </c>
-      <c r="E68" s="304" t="s">
-        <v>1863</v>
-      </c>
-      <c r="F68" s="301" t="s">
-        <v>1863</v>
+        <v>1855</v>
+      </c>
+      <c r="C68" s="293" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D68" s="294" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E68" s="300" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F68" s="297" t="s">
+        <v>1856</v>
       </c>
     </row>
   </sheetData>

--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="1864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="1850">
   <si>
     <t>編號</t>
   </si>
@@ -5477,10 +5477,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>靈魂屬魂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>魄、意識</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5489,10 +5485,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>忘、斷片</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>分際、分寸</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5513,14 +5505,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>界域屬域</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>界域屬域</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>目標、前進、前方、朝著</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5533,14 +5517,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>暫斷屬封</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>暫斷屬封</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>隔離、限制、阻隔、暫停、暫斷</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5629,18 +5605,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>生死歸生</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>愛心歸愛</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>語韻歸韻</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>活、生命</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5653,10 +5617,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>惡化、發作、感染</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>僵持、苟延</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5697,30 +5657,10 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>生死歸生、老死歸死</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>老死歸死、死心歸心</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>愛心歸愛、心病歸病</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>沉默、語病</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>語韻歸韻、語病歸語</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>心病歸病、語病歸語</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>表率、典範、茂盛、茁壯</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5757,30 +5697,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>花草屬草、花枝是動物</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>草根屬根</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>果實屬實</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>樹根屬根、樹枝屬枝</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>樹根屬根</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>樹枝屬枝</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>幼稚、枯槁、傾倒</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5845,22 +5761,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>金玉屬玉、玉石屬石</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>晶石偏石</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>鑽石偏鑽</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>礦石偏礦、金礦偏礦</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>額外留意</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5869,14 +5769,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>玉石屬石、晶石偏石、礦石偏礦、鑽石偏鑽</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>金玉屬玉、金礦偏礦</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>埋沒、荒廢</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5941,66 +5833,14 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>堆積、蒙蔽、積垢、累贅</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>塵土屬塵</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>衝擊、驚醒、迅速、震撼、突發、驚蟄</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>水氣屬水、火氣屬火、空氣屬氣、地氣屬地</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>水土屬地、水火屬火</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>光暗屬暗</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>雙符文最低</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>雙符文最高</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>滯、塞、閉阻、散逸</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>靈魂屬魂、潛意識歸夢</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>雙符文最高</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>土地屬地、塵土屬塵、水土屬地</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>光明屬光、火光屬光、月光歸地</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>土地偏地、地氣屬地、水土屬地、月光歸地</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>火光屬光、雷火屬雷、水火屬火、星火屬禍</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>描述天體的規律</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6029,14 +5869,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>多例外判斷</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>有固定詞意</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>定論的所有可能</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6057,10 +5889,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>日蝕、遮蔽、暫變、預期、偏差</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>時間、日期、月份、時刻、時間點、曆、行事曆、日常、計時</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6085,14 +5913,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>日光屬光、日月屬星</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>月光屬地、日月屬星</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>天體、軌道、運行</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6101,10 +5921,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>星火屬禍、日月屬星</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>交替、清醒、清晰、日月之間</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6129,10 +5945,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>假、假象、錯覺、海市蜃樓</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>時機、契機、巧合</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6173,27 +5985,11 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>夢幻屬幻</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>隨機、混沌、突變、不可預期、震盪、波動</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>定論、必然、法則</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命歸生</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>雙符文最低</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>事物的起點終點</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -6412,6 +6208,154 @@
   </si>
   <si>
     <t>開始抽張指引籤詩吧</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>發作、感染</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆積、蒙蔽、積垢</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>假、假象、錯覺、海市蜃樓、鏡花水月</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>鏡花水月多幻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>鏡花水月多幻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>日蝕、遮蔽、暫變、預期</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>生老病死多命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>死心是心</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>心病歸病</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>暫斷為封</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>暫斷為封</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>心病為病、語病是語</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>語韻為韻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>語韻為韻、語病為語</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>草根多地</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>水土為地</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>日光為光、月光為暗</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>花枝是動物、花枝招展為花</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>花枝招展為花</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>土地偏地、地氣屬地、水土屬地</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石為鑽</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>水土多地</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>風火雷土多玄</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>無多玄命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>星火為禍</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>空氣為氣</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>星火為禍、日月為星、明星沒有</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>意識歸魂而潛意識歸夢</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>忘、斷片</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例外判斷</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>事物的起點終點</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例外判斷</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例外判斷</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>德是保留字。給未定文字的代表集合。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>鑽石為鑽、月光石是石</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>日光為光、日月為星、日一個單字是星或時</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>月光為暗、日月為星、月一個單字是星或時</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -8326,142 +8270,6 @@
   <dxfs count="55">
     <dxf>
       <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border>
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -8800,6 +8608,142 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -9791,12 +9735,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="表格6" displayName="表格6" ref="A1:F68" totalsRowShown="0">
   <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="5"/>
-    <tableColumn id="2" name="名稱" dataDxfId="4"/>
-    <tableColumn id="6" name="靈魂課題" dataDxfId="3"/>
-    <tableColumn id="7" name="實踐挑戰" dataDxfId="2"/>
-    <tableColumn id="8" name="配套儀式建議" dataDxfId="1"/>
-    <tableColumn id="9" name="能量調和建議" dataDxfId="0"/>
+    <tableColumn id="1" name="編號" dataDxfId="18"/>
+    <tableColumn id="2" name="名稱" dataDxfId="17"/>
+    <tableColumn id="6" name="靈魂課題" dataDxfId="16"/>
+    <tableColumn id="7" name="實踐挑戰" dataDxfId="15"/>
+    <tableColumn id="8" name="配套儀式建議" dataDxfId="14"/>
+    <tableColumn id="9" name="能量調和建議" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9806,27 +9750,27 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="表格7" displayName="表格7" ref="A1:F68" totalsRowShown="0" headerRowCellStyle="40% - 輔色1">
   <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="18"/>
-    <tableColumn id="2" name="符文名稱" dataDxfId="17"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="16" dataCellStyle="20% - 輔色1"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="15" dataCellStyle="40% - 輔色1"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="14" dataCellStyle="20% - 輔色2"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="13" dataCellStyle="40% - 輔色2"/>
+    <tableColumn id="1" name="編號" dataDxfId="12"/>
+    <tableColumn id="2" name="符文名稱" dataDxfId="11"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="10" dataCellStyle="20% - 輔色1"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="9" dataCellStyle="40% - 輔色1"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="8" dataCellStyle="20% - 輔色2"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="7" dataCellStyle="40% - 輔色2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F68" totalsRowShown="0" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F68" totalsRowShown="0" dataDxfId="6">
   <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="11"/>
-    <tableColumn id="2" name="名稱" dataDxfId="10"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="9"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="8"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="7"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="6"/>
+    <tableColumn id="1" name="編號" dataDxfId="5"/>
+    <tableColumn id="2" name="名稱" dataDxfId="4"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="3"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="2"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="1"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11654,7 +11598,7 @@
         <v>36</v>
       </c>
       <c r="H50" s="282" t="s">
-        <v>1769</v>
+        <v>1729</v>
       </c>
       <c r="I50" s="283" t="s">
         <v>1326</v>
@@ -11686,7 +11630,7 @@
         <v>36</v>
       </c>
       <c r="H51" s="277" t="s">
-        <v>1768</v>
+        <v>1728</v>
       </c>
       <c r="I51" s="87" t="s">
         <v>1327</v>
@@ -11718,10 +11662,10 @@
         <v>16</v>
       </c>
       <c r="H52" s="277" t="s">
+        <v>1724</v>
+      </c>
+      <c r="I52" s="270" t="s">
         <v>1764</v>
-      </c>
-      <c r="I52" s="270" t="s">
-        <v>1815</v>
       </c>
       <c r="J52" s="271" t="s">
         <v>1393</v>
@@ -11782,7 +11726,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="277" t="s">
-        <v>1788</v>
+        <v>1743</v>
       </c>
       <c r="I54" s="270" t="s">
         <v>1329</v>
@@ -11910,7 +11854,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="282" t="s">
-        <v>1765</v>
+        <v>1725</v>
       </c>
       <c r="I58" s="283" t="s">
         <v>1333</v>
@@ -11942,7 +11886,7 @@
         <v>36</v>
       </c>
       <c r="H59" s="277" t="s">
-        <v>1766</v>
+        <v>1726</v>
       </c>
       <c r="I59" s="87" t="s">
         <v>1334</v>
@@ -11974,7 +11918,7 @@
         <v>153</v>
       </c>
       <c r="H60" s="277" t="s">
-        <v>1776</v>
+        <v>1734</v>
       </c>
       <c r="I60" s="270" t="s">
         <v>1335</v>
@@ -12006,7 +11950,7 @@
         <v>11</v>
       </c>
       <c r="H61" s="277" t="s">
-        <v>1767</v>
+        <v>1727</v>
       </c>
       <c r="I61" s="87" t="s">
         <v>1336</v>
@@ -12038,7 +11982,7 @@
         <v>36</v>
       </c>
       <c r="H62" s="277" t="s">
-        <v>1775</v>
+        <v>1733</v>
       </c>
       <c r="I62" s="270" t="s">
         <v>1337</v>
@@ -12134,7 +12078,7 @@
         <v>16</v>
       </c>
       <c r="H65" s="279" t="s">
-        <v>1777</v>
+        <v>1735</v>
       </c>
       <c r="I65" s="88" t="s">
         <v>1340</v>
@@ -12166,7 +12110,7 @@
         <v>153</v>
       </c>
       <c r="H66" s="282" t="s">
-        <v>1774</v>
+        <v>1732</v>
       </c>
       <c r="I66" s="283" t="s">
         <v>1627</v>
@@ -12198,7 +12142,7 @@
         <v>153</v>
       </c>
       <c r="H67" s="277" t="s">
-        <v>1773</v>
+        <v>1731</v>
       </c>
       <c r="I67" s="87" t="s">
         <v>1628</v>
@@ -12280,7 +12224,7 @@
         <v>1632</v>
       </c>
       <c r="F1" s="274" t="s">
-        <v>1729</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12291,14 +12235,12 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1662</v>
+        <v>1656</v>
       </c>
       <c r="D2" s="268" t="s">
-        <v>1663</v>
-      </c>
-      <c r="E2" s="268" t="s">
-        <v>1633</v>
-      </c>
+        <v>1657</v>
+      </c>
+      <c r="E2" s="268"/>
       <c r="F2" s="268"/>
     </row>
     <row r="3" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12309,13 +12251,13 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>1668</v>
+        <v>1662</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1758</v>
+        <v>1840</v>
       </c>
       <c r="F3" s="87"/>
     </row>
@@ -12327,10 +12269,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1664</v>
+        <v>1658</v>
       </c>
       <c r="D4" s="270" t="s">
-        <v>1665</v>
+        <v>1659</v>
       </c>
       <c r="E4" s="270"/>
       <c r="F4" s="270"/>
@@ -12343,13 +12285,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>1636</v>
+        <v>1841</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1666</v>
+        <v>1660</v>
       </c>
       <c r="F5" s="87"/>
     </row>
@@ -12361,14 +12303,12 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="D6" s="270" t="s">
-        <v>1638</v>
-      </c>
-      <c r="E6" s="270" t="s">
-        <v>1642</v>
-      </c>
+        <v>1636</v>
+      </c>
+      <c r="E6" s="270"/>
       <c r="F6" s="270"/>
     </row>
     <row r="7" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12379,14 +12319,12 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>1669</v>
-      </c>
-      <c r="E7" s="87" t="s">
-        <v>1643</v>
-      </c>
+        <v>1663</v>
+      </c>
+      <c r="E7" s="87"/>
       <c r="F7" s="87"/>
     </row>
     <row r="8" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12397,12 +12335,14 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1745</v>
+        <v>1718</v>
       </c>
       <c r="D8" s="270" t="s">
-        <v>1640</v>
-      </c>
-      <c r="E8" s="270"/>
+        <v>1638</v>
+      </c>
+      <c r="E8" s="270" t="s">
+        <v>1817</v>
+      </c>
       <c r="F8" s="270"/>
     </row>
     <row r="9" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12413,10 +12353,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1667</v>
+        <v>1661</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E9" s="88"/>
       <c r="F9" s="88"/>
@@ -12429,10 +12369,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="D10" s="268" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="E10" s="268"/>
       <c r="F10" s="268"/>
@@ -12445,13 +12385,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1658</v>
+        <v>1652</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1647</v>
+        <v>1822</v>
       </c>
       <c r="F11" s="87"/>
     </row>
@@ -12463,13 +12403,13 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1649</v>
+        <v>1643</v>
       </c>
       <c r="D12" s="270" t="s">
-        <v>1650</v>
+        <v>1644</v>
       </c>
       <c r="E12" s="270" t="s">
-        <v>1648</v>
+        <v>1823</v>
       </c>
       <c r="F12" s="270"/>
     </row>
@@ -12481,16 +12421,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1660</v>
+        <v>1654</v>
       </c>
       <c r="D13" s="87" t="s">
-        <v>1651</v>
+        <v>1645</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1659</v>
+        <v>1653</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>1730</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12501,13 +12441,13 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="D14" s="270" t="s">
         <v>1278</v>
       </c>
       <c r="E14" s="270" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="F14" s="270"/>
     </row>
@@ -12519,10 +12459,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1661</v>
+        <v>1655</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>1654</v>
+        <v>1648</v>
       </c>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
@@ -12535,13 +12475,13 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1655</v>
+        <v>1649</v>
       </c>
       <c r="D16" s="270" t="s">
-        <v>1656</v>
+        <v>1650</v>
       </c>
       <c r="E16" s="270" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="F16" s="270"/>
     </row>
@@ -12553,10 +12493,10 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1670</v>
+        <v>1664</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>1657</v>
+        <v>1651</v>
       </c>
       <c r="E17" s="88"/>
       <c r="F17" s="88"/>
@@ -12569,13 +12509,13 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1674</v>
+        <v>1665</v>
       </c>
       <c r="D18" s="268" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
       <c r="E18" s="268" t="s">
-        <v>1671</v>
+        <v>1819</v>
       </c>
       <c r="F18" s="268"/>
     </row>
@@ -12587,14 +12527,12 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1683</v>
+        <v>1673</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>1684</v>
-      </c>
-      <c r="E19" s="87" t="s">
-        <v>1688</v>
-      </c>
+        <v>1674</v>
+      </c>
+      <c r="E19" s="87"/>
       <c r="F19" s="87"/>
     </row>
     <row r="20" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12605,13 +12543,13 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="D20" s="270" t="s">
-        <v>1677</v>
+        <v>1813</v>
       </c>
       <c r="E20" s="270" t="s">
-        <v>1693</v>
+        <v>1824</v>
       </c>
       <c r="F20" s="270"/>
     </row>
@@ -12623,13 +12561,13 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1685</v>
+        <v>1675</v>
       </c>
       <c r="D21" s="87" t="s">
-        <v>1678</v>
+        <v>1668</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1689</v>
+        <v>1820</v>
       </c>
       <c r="F21" s="87"/>
     </row>
@@ -12641,13 +12579,13 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1679</v>
+        <v>1669</v>
       </c>
       <c r="D22" s="270" t="s">
-        <v>1680</v>
+        <v>1670</v>
       </c>
       <c r="E22" s="270" t="s">
-        <v>1690</v>
+        <v>1821</v>
       </c>
       <c r="F22" s="270"/>
     </row>
@@ -12659,14 +12597,12 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1681</v>
+        <v>1671</v>
       </c>
       <c r="D23" s="87" t="s">
-        <v>1682</v>
-      </c>
-      <c r="E23" s="87" t="s">
         <v>1672</v>
       </c>
+      <c r="E23" s="87"/>
       <c r="F23" s="87"/>
     </row>
     <row r="24" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12677,13 +12613,13 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1687</v>
+        <v>1677</v>
       </c>
       <c r="D24" s="270" t="s">
-        <v>1691</v>
+        <v>1678</v>
       </c>
       <c r="E24" s="270" t="s">
-        <v>1692</v>
+        <v>1826</v>
       </c>
       <c r="F24" s="270"/>
     </row>
@@ -12695,13 +12631,13 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1698</v>
+        <v>1683</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>1686</v>
+        <v>1676</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>1673</v>
+        <v>1825</v>
       </c>
       <c r="F25" s="88"/>
     </row>
@@ -12713,17 +12649,13 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1694</v>
+        <v>1679</v>
       </c>
       <c r="D26" s="268" t="s">
-        <v>1709</v>
-      </c>
-      <c r="E26" s="268" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F26" s="268" t="s">
-        <v>1755</v>
-      </c>
+        <v>1688</v>
+      </c>
+      <c r="E26" s="268"/>
+      <c r="F26" s="268"/>
     </row>
     <row r="27" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="114">
@@ -12733,16 +12665,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1695</v>
+        <v>1680</v>
       </c>
       <c r="D27" s="87" t="s">
-        <v>1696</v>
+        <v>1681</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1703</v>
+        <v>1830</v>
       </c>
       <c r="F27" s="87" t="s">
-        <v>1770</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12753,10 +12685,10 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1697</v>
+        <v>1682</v>
       </c>
       <c r="D28" s="270" t="s">
-        <v>1710</v>
+        <v>1689</v>
       </c>
       <c r="E28" s="270"/>
       <c r="F28" s="270"/>
@@ -12775,7 +12707,7 @@
         <v>1279</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1704</v>
+        <v>1827</v>
       </c>
       <c r="F29" s="87"/>
     </row>
@@ -12787,14 +12719,12 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1699</v>
+        <v>1684</v>
       </c>
       <c r="D30" s="270" t="s">
-        <v>1700</v>
-      </c>
-      <c r="E30" s="270" t="s">
-        <v>1707</v>
-      </c>
+        <v>1685</v>
+      </c>
+      <c r="E30" s="270"/>
       <c r="F30" s="270"/>
     </row>
     <row r="31" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12805,7 +12735,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1711</v>
+        <v>1690</v>
       </c>
       <c r="D31" s="87"/>
       <c r="E31" s="87"/>
@@ -12819,14 +12749,12 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1701</v>
+        <v>1686</v>
       </c>
       <c r="D32" s="270" t="s">
-        <v>1702</v>
-      </c>
-      <c r="E32" s="270" t="s">
-        <v>1705</v>
-      </c>
+        <v>1687</v>
+      </c>
+      <c r="E32" s="270"/>
       <c r="F32" s="270"/>
     </row>
     <row r="33" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12837,11 +12765,11 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1792</v>
+        <v>1746</v>
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="88" t="s">
-        <v>1708</v>
+        <v>1831</v>
       </c>
       <c r="F33" s="88"/>
     </row>
@@ -12853,14 +12781,12 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1712</v>
+        <v>1691</v>
       </c>
       <c r="D34" s="268" t="s">
-        <v>1713</v>
-      </c>
-      <c r="E34" s="268" t="s">
-        <v>1732</v>
-      </c>
+        <v>1692</v>
+      </c>
+      <c r="E34" s="268"/>
       <c r="F34" s="268"/>
     </row>
     <row r="35" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12871,14 +12797,12 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1714</v>
+        <v>1693</v>
       </c>
       <c r="D35" s="87" t="s">
-        <v>1715</v>
-      </c>
-      <c r="E35" s="87" t="s">
-        <v>1725</v>
-      </c>
+        <v>1694</v>
+      </c>
+      <c r="E35" s="87"/>
       <c r="F35" s="87"/>
     </row>
     <row r="36" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12889,14 +12813,12 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1716</v>
+        <v>1695</v>
       </c>
       <c r="D36" s="270" t="s">
-        <v>1717</v>
-      </c>
-      <c r="E36" s="270" t="s">
-        <v>1726</v>
-      </c>
+        <v>1696</v>
+      </c>
+      <c r="E36" s="270"/>
       <c r="F36" s="270"/>
     </row>
     <row r="37" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12907,13 +12829,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1718</v>
+        <v>1697</v>
       </c>
       <c r="D37" s="87" t="s">
-        <v>1719</v>
+        <v>1698</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1762</v>
+        <v>1832</v>
       </c>
       <c r="F37" s="87"/>
     </row>
@@ -12925,17 +12847,15 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1720</v>
+        <v>1699</v>
       </c>
       <c r="D38" s="270" t="s">
-        <v>1748</v>
+        <v>1721</v>
       </c>
       <c r="E38" s="288" t="s">
-        <v>1731</v>
-      </c>
-      <c r="F38" s="288" t="s">
-        <v>1771</v>
-      </c>
+        <v>1847</v>
+      </c>
+      <c r="F38" s="288"/>
     </row>
     <row r="39" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="114">
@@ -12945,13 +12865,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1721</v>
+        <v>1700</v>
       </c>
       <c r="D39" s="87" t="s">
-        <v>1722</v>
+        <v>1701</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1727</v>
+        <v>1833</v>
       </c>
       <c r="F39" s="87"/>
     </row>
@@ -12963,17 +12883,13 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1723</v>
+        <v>1702</v>
       </c>
       <c r="D40" s="270" t="s">
-        <v>1733</v>
-      </c>
-      <c r="E40" s="270" t="s">
-        <v>1728</v>
-      </c>
-      <c r="F40" s="270" t="s">
-        <v>1755</v>
-      </c>
+        <v>1706</v>
+      </c>
+      <c r="E40" s="270"/>
+      <c r="F40" s="270"/>
     </row>
     <row r="41" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="115">
@@ -12983,14 +12899,12 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1724</v>
+        <v>1703</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E41" s="88" t="s">
-        <v>1750</v>
-      </c>
+        <v>1814</v>
+      </c>
+      <c r="E41" s="88"/>
       <c r="F41" s="88"/>
     </row>
     <row r="42" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13001,17 +12915,15 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1734</v>
+        <v>1707</v>
       </c>
       <c r="D42" s="268" t="s">
-        <v>1735</v>
+        <v>1708</v>
       </c>
       <c r="E42" s="268" t="s">
-        <v>1761</v>
-      </c>
-      <c r="F42" s="268" t="s">
-        <v>1772</v>
-      </c>
+        <v>1829</v>
+      </c>
+      <c r="F42" s="268"/>
     </row>
     <row r="43" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="114">
@@ -13021,14 +12933,12 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1744</v>
+        <v>1717</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>1736</v>
-      </c>
-      <c r="E43" s="87" t="s">
-        <v>1754</v>
-      </c>
+        <v>1709</v>
+      </c>
+      <c r="E43" s="87"/>
       <c r="F43" s="87"/>
     </row>
     <row r="44" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13039,13 +12949,13 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1737</v>
+        <v>1710</v>
       </c>
       <c r="D44" s="270" t="s">
-        <v>1738</v>
+        <v>1711</v>
       </c>
       <c r="E44" s="270" t="s">
-        <v>1753</v>
+        <v>1834</v>
       </c>
       <c r="F44" s="270"/>
     </row>
@@ -13057,13 +12967,13 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1739</v>
+        <v>1712</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>1746</v>
+        <v>1719</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1763</v>
+        <v>1837</v>
       </c>
       <c r="F45" s="87"/>
     </row>
@@ -13075,15 +12985,13 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1740</v>
+        <v>1713</v>
       </c>
       <c r="D46" s="270" t="s">
-        <v>1741</v>
+        <v>1714</v>
       </c>
       <c r="E46" s="270"/>
-      <c r="F46" s="270" t="s">
-        <v>1755</v>
-      </c>
+      <c r="F46" s="270"/>
     </row>
     <row r="47" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="114">
@@ -13093,17 +13001,15 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1742</v>
+        <v>1715</v>
       </c>
       <c r="D47" s="87" t="s">
-        <v>1747</v>
+        <v>1720</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1760</v>
-      </c>
-      <c r="F47" s="87" t="s">
-        <v>1770</v>
-      </c>
+        <v>1828</v>
+      </c>
+      <c r="F47" s="87"/>
     </row>
     <row r="48" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="114">
@@ -13113,13 +13019,11 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1751</v>
+        <v>1722</v>
       </c>
       <c r="D48" s="270"/>
       <c r="E48" s="270"/>
-      <c r="F48" s="270" t="s">
-        <v>1756</v>
-      </c>
+      <c r="F48" s="270"/>
     </row>
     <row r="49" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="115">
@@ -13129,13 +13033,13 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1743</v>
+        <v>1716</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>1757</v>
+        <v>1723</v>
       </c>
       <c r="E49" s="88" t="s">
-        <v>1752</v>
+        <v>1838</v>
       </c>
       <c r="F49" s="88"/>
     </row>
@@ -13147,14 +13051,14 @@
         <v>122</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>1778</v>
+        <v>1818</v>
       </c>
       <c r="D50" s="268"/>
       <c r="E50" s="268" t="s">
-        <v>1785</v>
+        <v>1848</v>
       </c>
       <c r="F50" s="268" t="s">
-        <v>1730</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13165,14 +13069,14 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1782</v>
+        <v>1739</v>
       </c>
       <c r="D51" s="87"/>
       <c r="E51" s="87" t="s">
-        <v>1786</v>
+        <v>1849</v>
       </c>
       <c r="F51" s="87" t="s">
-        <v>1730</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13183,14 +13087,14 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1787</v>
+        <v>1742</v>
       </c>
       <c r="D52" s="270"/>
       <c r="E52" s="270" t="s">
-        <v>1789</v>
+        <v>1839</v>
       </c>
       <c r="F52" s="270" t="s">
-        <v>1756</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13201,7 +13105,7 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1783</v>
+        <v>1740</v>
       </c>
       <c r="D53" s="87"/>
       <c r="E53" s="87"/>
@@ -13215,13 +13119,11 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1790</v>
+        <v>1744</v>
       </c>
       <c r="D54" s="270"/>
       <c r="E54" s="270"/>
-      <c r="F54" s="270" t="s">
-        <v>1730</v>
-      </c>
+      <c r="F54" s="270"/>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="114">
@@ -13231,15 +13133,13 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1779</v>
+        <v>1736</v>
       </c>
       <c r="D55" s="87" t="s">
-        <v>1780</v>
+        <v>1737</v>
       </c>
       <c r="E55" s="87"/>
-      <c r="F55" s="87" t="s">
-        <v>1755</v>
-      </c>
+      <c r="F55" s="87"/>
     </row>
     <row r="56" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="114">
@@ -13249,10 +13149,10 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1791</v>
+        <v>1745</v>
       </c>
       <c r="D56" s="270" t="s">
-        <v>1781</v>
+        <v>1738</v>
       </c>
       <c r="E56" s="270"/>
       <c r="F56" s="270"/>
@@ -13265,10 +13165,10 @@
         <v>143</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>1802</v>
+        <v>1755</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>1784</v>
+        <v>1741</v>
       </c>
       <c r="E57" s="88"/>
       <c r="F57" s="88"/>
@@ -13281,15 +13181,13 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1793</v>
+        <v>1747</v>
       </c>
       <c r="D58" s="268"/>
       <c r="E58" s="268" t="s">
-        <v>1805</v>
-      </c>
-      <c r="F58" s="268" t="s">
-        <v>1730</v>
-      </c>
+        <v>1758</v>
+      </c>
+      <c r="F58" s="268"/>
     </row>
     <row r="59" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="114">
@@ -13299,15 +13197,13 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1794</v>
+        <v>1748</v>
       </c>
       <c r="D59" s="87"/>
       <c r="E59" s="87" t="s">
-        <v>1803</v>
-      </c>
-      <c r="F59" s="87" t="s">
-        <v>1730</v>
-      </c>
+        <v>1756</v>
+      </c>
+      <c r="F59" s="87"/>
     </row>
     <row r="60" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="114">
@@ -13317,10 +13213,12 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1804</v>
+        <v>1757</v>
       </c>
       <c r="D60" s="270"/>
-      <c r="E60" s="270"/>
+      <c r="E60" s="270" t="s">
+        <v>1836</v>
+      </c>
       <c r="F60" s="270"/>
     </row>
     <row r="61" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13331,14 +13229,12 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1806</v>
+        <v>1759</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>1795</v>
-      </c>
-      <c r="E61" s="87" t="s">
-        <v>1807</v>
-      </c>
+        <v>1749</v>
+      </c>
+      <c r="E61" s="87"/>
       <c r="F61" s="87"/>
     </row>
     <row r="62" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13349,11 +13245,11 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1796</v>
+        <v>1815</v>
       </c>
       <c r="D62" s="270"/>
       <c r="E62" s="270" t="s">
-        <v>1807</v>
+        <v>1816</v>
       </c>
       <c r="F62" s="270"/>
     </row>
@@ -13365,10 +13261,10 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1797</v>
+        <v>1750</v>
       </c>
       <c r="D63" s="87" t="s">
-        <v>1798</v>
+        <v>1751</v>
       </c>
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
@@ -13381,13 +13277,11 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1799</v>
+        <v>1752</v>
       </c>
       <c r="D64" s="270"/>
       <c r="E64" s="270"/>
-      <c r="F64" s="270" t="s">
-        <v>1759</v>
-      </c>
+      <c r="F64" s="270"/>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="115">
@@ -13397,17 +13291,13 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1800</v>
+        <v>1753</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>1801</v>
-      </c>
-      <c r="E65" s="88" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F65" s="88" t="s">
-        <v>1705</v>
-      </c>
+        <v>1754</v>
+      </c>
+      <c r="E65" s="88"/>
+      <c r="F65" s="88"/>
     </row>
     <row r="66" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="207">
@@ -13417,13 +13307,13 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D66" s="87"/>
-      <c r="E66" s="87"/>
-      <c r="F66" s="87" t="s">
-        <v>1811</v>
-      </c>
+        <v>1760</v>
+      </c>
+      <c r="D66" s="268"/>
+      <c r="E66" s="268" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F66" s="268"/>
     </row>
     <row r="67" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="208">
@@ -13433,15 +13323,13 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1809</v>
+        <v>1761</v>
       </c>
       <c r="D67" s="87"/>
       <c r="E67" s="87" t="s">
-        <v>1810</v>
-      </c>
-      <c r="F67" s="87" t="s">
-        <v>1755</v>
-      </c>
+        <v>1819</v>
+      </c>
+      <c r="F67" s="87"/>
     </row>
     <row r="68" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="209">
@@ -13451,14 +13339,16 @@
         <v>1273</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1813</v>
+        <v>1762</v>
       </c>
       <c r="D68" s="272" t="s">
-        <v>1814</v>
-      </c>
-      <c r="E68" s="272"/>
+        <v>1763</v>
+      </c>
+      <c r="E68" s="272" t="s">
+        <v>1846</v>
+      </c>
       <c r="F68" s="272" t="s">
-        <v>1812</v>
+        <v>1843</v>
       </c>
     </row>
   </sheetData>
@@ -16776,7 +16666,7 @@
         <v>1104</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>1857</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17216,7 +17106,7 @@
         <v>1191</v>
       </c>
       <c r="F46" s="99" t="s">
-        <v>1858</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17256,7 +17146,7 @@
         <v>1198</v>
       </c>
       <c r="F48" s="99" t="s">
-        <v>1859</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17610,7 +17500,7 @@
         <v>1267</v>
       </c>
       <c r="D66" s="86" t="s">
-        <v>1862</v>
+        <v>1811</v>
       </c>
       <c r="E66" s="86" t="s">
         <v>1268</v>
@@ -17630,7 +17520,7 @@
         <v>1270</v>
       </c>
       <c r="D67" s="87" t="s">
-        <v>1863</v>
+        <v>1812</v>
       </c>
       <c r="E67" s="87" t="s">
         <v>1271</v>
@@ -17644,19 +17534,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="88" t="s">
-        <v>1860</v>
+        <v>1809</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1861</v>
+        <v>1810</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>1862</v>
+        <v>1811</v>
       </c>
       <c r="E68" s="88" t="s">
-        <v>1862</v>
+        <v>1811</v>
       </c>
       <c r="F68" s="101" t="s">
-        <v>1862</v>
+        <v>1811</v>
       </c>
     </row>
   </sheetData>
@@ -18670,16 +18560,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="250" t="s">
-        <v>1816</v>
+        <v>1765</v>
       </c>
       <c r="D50" s="289" t="s">
-        <v>1817</v>
+        <v>1766</v>
       </c>
       <c r="E50" s="251" t="s">
-        <v>1818</v>
+        <v>1767</v>
       </c>
       <c r="F50" s="252" t="s">
-        <v>1819</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18690,16 +18580,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="253" t="s">
-        <v>1820</v>
+        <v>1769</v>
       </c>
       <c r="D51" s="254" t="s">
-        <v>1821</v>
+        <v>1770</v>
       </c>
       <c r="E51" s="140" t="s">
-        <v>1822</v>
+        <v>1771</v>
       </c>
       <c r="F51" s="249" t="s">
-        <v>1823</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18710,16 +18600,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="253" t="s">
-        <v>1824</v>
+        <v>1773</v>
       </c>
       <c r="D52" s="254" t="s">
-        <v>1825</v>
+        <v>1774</v>
       </c>
       <c r="E52" s="140" t="s">
-        <v>1826</v>
+        <v>1775</v>
       </c>
       <c r="F52" s="249" t="s">
-        <v>1827</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18950,16 +18840,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="253" t="s">
-        <v>1828</v>
+        <v>1777</v>
       </c>
       <c r="D64" s="254" t="s">
-        <v>1829</v>
+        <v>1778</v>
       </c>
       <c r="E64" s="140" t="s">
-        <v>1830</v>
+        <v>1779</v>
       </c>
       <c r="F64" s="249" t="s">
-        <v>1831</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18990,16 +18880,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="250" t="s">
-        <v>1832</v>
+        <v>1781</v>
       </c>
       <c r="D66" s="289" t="s">
-        <v>1833</v>
+        <v>1782</v>
       </c>
       <c r="E66" s="193" t="s">
         <v>761</v>
       </c>
       <c r="F66" s="252" t="s">
-        <v>1834</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19010,10 +18900,10 @@
         <v>168</v>
       </c>
       <c r="C67" s="255" t="s">
-        <v>1835</v>
+        <v>1784</v>
       </c>
       <c r="D67" s="256" t="s">
-        <v>1836</v>
+        <v>1785</v>
       </c>
       <c r="E67" s="199" t="s">
         <v>762</v>
@@ -19030,16 +18920,16 @@
         <v>1273</v>
       </c>
       <c r="C68" s="264" t="s">
-        <v>1837</v>
+        <v>1786</v>
       </c>
       <c r="D68" s="265" t="s">
-        <v>1838</v>
+        <v>1787</v>
       </c>
       <c r="E68" s="266" t="s">
-        <v>1839</v>
+        <v>1788</v>
       </c>
       <c r="F68" s="267" t="s">
-        <v>1840</v>
+        <v>1789</v>
       </c>
     </row>
   </sheetData>
@@ -20053,7 +19943,7 @@
         <v>122</v>
       </c>
       <c r="C50" s="224" t="s">
-        <v>1841</v>
+        <v>1790</v>
       </c>
       <c r="D50" s="225" t="s">
         <v>956</v>
@@ -20073,16 +19963,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="227" t="s">
-        <v>1842</v>
+        <v>1791</v>
       </c>
       <c r="D51" s="228" t="s">
-        <v>1843</v>
+        <v>1792</v>
       </c>
       <c r="E51" s="229" t="s">
-        <v>1844</v>
+        <v>1793</v>
       </c>
       <c r="F51" s="219" t="s">
-        <v>1845</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20093,16 +19983,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="227" t="s">
-        <v>1846</v>
+        <v>1795</v>
       </c>
       <c r="D52" s="228" t="s">
-        <v>1847</v>
+        <v>1796</v>
       </c>
       <c r="E52" s="229" t="s">
-        <v>1848</v>
+        <v>1797</v>
       </c>
       <c r="F52" s="219" t="s">
-        <v>1849</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20333,7 +20223,7 @@
         <v>160</v>
       </c>
       <c r="C64" s="227" t="s">
-        <v>1850</v>
+        <v>1799</v>
       </c>
       <c r="D64" s="228" t="s">
         <v>1003</v>
@@ -20373,7 +20263,7 @@
         <v>165</v>
       </c>
       <c r="C66" s="212" t="s">
-        <v>1851</v>
+        <v>1800</v>
       </c>
       <c r="D66" s="213" t="s">
         <v>1010</v>
@@ -20393,16 +20283,16 @@
         <v>168</v>
       </c>
       <c r="C67" s="216" t="s">
-        <v>1852</v>
+        <v>1801</v>
       </c>
       <c r="D67" s="217" t="s">
         <v>1013</v>
       </c>
       <c r="E67" s="299" t="s">
-        <v>1853</v>
+        <v>1802</v>
       </c>
       <c r="F67" s="296" t="s">
-        <v>1854</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20410,19 +20300,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="77" t="s">
-        <v>1855</v>
+        <v>1804</v>
       </c>
       <c r="C68" s="293" t="s">
-        <v>1856</v>
+        <v>1805</v>
       </c>
       <c r="D68" s="294" t="s">
-        <v>1856</v>
+        <v>1805</v>
       </c>
       <c r="E68" s="300" t="s">
-        <v>1856</v>
+        <v>1805</v>
       </c>
       <c r="F68" s="297" t="s">
-        <v>1856</v>
+        <v>1805</v>
       </c>
     </row>
   </sheetData>
